--- a/centro-cirurgico/Centro_Cirurgico_Escala.xlsx
+++ b/centro-cirurgico/Centro_Cirurgico_Escala.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Cabe até (min)</t>
+          <t>Minutos livres</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -1199,11 +1199,11 @@
         <v/>
       </c>
       <c r="J10" s="9">
-        <f>IF($N10="","",IF(MAX('Calc_Salas'!$E$2:$E$14)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$2:$C$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$2:$D$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$2:$E$14,1)&amp;" min)","—")))</f>
+        <f>IF($N10="","",IF(MAX('Calc_Salas'!$E$2:$E$14)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$2:$C$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$2:$D$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K10" s="10">
-        <f>IF(OR($N10="",MAX('Calc_Salas'!$E$2:$E$14)=0),"",MAX('Calc_Salas'!$F$2:$F$14))</f>
+        <f>IF(OR($N10="",MAX('Calc_Salas'!$E$2:$E$14)=0),"",MAX('Calc_Salas'!$E$2:$E$14))</f>
         <v/>
       </c>
       <c r="L10" s="10">
@@ -1263,11 +1263,11 @@
         <v/>
       </c>
       <c r="J11" s="9">
-        <f>IF($N11="","",IF(MAX('Calc_Salas'!$E$15:$E$27)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$15:$C$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$15:$D$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$15:$E$27,1)&amp;" min)","—")))</f>
+        <f>IF($N11="","",IF(MAX('Calc_Salas'!$E$15:$E$27)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$15:$C$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$15:$D$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K11" s="10">
-        <f>IF(OR($N11="",MAX('Calc_Salas'!$E$15:$E$27)=0),"",MAX('Calc_Salas'!$F$15:$F$27))</f>
+        <f>IF(OR($N11="",MAX('Calc_Salas'!$E$15:$E$27)=0),"",MAX('Calc_Salas'!$E$15:$E$27))</f>
         <v/>
       </c>
       <c r="L11" s="10">
@@ -1327,11 +1327,11 @@
         <v/>
       </c>
       <c r="J12" s="9">
-        <f>IF($N12="","",IF(MAX('Calc_Salas'!$E$28:$E$40)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$28:$C$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$28:$D$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$28:$E$40,1)&amp;" min)","—")))</f>
+        <f>IF($N12="","",IF(MAX('Calc_Salas'!$E$28:$E$40)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$28:$C$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$28:$D$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K12" s="10">
-        <f>IF(OR($N12="",MAX('Calc_Salas'!$E$28:$E$40)=0),"",MAX('Calc_Salas'!$F$28:$F$40))</f>
+        <f>IF(OR($N12="",MAX('Calc_Salas'!$E$28:$E$40)=0),"",MAX('Calc_Salas'!$E$28:$E$40))</f>
         <v/>
       </c>
       <c r="L12" s="10">
@@ -1391,11 +1391,11 @@
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>IF($N13="","",IF(MAX('Calc_Salas'!$E$41:$E$53)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$41:$C$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$41:$D$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$41:$E$53,1)&amp;" min)","—")))</f>
+        <f>IF($N13="","",IF(MAX('Calc_Salas'!$E$41:$E$53)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$41:$C$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$41:$D$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K13" s="10">
-        <f>IF(OR($N13="",MAX('Calc_Salas'!$E$41:$E$53)=0),"",MAX('Calc_Salas'!$F$41:$F$53))</f>
+        <f>IF(OR($N13="",MAX('Calc_Salas'!$E$41:$E$53)=0),"",MAX('Calc_Salas'!$E$41:$E$53))</f>
         <v/>
       </c>
       <c r="L13" s="10">
@@ -1455,11 +1455,11 @@
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>IF($N14="","",IF(MAX('Calc_Salas'!$E$54:$E$66)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$54:$C$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$54:$D$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$54:$E$66,1)&amp;" min)","—")))</f>
+        <f>IF($N14="","",IF(MAX('Calc_Salas'!$E$54:$E$66)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$54:$C$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$54:$D$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K14" s="10">
-        <f>IF(OR($N14="",MAX('Calc_Salas'!$E$54:$E$66)=0),"",MAX('Calc_Salas'!$F$54:$F$66))</f>
+        <f>IF(OR($N14="",MAX('Calc_Salas'!$E$54:$E$66)=0),"",MAX('Calc_Salas'!$E$54:$E$66))</f>
         <v/>
       </c>
       <c r="L14" s="10">
@@ -1519,11 +1519,11 @@
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>IF($N15="","",IF(MAX('Calc_Salas'!$E$67:$E$79)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$67:$C$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$67:$D$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$67:$E$79,1)&amp;" min)","—")))</f>
+        <f>IF($N15="","",IF(MAX('Calc_Salas'!$E$67:$E$79)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$67:$C$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$67:$D$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K15" s="10">
-        <f>IF(OR($N15="",MAX('Calc_Salas'!$E$67:$E$79)=0),"",MAX('Calc_Salas'!$F$67:$F$79))</f>
+        <f>IF(OR($N15="",MAX('Calc_Salas'!$E$67:$E$79)=0),"",MAX('Calc_Salas'!$E$67:$E$79))</f>
         <v/>
       </c>
       <c r="L15" s="10">
@@ -1583,11 +1583,11 @@
         <v/>
       </c>
       <c r="J16" s="9">
-        <f>IF($N16="","",IF(MAX('Calc_Salas'!$E$80:$E$92)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$80:$C$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$80:$D$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$80:$E$92,1)&amp;" min)","—")))</f>
+        <f>IF($N16="","",IF(MAX('Calc_Salas'!$E$80:$E$92)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$80:$C$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$80:$D$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K16" s="10">
-        <f>IF(OR($N16="",MAX('Calc_Salas'!$E$80:$E$92)=0),"",MAX('Calc_Salas'!$F$80:$F$92))</f>
+        <f>IF(OR($N16="",MAX('Calc_Salas'!$E$80:$E$92)=0),"",MAX('Calc_Salas'!$E$80:$E$92))</f>
         <v/>
       </c>
       <c r="L16" s="10">
@@ -1647,11 +1647,11 @@
         <v/>
       </c>
       <c r="J17" s="9">
-        <f>IF($N17="","",IF(MAX('Calc_Salas'!$E$93:$E$105)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$93:$C$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$93:$D$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$93:$E$105,1)&amp;" min)","—")))</f>
+        <f>IF($N17="","",IF(MAX('Calc_Salas'!$E$93:$E$105)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$93:$C$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$93:$D$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K17" s="10">
-        <f>IF(OR($N17="",MAX('Calc_Salas'!$E$93:$E$105)=0),"",MAX('Calc_Salas'!$F$93:$F$105))</f>
+        <f>IF(OR($N17="",MAX('Calc_Salas'!$E$93:$E$105)=0),"",MAX('Calc_Salas'!$E$93:$E$105))</f>
         <v/>
       </c>
       <c r="L17" s="10">
@@ -1707,11 +1707,11 @@
         <v/>
       </c>
       <c r="J18" s="9">
-        <f>IF($N18="","",IF(MAX('Calc_Salas'!$E$106:$E$118)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$106:$C$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$106:$D$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$106:$E$118,1)&amp;" min)","—")))</f>
+        <f>IF($N18="","",IF(MAX('Calc_Salas'!$E$106:$E$118)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$106:$C$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$106:$D$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K18" s="10">
-        <f>IF(OR($N18="",MAX('Calc_Salas'!$E$106:$E$118)=0),"",MAX('Calc_Salas'!$F$106:$F$118))</f>
+        <f>IF(OR($N18="",MAX('Calc_Salas'!$E$106:$E$118)=0),"",MAX('Calc_Salas'!$E$106:$E$118))</f>
         <v/>
       </c>
       <c r="L18" s="10">
@@ -1763,11 +1763,11 @@
         <v/>
       </c>
       <c r="J19" s="9">
-        <f>IF($N19="","",IF(MAX('Calc_Salas'!$E$119:$E$131)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$119:$C$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$119:$D$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$119:$E$131,1)&amp;" min)","—")))</f>
+        <f>IF($N19="","",IF(MAX('Calc_Salas'!$E$119:$E$131)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$119:$C$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$119:$D$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K19" s="10">
-        <f>IF(OR($N19="",MAX('Calc_Salas'!$E$119:$E$131)=0),"",MAX('Calc_Salas'!$F$119:$F$131))</f>
+        <f>IF(OR($N19="",MAX('Calc_Salas'!$E$119:$E$131)=0),"",MAX('Calc_Salas'!$E$119:$E$131))</f>
         <v/>
       </c>
       <c r="L19" s="10">
@@ -1823,11 +1823,11 @@
         <v/>
       </c>
       <c r="J20" s="9">
-        <f>IF($N20="","",IF(MAX('Calc_Salas'!$E$132:$E$144)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$132:$C$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$132:$D$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$132:$E$144,1)&amp;" min)","—")))</f>
+        <f>IF($N20="","",IF(MAX('Calc_Salas'!$E$132:$E$144)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$132:$C$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$132:$D$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K20" s="10">
-        <f>IF(OR($N20="",MAX('Calc_Salas'!$E$132:$E$144)=0),"",MAX('Calc_Salas'!$F$132:$F$144))</f>
+        <f>IF(OR($N20="",MAX('Calc_Salas'!$E$132:$E$144)=0),"",MAX('Calc_Salas'!$E$132:$E$144))</f>
         <v/>
       </c>
       <c r="L20" s="10">
@@ -1879,11 +1879,11 @@
         <v/>
       </c>
       <c r="J21" s="9">
-        <f>IF($N21="","",IF(MAX('Calc_Salas'!$E$145:$E$157)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$145:$C$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$145:$D$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$145:$E$157,1)&amp;" min)","—")))</f>
+        <f>IF($N21="","",IF(MAX('Calc_Salas'!$E$145:$E$157)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$145:$C$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$145:$D$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K21" s="10">
-        <f>IF(OR($N21="",MAX('Calc_Salas'!$E$145:$E$157)=0),"",MAX('Calc_Salas'!$F$145:$F$157))</f>
+        <f>IF(OR($N21="",MAX('Calc_Salas'!$E$145:$E$157)=0),"",MAX('Calc_Salas'!$E$145:$E$157))</f>
         <v/>
       </c>
       <c r="L21" s="10">
@@ -1935,11 +1935,11 @@
         <v/>
       </c>
       <c r="J22" s="9">
-        <f>IF($N22="","",IF(MAX('Calc_Salas'!$E$158:$E$170)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$158:$C$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$158:$D$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$158:$E$170,1)&amp;" min)","—")))</f>
+        <f>IF($N22="","",IF(MAX('Calc_Salas'!$E$158:$E$170)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$158:$C$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$158:$D$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K22" s="10">
-        <f>IF(OR($N22="",MAX('Calc_Salas'!$E$158:$E$170)=0),"",MAX('Calc_Salas'!$F$158:$F$170))</f>
+        <f>IF(OR($N22="",MAX('Calc_Salas'!$E$158:$E$170)=0),"",MAX('Calc_Salas'!$E$158:$E$170))</f>
         <v/>
       </c>
       <c r="L22" s="10">
@@ -1991,11 +1991,11 @@
         <v/>
       </c>
       <c r="J23" s="9">
-        <f>IF($N23="","",IF(MAX('Calc_Salas'!$E$171:$E$183)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$171:$C$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$171:$D$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$171:$E$183,1)&amp;" min)","—")))</f>
+        <f>IF($N23="","",IF(MAX('Calc_Salas'!$E$171:$E$183)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$171:$C$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$171:$D$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K23" s="10">
-        <f>IF(OR($N23="",MAX('Calc_Salas'!$E$171:$E$183)=0),"",MAX('Calc_Salas'!$F$171:$F$183))</f>
+        <f>IF(OR($N23="",MAX('Calc_Salas'!$E$171:$E$183)=0),"",MAX('Calc_Salas'!$E$171:$E$183))</f>
         <v/>
       </c>
       <c r="L23" s="10">
@@ -2047,11 +2047,11 @@
         <v/>
       </c>
       <c r="J24" s="9">
-        <f>IF($N24="","",IF(MAX('Calc_Salas'!$E$184:$E$196)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$184:$C$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$184:$D$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$184:$E$196,1)&amp;" min)","—")))</f>
+        <f>IF($N24="","",IF(MAX('Calc_Salas'!$E$184:$E$196)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$184:$C$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$184:$D$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K24" s="10">
-        <f>IF(OR($N24="",MAX('Calc_Salas'!$E$184:$E$196)=0),"",MAX('Calc_Salas'!$F$184:$F$196))</f>
+        <f>IF(OR($N24="",MAX('Calc_Salas'!$E$184:$E$196)=0),"",MAX('Calc_Salas'!$E$184:$E$196))</f>
         <v/>
       </c>
       <c r="L24" s="10">
@@ -2103,11 +2103,11 @@
         <v/>
       </c>
       <c r="J25" s="9">
-        <f>IF($N25="","",IF(MAX('Calc_Salas'!$E$197:$E$209)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$197:$C$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$197:$D$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$197:$E$209,1)&amp;" min)","—")))</f>
+        <f>IF($N25="","",IF(MAX('Calc_Salas'!$E$197:$E$209)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$197:$C$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$197:$D$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM"),"—")))</f>
         <v/>
       </c>
       <c r="K25" s="10">
-        <f>IF(OR($N25="",MAX('Calc_Salas'!$E$197:$E$209)=0),"",MAX('Calc_Salas'!$F$197:$F$209))</f>
+        <f>IF(OR($N25="",MAX('Calc_Salas'!$E$197:$E$209)=0),"",MAX('Calc_Salas'!$E$197:$E$209))</f>
         <v/>
       </c>
       <c r="L25" s="10">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="26" customHeight="1">
+    <row r="77" ht="40" customHeight="1">
       <c r="A77" s="17" t="inlineStr">
         <is>
           <t>Jogo de sala</t>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B77" s="18" t="inlineStr">
         <is>
-          <t>Sala vaga mostra o maior intervalo livre da sala com horário, e Cabe até diz de quanto cabe um encaixe já descontada a limpeza.</t>
+          <t>Sala vaga mostra o maior intervalo livre da sala, com horário, e Minutos livres diz o tamanho dele. Como a agenda do hospital já reserva a limpeza dentro do horário de cada cirurgia, o intervalo inteiro é aproveitável para um encaixe.</t>
         </is>
       </c>
     </row>
@@ -25143,11 +25143,11 @@
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Limpeza e preparação após cada cirurgia (min)</t>
+          <t>Limpeza a ACRESCENTAR depois de cada cirurgia (min)</t>
         </is>
       </c>
       <c r="B16" s="42" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -25167,6 +25167,13 @@
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Janela_Min</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>A agenda do hospital já reserva a limpeza dentro do horário de cada cirurgia: o horário de término é a sala liberada. Por isso aqui fica 0. Se um dia a agenda passar a trazer só o tempo cirúrgico, ponha 20 e a planilha volta a somar.</t>
         </is>
       </c>
     </row>
@@ -33118,7 +33125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -33147,11 +33154,6 @@
           <t>Duração (min)</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Cabe até (min)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -33173,10 +33175,6 @@
         <f>IF($C2="","",MAX(0,$D2-$C2))</f>
         <v/>
       </c>
-      <c r="F2">
-        <f>IF($E2="","",MAX(0,$E2-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -33198,10 +33196,6 @@
         <f>IF($C3="","",MAX(0,$D3-$C3))</f>
         <v/>
       </c>
-      <c r="F3">
-        <f>IF($E3="","",MAX(0,$E3-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -33223,10 +33217,6 @@
         <f>IF($C4="","",MAX(0,$D4-$C4))</f>
         <v/>
       </c>
-      <c r="F4">
-        <f>IF($E4="","",MAX(0,$E4-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -33248,10 +33238,6 @@
         <f>IF($C5="","",MAX(0,$D5-$C5))</f>
         <v/>
       </c>
-      <c r="F5">
-        <f>IF($E5="","",MAX(0,$E5-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -33273,10 +33259,6 @@
         <f>IF($C6="","",MAX(0,$D6-$C6))</f>
         <v/>
       </c>
-      <c r="F6">
-        <f>IF($E6="","",MAX(0,$E6-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -33298,10 +33280,6 @@
         <f>IF($C7="","",MAX(0,$D7-$C7))</f>
         <v/>
       </c>
-      <c r="F7">
-        <f>IF($E7="","",MAX(0,$E7-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -33323,10 +33301,6 @@
         <f>IF($C8="","",MAX(0,$D8-$C8))</f>
         <v/>
       </c>
-      <c r="F8">
-        <f>IF($E8="","",MAX(0,$E8-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -33348,10 +33322,6 @@
         <f>IF($C9="","",MAX(0,$D9-$C9))</f>
         <v/>
       </c>
-      <c r="F9">
-        <f>IF($E9="","",MAX(0,$E9-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -33373,10 +33343,6 @@
         <f>IF($C10="","",MAX(0,$D10-$C10))</f>
         <v/>
       </c>
-      <c r="F10">
-        <f>IF($E10="","",MAX(0,$E10-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -33398,10 +33364,6 @@
         <f>IF($C11="","",MAX(0,$D11-$C11))</f>
         <v/>
       </c>
-      <c r="F11">
-        <f>IF($E11="","",MAX(0,$E11-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -33423,10 +33385,6 @@
         <f>IF($C12="","",MAX(0,$D12-$C12))</f>
         <v/>
       </c>
-      <c r="F12">
-        <f>IF($E12="","",MAX(0,$E12-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -33448,10 +33406,6 @@
         <f>IF($C13="","",MAX(0,$D13-$C13))</f>
         <v/>
       </c>
-      <c r="F13">
-        <f>IF($E13="","",MAX(0,$E13-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -33473,10 +33427,6 @@
         <f>IF($C14="","",MAX(0,$D14-$C14))</f>
         <v/>
       </c>
-      <c r="F14">
-        <f>IF($E14="","",MAX(0,$E14-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -33498,10 +33448,6 @@
         <f>IF($C15="","",MAX(0,$D15-$C15))</f>
         <v/>
       </c>
-      <c r="F15">
-        <f>IF($E15="","",MAX(0,$E15-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -33523,10 +33469,6 @@
         <f>IF($C16="","",MAX(0,$D16-$C16))</f>
         <v/>
       </c>
-      <c r="F16">
-        <f>IF($E16="","",MAX(0,$E16-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -33548,10 +33490,6 @@
         <f>IF($C17="","",MAX(0,$D17-$C17))</f>
         <v/>
       </c>
-      <c r="F17">
-        <f>IF($E17="","",MAX(0,$E17-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -33573,10 +33511,6 @@
         <f>IF($C18="","",MAX(0,$D18-$C18))</f>
         <v/>
       </c>
-      <c r="F18">
-        <f>IF($E18="","",MAX(0,$E18-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -33598,10 +33532,6 @@
         <f>IF($C19="","",MAX(0,$D19-$C19))</f>
         <v/>
       </c>
-      <c r="F19">
-        <f>IF($E19="","",MAX(0,$E19-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -33623,10 +33553,6 @@
         <f>IF($C20="","",MAX(0,$D20-$C20))</f>
         <v/>
       </c>
-      <c r="F20">
-        <f>IF($E20="","",MAX(0,$E20-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -33648,10 +33574,6 @@
         <f>IF($C21="","",MAX(0,$D21-$C21))</f>
         <v/>
       </c>
-      <c r="F21">
-        <f>IF($E21="","",MAX(0,$E21-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -33673,10 +33595,6 @@
         <f>IF($C22="","",MAX(0,$D22-$C22))</f>
         <v/>
       </c>
-      <c r="F22">
-        <f>IF($E22="","",MAX(0,$E22-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -33698,10 +33616,6 @@
         <f>IF($C23="","",MAX(0,$D23-$C23))</f>
         <v/>
       </c>
-      <c r="F23">
-        <f>IF($E23="","",MAX(0,$E23-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -33723,10 +33637,6 @@
         <f>IF($C24="","",MAX(0,$D24-$C24))</f>
         <v/>
       </c>
-      <c r="F24">
-        <f>IF($E24="","",MAX(0,$E24-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -33748,10 +33658,6 @@
         <f>IF($C25="","",MAX(0,$D25-$C25))</f>
         <v/>
       </c>
-      <c r="F25">
-        <f>IF($E25="","",MAX(0,$E25-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -33773,10 +33679,6 @@
         <f>IF($C26="","",MAX(0,$D26-$C26))</f>
         <v/>
       </c>
-      <c r="F26">
-        <f>IF($E26="","",MAX(0,$E26-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -33798,10 +33700,6 @@
         <f>IF($C27="","",MAX(0,$D27-$C27))</f>
         <v/>
       </c>
-      <c r="F27">
-        <f>IF($E27="","",MAX(0,$E27-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -33823,10 +33721,6 @@
         <f>IF($C28="","",MAX(0,$D28-$C28))</f>
         <v/>
       </c>
-      <c r="F28">
-        <f>IF($E28="","",MAX(0,$E28-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -33848,10 +33742,6 @@
         <f>IF($C29="","",MAX(0,$D29-$C29))</f>
         <v/>
       </c>
-      <c r="F29">
-        <f>IF($E29="","",MAX(0,$E29-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -33873,10 +33763,6 @@
         <f>IF($C30="","",MAX(0,$D30-$C30))</f>
         <v/>
       </c>
-      <c r="F30">
-        <f>IF($E30="","",MAX(0,$E30-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -33898,10 +33784,6 @@
         <f>IF($C31="","",MAX(0,$D31-$C31))</f>
         <v/>
       </c>
-      <c r="F31">
-        <f>IF($E31="","",MAX(0,$E31-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -33923,10 +33805,6 @@
         <f>IF($C32="","",MAX(0,$D32-$C32))</f>
         <v/>
       </c>
-      <c r="F32">
-        <f>IF($E32="","",MAX(0,$E32-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -33948,10 +33826,6 @@
         <f>IF($C33="","",MAX(0,$D33-$C33))</f>
         <v/>
       </c>
-      <c r="F33">
-        <f>IF($E33="","",MAX(0,$E33-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -33973,10 +33847,6 @@
         <f>IF($C34="","",MAX(0,$D34-$C34))</f>
         <v/>
       </c>
-      <c r="F34">
-        <f>IF($E34="","",MAX(0,$E34-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -33998,10 +33868,6 @@
         <f>IF($C35="","",MAX(0,$D35-$C35))</f>
         <v/>
       </c>
-      <c r="F35">
-        <f>IF($E35="","",MAX(0,$E35-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -34023,10 +33889,6 @@
         <f>IF($C36="","",MAX(0,$D36-$C36))</f>
         <v/>
       </c>
-      <c r="F36">
-        <f>IF($E36="","",MAX(0,$E36-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -34048,10 +33910,6 @@
         <f>IF($C37="","",MAX(0,$D37-$C37))</f>
         <v/>
       </c>
-      <c r="F37">
-        <f>IF($E37="","",MAX(0,$E37-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -34073,10 +33931,6 @@
         <f>IF($C38="","",MAX(0,$D38-$C38))</f>
         <v/>
       </c>
-      <c r="F38">
-        <f>IF($E38="","",MAX(0,$E38-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -34098,10 +33952,6 @@
         <f>IF($C39="","",MAX(0,$D39-$C39))</f>
         <v/>
       </c>
-      <c r="F39">
-        <f>IF($E39="","",MAX(0,$E39-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -34123,10 +33973,6 @@
         <f>IF($C40="","",MAX(0,$D40-$C40))</f>
         <v/>
       </c>
-      <c r="F40">
-        <f>IF($E40="","",MAX(0,$E40-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -34148,10 +33994,6 @@
         <f>IF($C41="","",MAX(0,$D41-$C41))</f>
         <v/>
       </c>
-      <c r="F41">
-        <f>IF($E41="","",MAX(0,$E41-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -34173,10 +34015,6 @@
         <f>IF($C42="","",MAX(0,$D42-$C42))</f>
         <v/>
       </c>
-      <c r="F42">
-        <f>IF($E42="","",MAX(0,$E42-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -34198,10 +34036,6 @@
         <f>IF($C43="","",MAX(0,$D43-$C43))</f>
         <v/>
       </c>
-      <c r="F43">
-        <f>IF($E43="","",MAX(0,$E43-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -34223,10 +34057,6 @@
         <f>IF($C44="","",MAX(0,$D44-$C44))</f>
         <v/>
       </c>
-      <c r="F44">
-        <f>IF($E44="","",MAX(0,$E44-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -34248,10 +34078,6 @@
         <f>IF($C45="","",MAX(0,$D45-$C45))</f>
         <v/>
       </c>
-      <c r="F45">
-        <f>IF($E45="","",MAX(0,$E45-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -34273,10 +34099,6 @@
         <f>IF($C46="","",MAX(0,$D46-$C46))</f>
         <v/>
       </c>
-      <c r="F46">
-        <f>IF($E46="","",MAX(0,$E46-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -34298,10 +34120,6 @@
         <f>IF($C47="","",MAX(0,$D47-$C47))</f>
         <v/>
       </c>
-      <c r="F47">
-        <f>IF($E47="","",MAX(0,$E47-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -34323,10 +34141,6 @@
         <f>IF($C48="","",MAX(0,$D48-$C48))</f>
         <v/>
       </c>
-      <c r="F48">
-        <f>IF($E48="","",MAX(0,$E48-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -34348,10 +34162,6 @@
         <f>IF($C49="","",MAX(0,$D49-$C49))</f>
         <v/>
       </c>
-      <c r="F49">
-        <f>IF($E49="","",MAX(0,$E49-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -34373,10 +34183,6 @@
         <f>IF($C50="","",MAX(0,$D50-$C50))</f>
         <v/>
       </c>
-      <c r="F50">
-        <f>IF($E50="","",MAX(0,$E50-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -34398,10 +34204,6 @@
         <f>IF($C51="","",MAX(0,$D51-$C51))</f>
         <v/>
       </c>
-      <c r="F51">
-        <f>IF($E51="","",MAX(0,$E51-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -34423,10 +34225,6 @@
         <f>IF($C52="","",MAX(0,$D52-$C52))</f>
         <v/>
       </c>
-      <c r="F52">
-        <f>IF($E52="","",MAX(0,$E52-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -34448,10 +34246,6 @@
         <f>IF($C53="","",MAX(0,$D53-$C53))</f>
         <v/>
       </c>
-      <c r="F53">
-        <f>IF($E53="","",MAX(0,$E53-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -34473,10 +34267,6 @@
         <f>IF($C54="","",MAX(0,$D54-$C54))</f>
         <v/>
       </c>
-      <c r="F54">
-        <f>IF($E54="","",MAX(0,$E54-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -34498,10 +34288,6 @@
         <f>IF($C55="","",MAX(0,$D55-$C55))</f>
         <v/>
       </c>
-      <c r="F55">
-        <f>IF($E55="","",MAX(0,$E55-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -34523,10 +34309,6 @@
         <f>IF($C56="","",MAX(0,$D56-$C56))</f>
         <v/>
       </c>
-      <c r="F56">
-        <f>IF($E56="","",MAX(0,$E56-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -34548,10 +34330,6 @@
         <f>IF($C57="","",MAX(0,$D57-$C57))</f>
         <v/>
       </c>
-      <c r="F57">
-        <f>IF($E57="","",MAX(0,$E57-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -34573,10 +34351,6 @@
         <f>IF($C58="","",MAX(0,$D58-$C58))</f>
         <v/>
       </c>
-      <c r="F58">
-        <f>IF($E58="","",MAX(0,$E58-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -34598,10 +34372,6 @@
         <f>IF($C59="","",MAX(0,$D59-$C59))</f>
         <v/>
       </c>
-      <c r="F59">
-        <f>IF($E59="","",MAX(0,$E59-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -34623,10 +34393,6 @@
         <f>IF($C60="","",MAX(0,$D60-$C60))</f>
         <v/>
       </c>
-      <c r="F60">
-        <f>IF($E60="","",MAX(0,$E60-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -34648,10 +34414,6 @@
         <f>IF($C61="","",MAX(0,$D61-$C61))</f>
         <v/>
       </c>
-      <c r="F61">
-        <f>IF($E61="","",MAX(0,$E61-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -34673,10 +34435,6 @@
         <f>IF($C62="","",MAX(0,$D62-$C62))</f>
         <v/>
       </c>
-      <c r="F62">
-        <f>IF($E62="","",MAX(0,$E62-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -34698,10 +34456,6 @@
         <f>IF($C63="","",MAX(0,$D63-$C63))</f>
         <v/>
       </c>
-      <c r="F63">
-        <f>IF($E63="","",MAX(0,$E63-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -34723,10 +34477,6 @@
         <f>IF($C64="","",MAX(0,$D64-$C64))</f>
         <v/>
       </c>
-      <c r="F64">
-        <f>IF($E64="","",MAX(0,$E64-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -34748,10 +34498,6 @@
         <f>IF($C65="","",MAX(0,$D65-$C65))</f>
         <v/>
       </c>
-      <c r="F65">
-        <f>IF($E65="","",MAX(0,$E65-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -34773,10 +34519,6 @@
         <f>IF($C66="","",MAX(0,$D66-$C66))</f>
         <v/>
       </c>
-      <c r="F66">
-        <f>IF($E66="","",MAX(0,$E66-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -34798,10 +34540,6 @@
         <f>IF($C67="","",MAX(0,$D67-$C67))</f>
         <v/>
       </c>
-      <c r="F67">
-        <f>IF($E67="","",MAX(0,$E67-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -34823,10 +34561,6 @@
         <f>IF($C68="","",MAX(0,$D68-$C68))</f>
         <v/>
       </c>
-      <c r="F68">
-        <f>IF($E68="","",MAX(0,$E68-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -34848,10 +34582,6 @@
         <f>IF($C69="","",MAX(0,$D69-$C69))</f>
         <v/>
       </c>
-      <c r="F69">
-        <f>IF($E69="","",MAX(0,$E69-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -34873,10 +34603,6 @@
         <f>IF($C70="","",MAX(0,$D70-$C70))</f>
         <v/>
       </c>
-      <c r="F70">
-        <f>IF($E70="","",MAX(0,$E70-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -34898,10 +34624,6 @@
         <f>IF($C71="","",MAX(0,$D71-$C71))</f>
         <v/>
       </c>
-      <c r="F71">
-        <f>IF($E71="","",MAX(0,$E71-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -34923,10 +34645,6 @@
         <f>IF($C72="","",MAX(0,$D72-$C72))</f>
         <v/>
       </c>
-      <c r="F72">
-        <f>IF($E72="","",MAX(0,$E72-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -34948,10 +34666,6 @@
         <f>IF($C73="","",MAX(0,$D73-$C73))</f>
         <v/>
       </c>
-      <c r="F73">
-        <f>IF($E73="","",MAX(0,$E73-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -34973,10 +34687,6 @@
         <f>IF($C74="","",MAX(0,$D74-$C74))</f>
         <v/>
       </c>
-      <c r="F74">
-        <f>IF($E74="","",MAX(0,$E74-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -34998,10 +34708,6 @@
         <f>IF($C75="","",MAX(0,$D75-$C75))</f>
         <v/>
       </c>
-      <c r="F75">
-        <f>IF($E75="","",MAX(0,$E75-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -35023,10 +34729,6 @@
         <f>IF($C76="","",MAX(0,$D76-$C76))</f>
         <v/>
       </c>
-      <c r="F76">
-        <f>IF($E76="","",MAX(0,$E76-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -35048,10 +34750,6 @@
         <f>IF($C77="","",MAX(0,$D77-$C77))</f>
         <v/>
       </c>
-      <c r="F77">
-        <f>IF($E77="","",MAX(0,$E77-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -35073,10 +34771,6 @@
         <f>IF($C78="","",MAX(0,$D78-$C78))</f>
         <v/>
       </c>
-      <c r="F78">
-        <f>IF($E78="","",MAX(0,$E78-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -35098,10 +34792,6 @@
         <f>IF($C79="","",MAX(0,$D79-$C79))</f>
         <v/>
       </c>
-      <c r="F79">
-        <f>IF($E79="","",MAX(0,$E79-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -35123,10 +34813,6 @@
         <f>IF($C80="","",MAX(0,$D80-$C80))</f>
         <v/>
       </c>
-      <c r="F80">
-        <f>IF($E80="","",MAX(0,$E80-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -35148,10 +34834,6 @@
         <f>IF($C81="","",MAX(0,$D81-$C81))</f>
         <v/>
       </c>
-      <c r="F81">
-        <f>IF($E81="","",MAX(0,$E81-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -35173,10 +34855,6 @@
         <f>IF($C82="","",MAX(0,$D82-$C82))</f>
         <v/>
       </c>
-      <c r="F82">
-        <f>IF($E82="","",MAX(0,$E82-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -35198,10 +34876,6 @@
         <f>IF($C83="","",MAX(0,$D83-$C83))</f>
         <v/>
       </c>
-      <c r="F83">
-        <f>IF($E83="","",MAX(0,$E83-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -35223,10 +34897,6 @@
         <f>IF($C84="","",MAX(0,$D84-$C84))</f>
         <v/>
       </c>
-      <c r="F84">
-        <f>IF($E84="","",MAX(0,$E84-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -35248,10 +34918,6 @@
         <f>IF($C85="","",MAX(0,$D85-$C85))</f>
         <v/>
       </c>
-      <c r="F85">
-        <f>IF($E85="","",MAX(0,$E85-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -35273,10 +34939,6 @@
         <f>IF($C86="","",MAX(0,$D86-$C86))</f>
         <v/>
       </c>
-      <c r="F86">
-        <f>IF($E86="","",MAX(0,$E86-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -35298,10 +34960,6 @@
         <f>IF($C87="","",MAX(0,$D87-$C87))</f>
         <v/>
       </c>
-      <c r="F87">
-        <f>IF($E87="","",MAX(0,$E87-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -35323,10 +34981,6 @@
         <f>IF($C88="","",MAX(0,$D88-$C88))</f>
         <v/>
       </c>
-      <c r="F88">
-        <f>IF($E88="","",MAX(0,$E88-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -35348,10 +35002,6 @@
         <f>IF($C89="","",MAX(0,$D89-$C89))</f>
         <v/>
       </c>
-      <c r="F89">
-        <f>IF($E89="","",MAX(0,$E89-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -35373,10 +35023,6 @@
         <f>IF($C90="","",MAX(0,$D90-$C90))</f>
         <v/>
       </c>
-      <c r="F90">
-        <f>IF($E90="","",MAX(0,$E90-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -35398,10 +35044,6 @@
         <f>IF($C91="","",MAX(0,$D91-$C91))</f>
         <v/>
       </c>
-      <c r="F91">
-        <f>IF($E91="","",MAX(0,$E91-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -35423,10 +35065,6 @@
         <f>IF($C92="","",MAX(0,$D92-$C92))</f>
         <v/>
       </c>
-      <c r="F92">
-        <f>IF($E92="","",MAX(0,$E92-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -35448,10 +35086,6 @@
         <f>IF($C93="","",MAX(0,$D93-$C93))</f>
         <v/>
       </c>
-      <c r="F93">
-        <f>IF($E93="","",MAX(0,$E93-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -35473,10 +35107,6 @@
         <f>IF($C94="","",MAX(0,$D94-$C94))</f>
         <v/>
       </c>
-      <c r="F94">
-        <f>IF($E94="","",MAX(0,$E94-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -35498,10 +35128,6 @@
         <f>IF($C95="","",MAX(0,$D95-$C95))</f>
         <v/>
       </c>
-      <c r="F95">
-        <f>IF($E95="","",MAX(0,$E95-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -35523,10 +35149,6 @@
         <f>IF($C96="","",MAX(0,$D96-$C96))</f>
         <v/>
       </c>
-      <c r="F96">
-        <f>IF($E96="","",MAX(0,$E96-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -35548,10 +35170,6 @@
         <f>IF($C97="","",MAX(0,$D97-$C97))</f>
         <v/>
       </c>
-      <c r="F97">
-        <f>IF($E97="","",MAX(0,$E97-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -35573,10 +35191,6 @@
         <f>IF($C98="","",MAX(0,$D98-$C98))</f>
         <v/>
       </c>
-      <c r="F98">
-        <f>IF($E98="","",MAX(0,$E98-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -35598,10 +35212,6 @@
         <f>IF($C99="","",MAX(0,$D99-$C99))</f>
         <v/>
       </c>
-      <c r="F99">
-        <f>IF($E99="","",MAX(0,$E99-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -35623,10 +35233,6 @@
         <f>IF($C100="","",MAX(0,$D100-$C100))</f>
         <v/>
       </c>
-      <c r="F100">
-        <f>IF($E100="","",MAX(0,$E100-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -35648,10 +35254,6 @@
         <f>IF($C101="","",MAX(0,$D101-$C101))</f>
         <v/>
       </c>
-      <c r="F101">
-        <f>IF($E101="","",MAX(0,$E101-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -35673,10 +35275,6 @@
         <f>IF($C102="","",MAX(0,$D102-$C102))</f>
         <v/>
       </c>
-      <c r="F102">
-        <f>IF($E102="","",MAX(0,$E102-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -35698,10 +35296,6 @@
         <f>IF($C103="","",MAX(0,$D103-$C103))</f>
         <v/>
       </c>
-      <c r="F103">
-        <f>IF($E103="","",MAX(0,$E103-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -35723,10 +35317,6 @@
         <f>IF($C104="","",MAX(0,$D104-$C104))</f>
         <v/>
       </c>
-      <c r="F104">
-        <f>IF($E104="","",MAX(0,$E104-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -35748,10 +35338,6 @@
         <f>IF($C105="","",MAX(0,$D105-$C105))</f>
         <v/>
       </c>
-      <c r="F105">
-        <f>IF($E105="","",MAX(0,$E105-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -35773,10 +35359,6 @@
         <f>IF($C106="","",MAX(0,$D106-$C106))</f>
         <v/>
       </c>
-      <c r="F106">
-        <f>IF($E106="","",MAX(0,$E106-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -35798,10 +35380,6 @@
         <f>IF($C107="","",MAX(0,$D107-$C107))</f>
         <v/>
       </c>
-      <c r="F107">
-        <f>IF($E107="","",MAX(0,$E107-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -35823,10 +35401,6 @@
         <f>IF($C108="","",MAX(0,$D108-$C108))</f>
         <v/>
       </c>
-      <c r="F108">
-        <f>IF($E108="","",MAX(0,$E108-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -35848,10 +35422,6 @@
         <f>IF($C109="","",MAX(0,$D109-$C109))</f>
         <v/>
       </c>
-      <c r="F109">
-        <f>IF($E109="","",MAX(0,$E109-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -35873,10 +35443,6 @@
         <f>IF($C110="","",MAX(0,$D110-$C110))</f>
         <v/>
       </c>
-      <c r="F110">
-        <f>IF($E110="","",MAX(0,$E110-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -35898,10 +35464,6 @@
         <f>IF($C111="","",MAX(0,$D111-$C111))</f>
         <v/>
       </c>
-      <c r="F111">
-        <f>IF($E111="","",MAX(0,$E111-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -35923,10 +35485,6 @@
         <f>IF($C112="","",MAX(0,$D112-$C112))</f>
         <v/>
       </c>
-      <c r="F112">
-        <f>IF($E112="","",MAX(0,$E112-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -35948,10 +35506,6 @@
         <f>IF($C113="","",MAX(0,$D113-$C113))</f>
         <v/>
       </c>
-      <c r="F113">
-        <f>IF($E113="","",MAX(0,$E113-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -35973,10 +35527,6 @@
         <f>IF($C114="","",MAX(0,$D114-$C114))</f>
         <v/>
       </c>
-      <c r="F114">
-        <f>IF($E114="","",MAX(0,$E114-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -35998,10 +35548,6 @@
         <f>IF($C115="","",MAX(0,$D115-$C115))</f>
         <v/>
       </c>
-      <c r="F115">
-        <f>IF($E115="","",MAX(0,$E115-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -36023,10 +35569,6 @@
         <f>IF($C116="","",MAX(0,$D116-$C116))</f>
         <v/>
       </c>
-      <c r="F116">
-        <f>IF($E116="","",MAX(0,$E116-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -36048,10 +35590,6 @@
         <f>IF($C117="","",MAX(0,$D117-$C117))</f>
         <v/>
       </c>
-      <c r="F117">
-        <f>IF($E117="","",MAX(0,$E117-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -36073,10 +35611,6 @@
         <f>IF($C118="","",MAX(0,$D118-$C118))</f>
         <v/>
       </c>
-      <c r="F118">
-        <f>IF($E118="","",MAX(0,$E118-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -36098,10 +35632,6 @@
         <f>IF($C119="","",MAX(0,$D119-$C119))</f>
         <v/>
       </c>
-      <c r="F119">
-        <f>IF($E119="","",MAX(0,$E119-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -36123,10 +35653,6 @@
         <f>IF($C120="","",MAX(0,$D120-$C120))</f>
         <v/>
       </c>
-      <c r="F120">
-        <f>IF($E120="","",MAX(0,$E120-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -36148,10 +35674,6 @@
         <f>IF($C121="","",MAX(0,$D121-$C121))</f>
         <v/>
       </c>
-      <c r="F121">
-        <f>IF($E121="","",MAX(0,$E121-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -36173,10 +35695,6 @@
         <f>IF($C122="","",MAX(0,$D122-$C122))</f>
         <v/>
       </c>
-      <c r="F122">
-        <f>IF($E122="","",MAX(0,$E122-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -36198,10 +35716,6 @@
         <f>IF($C123="","",MAX(0,$D123-$C123))</f>
         <v/>
       </c>
-      <c r="F123">
-        <f>IF($E123="","",MAX(0,$E123-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -36223,10 +35737,6 @@
         <f>IF($C124="","",MAX(0,$D124-$C124))</f>
         <v/>
       </c>
-      <c r="F124">
-        <f>IF($E124="","",MAX(0,$E124-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -36248,10 +35758,6 @@
         <f>IF($C125="","",MAX(0,$D125-$C125))</f>
         <v/>
       </c>
-      <c r="F125">
-        <f>IF($E125="","",MAX(0,$E125-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -36273,10 +35779,6 @@
         <f>IF($C126="","",MAX(0,$D126-$C126))</f>
         <v/>
       </c>
-      <c r="F126">
-        <f>IF($E126="","",MAX(0,$E126-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -36298,10 +35800,6 @@
         <f>IF($C127="","",MAX(0,$D127-$C127))</f>
         <v/>
       </c>
-      <c r="F127">
-        <f>IF($E127="","",MAX(0,$E127-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -36323,10 +35821,6 @@
         <f>IF($C128="","",MAX(0,$D128-$C128))</f>
         <v/>
       </c>
-      <c r="F128">
-        <f>IF($E128="","",MAX(0,$E128-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -36348,10 +35842,6 @@
         <f>IF($C129="","",MAX(0,$D129-$C129))</f>
         <v/>
       </c>
-      <c r="F129">
-        <f>IF($E129="","",MAX(0,$E129-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -36373,10 +35863,6 @@
         <f>IF($C130="","",MAX(0,$D130-$C130))</f>
         <v/>
       </c>
-      <c r="F130">
-        <f>IF($E130="","",MAX(0,$E130-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -36398,10 +35884,6 @@
         <f>IF($C131="","",MAX(0,$D131-$C131))</f>
         <v/>
       </c>
-      <c r="F131">
-        <f>IF($E131="","",MAX(0,$E131-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -36423,10 +35905,6 @@
         <f>IF($C132="","",MAX(0,$D132-$C132))</f>
         <v/>
       </c>
-      <c r="F132">
-        <f>IF($E132="","",MAX(0,$E132-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -36448,10 +35926,6 @@
         <f>IF($C133="","",MAX(0,$D133-$C133))</f>
         <v/>
       </c>
-      <c r="F133">
-        <f>IF($E133="","",MAX(0,$E133-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -36473,10 +35947,6 @@
         <f>IF($C134="","",MAX(0,$D134-$C134))</f>
         <v/>
       </c>
-      <c r="F134">
-        <f>IF($E134="","",MAX(0,$E134-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -36498,10 +35968,6 @@
         <f>IF($C135="","",MAX(0,$D135-$C135))</f>
         <v/>
       </c>
-      <c r="F135">
-        <f>IF($E135="","",MAX(0,$E135-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -36523,10 +35989,6 @@
         <f>IF($C136="","",MAX(0,$D136-$C136))</f>
         <v/>
       </c>
-      <c r="F136">
-        <f>IF($E136="","",MAX(0,$E136-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -36548,10 +36010,6 @@
         <f>IF($C137="","",MAX(0,$D137-$C137))</f>
         <v/>
       </c>
-      <c r="F137">
-        <f>IF($E137="","",MAX(0,$E137-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -36573,10 +36031,6 @@
         <f>IF($C138="","",MAX(0,$D138-$C138))</f>
         <v/>
       </c>
-      <c r="F138">
-        <f>IF($E138="","",MAX(0,$E138-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -36598,10 +36052,6 @@
         <f>IF($C139="","",MAX(0,$D139-$C139))</f>
         <v/>
       </c>
-      <c r="F139">
-        <f>IF($E139="","",MAX(0,$E139-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -36623,10 +36073,6 @@
         <f>IF($C140="","",MAX(0,$D140-$C140))</f>
         <v/>
       </c>
-      <c r="F140">
-        <f>IF($E140="","",MAX(0,$E140-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -36648,10 +36094,6 @@
         <f>IF($C141="","",MAX(0,$D141-$C141))</f>
         <v/>
       </c>
-      <c r="F141">
-        <f>IF($E141="","",MAX(0,$E141-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -36673,10 +36115,6 @@
         <f>IF($C142="","",MAX(0,$D142-$C142))</f>
         <v/>
       </c>
-      <c r="F142">
-        <f>IF($E142="","",MAX(0,$E142-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -36698,10 +36136,6 @@
         <f>IF($C143="","",MAX(0,$D143-$C143))</f>
         <v/>
       </c>
-      <c r="F143">
-        <f>IF($E143="","",MAX(0,$E143-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -36723,10 +36157,6 @@
         <f>IF($C144="","",MAX(0,$D144-$C144))</f>
         <v/>
       </c>
-      <c r="F144">
-        <f>IF($E144="","",MAX(0,$E144-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -36748,10 +36178,6 @@
         <f>IF($C145="","",MAX(0,$D145-$C145))</f>
         <v/>
       </c>
-      <c r="F145">
-        <f>IF($E145="","",MAX(0,$E145-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -36773,10 +36199,6 @@
         <f>IF($C146="","",MAX(0,$D146-$C146))</f>
         <v/>
       </c>
-      <c r="F146">
-        <f>IF($E146="","",MAX(0,$E146-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -36798,10 +36220,6 @@
         <f>IF($C147="","",MAX(0,$D147-$C147))</f>
         <v/>
       </c>
-      <c r="F147">
-        <f>IF($E147="","",MAX(0,$E147-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -36823,10 +36241,6 @@
         <f>IF($C148="","",MAX(0,$D148-$C148))</f>
         <v/>
       </c>
-      <c r="F148">
-        <f>IF($E148="","",MAX(0,$E148-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -36848,10 +36262,6 @@
         <f>IF($C149="","",MAX(0,$D149-$C149))</f>
         <v/>
       </c>
-      <c r="F149">
-        <f>IF($E149="","",MAX(0,$E149-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -36873,10 +36283,6 @@
         <f>IF($C150="","",MAX(0,$D150-$C150))</f>
         <v/>
       </c>
-      <c r="F150">
-        <f>IF($E150="","",MAX(0,$E150-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -36898,10 +36304,6 @@
         <f>IF($C151="","",MAX(0,$D151-$C151))</f>
         <v/>
       </c>
-      <c r="F151">
-        <f>IF($E151="","",MAX(0,$E151-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -36923,10 +36325,6 @@
         <f>IF($C152="","",MAX(0,$D152-$C152))</f>
         <v/>
       </c>
-      <c r="F152">
-        <f>IF($E152="","",MAX(0,$E152-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -36948,10 +36346,6 @@
         <f>IF($C153="","",MAX(0,$D153-$C153))</f>
         <v/>
       </c>
-      <c r="F153">
-        <f>IF($E153="","",MAX(0,$E153-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -36973,10 +36367,6 @@
         <f>IF($C154="","",MAX(0,$D154-$C154))</f>
         <v/>
       </c>
-      <c r="F154">
-        <f>IF($E154="","",MAX(0,$E154-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -36998,10 +36388,6 @@
         <f>IF($C155="","",MAX(0,$D155-$C155))</f>
         <v/>
       </c>
-      <c r="F155">
-        <f>IF($E155="","",MAX(0,$E155-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -37023,10 +36409,6 @@
         <f>IF($C156="","",MAX(0,$D156-$C156))</f>
         <v/>
       </c>
-      <c r="F156">
-        <f>IF($E156="","",MAX(0,$E156-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -37048,10 +36430,6 @@
         <f>IF($C157="","",MAX(0,$D157-$C157))</f>
         <v/>
       </c>
-      <c r="F157">
-        <f>IF($E157="","",MAX(0,$E157-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -37073,10 +36451,6 @@
         <f>IF($C158="","",MAX(0,$D158-$C158))</f>
         <v/>
       </c>
-      <c r="F158">
-        <f>IF($E158="","",MAX(0,$E158-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -37098,10 +36472,6 @@
         <f>IF($C159="","",MAX(0,$D159-$C159))</f>
         <v/>
       </c>
-      <c r="F159">
-        <f>IF($E159="","",MAX(0,$E159-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -37123,10 +36493,6 @@
         <f>IF($C160="","",MAX(0,$D160-$C160))</f>
         <v/>
       </c>
-      <c r="F160">
-        <f>IF($E160="","",MAX(0,$E160-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -37148,10 +36514,6 @@
         <f>IF($C161="","",MAX(0,$D161-$C161))</f>
         <v/>
       </c>
-      <c r="F161">
-        <f>IF($E161="","",MAX(0,$E161-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -37173,10 +36535,6 @@
         <f>IF($C162="","",MAX(0,$D162-$C162))</f>
         <v/>
       </c>
-      <c r="F162">
-        <f>IF($E162="","",MAX(0,$E162-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -37198,10 +36556,6 @@
         <f>IF($C163="","",MAX(0,$D163-$C163))</f>
         <v/>
       </c>
-      <c r="F163">
-        <f>IF($E163="","",MAX(0,$E163-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -37223,10 +36577,6 @@
         <f>IF($C164="","",MAX(0,$D164-$C164))</f>
         <v/>
       </c>
-      <c r="F164">
-        <f>IF($E164="","",MAX(0,$E164-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -37248,10 +36598,6 @@
         <f>IF($C165="","",MAX(0,$D165-$C165))</f>
         <v/>
       </c>
-      <c r="F165">
-        <f>IF($E165="","",MAX(0,$E165-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -37273,10 +36619,6 @@
         <f>IF($C166="","",MAX(0,$D166-$C166))</f>
         <v/>
       </c>
-      <c r="F166">
-        <f>IF($E166="","",MAX(0,$E166-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -37298,10 +36640,6 @@
         <f>IF($C167="","",MAX(0,$D167-$C167))</f>
         <v/>
       </c>
-      <c r="F167">
-        <f>IF($E167="","",MAX(0,$E167-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -37323,10 +36661,6 @@
         <f>IF($C168="","",MAX(0,$D168-$C168))</f>
         <v/>
       </c>
-      <c r="F168">
-        <f>IF($E168="","",MAX(0,$E168-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -37348,10 +36682,6 @@
         <f>IF($C169="","",MAX(0,$D169-$C169))</f>
         <v/>
       </c>
-      <c r="F169">
-        <f>IF($E169="","",MAX(0,$E169-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -37373,10 +36703,6 @@
         <f>IF($C170="","",MAX(0,$D170-$C170))</f>
         <v/>
       </c>
-      <c r="F170">
-        <f>IF($E170="","",MAX(0,$E170-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -37398,10 +36724,6 @@
         <f>IF($C171="","",MAX(0,$D171-$C171))</f>
         <v/>
       </c>
-      <c r="F171">
-        <f>IF($E171="","",MAX(0,$E171-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -37423,10 +36745,6 @@
         <f>IF($C172="","",MAX(0,$D172-$C172))</f>
         <v/>
       </c>
-      <c r="F172">
-        <f>IF($E172="","",MAX(0,$E172-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -37448,10 +36766,6 @@
         <f>IF($C173="","",MAX(0,$D173-$C173))</f>
         <v/>
       </c>
-      <c r="F173">
-        <f>IF($E173="","",MAX(0,$E173-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -37473,10 +36787,6 @@
         <f>IF($C174="","",MAX(0,$D174-$C174))</f>
         <v/>
       </c>
-      <c r="F174">
-        <f>IF($E174="","",MAX(0,$E174-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -37498,10 +36808,6 @@
         <f>IF($C175="","",MAX(0,$D175-$C175))</f>
         <v/>
       </c>
-      <c r="F175">
-        <f>IF($E175="","",MAX(0,$E175-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -37523,10 +36829,6 @@
         <f>IF($C176="","",MAX(0,$D176-$C176))</f>
         <v/>
       </c>
-      <c r="F176">
-        <f>IF($E176="","",MAX(0,$E176-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -37548,10 +36850,6 @@
         <f>IF($C177="","",MAX(0,$D177-$C177))</f>
         <v/>
       </c>
-      <c r="F177">
-        <f>IF($E177="","",MAX(0,$E177-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -37573,10 +36871,6 @@
         <f>IF($C178="","",MAX(0,$D178-$C178))</f>
         <v/>
       </c>
-      <c r="F178">
-        <f>IF($E178="","",MAX(0,$E178-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -37598,10 +36892,6 @@
         <f>IF($C179="","",MAX(0,$D179-$C179))</f>
         <v/>
       </c>
-      <c r="F179">
-        <f>IF($E179="","",MAX(0,$E179-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -37623,10 +36913,6 @@
         <f>IF($C180="","",MAX(0,$D180-$C180))</f>
         <v/>
       </c>
-      <c r="F180">
-        <f>IF($E180="","",MAX(0,$E180-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -37648,10 +36934,6 @@
         <f>IF($C181="","",MAX(0,$D181-$C181))</f>
         <v/>
       </c>
-      <c r="F181">
-        <f>IF($E181="","",MAX(0,$E181-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -37673,10 +36955,6 @@
         <f>IF($C182="","",MAX(0,$D182-$C182))</f>
         <v/>
       </c>
-      <c r="F182">
-        <f>IF($E182="","",MAX(0,$E182-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -37698,10 +36976,6 @@
         <f>IF($C183="","",MAX(0,$D183-$C183))</f>
         <v/>
       </c>
-      <c r="F183">
-        <f>IF($E183="","",MAX(0,$E183-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -37723,10 +36997,6 @@
         <f>IF($C184="","",MAX(0,$D184-$C184))</f>
         <v/>
       </c>
-      <c r="F184">
-        <f>IF($E184="","",MAX(0,$E184-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -37748,10 +37018,6 @@
         <f>IF($C185="","",MAX(0,$D185-$C185))</f>
         <v/>
       </c>
-      <c r="F185">
-        <f>IF($E185="","",MAX(0,$E185-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -37773,10 +37039,6 @@
         <f>IF($C186="","",MAX(0,$D186-$C186))</f>
         <v/>
       </c>
-      <c r="F186">
-        <f>IF($E186="","",MAX(0,$E186-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -37798,10 +37060,6 @@
         <f>IF($C187="","",MAX(0,$D187-$C187))</f>
         <v/>
       </c>
-      <c r="F187">
-        <f>IF($E187="","",MAX(0,$E187-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -37823,10 +37081,6 @@
         <f>IF($C188="","",MAX(0,$D188-$C188))</f>
         <v/>
       </c>
-      <c r="F188">
-        <f>IF($E188="","",MAX(0,$E188-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -37848,10 +37102,6 @@
         <f>IF($C189="","",MAX(0,$D189-$C189))</f>
         <v/>
       </c>
-      <c r="F189">
-        <f>IF($E189="","",MAX(0,$E189-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -37873,10 +37123,6 @@
         <f>IF($C190="","",MAX(0,$D190-$C190))</f>
         <v/>
       </c>
-      <c r="F190">
-        <f>IF($E190="","",MAX(0,$E190-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -37898,10 +37144,6 @@
         <f>IF($C191="","",MAX(0,$D191-$C191))</f>
         <v/>
       </c>
-      <c r="F191">
-        <f>IF($E191="","",MAX(0,$E191-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -37923,10 +37165,6 @@
         <f>IF($C192="","",MAX(0,$D192-$C192))</f>
         <v/>
       </c>
-      <c r="F192">
-        <f>IF($E192="","",MAX(0,$E192-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -37948,10 +37186,6 @@
         <f>IF($C193="","",MAX(0,$D193-$C193))</f>
         <v/>
       </c>
-      <c r="F193">
-        <f>IF($E193="","",MAX(0,$E193-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -37973,10 +37207,6 @@
         <f>IF($C194="","",MAX(0,$D194-$C194))</f>
         <v/>
       </c>
-      <c r="F194">
-        <f>IF($E194="","",MAX(0,$E194-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -37998,10 +37228,6 @@
         <f>IF($C195="","",MAX(0,$D195-$C195))</f>
         <v/>
       </c>
-      <c r="F195">
-        <f>IF($E195="","",MAX(0,$E195-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -38023,10 +37249,6 @@
         <f>IF($C196="","",MAX(0,$D196-$C196))</f>
         <v/>
       </c>
-      <c r="F196">
-        <f>IF($E196="","",MAX(0,$E196-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -38048,10 +37270,6 @@
         <f>IF($C197="","",MAX(0,$D197-$C197))</f>
         <v/>
       </c>
-      <c r="F197">
-        <f>IF($E197="","",MAX(0,$E197-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -38073,10 +37291,6 @@
         <f>IF($C198="","",MAX(0,$D198-$C198))</f>
         <v/>
       </c>
-      <c r="F198">
-        <f>IF($E198="","",MAX(0,$E198-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -38098,10 +37312,6 @@
         <f>IF($C199="","",MAX(0,$D199-$C199))</f>
         <v/>
       </c>
-      <c r="F199">
-        <f>IF($E199="","",MAX(0,$E199-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -38123,10 +37333,6 @@
         <f>IF($C200="","",MAX(0,$D200-$C200))</f>
         <v/>
       </c>
-      <c r="F200">
-        <f>IF($E200="","",MAX(0,$E200-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -38148,10 +37354,6 @@
         <f>IF($C201="","",MAX(0,$D201-$C201))</f>
         <v/>
       </c>
-      <c r="F201">
-        <f>IF($E201="","",MAX(0,$E201-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -38173,10 +37375,6 @@
         <f>IF($C202="","",MAX(0,$D202-$C202))</f>
         <v/>
       </c>
-      <c r="F202">
-        <f>IF($E202="","",MAX(0,$E202-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -38198,10 +37396,6 @@
         <f>IF($C203="","",MAX(0,$D203-$C203))</f>
         <v/>
       </c>
-      <c r="F203">
-        <f>IF($E203="","",MAX(0,$E203-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -38223,10 +37417,6 @@
         <f>IF($C204="","",MAX(0,$D204-$C204))</f>
         <v/>
       </c>
-      <c r="F204">
-        <f>IF($E204="","",MAX(0,$E204-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -38248,10 +37438,6 @@
         <f>IF($C205="","",MAX(0,$D205-$C205))</f>
         <v/>
       </c>
-      <c r="F205">
-        <f>IF($E205="","",MAX(0,$E205-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -38273,10 +37459,6 @@
         <f>IF($C206="","",MAX(0,$D206-$C206))</f>
         <v/>
       </c>
-      <c r="F206">
-        <f>IF($E206="","",MAX(0,$E206-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -38298,10 +37480,6 @@
         <f>IF($C207="","",MAX(0,$D207-$C207))</f>
         <v/>
       </c>
-      <c r="F207">
-        <f>IF($E207="","",MAX(0,$E207-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -38323,10 +37501,6 @@
         <f>IF($C208="","",MAX(0,$D208-$C208))</f>
         <v/>
       </c>
-      <c r="F208">
-        <f>IF($E208="","",MAX(0,$E208-Limpeza_Min))</f>
-        <v/>
-      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -38346,10 +37520,6 @@
       </c>
       <c r="E209">
         <f>IF($C209="","",MAX(0,$D209-$C209))</f>
-        <v/>
-      </c>
-      <c r="F209">
-        <f>IF($E209="","",MAX(0,$E209-Limpeza_Min))</f>
         <v/>
       </c>
     </row>

--- a/centro-cirurgico/Centro_Cirurgico_Escala.xlsx
+++ b/centro-cirurgico/Centro_Cirurgico_Escala.xlsx
@@ -1035,7 +1035,11 @@
           <t>Postos sem equipe</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Maior atraso previsto (min)</t>
+        </is>
+      </c>
       <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="5" t="inlineStr"/>
@@ -1070,6 +1074,10 @@
       </c>
       <c r="H6" s="8">
         <f>COUNTIF($F$10:$F$25,"SEM EQUIPE")</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>MAX(0,$L$10:$L$25)</f>
         <v/>
       </c>
     </row>
@@ -1143,12 +1151,12 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Minutos livres</t>
+          <t>Cabe até (min)</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Outras janelas</t>
+          <t>Atraso previsto (min)</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1199,15 +1207,15 @@
         <v/>
       </c>
       <c r="J10" s="9">
-        <f>IF($N10="","",IF(MAX('Calc_Salas'!$E$2:$E$14)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$2:$C$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$2:$D$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N10="","",IF(MAX('Calc_Salas'!$E$2:$E$14)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$2:$C$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$2:$D$14,MATCH(LARGE('Calc_Salas'!$E$2:$E$14,1),'Calc_Salas'!$E$2:$E$14,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$2:$E$14,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K10" s="10">
-        <f>IF(OR($N10="",MAX('Calc_Salas'!$E$2:$E$14)=0),"",MAX('Calc_Salas'!$E$2:$E$14))</f>
+        <f>IF(OR($N10="",MAX('Calc_Salas'!$E$2:$E$14)=0),"",MAX('Calc_Salas'!$F$2:$F$14))</f>
         <v/>
       </c>
       <c r="L10" s="10">
-        <f>IF($N10="","",MAX(0,COUNTIF('Calc_Salas'!$E$2:$E$14,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N10="",'Calc'!$B2&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$2:$G$14))</f>
         <v/>
       </c>
       <c r="M10" s="9">
@@ -1263,15 +1271,15 @@
         <v/>
       </c>
       <c r="J11" s="9">
-        <f>IF($N11="","",IF(MAX('Calc_Salas'!$E$15:$E$27)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$15:$C$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$15:$D$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N11="","",IF(MAX('Calc_Salas'!$E$15:$E$27)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$15:$C$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$15:$D$27,MATCH(LARGE('Calc_Salas'!$E$15:$E$27,1),'Calc_Salas'!$E$15:$E$27,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$15:$E$27,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K11" s="10">
-        <f>IF(OR($N11="",MAX('Calc_Salas'!$E$15:$E$27)=0),"",MAX('Calc_Salas'!$E$15:$E$27))</f>
+        <f>IF(OR($N11="",MAX('Calc_Salas'!$E$15:$E$27)=0),"",MAX('Calc_Salas'!$F$15:$F$27))</f>
         <v/>
       </c>
       <c r="L11" s="10">
-        <f>IF($N11="","",MAX(0,COUNTIF('Calc_Salas'!$E$15:$E$27,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N11="",'Calc'!$B3&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$15:$G$27))</f>
         <v/>
       </c>
       <c r="M11" s="9">
@@ -1327,15 +1335,15 @@
         <v/>
       </c>
       <c r="J12" s="9">
-        <f>IF($N12="","",IF(MAX('Calc_Salas'!$E$28:$E$40)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$28:$C$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$28:$D$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N12="","",IF(MAX('Calc_Salas'!$E$28:$E$40)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$28:$C$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$28:$D$40,MATCH(LARGE('Calc_Salas'!$E$28:$E$40,1),'Calc_Salas'!$E$28:$E$40,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$28:$E$40,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K12" s="10">
-        <f>IF(OR($N12="",MAX('Calc_Salas'!$E$28:$E$40)=0),"",MAX('Calc_Salas'!$E$28:$E$40))</f>
+        <f>IF(OR($N12="",MAX('Calc_Salas'!$E$28:$E$40)=0),"",MAX('Calc_Salas'!$F$28:$F$40))</f>
         <v/>
       </c>
       <c r="L12" s="10">
-        <f>IF($N12="","",MAX(0,COUNTIF('Calc_Salas'!$E$28:$E$40,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N12="",'Calc'!$B4&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$28:$G$40))</f>
         <v/>
       </c>
       <c r="M12" s="9">
@@ -1391,15 +1399,15 @@
         <v/>
       </c>
       <c r="J13" s="9">
-        <f>IF($N13="","",IF(MAX('Calc_Salas'!$E$41:$E$53)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$41:$C$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$41:$D$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N13="","",IF(MAX('Calc_Salas'!$E$41:$E$53)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$41:$C$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$41:$D$53,MATCH(LARGE('Calc_Salas'!$E$41:$E$53,1),'Calc_Salas'!$E$41:$E$53,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$41:$E$53,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K13" s="10">
-        <f>IF(OR($N13="",MAX('Calc_Salas'!$E$41:$E$53)=0),"",MAX('Calc_Salas'!$E$41:$E$53))</f>
+        <f>IF(OR($N13="",MAX('Calc_Salas'!$E$41:$E$53)=0),"",MAX('Calc_Salas'!$F$41:$F$53))</f>
         <v/>
       </c>
       <c r="L13" s="10">
-        <f>IF($N13="","",MAX(0,COUNTIF('Calc_Salas'!$E$41:$E$53,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N13="",'Calc'!$B5&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$41:$G$53))</f>
         <v/>
       </c>
       <c r="M13" s="9">
@@ -1455,15 +1463,15 @@
         <v/>
       </c>
       <c r="J14" s="9">
-        <f>IF($N14="","",IF(MAX('Calc_Salas'!$E$54:$E$66)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$54:$C$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$54:$D$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N14="","",IF(MAX('Calc_Salas'!$E$54:$E$66)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$54:$C$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$54:$D$66,MATCH(LARGE('Calc_Salas'!$E$54:$E$66,1),'Calc_Salas'!$E$54:$E$66,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$54:$E$66,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K14" s="10">
-        <f>IF(OR($N14="",MAX('Calc_Salas'!$E$54:$E$66)=0),"",MAX('Calc_Salas'!$E$54:$E$66))</f>
+        <f>IF(OR($N14="",MAX('Calc_Salas'!$E$54:$E$66)=0),"",MAX('Calc_Salas'!$F$54:$F$66))</f>
         <v/>
       </c>
       <c r="L14" s="10">
-        <f>IF($N14="","",MAX(0,COUNTIF('Calc_Salas'!$E$54:$E$66,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N14="",'Calc'!$B6&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$54:$G$66))</f>
         <v/>
       </c>
       <c r="M14" s="9">
@@ -1519,15 +1527,15 @@
         <v/>
       </c>
       <c r="J15" s="9">
-        <f>IF($N15="","",IF(MAX('Calc_Salas'!$E$67:$E$79)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$67:$C$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$67:$D$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N15="","",IF(MAX('Calc_Salas'!$E$67:$E$79)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$67:$C$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$67:$D$79,MATCH(LARGE('Calc_Salas'!$E$67:$E$79,1),'Calc_Salas'!$E$67:$E$79,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$67:$E$79,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K15" s="10">
-        <f>IF(OR($N15="",MAX('Calc_Salas'!$E$67:$E$79)=0),"",MAX('Calc_Salas'!$E$67:$E$79))</f>
+        <f>IF(OR($N15="",MAX('Calc_Salas'!$E$67:$E$79)=0),"",MAX('Calc_Salas'!$F$67:$F$79))</f>
         <v/>
       </c>
       <c r="L15" s="10">
-        <f>IF($N15="","",MAX(0,COUNTIF('Calc_Salas'!$E$67:$E$79,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N15="",'Calc'!$B7&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$67:$G$79))</f>
         <v/>
       </c>
       <c r="M15" s="9">
@@ -1583,15 +1591,15 @@
         <v/>
       </c>
       <c r="J16" s="9">
-        <f>IF($N16="","",IF(MAX('Calc_Salas'!$E$80:$E$92)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$80:$C$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$80:$D$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N16="","",IF(MAX('Calc_Salas'!$E$80:$E$92)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$80:$C$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$80:$D$92,MATCH(LARGE('Calc_Salas'!$E$80:$E$92,1),'Calc_Salas'!$E$80:$E$92,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$80:$E$92,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K16" s="10">
-        <f>IF(OR($N16="",MAX('Calc_Salas'!$E$80:$E$92)=0),"",MAX('Calc_Salas'!$E$80:$E$92))</f>
+        <f>IF(OR($N16="",MAX('Calc_Salas'!$E$80:$E$92)=0),"",MAX('Calc_Salas'!$F$80:$F$92))</f>
         <v/>
       </c>
       <c r="L16" s="10">
-        <f>IF($N16="","",MAX(0,COUNTIF('Calc_Salas'!$E$80:$E$92,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N16="",'Calc'!$B8&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$80:$G$92))</f>
         <v/>
       </c>
       <c r="M16" s="9">
@@ -1647,15 +1655,15 @@
         <v/>
       </c>
       <c r="J17" s="9">
-        <f>IF($N17="","",IF(MAX('Calc_Salas'!$E$93:$E$105)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$93:$C$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$93:$D$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N17="","",IF(MAX('Calc_Salas'!$E$93:$E$105)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$93:$C$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$93:$D$105,MATCH(LARGE('Calc_Salas'!$E$93:$E$105,1),'Calc_Salas'!$E$93:$E$105,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$93:$E$105,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K17" s="10">
-        <f>IF(OR($N17="",MAX('Calc_Salas'!$E$93:$E$105)=0),"",MAX('Calc_Salas'!$E$93:$E$105))</f>
+        <f>IF(OR($N17="",MAX('Calc_Salas'!$E$93:$E$105)=0),"",MAX('Calc_Salas'!$F$93:$F$105))</f>
         <v/>
       </c>
       <c r="L17" s="10">
-        <f>IF($N17="","",MAX(0,COUNTIF('Calc_Salas'!$E$93:$E$105,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N17="",'Calc'!$B9&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$93:$G$105))</f>
         <v/>
       </c>
       <c r="M17" s="9">
@@ -1707,15 +1715,15 @@
         <v/>
       </c>
       <c r="J18" s="9">
-        <f>IF($N18="","",IF(MAX('Calc_Salas'!$E$106:$E$118)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$106:$C$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$106:$D$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N18="","",IF(MAX('Calc_Salas'!$E$106:$E$118)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$106:$C$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$106:$D$118,MATCH(LARGE('Calc_Salas'!$E$106:$E$118,1),'Calc_Salas'!$E$106:$E$118,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$106:$E$118,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K18" s="10">
-        <f>IF(OR($N18="",MAX('Calc_Salas'!$E$106:$E$118)=0),"",MAX('Calc_Salas'!$E$106:$E$118))</f>
+        <f>IF(OR($N18="",MAX('Calc_Salas'!$E$106:$E$118)=0),"",MAX('Calc_Salas'!$F$106:$F$118))</f>
         <v/>
       </c>
       <c r="L18" s="10">
-        <f>IF($N18="","",MAX(0,COUNTIF('Calc_Salas'!$E$106:$E$118,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N18="",'Calc'!$B10&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$106:$G$118))</f>
         <v/>
       </c>
       <c r="M18" s="9">
@@ -1763,15 +1771,15 @@
         <v/>
       </c>
       <c r="J19" s="9">
-        <f>IF($N19="","",IF(MAX('Calc_Salas'!$E$119:$E$131)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$119:$C$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$119:$D$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N19="","",IF(MAX('Calc_Salas'!$E$119:$E$131)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$119:$C$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$119:$D$131,MATCH(LARGE('Calc_Salas'!$E$119:$E$131,1),'Calc_Salas'!$E$119:$E$131,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$119:$E$131,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K19" s="10">
-        <f>IF(OR($N19="",MAX('Calc_Salas'!$E$119:$E$131)=0),"",MAX('Calc_Salas'!$E$119:$E$131))</f>
+        <f>IF(OR($N19="",MAX('Calc_Salas'!$E$119:$E$131)=0),"",MAX('Calc_Salas'!$F$119:$F$131))</f>
         <v/>
       </c>
       <c r="L19" s="10">
-        <f>IF($N19="","",MAX(0,COUNTIF('Calc_Salas'!$E$119:$E$131,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N19="",'Calc'!$B11&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$119:$G$131))</f>
         <v/>
       </c>
       <c r="M19" s="9">
@@ -1823,15 +1831,15 @@
         <v/>
       </c>
       <c r="J20" s="9">
-        <f>IF($N20="","",IF(MAX('Calc_Salas'!$E$132:$E$144)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$132:$C$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$132:$D$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N20="","",IF(MAX('Calc_Salas'!$E$132:$E$144)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$132:$C$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$132:$D$144,MATCH(LARGE('Calc_Salas'!$E$132:$E$144,1),'Calc_Salas'!$E$132:$E$144,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$132:$E$144,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K20" s="10">
-        <f>IF(OR($N20="",MAX('Calc_Salas'!$E$132:$E$144)=0),"",MAX('Calc_Salas'!$E$132:$E$144))</f>
+        <f>IF(OR($N20="",MAX('Calc_Salas'!$E$132:$E$144)=0),"",MAX('Calc_Salas'!$F$132:$F$144))</f>
         <v/>
       </c>
       <c r="L20" s="10">
-        <f>IF($N20="","",MAX(0,COUNTIF('Calc_Salas'!$E$132:$E$144,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N20="",'Calc'!$B12&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$132:$G$144))</f>
         <v/>
       </c>
       <c r="M20" s="9">
@@ -1879,15 +1887,15 @@
         <v/>
       </c>
       <c r="J21" s="9">
-        <f>IF($N21="","",IF(MAX('Calc_Salas'!$E$145:$E$157)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$145:$C$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$145:$D$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N21="","",IF(MAX('Calc_Salas'!$E$145:$E$157)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$145:$C$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$145:$D$157,MATCH(LARGE('Calc_Salas'!$E$145:$E$157,1),'Calc_Salas'!$E$145:$E$157,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$145:$E$157,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K21" s="10">
-        <f>IF(OR($N21="",MAX('Calc_Salas'!$E$145:$E$157)=0),"",MAX('Calc_Salas'!$E$145:$E$157))</f>
+        <f>IF(OR($N21="",MAX('Calc_Salas'!$E$145:$E$157)=0),"",MAX('Calc_Salas'!$F$145:$F$157))</f>
         <v/>
       </c>
       <c r="L21" s="10">
-        <f>IF($N21="","",MAX(0,COUNTIF('Calc_Salas'!$E$145:$E$157,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N21="",'Calc'!$B13&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$145:$G$157))</f>
         <v/>
       </c>
       <c r="M21" s="9">
@@ -1935,15 +1943,15 @@
         <v/>
       </c>
       <c r="J22" s="9">
-        <f>IF($N22="","",IF(MAX('Calc_Salas'!$E$158:$E$170)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$158:$C$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$158:$D$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N22="","",IF(MAX('Calc_Salas'!$E$158:$E$170)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$158:$C$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$158:$D$170,MATCH(LARGE('Calc_Salas'!$E$158:$E$170,1),'Calc_Salas'!$E$158:$E$170,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$158:$E$170,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K22" s="10">
-        <f>IF(OR($N22="",MAX('Calc_Salas'!$E$158:$E$170)=0),"",MAX('Calc_Salas'!$E$158:$E$170))</f>
+        <f>IF(OR($N22="",MAX('Calc_Salas'!$E$158:$E$170)=0),"",MAX('Calc_Salas'!$F$158:$F$170))</f>
         <v/>
       </c>
       <c r="L22" s="10">
-        <f>IF($N22="","",MAX(0,COUNTIF('Calc_Salas'!$E$158:$E$170,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N22="",'Calc'!$B14&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$158:$G$170))</f>
         <v/>
       </c>
       <c r="M22" s="9">
@@ -1991,15 +1999,15 @@
         <v/>
       </c>
       <c r="J23" s="9">
-        <f>IF($N23="","",IF(MAX('Calc_Salas'!$E$171:$E$183)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$171:$C$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$171:$D$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N23="","",IF(MAX('Calc_Salas'!$E$171:$E$183)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$171:$C$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$171:$D$183,MATCH(LARGE('Calc_Salas'!$E$171:$E$183,1),'Calc_Salas'!$E$171:$E$183,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$171:$E$183,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K23" s="10">
-        <f>IF(OR($N23="",MAX('Calc_Salas'!$E$171:$E$183)=0),"",MAX('Calc_Salas'!$E$171:$E$183))</f>
+        <f>IF(OR($N23="",MAX('Calc_Salas'!$E$171:$E$183)=0),"",MAX('Calc_Salas'!$F$171:$F$183))</f>
         <v/>
       </c>
       <c r="L23" s="10">
-        <f>IF($N23="","",MAX(0,COUNTIF('Calc_Salas'!$E$171:$E$183,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N23="",'Calc'!$B15&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$171:$G$183))</f>
         <v/>
       </c>
       <c r="M23" s="9">
@@ -2047,15 +2055,15 @@
         <v/>
       </c>
       <c r="J24" s="9">
-        <f>IF($N24="","",IF(MAX('Calc_Salas'!$E$184:$E$196)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$184:$C$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$184:$D$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N24="","",IF(MAX('Calc_Salas'!$E$184:$E$196)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$184:$C$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$184:$D$196,MATCH(LARGE('Calc_Salas'!$E$184:$E$196,1),'Calc_Salas'!$E$184:$E$196,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$184:$E$196,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K24" s="10">
-        <f>IF(OR($N24="",MAX('Calc_Salas'!$E$184:$E$196)=0),"",MAX('Calc_Salas'!$E$184:$E$196))</f>
+        <f>IF(OR($N24="",MAX('Calc_Salas'!$E$184:$E$196)=0),"",MAX('Calc_Salas'!$F$184:$F$196))</f>
         <v/>
       </c>
       <c r="L24" s="10">
-        <f>IF($N24="","",MAX(0,COUNTIF('Calc_Salas'!$E$184:$E$196,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N24="",'Calc'!$B16&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$184:$G$196))</f>
         <v/>
       </c>
       <c r="M24" s="9">
@@ -2103,15 +2111,15 @@
         <v/>
       </c>
       <c r="J25" s="9">
-        <f>IF($N25="","",IF(MAX('Calc_Salas'!$E$197:$E$209)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$197:$C$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$197:$D$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM"),"—")))</f>
+        <f>IF($N25="","",IF(MAX('Calc_Salas'!$E$197:$E$209)=0,"—",IFERROR(TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$C$197:$C$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM")&amp;" → "&amp;TEXT(MOD(Turno_Ini+INDEX('Calc_Salas'!$D$197:$D$209,MATCH(LARGE('Calc_Salas'!$E$197:$E$209,1),'Calc_Salas'!$E$197:$E$209,0))/1440,1),"HH:MM")&amp;" ("&amp;LARGE('Calc_Salas'!$E$197:$E$209,1)&amp;" min)","—")))</f>
         <v/>
       </c>
       <c r="K25" s="10">
-        <f>IF(OR($N25="",MAX('Calc_Salas'!$E$197:$E$209)=0),"",MAX('Calc_Salas'!$E$197:$E$209))</f>
+        <f>IF(OR($N25="",MAX('Calc_Salas'!$E$197:$E$209)=0),"",MAX('Calc_Salas'!$F$197:$F$209))</f>
         <v/>
       </c>
       <c r="L25" s="10">
-        <f>IF($N25="","",MAX(0,COUNTIF('Calc_Salas'!$E$197:$E$209,"&gt;="&amp;Janela_Min)-1))</f>
+        <f>IF(OR($N25="",'Calc'!$B17&lt;&gt;"Sala cirúrgica"),"",MAX('Calc_Salas'!$G$197:$G$209))</f>
         <v/>
       </c>
       <c r="M25" s="9">
@@ -3176,34 +3184,44 @@
       <formula>$G$6&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="expression" priority="15" dxfId="1">
+      <formula>$I$6&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L10:L25">
+    <cfRule type="expression" priority="16" dxfId="1">
+      <formula>AND($L10&lt;&gt;"",$L10&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="expression" priority="15" dxfId="2">
+    <cfRule type="expression" priority="17" dxfId="2">
       <formula>$H$6&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" priority="16" dxfId="0">
+    <cfRule type="expression" priority="18" dxfId="0">
       <formula>$E$6&gt;=$F$6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:B58">
-    <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"Disponível"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" dxfId="1">
+    <cfRule type="expression" priority="20" dxfId="1">
       <formula>AND($B29&lt;&gt;"",$B29&lt;&gt;"Disponível")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29:D58">
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="4">
       <formula>"—"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B61:B71">
-    <cfRule type="expression" priority="20" dxfId="2">
+    <cfRule type="expression" priority="22" dxfId="2">
       <formula>OR(LEFT($B61,4)="ERRO",LEFT($B61,8)="PENDENTE")</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3410,7 +3428,7 @@
         <v/>
       </c>
       <c r="O2" s="24">
-        <f>IF($B2="","",IF(COUNTIF(Postos_Cod,$B2)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B2)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B2,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E2)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H2)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C2)),NOT(ISNUMBER($D2))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C2),ISNUMBER($D2),MOD($D2-$C2,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J2&gt;0,OR($P2&gt;=Turno_Min,$Q2&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J2&gt;0,$K2&gt;0,COUNTIF(Mapa_Chave,$B2&amp;"#"&amp;$A2&amp;"#"&amp;($K2+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B2&amp;"#"&amp;$A2&amp;"#"&amp;($K2+1),Mapa_Chave,0))-$Q2&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J2&gt;0,SUMPRODUCT((Mapa_Sala=$B2)*(Mapa_Data=$A2)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q2)*(Mapa_RelFim&gt;$P2))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I2),$I2&gt;0,COUNTIF(Esp_Nome,$E2)&gt;0,$I2&gt;3*INDEX(Esp_Dur,MATCH($E2,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B2="","",IF(COUNTIF(Postos_Cod,$B2)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B2)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B2,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E2)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H2)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C2)),NOT(ISNUMBER($D2))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C2),ISNUMBER($D2),MOD($D2-$C2,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J2&gt;0,OR($P2&gt;=Turno_Min,$Q2&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J2&gt;0,SUMPRODUCT((Mapa_Sala=$B2)*(Mapa_Data=$A2)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q2)*(Mapa_RelFim&gt;$P2))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I2),$I2&gt;0,COUNTIF(Esp_Nome,$E2)&gt;0,$I2&gt;3*INDEX(Esp_Dur,MATCH($E2,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P2" s="12">
@@ -3494,7 +3512,7 @@
         <v/>
       </c>
       <c r="O3" s="24">
-        <f>IF($B3="","",IF(COUNTIF(Postos_Cod,$B3)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B3)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B3,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E3)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H3)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C3)),NOT(ISNUMBER($D3))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C3),ISNUMBER($D3),MOD($D3-$C3,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J3&gt;0,OR($P3&gt;=Turno_Min,$Q3&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J3&gt;0,$K3&gt;0,COUNTIF(Mapa_Chave,$B3&amp;"#"&amp;$A3&amp;"#"&amp;($K3+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B3&amp;"#"&amp;$A3&amp;"#"&amp;($K3+1),Mapa_Chave,0))-$Q3&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J3&gt;0,SUMPRODUCT((Mapa_Sala=$B3)*(Mapa_Data=$A3)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q3)*(Mapa_RelFim&gt;$P3))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I3),$I3&gt;0,COUNTIF(Esp_Nome,$E3)&gt;0,$I3&gt;3*INDEX(Esp_Dur,MATCH($E3,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B3="","",IF(COUNTIF(Postos_Cod,$B3)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B3)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B3,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E3)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H3)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C3)),NOT(ISNUMBER($D3))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C3),ISNUMBER($D3),MOD($D3-$C3,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J3&gt;0,OR($P3&gt;=Turno_Min,$Q3&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J3&gt;0,SUMPRODUCT((Mapa_Sala=$B3)*(Mapa_Data=$A3)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q3)*(Mapa_RelFim&gt;$P3))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I3),$I3&gt;0,COUNTIF(Esp_Nome,$E3)&gt;0,$I3&gt;3*INDEX(Esp_Dur,MATCH($E3,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P3" s="12">
@@ -3578,7 +3596,7 @@
         <v/>
       </c>
       <c r="O4" s="24">
-        <f>IF($B4="","",IF(COUNTIF(Postos_Cod,$B4)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B4)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B4,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E4)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H4)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C4)),NOT(ISNUMBER($D4))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C4),ISNUMBER($D4),MOD($D4-$C4,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J4&gt;0,OR($P4&gt;=Turno_Min,$Q4&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J4&gt;0,$K4&gt;0,COUNTIF(Mapa_Chave,$B4&amp;"#"&amp;$A4&amp;"#"&amp;($K4+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B4&amp;"#"&amp;$A4&amp;"#"&amp;($K4+1),Mapa_Chave,0))-$Q4&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J4&gt;0,SUMPRODUCT((Mapa_Sala=$B4)*(Mapa_Data=$A4)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q4)*(Mapa_RelFim&gt;$P4))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I4),$I4&gt;0,COUNTIF(Esp_Nome,$E4)&gt;0,$I4&gt;3*INDEX(Esp_Dur,MATCH($E4,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B4="","",IF(COUNTIF(Postos_Cod,$B4)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B4)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B4,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E4)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H4)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C4)),NOT(ISNUMBER($D4))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C4),ISNUMBER($D4),MOD($D4-$C4,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J4&gt;0,OR($P4&gt;=Turno_Min,$Q4&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J4&gt;0,SUMPRODUCT((Mapa_Sala=$B4)*(Mapa_Data=$A4)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q4)*(Mapa_RelFim&gt;$P4))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I4),$I4&gt;0,COUNTIF(Esp_Nome,$E4)&gt;0,$I4&gt;3*INDEX(Esp_Dur,MATCH($E4,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P4" s="12">
@@ -3662,7 +3680,7 @@
         <v/>
       </c>
       <c r="O5" s="24">
-        <f>IF($B5="","",IF(COUNTIF(Postos_Cod,$B5)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B5)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B5,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E5)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H5)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C5)),NOT(ISNUMBER($D5))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C5),ISNUMBER($D5),MOD($D5-$C5,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J5&gt;0,OR($P5&gt;=Turno_Min,$Q5&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J5&gt;0,$K5&gt;0,COUNTIF(Mapa_Chave,$B5&amp;"#"&amp;$A5&amp;"#"&amp;($K5+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B5&amp;"#"&amp;$A5&amp;"#"&amp;($K5+1),Mapa_Chave,0))-$Q5&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J5&gt;0,SUMPRODUCT((Mapa_Sala=$B5)*(Mapa_Data=$A5)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q5)*(Mapa_RelFim&gt;$P5))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I5),$I5&gt;0,COUNTIF(Esp_Nome,$E5)&gt;0,$I5&gt;3*INDEX(Esp_Dur,MATCH($E5,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B5="","",IF(COUNTIF(Postos_Cod,$B5)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B5)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B5,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E5)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H5)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C5)),NOT(ISNUMBER($D5))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C5),ISNUMBER($D5),MOD($D5-$C5,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J5&gt;0,OR($P5&gt;=Turno_Min,$Q5&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J5&gt;0,SUMPRODUCT((Mapa_Sala=$B5)*(Mapa_Data=$A5)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q5)*(Mapa_RelFim&gt;$P5))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I5),$I5&gt;0,COUNTIF(Esp_Nome,$E5)&gt;0,$I5&gt;3*INDEX(Esp_Dur,MATCH($E5,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P5" s="12">
@@ -3746,7 +3764,7 @@
         <v/>
       </c>
       <c r="O6" s="24">
-        <f>IF($B6="","",IF(COUNTIF(Postos_Cod,$B6)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B6)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B6,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E6)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H6)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C6)),NOT(ISNUMBER($D6))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C6),ISNUMBER($D6),MOD($D6-$C6,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J6&gt;0,OR($P6&gt;=Turno_Min,$Q6&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J6&gt;0,$K6&gt;0,COUNTIF(Mapa_Chave,$B6&amp;"#"&amp;$A6&amp;"#"&amp;($K6+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B6&amp;"#"&amp;$A6&amp;"#"&amp;($K6+1),Mapa_Chave,0))-$Q6&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J6&gt;0,SUMPRODUCT((Mapa_Sala=$B6)*(Mapa_Data=$A6)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q6)*(Mapa_RelFim&gt;$P6))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I6),$I6&gt;0,COUNTIF(Esp_Nome,$E6)&gt;0,$I6&gt;3*INDEX(Esp_Dur,MATCH($E6,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B6="","",IF(COUNTIF(Postos_Cod,$B6)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B6)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B6,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E6)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H6)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C6)),NOT(ISNUMBER($D6))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C6),ISNUMBER($D6),MOD($D6-$C6,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J6&gt;0,OR($P6&gt;=Turno_Min,$Q6&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J6&gt;0,SUMPRODUCT((Mapa_Sala=$B6)*(Mapa_Data=$A6)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q6)*(Mapa_RelFim&gt;$P6))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I6),$I6&gt;0,COUNTIF(Esp_Nome,$E6)&gt;0,$I6&gt;3*INDEX(Esp_Dur,MATCH($E6,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P6" s="12">
@@ -3830,7 +3848,7 @@
         <v/>
       </c>
       <c r="O7" s="24">
-        <f>IF($B7="","",IF(COUNTIF(Postos_Cod,$B7)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B7)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B7,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E7)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H7)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C7)),NOT(ISNUMBER($D7))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C7),ISNUMBER($D7),MOD($D7-$C7,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J7&gt;0,OR($P7&gt;=Turno_Min,$Q7&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J7&gt;0,$K7&gt;0,COUNTIF(Mapa_Chave,$B7&amp;"#"&amp;$A7&amp;"#"&amp;($K7+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B7&amp;"#"&amp;$A7&amp;"#"&amp;($K7+1),Mapa_Chave,0))-$Q7&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J7&gt;0,SUMPRODUCT((Mapa_Sala=$B7)*(Mapa_Data=$A7)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q7)*(Mapa_RelFim&gt;$P7))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I7),$I7&gt;0,COUNTIF(Esp_Nome,$E7)&gt;0,$I7&gt;3*INDEX(Esp_Dur,MATCH($E7,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B7="","",IF(COUNTIF(Postos_Cod,$B7)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B7)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B7,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E7)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H7)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C7)),NOT(ISNUMBER($D7))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C7),ISNUMBER($D7),MOD($D7-$C7,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J7&gt;0,OR($P7&gt;=Turno_Min,$Q7&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J7&gt;0,SUMPRODUCT((Mapa_Sala=$B7)*(Mapa_Data=$A7)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q7)*(Mapa_RelFim&gt;$P7))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I7),$I7&gt;0,COUNTIF(Esp_Nome,$E7)&gt;0,$I7&gt;3*INDEX(Esp_Dur,MATCH($E7,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P7" s="12">
@@ -3914,7 +3932,7 @@
         <v/>
       </c>
       <c r="O8" s="24">
-        <f>IF($B8="","",IF(COUNTIF(Postos_Cod,$B8)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B8)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B8,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E8)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H8)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C8)),NOT(ISNUMBER($D8))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C8),ISNUMBER($D8),MOD($D8-$C8,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J8&gt;0,OR($P8&gt;=Turno_Min,$Q8&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J8&gt;0,$K8&gt;0,COUNTIF(Mapa_Chave,$B8&amp;"#"&amp;$A8&amp;"#"&amp;($K8+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B8&amp;"#"&amp;$A8&amp;"#"&amp;($K8+1),Mapa_Chave,0))-$Q8&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J8&gt;0,SUMPRODUCT((Mapa_Sala=$B8)*(Mapa_Data=$A8)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q8)*(Mapa_RelFim&gt;$P8))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I8),$I8&gt;0,COUNTIF(Esp_Nome,$E8)&gt;0,$I8&gt;3*INDEX(Esp_Dur,MATCH($E8,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B8="","",IF(COUNTIF(Postos_Cod,$B8)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B8)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B8,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E8)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H8)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C8)),NOT(ISNUMBER($D8))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C8),ISNUMBER($D8),MOD($D8-$C8,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J8&gt;0,OR($P8&gt;=Turno_Min,$Q8&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J8&gt;0,SUMPRODUCT((Mapa_Sala=$B8)*(Mapa_Data=$A8)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q8)*(Mapa_RelFim&gt;$P8))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I8),$I8&gt;0,COUNTIF(Esp_Nome,$E8)&gt;0,$I8&gt;3*INDEX(Esp_Dur,MATCH($E8,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P8" s="12">
@@ -3998,7 +4016,7 @@
         <v/>
       </c>
       <c r="O9" s="24">
-        <f>IF($B9="","",IF(COUNTIF(Postos_Cod,$B9)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B9)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B9,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E9)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H9)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C9)),NOT(ISNUMBER($D9))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C9),ISNUMBER($D9),MOD($D9-$C9,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J9&gt;0,OR($P9&gt;=Turno_Min,$Q9&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J9&gt;0,$K9&gt;0,COUNTIF(Mapa_Chave,$B9&amp;"#"&amp;$A9&amp;"#"&amp;($K9+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B9&amp;"#"&amp;$A9&amp;"#"&amp;($K9+1),Mapa_Chave,0))-$Q9&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J9&gt;0,SUMPRODUCT((Mapa_Sala=$B9)*(Mapa_Data=$A9)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q9)*(Mapa_RelFim&gt;$P9))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I9),$I9&gt;0,COUNTIF(Esp_Nome,$E9)&gt;0,$I9&gt;3*INDEX(Esp_Dur,MATCH($E9,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B9="","",IF(COUNTIF(Postos_Cod,$B9)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B9)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B9,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E9)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H9)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C9)),NOT(ISNUMBER($D9))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C9),ISNUMBER($D9),MOD($D9-$C9,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J9&gt;0,OR($P9&gt;=Turno_Min,$Q9&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J9&gt;0,SUMPRODUCT((Mapa_Sala=$B9)*(Mapa_Data=$A9)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q9)*(Mapa_RelFim&gt;$P9))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I9),$I9&gt;0,COUNTIF(Esp_Nome,$E9)&gt;0,$I9&gt;3*INDEX(Esp_Dur,MATCH($E9,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P9" s="12">
@@ -4082,7 +4100,7 @@
         <v/>
       </c>
       <c r="O10" s="24">
-        <f>IF($B10="","",IF(COUNTIF(Postos_Cod,$B10)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B10)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B10,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E10)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H10)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C10)),NOT(ISNUMBER($D10))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C10),ISNUMBER($D10),MOD($D10-$C10,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J10&gt;0,OR($P10&gt;=Turno_Min,$Q10&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J10&gt;0,$K10&gt;0,COUNTIF(Mapa_Chave,$B10&amp;"#"&amp;$A10&amp;"#"&amp;($K10+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B10&amp;"#"&amp;$A10&amp;"#"&amp;($K10+1),Mapa_Chave,0))-$Q10&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J10&gt;0,SUMPRODUCT((Mapa_Sala=$B10)*(Mapa_Data=$A10)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q10)*(Mapa_RelFim&gt;$P10))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I10),$I10&gt;0,COUNTIF(Esp_Nome,$E10)&gt;0,$I10&gt;3*INDEX(Esp_Dur,MATCH($E10,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B10="","",IF(COUNTIF(Postos_Cod,$B10)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B10)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B10,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E10)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H10)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C10)),NOT(ISNUMBER($D10))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C10),ISNUMBER($D10),MOD($D10-$C10,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J10&gt;0,OR($P10&gt;=Turno_Min,$Q10&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J10&gt;0,SUMPRODUCT((Mapa_Sala=$B10)*(Mapa_Data=$A10)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q10)*(Mapa_RelFim&gt;$P10))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I10),$I10&gt;0,COUNTIF(Esp_Nome,$E10)&gt;0,$I10&gt;3*INDEX(Esp_Dur,MATCH($E10,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P10" s="12">
@@ -4166,7 +4184,7 @@
         <v/>
       </c>
       <c r="O11" s="24">
-        <f>IF($B11="","",IF(COUNTIF(Postos_Cod,$B11)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B11)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B11,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E11)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H11)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C11)),NOT(ISNUMBER($D11))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C11),ISNUMBER($D11),MOD($D11-$C11,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J11&gt;0,OR($P11&gt;=Turno_Min,$Q11&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J11&gt;0,$K11&gt;0,COUNTIF(Mapa_Chave,$B11&amp;"#"&amp;$A11&amp;"#"&amp;($K11+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B11&amp;"#"&amp;$A11&amp;"#"&amp;($K11+1),Mapa_Chave,0))-$Q11&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J11&gt;0,SUMPRODUCT((Mapa_Sala=$B11)*(Mapa_Data=$A11)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q11)*(Mapa_RelFim&gt;$P11))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I11),$I11&gt;0,COUNTIF(Esp_Nome,$E11)&gt;0,$I11&gt;3*INDEX(Esp_Dur,MATCH($E11,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B11="","",IF(COUNTIF(Postos_Cod,$B11)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B11)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B11,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E11)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H11)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C11)),NOT(ISNUMBER($D11))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C11),ISNUMBER($D11),MOD($D11-$C11,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J11&gt;0,OR($P11&gt;=Turno_Min,$Q11&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J11&gt;0,SUMPRODUCT((Mapa_Sala=$B11)*(Mapa_Data=$A11)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q11)*(Mapa_RelFim&gt;$P11))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I11),$I11&gt;0,COUNTIF(Esp_Nome,$E11)&gt;0,$I11&gt;3*INDEX(Esp_Dur,MATCH($E11,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P11" s="12">
@@ -4250,7 +4268,7 @@
         <v/>
       </c>
       <c r="O12" s="24">
-        <f>IF($B12="","",IF(COUNTIF(Postos_Cod,$B12)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B12)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B12,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E12)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H12)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C12)),NOT(ISNUMBER($D12))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C12),ISNUMBER($D12),MOD($D12-$C12,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J12&gt;0,OR($P12&gt;=Turno_Min,$Q12&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J12&gt;0,$K12&gt;0,COUNTIF(Mapa_Chave,$B12&amp;"#"&amp;$A12&amp;"#"&amp;($K12+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B12&amp;"#"&amp;$A12&amp;"#"&amp;($K12+1),Mapa_Chave,0))-$Q12&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J12&gt;0,SUMPRODUCT((Mapa_Sala=$B12)*(Mapa_Data=$A12)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q12)*(Mapa_RelFim&gt;$P12))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I12),$I12&gt;0,COUNTIF(Esp_Nome,$E12)&gt;0,$I12&gt;3*INDEX(Esp_Dur,MATCH($E12,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B12="","",IF(COUNTIF(Postos_Cod,$B12)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B12)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B12,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E12)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H12)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C12)),NOT(ISNUMBER($D12))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C12),ISNUMBER($D12),MOD($D12-$C12,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J12&gt;0,OR($P12&gt;=Turno_Min,$Q12&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J12&gt;0,SUMPRODUCT((Mapa_Sala=$B12)*(Mapa_Data=$A12)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q12)*(Mapa_RelFim&gt;$P12))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I12),$I12&gt;0,COUNTIF(Esp_Nome,$E12)&gt;0,$I12&gt;3*INDEX(Esp_Dur,MATCH($E12,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P12" s="12">
@@ -4334,7 +4352,7 @@
         <v/>
       </c>
       <c r="O13" s="24">
-        <f>IF($B13="","",IF(COUNTIF(Postos_Cod,$B13)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B13)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B13,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E13)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H13)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C13)),NOT(ISNUMBER($D13))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C13),ISNUMBER($D13),MOD($D13-$C13,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J13&gt;0,OR($P13&gt;=Turno_Min,$Q13&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J13&gt;0,$K13&gt;0,COUNTIF(Mapa_Chave,$B13&amp;"#"&amp;$A13&amp;"#"&amp;($K13+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B13&amp;"#"&amp;$A13&amp;"#"&amp;($K13+1),Mapa_Chave,0))-$Q13&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J13&gt;0,SUMPRODUCT((Mapa_Sala=$B13)*(Mapa_Data=$A13)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q13)*(Mapa_RelFim&gt;$P13))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I13),$I13&gt;0,COUNTIF(Esp_Nome,$E13)&gt;0,$I13&gt;3*INDEX(Esp_Dur,MATCH($E13,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B13="","",IF(COUNTIF(Postos_Cod,$B13)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B13)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B13,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E13)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H13)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C13)),NOT(ISNUMBER($D13))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C13),ISNUMBER($D13),MOD($D13-$C13,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J13&gt;0,OR($P13&gt;=Turno_Min,$Q13&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J13&gt;0,SUMPRODUCT((Mapa_Sala=$B13)*(Mapa_Data=$A13)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q13)*(Mapa_RelFim&gt;$P13))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I13),$I13&gt;0,COUNTIF(Esp_Nome,$E13)&gt;0,$I13&gt;3*INDEX(Esp_Dur,MATCH($E13,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P13" s="12">
@@ -4418,7 +4436,7 @@
         <v/>
       </c>
       <c r="O14" s="24">
-        <f>IF($B14="","",IF(COUNTIF(Postos_Cod,$B14)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B14)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B14,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E14)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H14)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C14)),NOT(ISNUMBER($D14))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C14),ISNUMBER($D14),MOD($D14-$C14,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J14&gt;0,OR($P14&gt;=Turno_Min,$Q14&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J14&gt;0,$K14&gt;0,COUNTIF(Mapa_Chave,$B14&amp;"#"&amp;$A14&amp;"#"&amp;($K14+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B14&amp;"#"&amp;$A14&amp;"#"&amp;($K14+1),Mapa_Chave,0))-$Q14&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J14&gt;0,SUMPRODUCT((Mapa_Sala=$B14)*(Mapa_Data=$A14)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q14)*(Mapa_RelFim&gt;$P14))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I14),$I14&gt;0,COUNTIF(Esp_Nome,$E14)&gt;0,$I14&gt;3*INDEX(Esp_Dur,MATCH($E14,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B14="","",IF(COUNTIF(Postos_Cod,$B14)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B14)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B14,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E14)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H14)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C14)),NOT(ISNUMBER($D14))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C14),ISNUMBER($D14),MOD($D14-$C14,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J14&gt;0,OR($P14&gt;=Turno_Min,$Q14&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J14&gt;0,SUMPRODUCT((Mapa_Sala=$B14)*(Mapa_Data=$A14)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q14)*(Mapa_RelFim&gt;$P14))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I14),$I14&gt;0,COUNTIF(Esp_Nome,$E14)&gt;0,$I14&gt;3*INDEX(Esp_Dur,MATCH($E14,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P14" s="12">
@@ -4502,7 +4520,7 @@
         <v/>
       </c>
       <c r="O15" s="24">
-        <f>IF($B15="","",IF(COUNTIF(Postos_Cod,$B15)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B15)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B15,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E15)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H15)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C15)),NOT(ISNUMBER($D15))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C15),ISNUMBER($D15),MOD($D15-$C15,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J15&gt;0,OR($P15&gt;=Turno_Min,$Q15&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J15&gt;0,$K15&gt;0,COUNTIF(Mapa_Chave,$B15&amp;"#"&amp;$A15&amp;"#"&amp;($K15+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B15&amp;"#"&amp;$A15&amp;"#"&amp;($K15+1),Mapa_Chave,0))-$Q15&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J15&gt;0,SUMPRODUCT((Mapa_Sala=$B15)*(Mapa_Data=$A15)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q15)*(Mapa_RelFim&gt;$P15))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I15),$I15&gt;0,COUNTIF(Esp_Nome,$E15)&gt;0,$I15&gt;3*INDEX(Esp_Dur,MATCH($E15,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B15="","",IF(COUNTIF(Postos_Cod,$B15)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B15)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B15,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E15)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H15)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C15)),NOT(ISNUMBER($D15))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C15),ISNUMBER($D15),MOD($D15-$C15,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J15&gt;0,OR($P15&gt;=Turno_Min,$Q15&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J15&gt;0,SUMPRODUCT((Mapa_Sala=$B15)*(Mapa_Data=$A15)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q15)*(Mapa_RelFim&gt;$P15))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I15),$I15&gt;0,COUNTIF(Esp_Nome,$E15)&gt;0,$I15&gt;3*INDEX(Esp_Dur,MATCH($E15,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P15" s="12">
@@ -4586,7 +4604,7 @@
         <v/>
       </c>
       <c r="O16" s="24">
-        <f>IF($B16="","",IF(COUNTIF(Postos_Cod,$B16)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B16)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B16,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E16)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H16)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C16)),NOT(ISNUMBER($D16))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C16),ISNUMBER($D16),MOD($D16-$C16,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J16&gt;0,OR($P16&gt;=Turno_Min,$Q16&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J16&gt;0,$K16&gt;0,COUNTIF(Mapa_Chave,$B16&amp;"#"&amp;$A16&amp;"#"&amp;($K16+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B16&amp;"#"&amp;$A16&amp;"#"&amp;($K16+1),Mapa_Chave,0))-$Q16&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J16&gt;0,SUMPRODUCT((Mapa_Sala=$B16)*(Mapa_Data=$A16)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q16)*(Mapa_RelFim&gt;$P16))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I16),$I16&gt;0,COUNTIF(Esp_Nome,$E16)&gt;0,$I16&gt;3*INDEX(Esp_Dur,MATCH($E16,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B16="","",IF(COUNTIF(Postos_Cod,$B16)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B16)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B16,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E16)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H16)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C16)),NOT(ISNUMBER($D16))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C16),ISNUMBER($D16),MOD($D16-$C16,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J16&gt;0,OR($P16&gt;=Turno_Min,$Q16&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J16&gt;0,SUMPRODUCT((Mapa_Sala=$B16)*(Mapa_Data=$A16)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q16)*(Mapa_RelFim&gt;$P16))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I16),$I16&gt;0,COUNTIF(Esp_Nome,$E16)&gt;0,$I16&gt;3*INDEX(Esp_Dur,MATCH($E16,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P16" s="12">
@@ -4670,7 +4688,7 @@
         <v/>
       </c>
       <c r="O17" s="24">
-        <f>IF($B17="","",IF(COUNTIF(Postos_Cod,$B17)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B17)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B17,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E17)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H17)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C17)),NOT(ISNUMBER($D17))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C17),ISNUMBER($D17),MOD($D17-$C17,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J17&gt;0,OR($P17&gt;=Turno_Min,$Q17&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J17&gt;0,$K17&gt;0,COUNTIF(Mapa_Chave,$B17&amp;"#"&amp;$A17&amp;"#"&amp;($K17+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B17&amp;"#"&amp;$A17&amp;"#"&amp;($K17+1),Mapa_Chave,0))-$Q17&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J17&gt;0,SUMPRODUCT((Mapa_Sala=$B17)*(Mapa_Data=$A17)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q17)*(Mapa_RelFim&gt;$P17))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I17),$I17&gt;0,COUNTIF(Esp_Nome,$E17)&gt;0,$I17&gt;3*INDEX(Esp_Dur,MATCH($E17,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B17="","",IF(COUNTIF(Postos_Cod,$B17)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B17)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B17,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E17)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H17)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C17)),NOT(ISNUMBER($D17))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C17),ISNUMBER($D17),MOD($D17-$C17,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J17&gt;0,OR($P17&gt;=Turno_Min,$Q17&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J17&gt;0,SUMPRODUCT((Mapa_Sala=$B17)*(Mapa_Data=$A17)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q17)*(Mapa_RelFim&gt;$P17))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I17),$I17&gt;0,COUNTIF(Esp_Nome,$E17)&gt;0,$I17&gt;3*INDEX(Esp_Dur,MATCH($E17,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P17" s="12">
@@ -4754,7 +4772,7 @@
         <v/>
       </c>
       <c r="O18" s="24">
-        <f>IF($B18="","",IF(COUNTIF(Postos_Cod,$B18)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B18)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B18,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E18)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H18)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C18)),NOT(ISNUMBER($D18))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C18),ISNUMBER($D18),MOD($D18-$C18,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J18&gt;0,OR($P18&gt;=Turno_Min,$Q18&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J18&gt;0,$K18&gt;0,COUNTIF(Mapa_Chave,$B18&amp;"#"&amp;$A18&amp;"#"&amp;($K18+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B18&amp;"#"&amp;$A18&amp;"#"&amp;($K18+1),Mapa_Chave,0))-$Q18&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J18&gt;0,SUMPRODUCT((Mapa_Sala=$B18)*(Mapa_Data=$A18)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q18)*(Mapa_RelFim&gt;$P18))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I18),$I18&gt;0,COUNTIF(Esp_Nome,$E18)&gt;0,$I18&gt;3*INDEX(Esp_Dur,MATCH($E18,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B18="","",IF(COUNTIF(Postos_Cod,$B18)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B18)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B18,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E18)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H18)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C18)),NOT(ISNUMBER($D18))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C18),ISNUMBER($D18),MOD($D18-$C18,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J18&gt;0,OR($P18&gt;=Turno_Min,$Q18&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J18&gt;0,SUMPRODUCT((Mapa_Sala=$B18)*(Mapa_Data=$A18)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q18)*(Mapa_RelFim&gt;$P18))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I18),$I18&gt;0,COUNTIF(Esp_Nome,$E18)&gt;0,$I18&gt;3*INDEX(Esp_Dur,MATCH($E18,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P18" s="12">
@@ -4812,7 +4830,7 @@
         <v/>
       </c>
       <c r="O19" s="24">
-        <f>IF($B19="","",IF(COUNTIF(Postos_Cod,$B19)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B19)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B19,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E19)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H19)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C19)),NOT(ISNUMBER($D19))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C19),ISNUMBER($D19),MOD($D19-$C19,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J19&gt;0,OR($P19&gt;=Turno_Min,$Q19&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J19&gt;0,$K19&gt;0,COUNTIF(Mapa_Chave,$B19&amp;"#"&amp;$A19&amp;"#"&amp;($K19+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B19&amp;"#"&amp;$A19&amp;"#"&amp;($K19+1),Mapa_Chave,0))-$Q19&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J19&gt;0,SUMPRODUCT((Mapa_Sala=$B19)*(Mapa_Data=$A19)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q19)*(Mapa_RelFim&gt;$P19))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I19),$I19&gt;0,COUNTIF(Esp_Nome,$E19)&gt;0,$I19&gt;3*INDEX(Esp_Dur,MATCH($E19,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B19="","",IF(COUNTIF(Postos_Cod,$B19)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B19)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B19,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E19)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H19)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C19)),NOT(ISNUMBER($D19))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C19),ISNUMBER($D19),MOD($D19-$C19,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J19&gt;0,OR($P19&gt;=Turno_Min,$Q19&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J19&gt;0,SUMPRODUCT((Mapa_Sala=$B19)*(Mapa_Data=$A19)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q19)*(Mapa_RelFim&gt;$P19))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I19),$I19&gt;0,COUNTIF(Esp_Nome,$E19)&gt;0,$I19&gt;3*INDEX(Esp_Dur,MATCH($E19,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P19" s="12">
@@ -4870,7 +4888,7 @@
         <v/>
       </c>
       <c r="O20" s="24">
-        <f>IF($B20="","",IF(COUNTIF(Postos_Cod,$B20)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B20)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B20,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E20)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H20)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C20)),NOT(ISNUMBER($D20))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C20),ISNUMBER($D20),MOD($D20-$C20,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J20&gt;0,OR($P20&gt;=Turno_Min,$Q20&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J20&gt;0,$K20&gt;0,COUNTIF(Mapa_Chave,$B20&amp;"#"&amp;$A20&amp;"#"&amp;($K20+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B20&amp;"#"&amp;$A20&amp;"#"&amp;($K20+1),Mapa_Chave,0))-$Q20&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J20&gt;0,SUMPRODUCT((Mapa_Sala=$B20)*(Mapa_Data=$A20)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q20)*(Mapa_RelFim&gt;$P20))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I20),$I20&gt;0,COUNTIF(Esp_Nome,$E20)&gt;0,$I20&gt;3*INDEX(Esp_Dur,MATCH($E20,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B20="","",IF(COUNTIF(Postos_Cod,$B20)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B20)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B20,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E20)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H20)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C20)),NOT(ISNUMBER($D20))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C20),ISNUMBER($D20),MOD($D20-$C20,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J20&gt;0,OR($P20&gt;=Turno_Min,$Q20&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J20&gt;0,SUMPRODUCT((Mapa_Sala=$B20)*(Mapa_Data=$A20)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q20)*(Mapa_RelFim&gt;$P20))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I20),$I20&gt;0,COUNTIF(Esp_Nome,$E20)&gt;0,$I20&gt;3*INDEX(Esp_Dur,MATCH($E20,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P20" s="12">
@@ -4928,7 +4946,7 @@
         <v/>
       </c>
       <c r="O21" s="24">
-        <f>IF($B21="","",IF(COUNTIF(Postos_Cod,$B21)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B21)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B21,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E21)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H21)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C21)),NOT(ISNUMBER($D21))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C21),ISNUMBER($D21),MOD($D21-$C21,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J21&gt;0,OR($P21&gt;=Turno_Min,$Q21&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J21&gt;0,$K21&gt;0,COUNTIF(Mapa_Chave,$B21&amp;"#"&amp;$A21&amp;"#"&amp;($K21+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B21&amp;"#"&amp;$A21&amp;"#"&amp;($K21+1),Mapa_Chave,0))-$Q21&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J21&gt;0,SUMPRODUCT((Mapa_Sala=$B21)*(Mapa_Data=$A21)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q21)*(Mapa_RelFim&gt;$P21))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I21),$I21&gt;0,COUNTIF(Esp_Nome,$E21)&gt;0,$I21&gt;3*INDEX(Esp_Dur,MATCH($E21,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B21="","",IF(COUNTIF(Postos_Cod,$B21)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B21)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B21,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E21)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H21)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C21)),NOT(ISNUMBER($D21))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C21),ISNUMBER($D21),MOD($D21-$C21,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J21&gt;0,OR($P21&gt;=Turno_Min,$Q21&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J21&gt;0,SUMPRODUCT((Mapa_Sala=$B21)*(Mapa_Data=$A21)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q21)*(Mapa_RelFim&gt;$P21))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I21),$I21&gt;0,COUNTIF(Esp_Nome,$E21)&gt;0,$I21&gt;3*INDEX(Esp_Dur,MATCH($E21,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P21" s="12">
@@ -4986,7 +5004,7 @@
         <v/>
       </c>
       <c r="O22" s="24">
-        <f>IF($B22="","",IF(COUNTIF(Postos_Cod,$B22)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B22)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B22,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E22)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H22)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C22)),NOT(ISNUMBER($D22))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C22),ISNUMBER($D22),MOD($D22-$C22,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J22&gt;0,OR($P22&gt;=Turno_Min,$Q22&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J22&gt;0,$K22&gt;0,COUNTIF(Mapa_Chave,$B22&amp;"#"&amp;$A22&amp;"#"&amp;($K22+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B22&amp;"#"&amp;$A22&amp;"#"&amp;($K22+1),Mapa_Chave,0))-$Q22&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J22&gt;0,SUMPRODUCT((Mapa_Sala=$B22)*(Mapa_Data=$A22)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q22)*(Mapa_RelFim&gt;$P22))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I22),$I22&gt;0,COUNTIF(Esp_Nome,$E22)&gt;0,$I22&gt;3*INDEX(Esp_Dur,MATCH($E22,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B22="","",IF(COUNTIF(Postos_Cod,$B22)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B22)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B22,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E22)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H22)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C22)),NOT(ISNUMBER($D22))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C22),ISNUMBER($D22),MOD($D22-$C22,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J22&gt;0,OR($P22&gt;=Turno_Min,$Q22&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J22&gt;0,SUMPRODUCT((Mapa_Sala=$B22)*(Mapa_Data=$A22)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q22)*(Mapa_RelFim&gt;$P22))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I22),$I22&gt;0,COUNTIF(Esp_Nome,$E22)&gt;0,$I22&gt;3*INDEX(Esp_Dur,MATCH($E22,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P22" s="12">
@@ -5044,7 +5062,7 @@
         <v/>
       </c>
       <c r="O23" s="24">
-        <f>IF($B23="","",IF(COUNTIF(Postos_Cod,$B23)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B23)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B23,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E23)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H23)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C23)),NOT(ISNUMBER($D23))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C23),ISNUMBER($D23),MOD($D23-$C23,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J23&gt;0,OR($P23&gt;=Turno_Min,$Q23&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J23&gt;0,$K23&gt;0,COUNTIF(Mapa_Chave,$B23&amp;"#"&amp;$A23&amp;"#"&amp;($K23+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B23&amp;"#"&amp;$A23&amp;"#"&amp;($K23+1),Mapa_Chave,0))-$Q23&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J23&gt;0,SUMPRODUCT((Mapa_Sala=$B23)*(Mapa_Data=$A23)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q23)*(Mapa_RelFim&gt;$P23))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I23),$I23&gt;0,COUNTIF(Esp_Nome,$E23)&gt;0,$I23&gt;3*INDEX(Esp_Dur,MATCH($E23,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B23="","",IF(COUNTIF(Postos_Cod,$B23)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B23)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B23,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E23)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H23)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C23)),NOT(ISNUMBER($D23))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C23),ISNUMBER($D23),MOD($D23-$C23,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J23&gt;0,OR($P23&gt;=Turno_Min,$Q23&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J23&gt;0,SUMPRODUCT((Mapa_Sala=$B23)*(Mapa_Data=$A23)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q23)*(Mapa_RelFim&gt;$P23))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I23),$I23&gt;0,COUNTIF(Esp_Nome,$E23)&gt;0,$I23&gt;3*INDEX(Esp_Dur,MATCH($E23,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P23" s="12">
@@ -5102,7 +5120,7 @@
         <v/>
       </c>
       <c r="O24" s="24">
-        <f>IF($B24="","",IF(COUNTIF(Postos_Cod,$B24)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B24)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B24,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E24)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H24)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C24)),NOT(ISNUMBER($D24))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C24),ISNUMBER($D24),MOD($D24-$C24,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J24&gt;0,OR($P24&gt;=Turno_Min,$Q24&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J24&gt;0,$K24&gt;0,COUNTIF(Mapa_Chave,$B24&amp;"#"&amp;$A24&amp;"#"&amp;($K24+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B24&amp;"#"&amp;$A24&amp;"#"&amp;($K24+1),Mapa_Chave,0))-$Q24&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J24&gt;0,SUMPRODUCT((Mapa_Sala=$B24)*(Mapa_Data=$A24)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q24)*(Mapa_RelFim&gt;$P24))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I24),$I24&gt;0,COUNTIF(Esp_Nome,$E24)&gt;0,$I24&gt;3*INDEX(Esp_Dur,MATCH($E24,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B24="","",IF(COUNTIF(Postos_Cod,$B24)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B24)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B24,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E24)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H24)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C24)),NOT(ISNUMBER($D24))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C24),ISNUMBER($D24),MOD($D24-$C24,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J24&gt;0,OR($P24&gt;=Turno_Min,$Q24&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J24&gt;0,SUMPRODUCT((Mapa_Sala=$B24)*(Mapa_Data=$A24)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q24)*(Mapa_RelFim&gt;$P24))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I24),$I24&gt;0,COUNTIF(Esp_Nome,$E24)&gt;0,$I24&gt;3*INDEX(Esp_Dur,MATCH($E24,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P24" s="12">
@@ -5160,7 +5178,7 @@
         <v/>
       </c>
       <c r="O25" s="24">
-        <f>IF($B25="","",IF(COUNTIF(Postos_Cod,$B25)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B25)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B25,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E25)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H25)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C25)),NOT(ISNUMBER($D25))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C25),ISNUMBER($D25),MOD($D25-$C25,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J25&gt;0,OR($P25&gt;=Turno_Min,$Q25&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J25&gt;0,$K25&gt;0,COUNTIF(Mapa_Chave,$B25&amp;"#"&amp;$A25&amp;"#"&amp;($K25+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B25&amp;"#"&amp;$A25&amp;"#"&amp;($K25+1),Mapa_Chave,0))-$Q25&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J25&gt;0,SUMPRODUCT((Mapa_Sala=$B25)*(Mapa_Data=$A25)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q25)*(Mapa_RelFim&gt;$P25))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I25),$I25&gt;0,COUNTIF(Esp_Nome,$E25)&gt;0,$I25&gt;3*INDEX(Esp_Dur,MATCH($E25,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B25="","",IF(COUNTIF(Postos_Cod,$B25)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B25)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B25,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E25)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H25)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C25)),NOT(ISNUMBER($D25))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C25),ISNUMBER($D25),MOD($D25-$C25,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J25&gt;0,OR($P25&gt;=Turno_Min,$Q25&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J25&gt;0,SUMPRODUCT((Mapa_Sala=$B25)*(Mapa_Data=$A25)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q25)*(Mapa_RelFim&gt;$P25))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I25),$I25&gt;0,COUNTIF(Esp_Nome,$E25)&gt;0,$I25&gt;3*INDEX(Esp_Dur,MATCH($E25,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P25" s="12">
@@ -5218,7 +5236,7 @@
         <v/>
       </c>
       <c r="O26" s="24">
-        <f>IF($B26="","",IF(COUNTIF(Postos_Cod,$B26)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B26)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B26,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E26)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H26)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C26)),NOT(ISNUMBER($D26))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C26),ISNUMBER($D26),MOD($D26-$C26,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J26&gt;0,OR($P26&gt;=Turno_Min,$Q26&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J26&gt;0,$K26&gt;0,COUNTIF(Mapa_Chave,$B26&amp;"#"&amp;$A26&amp;"#"&amp;($K26+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B26&amp;"#"&amp;$A26&amp;"#"&amp;($K26+1),Mapa_Chave,0))-$Q26&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J26&gt;0,SUMPRODUCT((Mapa_Sala=$B26)*(Mapa_Data=$A26)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q26)*(Mapa_RelFim&gt;$P26))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I26),$I26&gt;0,COUNTIF(Esp_Nome,$E26)&gt;0,$I26&gt;3*INDEX(Esp_Dur,MATCH($E26,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B26="","",IF(COUNTIF(Postos_Cod,$B26)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B26)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B26,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E26)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H26)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C26)),NOT(ISNUMBER($D26))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C26),ISNUMBER($D26),MOD($D26-$C26,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J26&gt;0,OR($P26&gt;=Turno_Min,$Q26&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J26&gt;0,SUMPRODUCT((Mapa_Sala=$B26)*(Mapa_Data=$A26)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q26)*(Mapa_RelFim&gt;$P26))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I26),$I26&gt;0,COUNTIF(Esp_Nome,$E26)&gt;0,$I26&gt;3*INDEX(Esp_Dur,MATCH($E26,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P26" s="12">
@@ -5276,7 +5294,7 @@
         <v/>
       </c>
       <c r="O27" s="24">
-        <f>IF($B27="","",IF(COUNTIF(Postos_Cod,$B27)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B27)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B27,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E27)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H27)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C27)),NOT(ISNUMBER($D27))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C27),ISNUMBER($D27),MOD($D27-$C27,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J27&gt;0,OR($P27&gt;=Turno_Min,$Q27&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J27&gt;0,$K27&gt;0,COUNTIF(Mapa_Chave,$B27&amp;"#"&amp;$A27&amp;"#"&amp;($K27+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B27&amp;"#"&amp;$A27&amp;"#"&amp;($K27+1),Mapa_Chave,0))-$Q27&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J27&gt;0,SUMPRODUCT((Mapa_Sala=$B27)*(Mapa_Data=$A27)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q27)*(Mapa_RelFim&gt;$P27))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I27),$I27&gt;0,COUNTIF(Esp_Nome,$E27)&gt;0,$I27&gt;3*INDEX(Esp_Dur,MATCH($E27,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B27="","",IF(COUNTIF(Postos_Cod,$B27)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B27)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B27,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E27)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H27)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C27)),NOT(ISNUMBER($D27))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C27),ISNUMBER($D27),MOD($D27-$C27,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J27&gt;0,OR($P27&gt;=Turno_Min,$Q27&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J27&gt;0,SUMPRODUCT((Mapa_Sala=$B27)*(Mapa_Data=$A27)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q27)*(Mapa_RelFim&gt;$P27))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I27),$I27&gt;0,COUNTIF(Esp_Nome,$E27)&gt;0,$I27&gt;3*INDEX(Esp_Dur,MATCH($E27,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P27" s="12">
@@ -5334,7 +5352,7 @@
         <v/>
       </c>
       <c r="O28" s="24">
-        <f>IF($B28="","",IF(COUNTIF(Postos_Cod,$B28)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B28)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B28,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E28)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H28)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C28)),NOT(ISNUMBER($D28))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C28),ISNUMBER($D28),MOD($D28-$C28,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J28&gt;0,OR($P28&gt;=Turno_Min,$Q28&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J28&gt;0,$K28&gt;0,COUNTIF(Mapa_Chave,$B28&amp;"#"&amp;$A28&amp;"#"&amp;($K28+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B28&amp;"#"&amp;$A28&amp;"#"&amp;($K28+1),Mapa_Chave,0))-$Q28&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J28&gt;0,SUMPRODUCT((Mapa_Sala=$B28)*(Mapa_Data=$A28)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q28)*(Mapa_RelFim&gt;$P28))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I28),$I28&gt;0,COUNTIF(Esp_Nome,$E28)&gt;0,$I28&gt;3*INDEX(Esp_Dur,MATCH($E28,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B28="","",IF(COUNTIF(Postos_Cod,$B28)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B28)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B28,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E28)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H28)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C28)),NOT(ISNUMBER($D28))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C28),ISNUMBER($D28),MOD($D28-$C28,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J28&gt;0,OR($P28&gt;=Turno_Min,$Q28&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J28&gt;0,SUMPRODUCT((Mapa_Sala=$B28)*(Mapa_Data=$A28)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q28)*(Mapa_RelFim&gt;$P28))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I28),$I28&gt;0,COUNTIF(Esp_Nome,$E28)&gt;0,$I28&gt;3*INDEX(Esp_Dur,MATCH($E28,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P28" s="12">
@@ -5392,7 +5410,7 @@
         <v/>
       </c>
       <c r="O29" s="24">
-        <f>IF($B29="","",IF(COUNTIF(Postos_Cod,$B29)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B29)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B29,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E29)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H29)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C29)),NOT(ISNUMBER($D29))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C29),ISNUMBER($D29),MOD($D29-$C29,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J29&gt;0,OR($P29&gt;=Turno_Min,$Q29&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J29&gt;0,$K29&gt;0,COUNTIF(Mapa_Chave,$B29&amp;"#"&amp;$A29&amp;"#"&amp;($K29+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B29&amp;"#"&amp;$A29&amp;"#"&amp;($K29+1),Mapa_Chave,0))-$Q29&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J29&gt;0,SUMPRODUCT((Mapa_Sala=$B29)*(Mapa_Data=$A29)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q29)*(Mapa_RelFim&gt;$P29))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I29),$I29&gt;0,COUNTIF(Esp_Nome,$E29)&gt;0,$I29&gt;3*INDEX(Esp_Dur,MATCH($E29,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B29="","",IF(COUNTIF(Postos_Cod,$B29)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B29)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B29,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E29)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H29)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C29)),NOT(ISNUMBER($D29))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C29),ISNUMBER($D29),MOD($D29-$C29,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J29&gt;0,OR($P29&gt;=Turno_Min,$Q29&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J29&gt;0,SUMPRODUCT((Mapa_Sala=$B29)*(Mapa_Data=$A29)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q29)*(Mapa_RelFim&gt;$P29))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I29),$I29&gt;0,COUNTIF(Esp_Nome,$E29)&gt;0,$I29&gt;3*INDEX(Esp_Dur,MATCH($E29,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P29" s="12">
@@ -5450,7 +5468,7 @@
         <v/>
       </c>
       <c r="O30" s="24">
-        <f>IF($B30="","",IF(COUNTIF(Postos_Cod,$B30)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B30)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B30,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E30)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H30)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C30)),NOT(ISNUMBER($D30))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C30),ISNUMBER($D30),MOD($D30-$C30,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J30&gt;0,OR($P30&gt;=Turno_Min,$Q30&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J30&gt;0,$K30&gt;0,COUNTIF(Mapa_Chave,$B30&amp;"#"&amp;$A30&amp;"#"&amp;($K30+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B30&amp;"#"&amp;$A30&amp;"#"&amp;($K30+1),Mapa_Chave,0))-$Q30&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J30&gt;0,SUMPRODUCT((Mapa_Sala=$B30)*(Mapa_Data=$A30)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q30)*(Mapa_RelFim&gt;$P30))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I30),$I30&gt;0,COUNTIF(Esp_Nome,$E30)&gt;0,$I30&gt;3*INDEX(Esp_Dur,MATCH($E30,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B30="","",IF(COUNTIF(Postos_Cod,$B30)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B30)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B30,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E30)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H30)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C30)),NOT(ISNUMBER($D30))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C30),ISNUMBER($D30),MOD($D30-$C30,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J30&gt;0,OR($P30&gt;=Turno_Min,$Q30&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J30&gt;0,SUMPRODUCT((Mapa_Sala=$B30)*(Mapa_Data=$A30)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q30)*(Mapa_RelFim&gt;$P30))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I30),$I30&gt;0,COUNTIF(Esp_Nome,$E30)&gt;0,$I30&gt;3*INDEX(Esp_Dur,MATCH($E30,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P30" s="12">
@@ -5508,7 +5526,7 @@
         <v/>
       </c>
       <c r="O31" s="24">
-        <f>IF($B31="","",IF(COUNTIF(Postos_Cod,$B31)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B31)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B31,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E31)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H31)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C31)),NOT(ISNUMBER($D31))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C31),ISNUMBER($D31),MOD($D31-$C31,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J31&gt;0,OR($P31&gt;=Turno_Min,$Q31&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J31&gt;0,$K31&gt;0,COUNTIF(Mapa_Chave,$B31&amp;"#"&amp;$A31&amp;"#"&amp;($K31+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B31&amp;"#"&amp;$A31&amp;"#"&amp;($K31+1),Mapa_Chave,0))-$Q31&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J31&gt;0,SUMPRODUCT((Mapa_Sala=$B31)*(Mapa_Data=$A31)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q31)*(Mapa_RelFim&gt;$P31))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I31),$I31&gt;0,COUNTIF(Esp_Nome,$E31)&gt;0,$I31&gt;3*INDEX(Esp_Dur,MATCH($E31,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B31="","",IF(COUNTIF(Postos_Cod,$B31)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B31)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B31,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E31)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H31)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C31)),NOT(ISNUMBER($D31))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C31),ISNUMBER($D31),MOD($D31-$C31,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J31&gt;0,OR($P31&gt;=Turno_Min,$Q31&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J31&gt;0,SUMPRODUCT((Mapa_Sala=$B31)*(Mapa_Data=$A31)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q31)*(Mapa_RelFim&gt;$P31))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I31),$I31&gt;0,COUNTIF(Esp_Nome,$E31)&gt;0,$I31&gt;3*INDEX(Esp_Dur,MATCH($E31,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P31" s="12">
@@ -5566,7 +5584,7 @@
         <v/>
       </c>
       <c r="O32" s="24">
-        <f>IF($B32="","",IF(COUNTIF(Postos_Cod,$B32)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B32)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B32,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E32)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H32)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C32)),NOT(ISNUMBER($D32))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C32),ISNUMBER($D32),MOD($D32-$C32,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J32&gt;0,OR($P32&gt;=Turno_Min,$Q32&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J32&gt;0,$K32&gt;0,COUNTIF(Mapa_Chave,$B32&amp;"#"&amp;$A32&amp;"#"&amp;($K32+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B32&amp;"#"&amp;$A32&amp;"#"&amp;($K32+1),Mapa_Chave,0))-$Q32&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J32&gt;0,SUMPRODUCT((Mapa_Sala=$B32)*(Mapa_Data=$A32)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q32)*(Mapa_RelFim&gt;$P32))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I32),$I32&gt;0,COUNTIF(Esp_Nome,$E32)&gt;0,$I32&gt;3*INDEX(Esp_Dur,MATCH($E32,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B32="","",IF(COUNTIF(Postos_Cod,$B32)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B32)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B32,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E32)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H32)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C32)),NOT(ISNUMBER($D32))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C32),ISNUMBER($D32),MOD($D32-$C32,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J32&gt;0,OR($P32&gt;=Turno_Min,$Q32&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J32&gt;0,SUMPRODUCT((Mapa_Sala=$B32)*(Mapa_Data=$A32)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q32)*(Mapa_RelFim&gt;$P32))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I32),$I32&gt;0,COUNTIF(Esp_Nome,$E32)&gt;0,$I32&gt;3*INDEX(Esp_Dur,MATCH($E32,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P32" s="12">
@@ -5624,7 +5642,7 @@
         <v/>
       </c>
       <c r="O33" s="24">
-        <f>IF($B33="","",IF(COUNTIF(Postos_Cod,$B33)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B33)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B33,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E33)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H33)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C33)),NOT(ISNUMBER($D33))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C33),ISNUMBER($D33),MOD($D33-$C33,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J33&gt;0,OR($P33&gt;=Turno_Min,$Q33&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J33&gt;0,$K33&gt;0,COUNTIF(Mapa_Chave,$B33&amp;"#"&amp;$A33&amp;"#"&amp;($K33+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B33&amp;"#"&amp;$A33&amp;"#"&amp;($K33+1),Mapa_Chave,0))-$Q33&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J33&gt;0,SUMPRODUCT((Mapa_Sala=$B33)*(Mapa_Data=$A33)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q33)*(Mapa_RelFim&gt;$P33))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I33),$I33&gt;0,COUNTIF(Esp_Nome,$E33)&gt;0,$I33&gt;3*INDEX(Esp_Dur,MATCH($E33,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B33="","",IF(COUNTIF(Postos_Cod,$B33)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B33)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B33,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E33)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H33)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C33)),NOT(ISNUMBER($D33))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C33),ISNUMBER($D33),MOD($D33-$C33,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J33&gt;0,OR($P33&gt;=Turno_Min,$Q33&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J33&gt;0,SUMPRODUCT((Mapa_Sala=$B33)*(Mapa_Data=$A33)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q33)*(Mapa_RelFim&gt;$P33))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I33),$I33&gt;0,COUNTIF(Esp_Nome,$E33)&gt;0,$I33&gt;3*INDEX(Esp_Dur,MATCH($E33,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P33" s="12">
@@ -5682,7 +5700,7 @@
         <v/>
       </c>
       <c r="O34" s="24">
-        <f>IF($B34="","",IF(COUNTIF(Postos_Cod,$B34)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B34)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B34,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E34)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H34)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C34)),NOT(ISNUMBER($D34))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C34),ISNUMBER($D34),MOD($D34-$C34,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J34&gt;0,OR($P34&gt;=Turno_Min,$Q34&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J34&gt;0,$K34&gt;0,COUNTIF(Mapa_Chave,$B34&amp;"#"&amp;$A34&amp;"#"&amp;($K34+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B34&amp;"#"&amp;$A34&amp;"#"&amp;($K34+1),Mapa_Chave,0))-$Q34&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J34&gt;0,SUMPRODUCT((Mapa_Sala=$B34)*(Mapa_Data=$A34)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q34)*(Mapa_RelFim&gt;$P34))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I34),$I34&gt;0,COUNTIF(Esp_Nome,$E34)&gt;0,$I34&gt;3*INDEX(Esp_Dur,MATCH($E34,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B34="","",IF(COUNTIF(Postos_Cod,$B34)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B34)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B34,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E34)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H34)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C34)),NOT(ISNUMBER($D34))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C34),ISNUMBER($D34),MOD($D34-$C34,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J34&gt;0,OR($P34&gt;=Turno_Min,$Q34&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J34&gt;0,SUMPRODUCT((Mapa_Sala=$B34)*(Mapa_Data=$A34)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q34)*(Mapa_RelFim&gt;$P34))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I34),$I34&gt;0,COUNTIF(Esp_Nome,$E34)&gt;0,$I34&gt;3*INDEX(Esp_Dur,MATCH($E34,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P34" s="12">
@@ -5740,7 +5758,7 @@
         <v/>
       </c>
       <c r="O35" s="24">
-        <f>IF($B35="","",IF(COUNTIF(Postos_Cod,$B35)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B35)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B35,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E35)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H35)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C35)),NOT(ISNUMBER($D35))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C35),ISNUMBER($D35),MOD($D35-$C35,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J35&gt;0,OR($P35&gt;=Turno_Min,$Q35&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J35&gt;0,$K35&gt;0,COUNTIF(Mapa_Chave,$B35&amp;"#"&amp;$A35&amp;"#"&amp;($K35+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B35&amp;"#"&amp;$A35&amp;"#"&amp;($K35+1),Mapa_Chave,0))-$Q35&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J35&gt;0,SUMPRODUCT((Mapa_Sala=$B35)*(Mapa_Data=$A35)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q35)*(Mapa_RelFim&gt;$P35))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I35),$I35&gt;0,COUNTIF(Esp_Nome,$E35)&gt;0,$I35&gt;3*INDEX(Esp_Dur,MATCH($E35,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B35="","",IF(COUNTIF(Postos_Cod,$B35)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B35)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B35,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E35)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H35)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C35)),NOT(ISNUMBER($D35))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C35),ISNUMBER($D35),MOD($D35-$C35,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J35&gt;0,OR($P35&gt;=Turno_Min,$Q35&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J35&gt;0,SUMPRODUCT((Mapa_Sala=$B35)*(Mapa_Data=$A35)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q35)*(Mapa_RelFim&gt;$P35))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I35),$I35&gt;0,COUNTIF(Esp_Nome,$E35)&gt;0,$I35&gt;3*INDEX(Esp_Dur,MATCH($E35,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P35" s="12">
@@ -5798,7 +5816,7 @@
         <v/>
       </c>
       <c r="O36" s="24">
-        <f>IF($B36="","",IF(COUNTIF(Postos_Cod,$B36)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B36)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B36,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E36)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H36)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C36)),NOT(ISNUMBER($D36))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C36),ISNUMBER($D36),MOD($D36-$C36,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J36&gt;0,OR($P36&gt;=Turno_Min,$Q36&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J36&gt;0,$K36&gt;0,COUNTIF(Mapa_Chave,$B36&amp;"#"&amp;$A36&amp;"#"&amp;($K36+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B36&amp;"#"&amp;$A36&amp;"#"&amp;($K36+1),Mapa_Chave,0))-$Q36&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J36&gt;0,SUMPRODUCT((Mapa_Sala=$B36)*(Mapa_Data=$A36)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q36)*(Mapa_RelFim&gt;$P36))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I36),$I36&gt;0,COUNTIF(Esp_Nome,$E36)&gt;0,$I36&gt;3*INDEX(Esp_Dur,MATCH($E36,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B36="","",IF(COUNTIF(Postos_Cod,$B36)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B36)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B36,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E36)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H36)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C36)),NOT(ISNUMBER($D36))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C36),ISNUMBER($D36),MOD($D36-$C36,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J36&gt;0,OR($P36&gt;=Turno_Min,$Q36&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J36&gt;0,SUMPRODUCT((Mapa_Sala=$B36)*(Mapa_Data=$A36)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q36)*(Mapa_RelFim&gt;$P36))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I36),$I36&gt;0,COUNTIF(Esp_Nome,$E36)&gt;0,$I36&gt;3*INDEX(Esp_Dur,MATCH($E36,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P36" s="12">
@@ -5856,7 +5874,7 @@
         <v/>
       </c>
       <c r="O37" s="24">
-        <f>IF($B37="","",IF(COUNTIF(Postos_Cod,$B37)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B37)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B37,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E37)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H37)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C37)),NOT(ISNUMBER($D37))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C37),ISNUMBER($D37),MOD($D37-$C37,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J37&gt;0,OR($P37&gt;=Turno_Min,$Q37&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J37&gt;0,$K37&gt;0,COUNTIF(Mapa_Chave,$B37&amp;"#"&amp;$A37&amp;"#"&amp;($K37+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B37&amp;"#"&amp;$A37&amp;"#"&amp;($K37+1),Mapa_Chave,0))-$Q37&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J37&gt;0,SUMPRODUCT((Mapa_Sala=$B37)*(Mapa_Data=$A37)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q37)*(Mapa_RelFim&gt;$P37))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I37),$I37&gt;0,COUNTIF(Esp_Nome,$E37)&gt;0,$I37&gt;3*INDEX(Esp_Dur,MATCH($E37,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B37="","",IF(COUNTIF(Postos_Cod,$B37)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B37)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B37,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E37)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H37)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C37)),NOT(ISNUMBER($D37))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C37),ISNUMBER($D37),MOD($D37-$C37,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J37&gt;0,OR($P37&gt;=Turno_Min,$Q37&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J37&gt;0,SUMPRODUCT((Mapa_Sala=$B37)*(Mapa_Data=$A37)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q37)*(Mapa_RelFim&gt;$P37))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I37),$I37&gt;0,COUNTIF(Esp_Nome,$E37)&gt;0,$I37&gt;3*INDEX(Esp_Dur,MATCH($E37,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P37" s="12">
@@ -5914,7 +5932,7 @@
         <v/>
       </c>
       <c r="O38" s="24">
-        <f>IF($B38="","",IF(COUNTIF(Postos_Cod,$B38)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B38)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B38,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E38)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H38)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C38)),NOT(ISNUMBER($D38))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C38),ISNUMBER($D38),MOD($D38-$C38,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J38&gt;0,OR($P38&gt;=Turno_Min,$Q38&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J38&gt;0,$K38&gt;0,COUNTIF(Mapa_Chave,$B38&amp;"#"&amp;$A38&amp;"#"&amp;($K38+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B38&amp;"#"&amp;$A38&amp;"#"&amp;($K38+1),Mapa_Chave,0))-$Q38&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J38&gt;0,SUMPRODUCT((Mapa_Sala=$B38)*(Mapa_Data=$A38)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q38)*(Mapa_RelFim&gt;$P38))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I38),$I38&gt;0,COUNTIF(Esp_Nome,$E38)&gt;0,$I38&gt;3*INDEX(Esp_Dur,MATCH($E38,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B38="","",IF(COUNTIF(Postos_Cod,$B38)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B38)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B38,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E38)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H38)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C38)),NOT(ISNUMBER($D38))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C38),ISNUMBER($D38),MOD($D38-$C38,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J38&gt;0,OR($P38&gt;=Turno_Min,$Q38&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J38&gt;0,SUMPRODUCT((Mapa_Sala=$B38)*(Mapa_Data=$A38)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q38)*(Mapa_RelFim&gt;$P38))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I38),$I38&gt;0,COUNTIF(Esp_Nome,$E38)&gt;0,$I38&gt;3*INDEX(Esp_Dur,MATCH($E38,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P38" s="12">
@@ -5972,7 +5990,7 @@
         <v/>
       </c>
       <c r="O39" s="24">
-        <f>IF($B39="","",IF(COUNTIF(Postos_Cod,$B39)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B39)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B39,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E39)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H39)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C39)),NOT(ISNUMBER($D39))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C39),ISNUMBER($D39),MOD($D39-$C39,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J39&gt;0,OR($P39&gt;=Turno_Min,$Q39&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J39&gt;0,$K39&gt;0,COUNTIF(Mapa_Chave,$B39&amp;"#"&amp;$A39&amp;"#"&amp;($K39+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B39&amp;"#"&amp;$A39&amp;"#"&amp;($K39+1),Mapa_Chave,0))-$Q39&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J39&gt;0,SUMPRODUCT((Mapa_Sala=$B39)*(Mapa_Data=$A39)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q39)*(Mapa_RelFim&gt;$P39))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I39),$I39&gt;0,COUNTIF(Esp_Nome,$E39)&gt;0,$I39&gt;3*INDEX(Esp_Dur,MATCH($E39,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B39="","",IF(COUNTIF(Postos_Cod,$B39)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B39)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B39,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E39)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H39)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C39)),NOT(ISNUMBER($D39))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C39),ISNUMBER($D39),MOD($D39-$C39,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J39&gt;0,OR($P39&gt;=Turno_Min,$Q39&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J39&gt;0,SUMPRODUCT((Mapa_Sala=$B39)*(Mapa_Data=$A39)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q39)*(Mapa_RelFim&gt;$P39))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I39),$I39&gt;0,COUNTIF(Esp_Nome,$E39)&gt;0,$I39&gt;3*INDEX(Esp_Dur,MATCH($E39,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P39" s="12">
@@ -6030,7 +6048,7 @@
         <v/>
       </c>
       <c r="O40" s="24">
-        <f>IF($B40="","",IF(COUNTIF(Postos_Cod,$B40)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B40)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B40,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E40)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H40)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C40)),NOT(ISNUMBER($D40))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C40),ISNUMBER($D40),MOD($D40-$C40,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J40&gt;0,OR($P40&gt;=Turno_Min,$Q40&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J40&gt;0,$K40&gt;0,COUNTIF(Mapa_Chave,$B40&amp;"#"&amp;$A40&amp;"#"&amp;($K40+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B40&amp;"#"&amp;$A40&amp;"#"&amp;($K40+1),Mapa_Chave,0))-$Q40&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J40&gt;0,SUMPRODUCT((Mapa_Sala=$B40)*(Mapa_Data=$A40)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q40)*(Mapa_RelFim&gt;$P40))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I40),$I40&gt;0,COUNTIF(Esp_Nome,$E40)&gt;0,$I40&gt;3*INDEX(Esp_Dur,MATCH($E40,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B40="","",IF(COUNTIF(Postos_Cod,$B40)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B40)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B40,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E40)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H40)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C40)),NOT(ISNUMBER($D40))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C40),ISNUMBER($D40),MOD($D40-$C40,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J40&gt;0,OR($P40&gt;=Turno_Min,$Q40&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J40&gt;0,SUMPRODUCT((Mapa_Sala=$B40)*(Mapa_Data=$A40)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q40)*(Mapa_RelFim&gt;$P40))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I40),$I40&gt;0,COUNTIF(Esp_Nome,$E40)&gt;0,$I40&gt;3*INDEX(Esp_Dur,MATCH($E40,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P40" s="12">
@@ -6088,7 +6106,7 @@
         <v/>
       </c>
       <c r="O41" s="24">
-        <f>IF($B41="","",IF(COUNTIF(Postos_Cod,$B41)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B41)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B41,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E41)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H41)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C41)),NOT(ISNUMBER($D41))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C41),ISNUMBER($D41),MOD($D41-$C41,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J41&gt;0,OR($P41&gt;=Turno_Min,$Q41&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J41&gt;0,$K41&gt;0,COUNTIF(Mapa_Chave,$B41&amp;"#"&amp;$A41&amp;"#"&amp;($K41+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B41&amp;"#"&amp;$A41&amp;"#"&amp;($K41+1),Mapa_Chave,0))-$Q41&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J41&gt;0,SUMPRODUCT((Mapa_Sala=$B41)*(Mapa_Data=$A41)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q41)*(Mapa_RelFim&gt;$P41))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I41),$I41&gt;0,COUNTIF(Esp_Nome,$E41)&gt;0,$I41&gt;3*INDEX(Esp_Dur,MATCH($E41,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B41="","",IF(COUNTIF(Postos_Cod,$B41)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B41)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B41,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E41)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H41)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C41)),NOT(ISNUMBER($D41))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C41),ISNUMBER($D41),MOD($D41-$C41,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J41&gt;0,OR($P41&gt;=Turno_Min,$Q41&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J41&gt;0,SUMPRODUCT((Mapa_Sala=$B41)*(Mapa_Data=$A41)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q41)*(Mapa_RelFim&gt;$P41))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I41),$I41&gt;0,COUNTIF(Esp_Nome,$E41)&gt;0,$I41&gt;3*INDEX(Esp_Dur,MATCH($E41,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P41" s="12">
@@ -6146,7 +6164,7 @@
         <v/>
       </c>
       <c r="O42" s="24">
-        <f>IF($B42="","",IF(COUNTIF(Postos_Cod,$B42)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B42)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B42,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E42)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H42)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C42)),NOT(ISNUMBER($D42))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C42),ISNUMBER($D42),MOD($D42-$C42,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J42&gt;0,OR($P42&gt;=Turno_Min,$Q42&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J42&gt;0,$K42&gt;0,COUNTIF(Mapa_Chave,$B42&amp;"#"&amp;$A42&amp;"#"&amp;($K42+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B42&amp;"#"&amp;$A42&amp;"#"&amp;($K42+1),Mapa_Chave,0))-$Q42&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J42&gt;0,SUMPRODUCT((Mapa_Sala=$B42)*(Mapa_Data=$A42)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q42)*(Mapa_RelFim&gt;$P42))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I42),$I42&gt;0,COUNTIF(Esp_Nome,$E42)&gt;0,$I42&gt;3*INDEX(Esp_Dur,MATCH($E42,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B42="","",IF(COUNTIF(Postos_Cod,$B42)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B42)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B42,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E42)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H42)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C42)),NOT(ISNUMBER($D42))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C42),ISNUMBER($D42),MOD($D42-$C42,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J42&gt;0,OR($P42&gt;=Turno_Min,$Q42&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J42&gt;0,SUMPRODUCT((Mapa_Sala=$B42)*(Mapa_Data=$A42)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q42)*(Mapa_RelFim&gt;$P42))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I42),$I42&gt;0,COUNTIF(Esp_Nome,$E42)&gt;0,$I42&gt;3*INDEX(Esp_Dur,MATCH($E42,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P42" s="12">
@@ -6204,7 +6222,7 @@
         <v/>
       </c>
       <c r="O43" s="24">
-        <f>IF($B43="","",IF(COUNTIF(Postos_Cod,$B43)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B43)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B43,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E43)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H43)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C43)),NOT(ISNUMBER($D43))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C43),ISNUMBER($D43),MOD($D43-$C43,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J43&gt;0,OR($P43&gt;=Turno_Min,$Q43&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J43&gt;0,$K43&gt;0,COUNTIF(Mapa_Chave,$B43&amp;"#"&amp;$A43&amp;"#"&amp;($K43+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B43&amp;"#"&amp;$A43&amp;"#"&amp;($K43+1),Mapa_Chave,0))-$Q43&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J43&gt;0,SUMPRODUCT((Mapa_Sala=$B43)*(Mapa_Data=$A43)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q43)*(Mapa_RelFim&gt;$P43))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I43),$I43&gt;0,COUNTIF(Esp_Nome,$E43)&gt;0,$I43&gt;3*INDEX(Esp_Dur,MATCH($E43,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B43="","",IF(COUNTIF(Postos_Cod,$B43)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B43)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B43,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E43)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H43)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C43)),NOT(ISNUMBER($D43))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C43),ISNUMBER($D43),MOD($D43-$C43,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J43&gt;0,OR($P43&gt;=Turno_Min,$Q43&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J43&gt;0,SUMPRODUCT((Mapa_Sala=$B43)*(Mapa_Data=$A43)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q43)*(Mapa_RelFim&gt;$P43))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I43),$I43&gt;0,COUNTIF(Esp_Nome,$E43)&gt;0,$I43&gt;3*INDEX(Esp_Dur,MATCH($E43,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P43" s="12">
@@ -6262,7 +6280,7 @@
         <v/>
       </c>
       <c r="O44" s="24">
-        <f>IF($B44="","",IF(COUNTIF(Postos_Cod,$B44)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B44)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B44,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E44)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H44)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C44)),NOT(ISNUMBER($D44))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C44),ISNUMBER($D44),MOD($D44-$C44,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J44&gt;0,OR($P44&gt;=Turno_Min,$Q44&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J44&gt;0,$K44&gt;0,COUNTIF(Mapa_Chave,$B44&amp;"#"&amp;$A44&amp;"#"&amp;($K44+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B44&amp;"#"&amp;$A44&amp;"#"&amp;($K44+1),Mapa_Chave,0))-$Q44&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J44&gt;0,SUMPRODUCT((Mapa_Sala=$B44)*(Mapa_Data=$A44)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q44)*(Mapa_RelFim&gt;$P44))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I44),$I44&gt;0,COUNTIF(Esp_Nome,$E44)&gt;0,$I44&gt;3*INDEX(Esp_Dur,MATCH($E44,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B44="","",IF(COUNTIF(Postos_Cod,$B44)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B44)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B44,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E44)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H44)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C44)),NOT(ISNUMBER($D44))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C44),ISNUMBER($D44),MOD($D44-$C44,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J44&gt;0,OR($P44&gt;=Turno_Min,$Q44&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J44&gt;0,SUMPRODUCT((Mapa_Sala=$B44)*(Mapa_Data=$A44)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q44)*(Mapa_RelFim&gt;$P44))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I44),$I44&gt;0,COUNTIF(Esp_Nome,$E44)&gt;0,$I44&gt;3*INDEX(Esp_Dur,MATCH($E44,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P44" s="12">
@@ -6320,7 +6338,7 @@
         <v/>
       </c>
       <c r="O45" s="24">
-        <f>IF($B45="","",IF(COUNTIF(Postos_Cod,$B45)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B45)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B45,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E45)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H45)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C45)),NOT(ISNUMBER($D45))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C45),ISNUMBER($D45),MOD($D45-$C45,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J45&gt;0,OR($P45&gt;=Turno_Min,$Q45&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J45&gt;0,$K45&gt;0,COUNTIF(Mapa_Chave,$B45&amp;"#"&amp;$A45&amp;"#"&amp;($K45+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B45&amp;"#"&amp;$A45&amp;"#"&amp;($K45+1),Mapa_Chave,0))-$Q45&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J45&gt;0,SUMPRODUCT((Mapa_Sala=$B45)*(Mapa_Data=$A45)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q45)*(Mapa_RelFim&gt;$P45))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I45),$I45&gt;0,COUNTIF(Esp_Nome,$E45)&gt;0,$I45&gt;3*INDEX(Esp_Dur,MATCH($E45,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B45="","",IF(COUNTIF(Postos_Cod,$B45)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B45)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B45,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E45)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H45)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C45)),NOT(ISNUMBER($D45))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C45),ISNUMBER($D45),MOD($D45-$C45,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J45&gt;0,OR($P45&gt;=Turno_Min,$Q45&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J45&gt;0,SUMPRODUCT((Mapa_Sala=$B45)*(Mapa_Data=$A45)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q45)*(Mapa_RelFim&gt;$P45))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I45),$I45&gt;0,COUNTIF(Esp_Nome,$E45)&gt;0,$I45&gt;3*INDEX(Esp_Dur,MATCH($E45,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P45" s="12">
@@ -6378,7 +6396,7 @@
         <v/>
       </c>
       <c r="O46" s="24">
-        <f>IF($B46="","",IF(COUNTIF(Postos_Cod,$B46)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B46)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B46,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E46)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H46)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C46)),NOT(ISNUMBER($D46))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C46),ISNUMBER($D46),MOD($D46-$C46,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J46&gt;0,OR($P46&gt;=Turno_Min,$Q46&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J46&gt;0,$K46&gt;0,COUNTIF(Mapa_Chave,$B46&amp;"#"&amp;$A46&amp;"#"&amp;($K46+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B46&amp;"#"&amp;$A46&amp;"#"&amp;($K46+1),Mapa_Chave,0))-$Q46&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J46&gt;0,SUMPRODUCT((Mapa_Sala=$B46)*(Mapa_Data=$A46)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q46)*(Mapa_RelFim&gt;$P46))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I46),$I46&gt;0,COUNTIF(Esp_Nome,$E46)&gt;0,$I46&gt;3*INDEX(Esp_Dur,MATCH($E46,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B46="","",IF(COUNTIF(Postos_Cod,$B46)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B46)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B46,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E46)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H46)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C46)),NOT(ISNUMBER($D46))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C46),ISNUMBER($D46),MOD($D46-$C46,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J46&gt;0,OR($P46&gt;=Turno_Min,$Q46&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J46&gt;0,SUMPRODUCT((Mapa_Sala=$B46)*(Mapa_Data=$A46)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q46)*(Mapa_RelFim&gt;$P46))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I46),$I46&gt;0,COUNTIF(Esp_Nome,$E46)&gt;0,$I46&gt;3*INDEX(Esp_Dur,MATCH($E46,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P46" s="12">
@@ -6436,7 +6454,7 @@
         <v/>
       </c>
       <c r="O47" s="24">
-        <f>IF($B47="","",IF(COUNTIF(Postos_Cod,$B47)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B47)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B47,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E47)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H47)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C47)),NOT(ISNUMBER($D47))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C47),ISNUMBER($D47),MOD($D47-$C47,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J47&gt;0,OR($P47&gt;=Turno_Min,$Q47&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J47&gt;0,$K47&gt;0,COUNTIF(Mapa_Chave,$B47&amp;"#"&amp;$A47&amp;"#"&amp;($K47+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B47&amp;"#"&amp;$A47&amp;"#"&amp;($K47+1),Mapa_Chave,0))-$Q47&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J47&gt;0,SUMPRODUCT((Mapa_Sala=$B47)*(Mapa_Data=$A47)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q47)*(Mapa_RelFim&gt;$P47))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I47),$I47&gt;0,COUNTIF(Esp_Nome,$E47)&gt;0,$I47&gt;3*INDEX(Esp_Dur,MATCH($E47,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B47="","",IF(COUNTIF(Postos_Cod,$B47)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B47)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B47,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E47)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H47)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C47)),NOT(ISNUMBER($D47))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C47),ISNUMBER($D47),MOD($D47-$C47,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J47&gt;0,OR($P47&gt;=Turno_Min,$Q47&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J47&gt;0,SUMPRODUCT((Mapa_Sala=$B47)*(Mapa_Data=$A47)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q47)*(Mapa_RelFim&gt;$P47))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I47),$I47&gt;0,COUNTIF(Esp_Nome,$E47)&gt;0,$I47&gt;3*INDEX(Esp_Dur,MATCH($E47,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P47" s="12">
@@ -6494,7 +6512,7 @@
         <v/>
       </c>
       <c r="O48" s="24">
-        <f>IF($B48="","",IF(COUNTIF(Postos_Cod,$B48)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B48)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B48,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E48)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H48)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C48)),NOT(ISNUMBER($D48))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C48),ISNUMBER($D48),MOD($D48-$C48,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J48&gt;0,OR($P48&gt;=Turno_Min,$Q48&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J48&gt;0,$K48&gt;0,COUNTIF(Mapa_Chave,$B48&amp;"#"&amp;$A48&amp;"#"&amp;($K48+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B48&amp;"#"&amp;$A48&amp;"#"&amp;($K48+1),Mapa_Chave,0))-$Q48&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J48&gt;0,SUMPRODUCT((Mapa_Sala=$B48)*(Mapa_Data=$A48)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q48)*(Mapa_RelFim&gt;$P48))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I48),$I48&gt;0,COUNTIF(Esp_Nome,$E48)&gt;0,$I48&gt;3*INDEX(Esp_Dur,MATCH($E48,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B48="","",IF(COUNTIF(Postos_Cod,$B48)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B48)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B48,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E48)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H48)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C48)),NOT(ISNUMBER($D48))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C48),ISNUMBER($D48),MOD($D48-$C48,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J48&gt;0,OR($P48&gt;=Turno_Min,$Q48&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J48&gt;0,SUMPRODUCT((Mapa_Sala=$B48)*(Mapa_Data=$A48)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q48)*(Mapa_RelFim&gt;$P48))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I48),$I48&gt;0,COUNTIF(Esp_Nome,$E48)&gt;0,$I48&gt;3*INDEX(Esp_Dur,MATCH($E48,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P48" s="12">
@@ -6552,7 +6570,7 @@
         <v/>
       </c>
       <c r="O49" s="24">
-        <f>IF($B49="","",IF(COUNTIF(Postos_Cod,$B49)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B49)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B49,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E49)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H49)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C49)),NOT(ISNUMBER($D49))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C49),ISNUMBER($D49),MOD($D49-$C49,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J49&gt;0,OR($P49&gt;=Turno_Min,$Q49&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J49&gt;0,$K49&gt;0,COUNTIF(Mapa_Chave,$B49&amp;"#"&amp;$A49&amp;"#"&amp;($K49+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B49&amp;"#"&amp;$A49&amp;"#"&amp;($K49+1),Mapa_Chave,0))-$Q49&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J49&gt;0,SUMPRODUCT((Mapa_Sala=$B49)*(Mapa_Data=$A49)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q49)*(Mapa_RelFim&gt;$P49))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I49),$I49&gt;0,COUNTIF(Esp_Nome,$E49)&gt;0,$I49&gt;3*INDEX(Esp_Dur,MATCH($E49,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B49="","",IF(COUNTIF(Postos_Cod,$B49)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B49)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B49,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E49)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H49)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C49)),NOT(ISNUMBER($D49))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C49),ISNUMBER($D49),MOD($D49-$C49,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J49&gt;0,OR($P49&gt;=Turno_Min,$Q49&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J49&gt;0,SUMPRODUCT((Mapa_Sala=$B49)*(Mapa_Data=$A49)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q49)*(Mapa_RelFim&gt;$P49))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I49),$I49&gt;0,COUNTIF(Esp_Nome,$E49)&gt;0,$I49&gt;3*INDEX(Esp_Dur,MATCH($E49,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P49" s="12">
@@ -6610,7 +6628,7 @@
         <v/>
       </c>
       <c r="O50" s="24">
-        <f>IF($B50="","",IF(COUNTIF(Postos_Cod,$B50)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B50)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B50,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E50)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H50)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C50)),NOT(ISNUMBER($D50))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C50),ISNUMBER($D50),MOD($D50-$C50,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J50&gt;0,OR($P50&gt;=Turno_Min,$Q50&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J50&gt;0,$K50&gt;0,COUNTIF(Mapa_Chave,$B50&amp;"#"&amp;$A50&amp;"#"&amp;($K50+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B50&amp;"#"&amp;$A50&amp;"#"&amp;($K50+1),Mapa_Chave,0))-$Q50&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J50&gt;0,SUMPRODUCT((Mapa_Sala=$B50)*(Mapa_Data=$A50)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q50)*(Mapa_RelFim&gt;$P50))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I50),$I50&gt;0,COUNTIF(Esp_Nome,$E50)&gt;0,$I50&gt;3*INDEX(Esp_Dur,MATCH($E50,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B50="","",IF(COUNTIF(Postos_Cod,$B50)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B50)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B50,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E50)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H50)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C50)),NOT(ISNUMBER($D50))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C50),ISNUMBER($D50),MOD($D50-$C50,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J50&gt;0,OR($P50&gt;=Turno_Min,$Q50&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J50&gt;0,SUMPRODUCT((Mapa_Sala=$B50)*(Mapa_Data=$A50)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q50)*(Mapa_RelFim&gt;$P50))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I50),$I50&gt;0,COUNTIF(Esp_Nome,$E50)&gt;0,$I50&gt;3*INDEX(Esp_Dur,MATCH($E50,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P50" s="12">
@@ -6668,7 +6686,7 @@
         <v/>
       </c>
       <c r="O51" s="24">
-        <f>IF($B51="","",IF(COUNTIF(Postos_Cod,$B51)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B51)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B51,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E51)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H51)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C51)),NOT(ISNUMBER($D51))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C51),ISNUMBER($D51),MOD($D51-$C51,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J51&gt;0,OR($P51&gt;=Turno_Min,$Q51&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J51&gt;0,$K51&gt;0,COUNTIF(Mapa_Chave,$B51&amp;"#"&amp;$A51&amp;"#"&amp;($K51+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B51&amp;"#"&amp;$A51&amp;"#"&amp;($K51+1),Mapa_Chave,0))-$Q51&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J51&gt;0,SUMPRODUCT((Mapa_Sala=$B51)*(Mapa_Data=$A51)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q51)*(Mapa_RelFim&gt;$P51))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I51),$I51&gt;0,COUNTIF(Esp_Nome,$E51)&gt;0,$I51&gt;3*INDEX(Esp_Dur,MATCH($E51,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B51="","",IF(COUNTIF(Postos_Cod,$B51)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B51)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B51,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E51)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H51)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C51)),NOT(ISNUMBER($D51))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C51),ISNUMBER($D51),MOD($D51-$C51,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J51&gt;0,OR($P51&gt;=Turno_Min,$Q51&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J51&gt;0,SUMPRODUCT((Mapa_Sala=$B51)*(Mapa_Data=$A51)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q51)*(Mapa_RelFim&gt;$P51))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I51),$I51&gt;0,COUNTIF(Esp_Nome,$E51)&gt;0,$I51&gt;3*INDEX(Esp_Dur,MATCH($E51,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P51" s="12">
@@ -6726,7 +6744,7 @@
         <v/>
       </c>
       <c r="O52" s="24">
-        <f>IF($B52="","",IF(COUNTIF(Postos_Cod,$B52)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B52)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B52,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E52)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H52)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C52)),NOT(ISNUMBER($D52))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C52),ISNUMBER($D52),MOD($D52-$C52,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J52&gt;0,OR($P52&gt;=Turno_Min,$Q52&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J52&gt;0,$K52&gt;0,COUNTIF(Mapa_Chave,$B52&amp;"#"&amp;$A52&amp;"#"&amp;($K52+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B52&amp;"#"&amp;$A52&amp;"#"&amp;($K52+1),Mapa_Chave,0))-$Q52&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J52&gt;0,SUMPRODUCT((Mapa_Sala=$B52)*(Mapa_Data=$A52)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q52)*(Mapa_RelFim&gt;$P52))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I52),$I52&gt;0,COUNTIF(Esp_Nome,$E52)&gt;0,$I52&gt;3*INDEX(Esp_Dur,MATCH($E52,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B52="","",IF(COUNTIF(Postos_Cod,$B52)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B52)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B52,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E52)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H52)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C52)),NOT(ISNUMBER($D52))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C52),ISNUMBER($D52),MOD($D52-$C52,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J52&gt;0,OR($P52&gt;=Turno_Min,$Q52&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J52&gt;0,SUMPRODUCT((Mapa_Sala=$B52)*(Mapa_Data=$A52)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q52)*(Mapa_RelFim&gt;$P52))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I52),$I52&gt;0,COUNTIF(Esp_Nome,$E52)&gt;0,$I52&gt;3*INDEX(Esp_Dur,MATCH($E52,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P52" s="12">
@@ -6784,7 +6802,7 @@
         <v/>
       </c>
       <c r="O53" s="24">
-        <f>IF($B53="","",IF(COUNTIF(Postos_Cod,$B53)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B53)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B53,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E53)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H53)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C53)),NOT(ISNUMBER($D53))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C53),ISNUMBER($D53),MOD($D53-$C53,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J53&gt;0,OR($P53&gt;=Turno_Min,$Q53&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J53&gt;0,$K53&gt;0,COUNTIF(Mapa_Chave,$B53&amp;"#"&amp;$A53&amp;"#"&amp;($K53+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B53&amp;"#"&amp;$A53&amp;"#"&amp;($K53+1),Mapa_Chave,0))-$Q53&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J53&gt;0,SUMPRODUCT((Mapa_Sala=$B53)*(Mapa_Data=$A53)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q53)*(Mapa_RelFim&gt;$P53))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I53),$I53&gt;0,COUNTIF(Esp_Nome,$E53)&gt;0,$I53&gt;3*INDEX(Esp_Dur,MATCH($E53,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B53="","",IF(COUNTIF(Postos_Cod,$B53)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B53)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B53,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E53)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H53)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C53)),NOT(ISNUMBER($D53))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C53),ISNUMBER($D53),MOD($D53-$C53,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J53&gt;0,OR($P53&gt;=Turno_Min,$Q53&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J53&gt;0,SUMPRODUCT((Mapa_Sala=$B53)*(Mapa_Data=$A53)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q53)*(Mapa_RelFim&gt;$P53))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I53),$I53&gt;0,COUNTIF(Esp_Nome,$E53)&gt;0,$I53&gt;3*INDEX(Esp_Dur,MATCH($E53,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P53" s="12">
@@ -6842,7 +6860,7 @@
         <v/>
       </c>
       <c r="O54" s="24">
-        <f>IF($B54="","",IF(COUNTIF(Postos_Cod,$B54)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B54)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B54,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E54)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H54)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C54)),NOT(ISNUMBER($D54))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C54),ISNUMBER($D54),MOD($D54-$C54,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J54&gt;0,OR($P54&gt;=Turno_Min,$Q54&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J54&gt;0,$K54&gt;0,COUNTIF(Mapa_Chave,$B54&amp;"#"&amp;$A54&amp;"#"&amp;($K54+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B54&amp;"#"&amp;$A54&amp;"#"&amp;($K54+1),Mapa_Chave,0))-$Q54&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J54&gt;0,SUMPRODUCT((Mapa_Sala=$B54)*(Mapa_Data=$A54)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q54)*(Mapa_RelFim&gt;$P54))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I54),$I54&gt;0,COUNTIF(Esp_Nome,$E54)&gt;0,$I54&gt;3*INDEX(Esp_Dur,MATCH($E54,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B54="","",IF(COUNTIF(Postos_Cod,$B54)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B54)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B54,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E54)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H54)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C54)),NOT(ISNUMBER($D54))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C54),ISNUMBER($D54),MOD($D54-$C54,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J54&gt;0,OR($P54&gt;=Turno_Min,$Q54&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J54&gt;0,SUMPRODUCT((Mapa_Sala=$B54)*(Mapa_Data=$A54)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q54)*(Mapa_RelFim&gt;$P54))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I54),$I54&gt;0,COUNTIF(Esp_Nome,$E54)&gt;0,$I54&gt;3*INDEX(Esp_Dur,MATCH($E54,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P54" s="12">
@@ -6900,7 +6918,7 @@
         <v/>
       </c>
       <c r="O55" s="24">
-        <f>IF($B55="","",IF(COUNTIF(Postos_Cod,$B55)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B55)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B55,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E55)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H55)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C55)),NOT(ISNUMBER($D55))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C55),ISNUMBER($D55),MOD($D55-$C55,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J55&gt;0,OR($P55&gt;=Turno_Min,$Q55&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J55&gt;0,$K55&gt;0,COUNTIF(Mapa_Chave,$B55&amp;"#"&amp;$A55&amp;"#"&amp;($K55+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B55&amp;"#"&amp;$A55&amp;"#"&amp;($K55+1),Mapa_Chave,0))-$Q55&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J55&gt;0,SUMPRODUCT((Mapa_Sala=$B55)*(Mapa_Data=$A55)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q55)*(Mapa_RelFim&gt;$P55))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I55),$I55&gt;0,COUNTIF(Esp_Nome,$E55)&gt;0,$I55&gt;3*INDEX(Esp_Dur,MATCH($E55,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B55="","",IF(COUNTIF(Postos_Cod,$B55)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B55)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B55,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E55)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H55)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C55)),NOT(ISNUMBER($D55))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C55),ISNUMBER($D55),MOD($D55-$C55,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J55&gt;0,OR($P55&gt;=Turno_Min,$Q55&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J55&gt;0,SUMPRODUCT((Mapa_Sala=$B55)*(Mapa_Data=$A55)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q55)*(Mapa_RelFim&gt;$P55))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I55),$I55&gt;0,COUNTIF(Esp_Nome,$E55)&gt;0,$I55&gt;3*INDEX(Esp_Dur,MATCH($E55,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P55" s="12">
@@ -6958,7 +6976,7 @@
         <v/>
       </c>
       <c r="O56" s="24">
-        <f>IF($B56="","",IF(COUNTIF(Postos_Cod,$B56)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B56)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B56,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E56)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H56)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C56)),NOT(ISNUMBER($D56))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C56),ISNUMBER($D56),MOD($D56-$C56,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J56&gt;0,OR($P56&gt;=Turno_Min,$Q56&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J56&gt;0,$K56&gt;0,COUNTIF(Mapa_Chave,$B56&amp;"#"&amp;$A56&amp;"#"&amp;($K56+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B56&amp;"#"&amp;$A56&amp;"#"&amp;($K56+1),Mapa_Chave,0))-$Q56&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J56&gt;0,SUMPRODUCT((Mapa_Sala=$B56)*(Mapa_Data=$A56)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q56)*(Mapa_RelFim&gt;$P56))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I56),$I56&gt;0,COUNTIF(Esp_Nome,$E56)&gt;0,$I56&gt;3*INDEX(Esp_Dur,MATCH($E56,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B56="","",IF(COUNTIF(Postos_Cod,$B56)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B56)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B56,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E56)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H56)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C56)),NOT(ISNUMBER($D56))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C56),ISNUMBER($D56),MOD($D56-$C56,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J56&gt;0,OR($P56&gt;=Turno_Min,$Q56&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J56&gt;0,SUMPRODUCT((Mapa_Sala=$B56)*(Mapa_Data=$A56)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q56)*(Mapa_RelFim&gt;$P56))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I56),$I56&gt;0,COUNTIF(Esp_Nome,$E56)&gt;0,$I56&gt;3*INDEX(Esp_Dur,MATCH($E56,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P56" s="12">
@@ -7016,7 +7034,7 @@
         <v/>
       </c>
       <c r="O57" s="24">
-        <f>IF($B57="","",IF(COUNTIF(Postos_Cod,$B57)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B57)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B57,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E57)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H57)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C57)),NOT(ISNUMBER($D57))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C57),ISNUMBER($D57),MOD($D57-$C57,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J57&gt;0,OR($P57&gt;=Turno_Min,$Q57&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J57&gt;0,$K57&gt;0,COUNTIF(Mapa_Chave,$B57&amp;"#"&amp;$A57&amp;"#"&amp;($K57+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B57&amp;"#"&amp;$A57&amp;"#"&amp;($K57+1),Mapa_Chave,0))-$Q57&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J57&gt;0,SUMPRODUCT((Mapa_Sala=$B57)*(Mapa_Data=$A57)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q57)*(Mapa_RelFim&gt;$P57))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I57),$I57&gt;0,COUNTIF(Esp_Nome,$E57)&gt;0,$I57&gt;3*INDEX(Esp_Dur,MATCH($E57,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B57="","",IF(COUNTIF(Postos_Cod,$B57)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B57)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B57,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E57)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H57)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C57)),NOT(ISNUMBER($D57))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C57),ISNUMBER($D57),MOD($D57-$C57,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J57&gt;0,OR($P57&gt;=Turno_Min,$Q57&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J57&gt;0,SUMPRODUCT((Mapa_Sala=$B57)*(Mapa_Data=$A57)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q57)*(Mapa_RelFim&gt;$P57))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I57),$I57&gt;0,COUNTIF(Esp_Nome,$E57)&gt;0,$I57&gt;3*INDEX(Esp_Dur,MATCH($E57,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P57" s="12">
@@ -7074,7 +7092,7 @@
         <v/>
       </c>
       <c r="O58" s="24">
-        <f>IF($B58="","",IF(COUNTIF(Postos_Cod,$B58)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B58)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B58,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E58)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H58)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C58)),NOT(ISNUMBER($D58))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C58),ISNUMBER($D58),MOD($D58-$C58,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J58&gt;0,OR($P58&gt;=Turno_Min,$Q58&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J58&gt;0,$K58&gt;0,COUNTIF(Mapa_Chave,$B58&amp;"#"&amp;$A58&amp;"#"&amp;($K58+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B58&amp;"#"&amp;$A58&amp;"#"&amp;($K58+1),Mapa_Chave,0))-$Q58&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J58&gt;0,SUMPRODUCT((Mapa_Sala=$B58)*(Mapa_Data=$A58)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q58)*(Mapa_RelFim&gt;$P58))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I58),$I58&gt;0,COUNTIF(Esp_Nome,$E58)&gt;0,$I58&gt;3*INDEX(Esp_Dur,MATCH($E58,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B58="","",IF(COUNTIF(Postos_Cod,$B58)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B58)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B58,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E58)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H58)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C58)),NOT(ISNUMBER($D58))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C58),ISNUMBER($D58),MOD($D58-$C58,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J58&gt;0,OR($P58&gt;=Turno_Min,$Q58&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J58&gt;0,SUMPRODUCT((Mapa_Sala=$B58)*(Mapa_Data=$A58)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q58)*(Mapa_RelFim&gt;$P58))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I58),$I58&gt;0,COUNTIF(Esp_Nome,$E58)&gt;0,$I58&gt;3*INDEX(Esp_Dur,MATCH($E58,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P58" s="12">
@@ -7132,7 +7150,7 @@
         <v/>
       </c>
       <c r="O59" s="24">
-        <f>IF($B59="","",IF(COUNTIF(Postos_Cod,$B59)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B59)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B59,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E59)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H59)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C59)),NOT(ISNUMBER($D59))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C59),ISNUMBER($D59),MOD($D59-$C59,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J59&gt;0,OR($P59&gt;=Turno_Min,$Q59&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J59&gt;0,$K59&gt;0,COUNTIF(Mapa_Chave,$B59&amp;"#"&amp;$A59&amp;"#"&amp;($K59+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B59&amp;"#"&amp;$A59&amp;"#"&amp;($K59+1),Mapa_Chave,0))-$Q59&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J59&gt;0,SUMPRODUCT((Mapa_Sala=$B59)*(Mapa_Data=$A59)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q59)*(Mapa_RelFim&gt;$P59))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I59),$I59&gt;0,COUNTIF(Esp_Nome,$E59)&gt;0,$I59&gt;3*INDEX(Esp_Dur,MATCH($E59,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B59="","",IF(COUNTIF(Postos_Cod,$B59)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B59)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B59,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E59)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H59)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C59)),NOT(ISNUMBER($D59))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C59),ISNUMBER($D59),MOD($D59-$C59,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J59&gt;0,OR($P59&gt;=Turno_Min,$Q59&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J59&gt;0,SUMPRODUCT((Mapa_Sala=$B59)*(Mapa_Data=$A59)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q59)*(Mapa_RelFim&gt;$P59))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I59),$I59&gt;0,COUNTIF(Esp_Nome,$E59)&gt;0,$I59&gt;3*INDEX(Esp_Dur,MATCH($E59,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P59" s="12">
@@ -7190,7 +7208,7 @@
         <v/>
       </c>
       <c r="O60" s="24">
-        <f>IF($B60="","",IF(COUNTIF(Postos_Cod,$B60)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B60)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B60,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E60)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H60)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C60)),NOT(ISNUMBER($D60))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C60),ISNUMBER($D60),MOD($D60-$C60,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J60&gt;0,OR($P60&gt;=Turno_Min,$Q60&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J60&gt;0,$K60&gt;0,COUNTIF(Mapa_Chave,$B60&amp;"#"&amp;$A60&amp;"#"&amp;($K60+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B60&amp;"#"&amp;$A60&amp;"#"&amp;($K60+1),Mapa_Chave,0))-$Q60&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J60&gt;0,SUMPRODUCT((Mapa_Sala=$B60)*(Mapa_Data=$A60)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q60)*(Mapa_RelFim&gt;$P60))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I60),$I60&gt;0,COUNTIF(Esp_Nome,$E60)&gt;0,$I60&gt;3*INDEX(Esp_Dur,MATCH($E60,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B60="","",IF(COUNTIF(Postos_Cod,$B60)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B60)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B60,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E60)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H60)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C60)),NOT(ISNUMBER($D60))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C60),ISNUMBER($D60),MOD($D60-$C60,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J60&gt;0,OR($P60&gt;=Turno_Min,$Q60&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J60&gt;0,SUMPRODUCT((Mapa_Sala=$B60)*(Mapa_Data=$A60)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q60)*(Mapa_RelFim&gt;$P60))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I60),$I60&gt;0,COUNTIF(Esp_Nome,$E60)&gt;0,$I60&gt;3*INDEX(Esp_Dur,MATCH($E60,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P60" s="12">
@@ -7248,7 +7266,7 @@
         <v/>
       </c>
       <c r="O61" s="24">
-        <f>IF($B61="","",IF(COUNTIF(Postos_Cod,$B61)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B61)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B61,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E61)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H61)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C61)),NOT(ISNUMBER($D61))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C61),ISNUMBER($D61),MOD($D61-$C61,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J61&gt;0,OR($P61&gt;=Turno_Min,$Q61&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J61&gt;0,$K61&gt;0,COUNTIF(Mapa_Chave,$B61&amp;"#"&amp;$A61&amp;"#"&amp;($K61+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B61&amp;"#"&amp;$A61&amp;"#"&amp;($K61+1),Mapa_Chave,0))-$Q61&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J61&gt;0,SUMPRODUCT((Mapa_Sala=$B61)*(Mapa_Data=$A61)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q61)*(Mapa_RelFim&gt;$P61))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I61),$I61&gt;0,COUNTIF(Esp_Nome,$E61)&gt;0,$I61&gt;3*INDEX(Esp_Dur,MATCH($E61,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B61="","",IF(COUNTIF(Postos_Cod,$B61)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B61)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B61,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E61)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H61)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C61)),NOT(ISNUMBER($D61))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C61),ISNUMBER($D61),MOD($D61-$C61,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J61&gt;0,OR($P61&gt;=Turno_Min,$Q61&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J61&gt;0,SUMPRODUCT((Mapa_Sala=$B61)*(Mapa_Data=$A61)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q61)*(Mapa_RelFim&gt;$P61))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I61),$I61&gt;0,COUNTIF(Esp_Nome,$E61)&gt;0,$I61&gt;3*INDEX(Esp_Dur,MATCH($E61,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P61" s="12">
@@ -7306,7 +7324,7 @@
         <v/>
       </c>
       <c r="O62" s="24">
-        <f>IF($B62="","",IF(COUNTIF(Postos_Cod,$B62)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B62)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B62,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E62)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H62)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C62)),NOT(ISNUMBER($D62))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C62),ISNUMBER($D62),MOD($D62-$C62,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J62&gt;0,OR($P62&gt;=Turno_Min,$Q62&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J62&gt;0,$K62&gt;0,COUNTIF(Mapa_Chave,$B62&amp;"#"&amp;$A62&amp;"#"&amp;($K62+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B62&amp;"#"&amp;$A62&amp;"#"&amp;($K62+1),Mapa_Chave,0))-$Q62&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J62&gt;0,SUMPRODUCT((Mapa_Sala=$B62)*(Mapa_Data=$A62)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q62)*(Mapa_RelFim&gt;$P62))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I62),$I62&gt;0,COUNTIF(Esp_Nome,$E62)&gt;0,$I62&gt;3*INDEX(Esp_Dur,MATCH($E62,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B62="","",IF(COUNTIF(Postos_Cod,$B62)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B62)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B62,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E62)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H62)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C62)),NOT(ISNUMBER($D62))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C62),ISNUMBER($D62),MOD($D62-$C62,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J62&gt;0,OR($P62&gt;=Turno_Min,$Q62&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J62&gt;0,SUMPRODUCT((Mapa_Sala=$B62)*(Mapa_Data=$A62)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q62)*(Mapa_RelFim&gt;$P62))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I62),$I62&gt;0,COUNTIF(Esp_Nome,$E62)&gt;0,$I62&gt;3*INDEX(Esp_Dur,MATCH($E62,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P62" s="12">
@@ -7364,7 +7382,7 @@
         <v/>
       </c>
       <c r="O63" s="24">
-        <f>IF($B63="","",IF(COUNTIF(Postos_Cod,$B63)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B63)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B63,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E63)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H63)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C63)),NOT(ISNUMBER($D63))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C63),ISNUMBER($D63),MOD($D63-$C63,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J63&gt;0,OR($P63&gt;=Turno_Min,$Q63&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J63&gt;0,$K63&gt;0,COUNTIF(Mapa_Chave,$B63&amp;"#"&amp;$A63&amp;"#"&amp;($K63+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B63&amp;"#"&amp;$A63&amp;"#"&amp;($K63+1),Mapa_Chave,0))-$Q63&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J63&gt;0,SUMPRODUCT((Mapa_Sala=$B63)*(Mapa_Data=$A63)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q63)*(Mapa_RelFim&gt;$P63))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I63),$I63&gt;0,COUNTIF(Esp_Nome,$E63)&gt;0,$I63&gt;3*INDEX(Esp_Dur,MATCH($E63,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B63="","",IF(COUNTIF(Postos_Cod,$B63)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B63)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B63,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E63)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H63)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C63)),NOT(ISNUMBER($D63))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C63),ISNUMBER($D63),MOD($D63-$C63,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J63&gt;0,OR($P63&gt;=Turno_Min,$Q63&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J63&gt;0,SUMPRODUCT((Mapa_Sala=$B63)*(Mapa_Data=$A63)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q63)*(Mapa_RelFim&gt;$P63))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I63),$I63&gt;0,COUNTIF(Esp_Nome,$E63)&gt;0,$I63&gt;3*INDEX(Esp_Dur,MATCH($E63,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P63" s="12">
@@ -7422,7 +7440,7 @@
         <v/>
       </c>
       <c r="O64" s="24">
-        <f>IF($B64="","",IF(COUNTIF(Postos_Cod,$B64)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B64)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B64,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E64)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H64)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C64)),NOT(ISNUMBER($D64))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C64),ISNUMBER($D64),MOD($D64-$C64,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J64&gt;0,OR($P64&gt;=Turno_Min,$Q64&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J64&gt;0,$K64&gt;0,COUNTIF(Mapa_Chave,$B64&amp;"#"&amp;$A64&amp;"#"&amp;($K64+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B64&amp;"#"&amp;$A64&amp;"#"&amp;($K64+1),Mapa_Chave,0))-$Q64&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J64&gt;0,SUMPRODUCT((Mapa_Sala=$B64)*(Mapa_Data=$A64)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q64)*(Mapa_RelFim&gt;$P64))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I64),$I64&gt;0,COUNTIF(Esp_Nome,$E64)&gt;0,$I64&gt;3*INDEX(Esp_Dur,MATCH($E64,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B64="","",IF(COUNTIF(Postos_Cod,$B64)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B64)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B64,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E64)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H64)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C64)),NOT(ISNUMBER($D64))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C64),ISNUMBER($D64),MOD($D64-$C64,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J64&gt;0,OR($P64&gt;=Turno_Min,$Q64&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J64&gt;0,SUMPRODUCT((Mapa_Sala=$B64)*(Mapa_Data=$A64)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q64)*(Mapa_RelFim&gt;$P64))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I64),$I64&gt;0,COUNTIF(Esp_Nome,$E64)&gt;0,$I64&gt;3*INDEX(Esp_Dur,MATCH($E64,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P64" s="12">
@@ -7480,7 +7498,7 @@
         <v/>
       </c>
       <c r="O65" s="24">
-        <f>IF($B65="","",IF(COUNTIF(Postos_Cod,$B65)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B65)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B65,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E65)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H65)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C65)),NOT(ISNUMBER($D65))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C65),ISNUMBER($D65),MOD($D65-$C65,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J65&gt;0,OR($P65&gt;=Turno_Min,$Q65&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J65&gt;0,$K65&gt;0,COUNTIF(Mapa_Chave,$B65&amp;"#"&amp;$A65&amp;"#"&amp;($K65+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B65&amp;"#"&amp;$A65&amp;"#"&amp;($K65+1),Mapa_Chave,0))-$Q65&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J65&gt;0,SUMPRODUCT((Mapa_Sala=$B65)*(Mapa_Data=$A65)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q65)*(Mapa_RelFim&gt;$P65))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I65),$I65&gt;0,COUNTIF(Esp_Nome,$E65)&gt;0,$I65&gt;3*INDEX(Esp_Dur,MATCH($E65,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B65="","",IF(COUNTIF(Postos_Cod,$B65)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B65)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B65,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E65)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H65)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C65)),NOT(ISNUMBER($D65))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C65),ISNUMBER($D65),MOD($D65-$C65,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J65&gt;0,OR($P65&gt;=Turno_Min,$Q65&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J65&gt;0,SUMPRODUCT((Mapa_Sala=$B65)*(Mapa_Data=$A65)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q65)*(Mapa_RelFim&gt;$P65))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I65),$I65&gt;0,COUNTIF(Esp_Nome,$E65)&gt;0,$I65&gt;3*INDEX(Esp_Dur,MATCH($E65,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P65" s="12">
@@ -7538,7 +7556,7 @@
         <v/>
       </c>
       <c r="O66" s="24">
-        <f>IF($B66="","",IF(COUNTIF(Postos_Cod,$B66)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B66)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B66,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E66)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H66)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C66)),NOT(ISNUMBER($D66))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C66),ISNUMBER($D66),MOD($D66-$C66,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J66&gt;0,OR($P66&gt;=Turno_Min,$Q66&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J66&gt;0,$K66&gt;0,COUNTIF(Mapa_Chave,$B66&amp;"#"&amp;$A66&amp;"#"&amp;($K66+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B66&amp;"#"&amp;$A66&amp;"#"&amp;($K66+1),Mapa_Chave,0))-$Q66&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J66&gt;0,SUMPRODUCT((Mapa_Sala=$B66)*(Mapa_Data=$A66)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q66)*(Mapa_RelFim&gt;$P66))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I66),$I66&gt;0,COUNTIF(Esp_Nome,$E66)&gt;0,$I66&gt;3*INDEX(Esp_Dur,MATCH($E66,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B66="","",IF(COUNTIF(Postos_Cod,$B66)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B66)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B66,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E66)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H66)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C66)),NOT(ISNUMBER($D66))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C66),ISNUMBER($D66),MOD($D66-$C66,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J66&gt;0,OR($P66&gt;=Turno_Min,$Q66&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J66&gt;0,SUMPRODUCT((Mapa_Sala=$B66)*(Mapa_Data=$A66)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q66)*(Mapa_RelFim&gt;$P66))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I66),$I66&gt;0,COUNTIF(Esp_Nome,$E66)&gt;0,$I66&gt;3*INDEX(Esp_Dur,MATCH($E66,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P66" s="12">
@@ -7596,7 +7614,7 @@
         <v/>
       </c>
       <c r="O67" s="24">
-        <f>IF($B67="","",IF(COUNTIF(Postos_Cod,$B67)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B67)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B67,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E67)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H67)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C67)),NOT(ISNUMBER($D67))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C67),ISNUMBER($D67),MOD($D67-$C67,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J67&gt;0,OR($P67&gt;=Turno_Min,$Q67&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J67&gt;0,$K67&gt;0,COUNTIF(Mapa_Chave,$B67&amp;"#"&amp;$A67&amp;"#"&amp;($K67+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B67&amp;"#"&amp;$A67&amp;"#"&amp;($K67+1),Mapa_Chave,0))-$Q67&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J67&gt;0,SUMPRODUCT((Mapa_Sala=$B67)*(Mapa_Data=$A67)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q67)*(Mapa_RelFim&gt;$P67))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I67),$I67&gt;0,COUNTIF(Esp_Nome,$E67)&gt;0,$I67&gt;3*INDEX(Esp_Dur,MATCH($E67,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B67="","",IF(COUNTIF(Postos_Cod,$B67)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B67)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B67,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E67)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H67)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C67)),NOT(ISNUMBER($D67))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C67),ISNUMBER($D67),MOD($D67-$C67,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J67&gt;0,OR($P67&gt;=Turno_Min,$Q67&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J67&gt;0,SUMPRODUCT((Mapa_Sala=$B67)*(Mapa_Data=$A67)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q67)*(Mapa_RelFim&gt;$P67))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I67),$I67&gt;0,COUNTIF(Esp_Nome,$E67)&gt;0,$I67&gt;3*INDEX(Esp_Dur,MATCH($E67,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P67" s="12">
@@ -7654,7 +7672,7 @@
         <v/>
       </c>
       <c r="O68" s="24">
-        <f>IF($B68="","",IF(COUNTIF(Postos_Cod,$B68)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B68)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B68,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E68)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H68)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C68)),NOT(ISNUMBER($D68))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C68),ISNUMBER($D68),MOD($D68-$C68,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J68&gt;0,OR($P68&gt;=Turno_Min,$Q68&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J68&gt;0,$K68&gt;0,COUNTIF(Mapa_Chave,$B68&amp;"#"&amp;$A68&amp;"#"&amp;($K68+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B68&amp;"#"&amp;$A68&amp;"#"&amp;($K68+1),Mapa_Chave,0))-$Q68&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J68&gt;0,SUMPRODUCT((Mapa_Sala=$B68)*(Mapa_Data=$A68)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q68)*(Mapa_RelFim&gt;$P68))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I68),$I68&gt;0,COUNTIF(Esp_Nome,$E68)&gt;0,$I68&gt;3*INDEX(Esp_Dur,MATCH($E68,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B68="","",IF(COUNTIF(Postos_Cod,$B68)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B68)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B68,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E68)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H68)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C68)),NOT(ISNUMBER($D68))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C68),ISNUMBER($D68),MOD($D68-$C68,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J68&gt;0,OR($P68&gt;=Turno_Min,$Q68&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J68&gt;0,SUMPRODUCT((Mapa_Sala=$B68)*(Mapa_Data=$A68)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q68)*(Mapa_RelFim&gt;$P68))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I68),$I68&gt;0,COUNTIF(Esp_Nome,$E68)&gt;0,$I68&gt;3*INDEX(Esp_Dur,MATCH($E68,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P68" s="12">
@@ -7712,7 +7730,7 @@
         <v/>
       </c>
       <c r="O69" s="24">
-        <f>IF($B69="","",IF(COUNTIF(Postos_Cod,$B69)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B69)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B69,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E69)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H69)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C69)),NOT(ISNUMBER($D69))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C69),ISNUMBER($D69),MOD($D69-$C69,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J69&gt;0,OR($P69&gt;=Turno_Min,$Q69&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J69&gt;0,$K69&gt;0,COUNTIF(Mapa_Chave,$B69&amp;"#"&amp;$A69&amp;"#"&amp;($K69+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B69&amp;"#"&amp;$A69&amp;"#"&amp;($K69+1),Mapa_Chave,0))-$Q69&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J69&gt;0,SUMPRODUCT((Mapa_Sala=$B69)*(Mapa_Data=$A69)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q69)*(Mapa_RelFim&gt;$P69))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I69),$I69&gt;0,COUNTIF(Esp_Nome,$E69)&gt;0,$I69&gt;3*INDEX(Esp_Dur,MATCH($E69,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B69="","",IF(COUNTIF(Postos_Cod,$B69)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B69)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B69,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E69)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H69)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C69)),NOT(ISNUMBER($D69))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C69),ISNUMBER($D69),MOD($D69-$C69,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J69&gt;0,OR($P69&gt;=Turno_Min,$Q69&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J69&gt;0,SUMPRODUCT((Mapa_Sala=$B69)*(Mapa_Data=$A69)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q69)*(Mapa_RelFim&gt;$P69))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I69),$I69&gt;0,COUNTIF(Esp_Nome,$E69)&gt;0,$I69&gt;3*INDEX(Esp_Dur,MATCH($E69,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P69" s="12">
@@ -7770,7 +7788,7 @@
         <v/>
       </c>
       <c r="O70" s="24">
-        <f>IF($B70="","",IF(COUNTIF(Postos_Cod,$B70)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B70)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B70,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E70)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H70)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C70)),NOT(ISNUMBER($D70))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C70),ISNUMBER($D70),MOD($D70-$C70,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J70&gt;0,OR($P70&gt;=Turno_Min,$Q70&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J70&gt;0,$K70&gt;0,COUNTIF(Mapa_Chave,$B70&amp;"#"&amp;$A70&amp;"#"&amp;($K70+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B70&amp;"#"&amp;$A70&amp;"#"&amp;($K70+1),Mapa_Chave,0))-$Q70&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J70&gt;0,SUMPRODUCT((Mapa_Sala=$B70)*(Mapa_Data=$A70)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q70)*(Mapa_RelFim&gt;$P70))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I70),$I70&gt;0,COUNTIF(Esp_Nome,$E70)&gt;0,$I70&gt;3*INDEX(Esp_Dur,MATCH($E70,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B70="","",IF(COUNTIF(Postos_Cod,$B70)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B70)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B70,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E70)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H70)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C70)),NOT(ISNUMBER($D70))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C70),ISNUMBER($D70),MOD($D70-$C70,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J70&gt;0,OR($P70&gt;=Turno_Min,$Q70&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J70&gt;0,SUMPRODUCT((Mapa_Sala=$B70)*(Mapa_Data=$A70)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q70)*(Mapa_RelFim&gt;$P70))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I70),$I70&gt;0,COUNTIF(Esp_Nome,$E70)&gt;0,$I70&gt;3*INDEX(Esp_Dur,MATCH($E70,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P70" s="12">
@@ -7828,7 +7846,7 @@
         <v/>
       </c>
       <c r="O71" s="24">
-        <f>IF($B71="","",IF(COUNTIF(Postos_Cod,$B71)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B71)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B71,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E71)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H71)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C71)),NOT(ISNUMBER($D71))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C71),ISNUMBER($D71),MOD($D71-$C71,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J71&gt;0,OR($P71&gt;=Turno_Min,$Q71&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J71&gt;0,$K71&gt;0,COUNTIF(Mapa_Chave,$B71&amp;"#"&amp;$A71&amp;"#"&amp;($K71+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B71&amp;"#"&amp;$A71&amp;"#"&amp;($K71+1),Mapa_Chave,0))-$Q71&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J71&gt;0,SUMPRODUCT((Mapa_Sala=$B71)*(Mapa_Data=$A71)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q71)*(Mapa_RelFim&gt;$P71))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I71),$I71&gt;0,COUNTIF(Esp_Nome,$E71)&gt;0,$I71&gt;3*INDEX(Esp_Dur,MATCH($E71,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B71="","",IF(COUNTIF(Postos_Cod,$B71)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B71)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B71,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E71)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H71)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C71)),NOT(ISNUMBER($D71))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C71),ISNUMBER($D71),MOD($D71-$C71,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J71&gt;0,OR($P71&gt;=Turno_Min,$Q71&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J71&gt;0,SUMPRODUCT((Mapa_Sala=$B71)*(Mapa_Data=$A71)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q71)*(Mapa_RelFim&gt;$P71))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I71),$I71&gt;0,COUNTIF(Esp_Nome,$E71)&gt;0,$I71&gt;3*INDEX(Esp_Dur,MATCH($E71,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P71" s="12">
@@ -7886,7 +7904,7 @@
         <v/>
       </c>
       <c r="O72" s="24">
-        <f>IF($B72="","",IF(COUNTIF(Postos_Cod,$B72)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B72)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B72,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E72)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H72)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C72)),NOT(ISNUMBER($D72))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C72),ISNUMBER($D72),MOD($D72-$C72,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J72&gt;0,OR($P72&gt;=Turno_Min,$Q72&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J72&gt;0,$K72&gt;0,COUNTIF(Mapa_Chave,$B72&amp;"#"&amp;$A72&amp;"#"&amp;($K72+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B72&amp;"#"&amp;$A72&amp;"#"&amp;($K72+1),Mapa_Chave,0))-$Q72&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J72&gt;0,SUMPRODUCT((Mapa_Sala=$B72)*(Mapa_Data=$A72)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q72)*(Mapa_RelFim&gt;$P72))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I72),$I72&gt;0,COUNTIF(Esp_Nome,$E72)&gt;0,$I72&gt;3*INDEX(Esp_Dur,MATCH($E72,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B72="","",IF(COUNTIF(Postos_Cod,$B72)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B72)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B72,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E72)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H72)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C72)),NOT(ISNUMBER($D72))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C72),ISNUMBER($D72),MOD($D72-$C72,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J72&gt;0,OR($P72&gt;=Turno_Min,$Q72&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J72&gt;0,SUMPRODUCT((Mapa_Sala=$B72)*(Mapa_Data=$A72)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q72)*(Mapa_RelFim&gt;$P72))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I72),$I72&gt;0,COUNTIF(Esp_Nome,$E72)&gt;0,$I72&gt;3*INDEX(Esp_Dur,MATCH($E72,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P72" s="12">
@@ -7944,7 +7962,7 @@
         <v/>
       </c>
       <c r="O73" s="24">
-        <f>IF($B73="","",IF(COUNTIF(Postos_Cod,$B73)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B73)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B73,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E73)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H73)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C73)),NOT(ISNUMBER($D73))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C73),ISNUMBER($D73),MOD($D73-$C73,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J73&gt;0,OR($P73&gt;=Turno_Min,$Q73&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J73&gt;0,$K73&gt;0,COUNTIF(Mapa_Chave,$B73&amp;"#"&amp;$A73&amp;"#"&amp;($K73+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B73&amp;"#"&amp;$A73&amp;"#"&amp;($K73+1),Mapa_Chave,0))-$Q73&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J73&gt;0,SUMPRODUCT((Mapa_Sala=$B73)*(Mapa_Data=$A73)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q73)*(Mapa_RelFim&gt;$P73))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I73),$I73&gt;0,COUNTIF(Esp_Nome,$E73)&gt;0,$I73&gt;3*INDEX(Esp_Dur,MATCH($E73,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B73="","",IF(COUNTIF(Postos_Cod,$B73)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B73)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B73,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E73)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H73)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C73)),NOT(ISNUMBER($D73))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C73),ISNUMBER($D73),MOD($D73-$C73,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J73&gt;0,OR($P73&gt;=Turno_Min,$Q73&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J73&gt;0,SUMPRODUCT((Mapa_Sala=$B73)*(Mapa_Data=$A73)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q73)*(Mapa_RelFim&gt;$P73))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I73),$I73&gt;0,COUNTIF(Esp_Nome,$E73)&gt;0,$I73&gt;3*INDEX(Esp_Dur,MATCH($E73,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P73" s="12">
@@ -8002,7 +8020,7 @@
         <v/>
       </c>
       <c r="O74" s="24">
-        <f>IF($B74="","",IF(COUNTIF(Postos_Cod,$B74)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B74)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B74,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E74)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H74)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C74)),NOT(ISNUMBER($D74))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C74),ISNUMBER($D74),MOD($D74-$C74,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J74&gt;0,OR($P74&gt;=Turno_Min,$Q74&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J74&gt;0,$K74&gt;0,COUNTIF(Mapa_Chave,$B74&amp;"#"&amp;$A74&amp;"#"&amp;($K74+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B74&amp;"#"&amp;$A74&amp;"#"&amp;($K74+1),Mapa_Chave,0))-$Q74&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J74&gt;0,SUMPRODUCT((Mapa_Sala=$B74)*(Mapa_Data=$A74)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q74)*(Mapa_RelFim&gt;$P74))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I74),$I74&gt;0,COUNTIF(Esp_Nome,$E74)&gt;0,$I74&gt;3*INDEX(Esp_Dur,MATCH($E74,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B74="","",IF(COUNTIF(Postos_Cod,$B74)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B74)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B74,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E74)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H74)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C74)),NOT(ISNUMBER($D74))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C74),ISNUMBER($D74),MOD($D74-$C74,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J74&gt;0,OR($P74&gt;=Turno_Min,$Q74&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J74&gt;0,SUMPRODUCT((Mapa_Sala=$B74)*(Mapa_Data=$A74)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q74)*(Mapa_RelFim&gt;$P74))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I74),$I74&gt;0,COUNTIF(Esp_Nome,$E74)&gt;0,$I74&gt;3*INDEX(Esp_Dur,MATCH($E74,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P74" s="12">
@@ -8060,7 +8078,7 @@
         <v/>
       </c>
       <c r="O75" s="24">
-        <f>IF($B75="","",IF(COUNTIF(Postos_Cod,$B75)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B75)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B75,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E75)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H75)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C75)),NOT(ISNUMBER($D75))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C75),ISNUMBER($D75),MOD($D75-$C75,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J75&gt;0,OR($P75&gt;=Turno_Min,$Q75&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J75&gt;0,$K75&gt;0,COUNTIF(Mapa_Chave,$B75&amp;"#"&amp;$A75&amp;"#"&amp;($K75+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B75&amp;"#"&amp;$A75&amp;"#"&amp;($K75+1),Mapa_Chave,0))-$Q75&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J75&gt;0,SUMPRODUCT((Mapa_Sala=$B75)*(Mapa_Data=$A75)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q75)*(Mapa_RelFim&gt;$P75))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I75),$I75&gt;0,COUNTIF(Esp_Nome,$E75)&gt;0,$I75&gt;3*INDEX(Esp_Dur,MATCH($E75,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B75="","",IF(COUNTIF(Postos_Cod,$B75)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B75)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B75,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E75)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H75)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C75)),NOT(ISNUMBER($D75))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C75),ISNUMBER($D75),MOD($D75-$C75,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J75&gt;0,OR($P75&gt;=Turno_Min,$Q75&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J75&gt;0,SUMPRODUCT((Mapa_Sala=$B75)*(Mapa_Data=$A75)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q75)*(Mapa_RelFim&gt;$P75))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I75),$I75&gt;0,COUNTIF(Esp_Nome,$E75)&gt;0,$I75&gt;3*INDEX(Esp_Dur,MATCH($E75,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P75" s="12">
@@ -8118,7 +8136,7 @@
         <v/>
       </c>
       <c r="O76" s="24">
-        <f>IF($B76="","",IF(COUNTIF(Postos_Cod,$B76)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B76)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B76,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E76)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H76)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C76)),NOT(ISNUMBER($D76))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C76),ISNUMBER($D76),MOD($D76-$C76,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J76&gt;0,OR($P76&gt;=Turno_Min,$Q76&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J76&gt;0,$K76&gt;0,COUNTIF(Mapa_Chave,$B76&amp;"#"&amp;$A76&amp;"#"&amp;($K76+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B76&amp;"#"&amp;$A76&amp;"#"&amp;($K76+1),Mapa_Chave,0))-$Q76&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J76&gt;0,SUMPRODUCT((Mapa_Sala=$B76)*(Mapa_Data=$A76)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q76)*(Mapa_RelFim&gt;$P76))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I76),$I76&gt;0,COUNTIF(Esp_Nome,$E76)&gt;0,$I76&gt;3*INDEX(Esp_Dur,MATCH($E76,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B76="","",IF(COUNTIF(Postos_Cod,$B76)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B76)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B76,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E76)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H76)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C76)),NOT(ISNUMBER($D76))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C76),ISNUMBER($D76),MOD($D76-$C76,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J76&gt;0,OR($P76&gt;=Turno_Min,$Q76&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J76&gt;0,SUMPRODUCT((Mapa_Sala=$B76)*(Mapa_Data=$A76)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q76)*(Mapa_RelFim&gt;$P76))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I76),$I76&gt;0,COUNTIF(Esp_Nome,$E76)&gt;0,$I76&gt;3*INDEX(Esp_Dur,MATCH($E76,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P76" s="12">
@@ -8176,7 +8194,7 @@
         <v/>
       </c>
       <c r="O77" s="24">
-        <f>IF($B77="","",IF(COUNTIF(Postos_Cod,$B77)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B77)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B77,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E77)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H77)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C77)),NOT(ISNUMBER($D77))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C77),ISNUMBER($D77),MOD($D77-$C77,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J77&gt;0,OR($P77&gt;=Turno_Min,$Q77&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J77&gt;0,$K77&gt;0,COUNTIF(Mapa_Chave,$B77&amp;"#"&amp;$A77&amp;"#"&amp;($K77+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B77&amp;"#"&amp;$A77&amp;"#"&amp;($K77+1),Mapa_Chave,0))-$Q77&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J77&gt;0,SUMPRODUCT((Mapa_Sala=$B77)*(Mapa_Data=$A77)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q77)*(Mapa_RelFim&gt;$P77))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I77),$I77&gt;0,COUNTIF(Esp_Nome,$E77)&gt;0,$I77&gt;3*INDEX(Esp_Dur,MATCH($E77,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B77="","",IF(COUNTIF(Postos_Cod,$B77)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B77)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B77,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E77)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H77)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C77)),NOT(ISNUMBER($D77))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C77),ISNUMBER($D77),MOD($D77-$C77,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J77&gt;0,OR($P77&gt;=Turno_Min,$Q77&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J77&gt;0,SUMPRODUCT((Mapa_Sala=$B77)*(Mapa_Data=$A77)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q77)*(Mapa_RelFim&gt;$P77))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I77),$I77&gt;0,COUNTIF(Esp_Nome,$E77)&gt;0,$I77&gt;3*INDEX(Esp_Dur,MATCH($E77,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P77" s="12">
@@ -8234,7 +8252,7 @@
         <v/>
       </c>
       <c r="O78" s="24">
-        <f>IF($B78="","",IF(COUNTIF(Postos_Cod,$B78)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B78)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B78,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E78)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H78)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C78)),NOT(ISNUMBER($D78))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C78),ISNUMBER($D78),MOD($D78-$C78,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J78&gt;0,OR($P78&gt;=Turno_Min,$Q78&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J78&gt;0,$K78&gt;0,COUNTIF(Mapa_Chave,$B78&amp;"#"&amp;$A78&amp;"#"&amp;($K78+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B78&amp;"#"&amp;$A78&amp;"#"&amp;($K78+1),Mapa_Chave,0))-$Q78&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J78&gt;0,SUMPRODUCT((Mapa_Sala=$B78)*(Mapa_Data=$A78)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q78)*(Mapa_RelFim&gt;$P78))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I78),$I78&gt;0,COUNTIF(Esp_Nome,$E78)&gt;0,$I78&gt;3*INDEX(Esp_Dur,MATCH($E78,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B78="","",IF(COUNTIF(Postos_Cod,$B78)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B78)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B78,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E78)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H78)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C78)),NOT(ISNUMBER($D78))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C78),ISNUMBER($D78),MOD($D78-$C78,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J78&gt;0,OR($P78&gt;=Turno_Min,$Q78&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J78&gt;0,SUMPRODUCT((Mapa_Sala=$B78)*(Mapa_Data=$A78)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q78)*(Mapa_RelFim&gt;$P78))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I78),$I78&gt;0,COUNTIF(Esp_Nome,$E78)&gt;0,$I78&gt;3*INDEX(Esp_Dur,MATCH($E78,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P78" s="12">
@@ -8292,7 +8310,7 @@
         <v/>
       </c>
       <c r="O79" s="24">
-        <f>IF($B79="","",IF(COUNTIF(Postos_Cod,$B79)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B79)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B79,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E79)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H79)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C79)),NOT(ISNUMBER($D79))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C79),ISNUMBER($D79),MOD($D79-$C79,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J79&gt;0,OR($P79&gt;=Turno_Min,$Q79&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J79&gt;0,$K79&gt;0,COUNTIF(Mapa_Chave,$B79&amp;"#"&amp;$A79&amp;"#"&amp;($K79+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B79&amp;"#"&amp;$A79&amp;"#"&amp;($K79+1),Mapa_Chave,0))-$Q79&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J79&gt;0,SUMPRODUCT((Mapa_Sala=$B79)*(Mapa_Data=$A79)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q79)*(Mapa_RelFim&gt;$P79))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I79),$I79&gt;0,COUNTIF(Esp_Nome,$E79)&gt;0,$I79&gt;3*INDEX(Esp_Dur,MATCH($E79,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B79="","",IF(COUNTIF(Postos_Cod,$B79)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B79)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B79,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E79)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H79)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C79)),NOT(ISNUMBER($D79))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C79),ISNUMBER($D79),MOD($D79-$C79,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J79&gt;0,OR($P79&gt;=Turno_Min,$Q79&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J79&gt;0,SUMPRODUCT((Mapa_Sala=$B79)*(Mapa_Data=$A79)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q79)*(Mapa_RelFim&gt;$P79))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I79),$I79&gt;0,COUNTIF(Esp_Nome,$E79)&gt;0,$I79&gt;3*INDEX(Esp_Dur,MATCH($E79,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P79" s="12">
@@ -8350,7 +8368,7 @@
         <v/>
       </c>
       <c r="O80" s="24">
-        <f>IF($B80="","",IF(COUNTIF(Postos_Cod,$B80)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B80)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B80,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E80)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H80)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C80)),NOT(ISNUMBER($D80))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C80),ISNUMBER($D80),MOD($D80-$C80,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J80&gt;0,OR($P80&gt;=Turno_Min,$Q80&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J80&gt;0,$K80&gt;0,COUNTIF(Mapa_Chave,$B80&amp;"#"&amp;$A80&amp;"#"&amp;($K80+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B80&amp;"#"&amp;$A80&amp;"#"&amp;($K80+1),Mapa_Chave,0))-$Q80&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J80&gt;0,SUMPRODUCT((Mapa_Sala=$B80)*(Mapa_Data=$A80)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q80)*(Mapa_RelFim&gt;$P80))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I80),$I80&gt;0,COUNTIF(Esp_Nome,$E80)&gt;0,$I80&gt;3*INDEX(Esp_Dur,MATCH($E80,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B80="","",IF(COUNTIF(Postos_Cod,$B80)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B80)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B80,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E80)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H80)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C80)),NOT(ISNUMBER($D80))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C80),ISNUMBER($D80),MOD($D80-$C80,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J80&gt;0,OR($P80&gt;=Turno_Min,$Q80&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J80&gt;0,SUMPRODUCT((Mapa_Sala=$B80)*(Mapa_Data=$A80)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q80)*(Mapa_RelFim&gt;$P80))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I80),$I80&gt;0,COUNTIF(Esp_Nome,$E80)&gt;0,$I80&gt;3*INDEX(Esp_Dur,MATCH($E80,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P80" s="12">
@@ -8408,7 +8426,7 @@
         <v/>
       </c>
       <c r="O81" s="24">
-        <f>IF($B81="","",IF(COUNTIF(Postos_Cod,$B81)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B81)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B81,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E81)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H81)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C81)),NOT(ISNUMBER($D81))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C81),ISNUMBER($D81),MOD($D81-$C81,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J81&gt;0,OR($P81&gt;=Turno_Min,$Q81&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J81&gt;0,$K81&gt;0,COUNTIF(Mapa_Chave,$B81&amp;"#"&amp;$A81&amp;"#"&amp;($K81+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B81&amp;"#"&amp;$A81&amp;"#"&amp;($K81+1),Mapa_Chave,0))-$Q81&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J81&gt;0,SUMPRODUCT((Mapa_Sala=$B81)*(Mapa_Data=$A81)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q81)*(Mapa_RelFim&gt;$P81))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I81),$I81&gt;0,COUNTIF(Esp_Nome,$E81)&gt;0,$I81&gt;3*INDEX(Esp_Dur,MATCH($E81,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B81="","",IF(COUNTIF(Postos_Cod,$B81)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B81)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B81,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E81)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H81)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C81)),NOT(ISNUMBER($D81))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C81),ISNUMBER($D81),MOD($D81-$C81,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J81&gt;0,OR($P81&gt;=Turno_Min,$Q81&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J81&gt;0,SUMPRODUCT((Mapa_Sala=$B81)*(Mapa_Data=$A81)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q81)*(Mapa_RelFim&gt;$P81))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I81),$I81&gt;0,COUNTIF(Esp_Nome,$E81)&gt;0,$I81&gt;3*INDEX(Esp_Dur,MATCH($E81,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P81" s="12">
@@ -8466,7 +8484,7 @@
         <v/>
       </c>
       <c r="O82" s="24">
-        <f>IF($B82="","",IF(COUNTIF(Postos_Cod,$B82)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B82)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B82,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E82)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H82)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C82)),NOT(ISNUMBER($D82))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C82),ISNUMBER($D82),MOD($D82-$C82,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J82&gt;0,OR($P82&gt;=Turno_Min,$Q82&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J82&gt;0,$K82&gt;0,COUNTIF(Mapa_Chave,$B82&amp;"#"&amp;$A82&amp;"#"&amp;($K82+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B82&amp;"#"&amp;$A82&amp;"#"&amp;($K82+1),Mapa_Chave,0))-$Q82&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J82&gt;0,SUMPRODUCT((Mapa_Sala=$B82)*(Mapa_Data=$A82)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q82)*(Mapa_RelFim&gt;$P82))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I82),$I82&gt;0,COUNTIF(Esp_Nome,$E82)&gt;0,$I82&gt;3*INDEX(Esp_Dur,MATCH($E82,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B82="","",IF(COUNTIF(Postos_Cod,$B82)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B82)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B82,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E82)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H82)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C82)),NOT(ISNUMBER($D82))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C82),ISNUMBER($D82),MOD($D82-$C82,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J82&gt;0,OR($P82&gt;=Turno_Min,$Q82&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J82&gt;0,SUMPRODUCT((Mapa_Sala=$B82)*(Mapa_Data=$A82)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q82)*(Mapa_RelFim&gt;$P82))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I82),$I82&gt;0,COUNTIF(Esp_Nome,$E82)&gt;0,$I82&gt;3*INDEX(Esp_Dur,MATCH($E82,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P82" s="12">
@@ -8524,7 +8542,7 @@
         <v/>
       </c>
       <c r="O83" s="24">
-        <f>IF($B83="","",IF(COUNTIF(Postos_Cod,$B83)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B83)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B83,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E83)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H83)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C83)),NOT(ISNUMBER($D83))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C83),ISNUMBER($D83),MOD($D83-$C83,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J83&gt;0,OR($P83&gt;=Turno_Min,$Q83&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J83&gt;0,$K83&gt;0,COUNTIF(Mapa_Chave,$B83&amp;"#"&amp;$A83&amp;"#"&amp;($K83+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B83&amp;"#"&amp;$A83&amp;"#"&amp;($K83+1),Mapa_Chave,0))-$Q83&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J83&gt;0,SUMPRODUCT((Mapa_Sala=$B83)*(Mapa_Data=$A83)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q83)*(Mapa_RelFim&gt;$P83))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I83),$I83&gt;0,COUNTIF(Esp_Nome,$E83)&gt;0,$I83&gt;3*INDEX(Esp_Dur,MATCH($E83,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B83="","",IF(COUNTIF(Postos_Cod,$B83)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B83)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B83,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E83)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H83)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C83)),NOT(ISNUMBER($D83))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C83),ISNUMBER($D83),MOD($D83-$C83,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J83&gt;0,OR($P83&gt;=Turno_Min,$Q83&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J83&gt;0,SUMPRODUCT((Mapa_Sala=$B83)*(Mapa_Data=$A83)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q83)*(Mapa_RelFim&gt;$P83))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I83),$I83&gt;0,COUNTIF(Esp_Nome,$E83)&gt;0,$I83&gt;3*INDEX(Esp_Dur,MATCH($E83,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P83" s="12">
@@ -8582,7 +8600,7 @@
         <v/>
       </c>
       <c r="O84" s="24">
-        <f>IF($B84="","",IF(COUNTIF(Postos_Cod,$B84)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B84)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B84,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E84)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H84)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C84)),NOT(ISNUMBER($D84))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C84),ISNUMBER($D84),MOD($D84-$C84,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J84&gt;0,OR($P84&gt;=Turno_Min,$Q84&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J84&gt;0,$K84&gt;0,COUNTIF(Mapa_Chave,$B84&amp;"#"&amp;$A84&amp;"#"&amp;($K84+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B84&amp;"#"&amp;$A84&amp;"#"&amp;($K84+1),Mapa_Chave,0))-$Q84&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J84&gt;0,SUMPRODUCT((Mapa_Sala=$B84)*(Mapa_Data=$A84)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q84)*(Mapa_RelFim&gt;$P84))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I84),$I84&gt;0,COUNTIF(Esp_Nome,$E84)&gt;0,$I84&gt;3*INDEX(Esp_Dur,MATCH($E84,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B84="","",IF(COUNTIF(Postos_Cod,$B84)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B84)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B84,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E84)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H84)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C84)),NOT(ISNUMBER($D84))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C84),ISNUMBER($D84),MOD($D84-$C84,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J84&gt;0,OR($P84&gt;=Turno_Min,$Q84&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J84&gt;0,SUMPRODUCT((Mapa_Sala=$B84)*(Mapa_Data=$A84)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q84)*(Mapa_RelFim&gt;$P84))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I84),$I84&gt;0,COUNTIF(Esp_Nome,$E84)&gt;0,$I84&gt;3*INDEX(Esp_Dur,MATCH($E84,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P84" s="12">
@@ -8640,7 +8658,7 @@
         <v/>
       </c>
       <c r="O85" s="24">
-        <f>IF($B85="","",IF(COUNTIF(Postos_Cod,$B85)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B85)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B85,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E85)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H85)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C85)),NOT(ISNUMBER($D85))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C85),ISNUMBER($D85),MOD($D85-$C85,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J85&gt;0,OR($P85&gt;=Turno_Min,$Q85&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J85&gt;0,$K85&gt;0,COUNTIF(Mapa_Chave,$B85&amp;"#"&amp;$A85&amp;"#"&amp;($K85+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B85&amp;"#"&amp;$A85&amp;"#"&amp;($K85+1),Mapa_Chave,0))-$Q85&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J85&gt;0,SUMPRODUCT((Mapa_Sala=$B85)*(Mapa_Data=$A85)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q85)*(Mapa_RelFim&gt;$P85))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I85),$I85&gt;0,COUNTIF(Esp_Nome,$E85)&gt;0,$I85&gt;3*INDEX(Esp_Dur,MATCH($E85,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B85="","",IF(COUNTIF(Postos_Cod,$B85)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B85)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B85,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E85)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H85)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C85)),NOT(ISNUMBER($D85))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C85),ISNUMBER($D85),MOD($D85-$C85,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J85&gt;0,OR($P85&gt;=Turno_Min,$Q85&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J85&gt;0,SUMPRODUCT((Mapa_Sala=$B85)*(Mapa_Data=$A85)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q85)*(Mapa_RelFim&gt;$P85))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I85),$I85&gt;0,COUNTIF(Esp_Nome,$E85)&gt;0,$I85&gt;3*INDEX(Esp_Dur,MATCH($E85,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P85" s="12">
@@ -8698,7 +8716,7 @@
         <v/>
       </c>
       <c r="O86" s="24">
-        <f>IF($B86="","",IF(COUNTIF(Postos_Cod,$B86)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B86)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B86,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E86)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H86)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C86)),NOT(ISNUMBER($D86))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C86),ISNUMBER($D86),MOD($D86-$C86,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J86&gt;0,OR($P86&gt;=Turno_Min,$Q86&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J86&gt;0,$K86&gt;0,COUNTIF(Mapa_Chave,$B86&amp;"#"&amp;$A86&amp;"#"&amp;($K86+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B86&amp;"#"&amp;$A86&amp;"#"&amp;($K86+1),Mapa_Chave,0))-$Q86&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J86&gt;0,SUMPRODUCT((Mapa_Sala=$B86)*(Mapa_Data=$A86)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q86)*(Mapa_RelFim&gt;$P86))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I86),$I86&gt;0,COUNTIF(Esp_Nome,$E86)&gt;0,$I86&gt;3*INDEX(Esp_Dur,MATCH($E86,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B86="","",IF(COUNTIF(Postos_Cod,$B86)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B86)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B86,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E86)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H86)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C86)),NOT(ISNUMBER($D86))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C86),ISNUMBER($D86),MOD($D86-$C86,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J86&gt;0,OR($P86&gt;=Turno_Min,$Q86&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J86&gt;0,SUMPRODUCT((Mapa_Sala=$B86)*(Mapa_Data=$A86)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q86)*(Mapa_RelFim&gt;$P86))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I86),$I86&gt;0,COUNTIF(Esp_Nome,$E86)&gt;0,$I86&gt;3*INDEX(Esp_Dur,MATCH($E86,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P86" s="12">
@@ -8756,7 +8774,7 @@
         <v/>
       </c>
       <c r="O87" s="24">
-        <f>IF($B87="","",IF(COUNTIF(Postos_Cod,$B87)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B87)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B87,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E87)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H87)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C87)),NOT(ISNUMBER($D87))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C87),ISNUMBER($D87),MOD($D87-$C87,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J87&gt;0,OR($P87&gt;=Turno_Min,$Q87&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J87&gt;0,$K87&gt;0,COUNTIF(Mapa_Chave,$B87&amp;"#"&amp;$A87&amp;"#"&amp;($K87+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B87&amp;"#"&amp;$A87&amp;"#"&amp;($K87+1),Mapa_Chave,0))-$Q87&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J87&gt;0,SUMPRODUCT((Mapa_Sala=$B87)*(Mapa_Data=$A87)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q87)*(Mapa_RelFim&gt;$P87))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I87),$I87&gt;0,COUNTIF(Esp_Nome,$E87)&gt;0,$I87&gt;3*INDEX(Esp_Dur,MATCH($E87,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B87="","",IF(COUNTIF(Postos_Cod,$B87)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B87)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B87,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E87)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H87)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C87)),NOT(ISNUMBER($D87))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C87),ISNUMBER($D87),MOD($D87-$C87,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J87&gt;0,OR($P87&gt;=Turno_Min,$Q87&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J87&gt;0,SUMPRODUCT((Mapa_Sala=$B87)*(Mapa_Data=$A87)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q87)*(Mapa_RelFim&gt;$P87))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I87),$I87&gt;0,COUNTIF(Esp_Nome,$E87)&gt;0,$I87&gt;3*INDEX(Esp_Dur,MATCH($E87,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P87" s="12">
@@ -8814,7 +8832,7 @@
         <v/>
       </c>
       <c r="O88" s="24">
-        <f>IF($B88="","",IF(COUNTIF(Postos_Cod,$B88)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B88)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B88,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E88)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H88)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C88)),NOT(ISNUMBER($D88))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C88),ISNUMBER($D88),MOD($D88-$C88,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J88&gt;0,OR($P88&gt;=Turno_Min,$Q88&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J88&gt;0,$K88&gt;0,COUNTIF(Mapa_Chave,$B88&amp;"#"&amp;$A88&amp;"#"&amp;($K88+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B88&amp;"#"&amp;$A88&amp;"#"&amp;($K88+1),Mapa_Chave,0))-$Q88&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J88&gt;0,SUMPRODUCT((Mapa_Sala=$B88)*(Mapa_Data=$A88)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q88)*(Mapa_RelFim&gt;$P88))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I88),$I88&gt;0,COUNTIF(Esp_Nome,$E88)&gt;0,$I88&gt;3*INDEX(Esp_Dur,MATCH($E88,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B88="","",IF(COUNTIF(Postos_Cod,$B88)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B88)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B88,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E88)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H88)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C88)),NOT(ISNUMBER($D88))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C88),ISNUMBER($D88),MOD($D88-$C88,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J88&gt;0,OR($P88&gt;=Turno_Min,$Q88&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J88&gt;0,SUMPRODUCT((Mapa_Sala=$B88)*(Mapa_Data=$A88)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q88)*(Mapa_RelFim&gt;$P88))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I88),$I88&gt;0,COUNTIF(Esp_Nome,$E88)&gt;0,$I88&gt;3*INDEX(Esp_Dur,MATCH($E88,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P88" s="12">
@@ -8872,7 +8890,7 @@
         <v/>
       </c>
       <c r="O89" s="24">
-        <f>IF($B89="","",IF(COUNTIF(Postos_Cod,$B89)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B89)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B89,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E89)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H89)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C89)),NOT(ISNUMBER($D89))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C89),ISNUMBER($D89),MOD($D89-$C89,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J89&gt;0,OR($P89&gt;=Turno_Min,$Q89&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J89&gt;0,$K89&gt;0,COUNTIF(Mapa_Chave,$B89&amp;"#"&amp;$A89&amp;"#"&amp;($K89+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B89&amp;"#"&amp;$A89&amp;"#"&amp;($K89+1),Mapa_Chave,0))-$Q89&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J89&gt;0,SUMPRODUCT((Mapa_Sala=$B89)*(Mapa_Data=$A89)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q89)*(Mapa_RelFim&gt;$P89))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I89),$I89&gt;0,COUNTIF(Esp_Nome,$E89)&gt;0,$I89&gt;3*INDEX(Esp_Dur,MATCH($E89,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B89="","",IF(COUNTIF(Postos_Cod,$B89)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B89)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B89,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E89)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H89)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C89)),NOT(ISNUMBER($D89))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C89),ISNUMBER($D89),MOD($D89-$C89,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J89&gt;0,OR($P89&gt;=Turno_Min,$Q89&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J89&gt;0,SUMPRODUCT((Mapa_Sala=$B89)*(Mapa_Data=$A89)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q89)*(Mapa_RelFim&gt;$P89))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I89),$I89&gt;0,COUNTIF(Esp_Nome,$E89)&gt;0,$I89&gt;3*INDEX(Esp_Dur,MATCH($E89,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P89" s="12">
@@ -8930,7 +8948,7 @@
         <v/>
       </c>
       <c r="O90" s="24">
-        <f>IF($B90="","",IF(COUNTIF(Postos_Cod,$B90)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B90)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B90,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E90)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H90)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C90)),NOT(ISNUMBER($D90))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C90),ISNUMBER($D90),MOD($D90-$C90,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J90&gt;0,OR($P90&gt;=Turno_Min,$Q90&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J90&gt;0,$K90&gt;0,COUNTIF(Mapa_Chave,$B90&amp;"#"&amp;$A90&amp;"#"&amp;($K90+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B90&amp;"#"&amp;$A90&amp;"#"&amp;($K90+1),Mapa_Chave,0))-$Q90&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J90&gt;0,SUMPRODUCT((Mapa_Sala=$B90)*(Mapa_Data=$A90)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q90)*(Mapa_RelFim&gt;$P90))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I90),$I90&gt;0,COUNTIF(Esp_Nome,$E90)&gt;0,$I90&gt;3*INDEX(Esp_Dur,MATCH($E90,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B90="","",IF(COUNTIF(Postos_Cod,$B90)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B90)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B90,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E90)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H90)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C90)),NOT(ISNUMBER($D90))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C90),ISNUMBER($D90),MOD($D90-$C90,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J90&gt;0,OR($P90&gt;=Turno_Min,$Q90&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J90&gt;0,SUMPRODUCT((Mapa_Sala=$B90)*(Mapa_Data=$A90)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q90)*(Mapa_RelFim&gt;$P90))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I90),$I90&gt;0,COUNTIF(Esp_Nome,$E90)&gt;0,$I90&gt;3*INDEX(Esp_Dur,MATCH($E90,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P90" s="12">
@@ -8988,7 +9006,7 @@
         <v/>
       </c>
       <c r="O91" s="24">
-        <f>IF($B91="","",IF(COUNTIF(Postos_Cod,$B91)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B91)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B91,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E91)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H91)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C91)),NOT(ISNUMBER($D91))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C91),ISNUMBER($D91),MOD($D91-$C91,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J91&gt;0,OR($P91&gt;=Turno_Min,$Q91&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J91&gt;0,$K91&gt;0,COUNTIF(Mapa_Chave,$B91&amp;"#"&amp;$A91&amp;"#"&amp;($K91+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B91&amp;"#"&amp;$A91&amp;"#"&amp;($K91+1),Mapa_Chave,0))-$Q91&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J91&gt;0,SUMPRODUCT((Mapa_Sala=$B91)*(Mapa_Data=$A91)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q91)*(Mapa_RelFim&gt;$P91))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I91),$I91&gt;0,COUNTIF(Esp_Nome,$E91)&gt;0,$I91&gt;3*INDEX(Esp_Dur,MATCH($E91,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B91="","",IF(COUNTIF(Postos_Cod,$B91)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B91)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B91,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E91)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H91)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C91)),NOT(ISNUMBER($D91))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C91),ISNUMBER($D91),MOD($D91-$C91,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J91&gt;0,OR($P91&gt;=Turno_Min,$Q91&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J91&gt;0,SUMPRODUCT((Mapa_Sala=$B91)*(Mapa_Data=$A91)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q91)*(Mapa_RelFim&gt;$P91))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I91),$I91&gt;0,COUNTIF(Esp_Nome,$E91)&gt;0,$I91&gt;3*INDEX(Esp_Dur,MATCH($E91,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P91" s="12">
@@ -9046,7 +9064,7 @@
         <v/>
       </c>
       <c r="O92" s="24">
-        <f>IF($B92="","",IF(COUNTIF(Postos_Cod,$B92)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B92)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B92,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E92)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H92)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C92)),NOT(ISNUMBER($D92))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C92),ISNUMBER($D92),MOD($D92-$C92,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J92&gt;0,OR($P92&gt;=Turno_Min,$Q92&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J92&gt;0,$K92&gt;0,COUNTIF(Mapa_Chave,$B92&amp;"#"&amp;$A92&amp;"#"&amp;($K92+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B92&amp;"#"&amp;$A92&amp;"#"&amp;($K92+1),Mapa_Chave,0))-$Q92&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J92&gt;0,SUMPRODUCT((Mapa_Sala=$B92)*(Mapa_Data=$A92)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q92)*(Mapa_RelFim&gt;$P92))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I92),$I92&gt;0,COUNTIF(Esp_Nome,$E92)&gt;0,$I92&gt;3*INDEX(Esp_Dur,MATCH($E92,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B92="","",IF(COUNTIF(Postos_Cod,$B92)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B92)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B92,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E92)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H92)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C92)),NOT(ISNUMBER($D92))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C92),ISNUMBER($D92),MOD($D92-$C92,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J92&gt;0,OR($P92&gt;=Turno_Min,$Q92&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J92&gt;0,SUMPRODUCT((Mapa_Sala=$B92)*(Mapa_Data=$A92)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q92)*(Mapa_RelFim&gt;$P92))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I92),$I92&gt;0,COUNTIF(Esp_Nome,$E92)&gt;0,$I92&gt;3*INDEX(Esp_Dur,MATCH($E92,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P92" s="12">
@@ -9104,7 +9122,7 @@
         <v/>
       </c>
       <c r="O93" s="24">
-        <f>IF($B93="","",IF(COUNTIF(Postos_Cod,$B93)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B93)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B93,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E93)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H93)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C93)),NOT(ISNUMBER($D93))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C93),ISNUMBER($D93),MOD($D93-$C93,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J93&gt;0,OR($P93&gt;=Turno_Min,$Q93&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J93&gt;0,$K93&gt;0,COUNTIF(Mapa_Chave,$B93&amp;"#"&amp;$A93&amp;"#"&amp;($K93+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B93&amp;"#"&amp;$A93&amp;"#"&amp;($K93+1),Mapa_Chave,0))-$Q93&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J93&gt;0,SUMPRODUCT((Mapa_Sala=$B93)*(Mapa_Data=$A93)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q93)*(Mapa_RelFim&gt;$P93))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I93),$I93&gt;0,COUNTIF(Esp_Nome,$E93)&gt;0,$I93&gt;3*INDEX(Esp_Dur,MATCH($E93,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B93="","",IF(COUNTIF(Postos_Cod,$B93)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B93)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B93,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E93)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H93)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C93)),NOT(ISNUMBER($D93))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C93),ISNUMBER($D93),MOD($D93-$C93,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J93&gt;0,OR($P93&gt;=Turno_Min,$Q93&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J93&gt;0,SUMPRODUCT((Mapa_Sala=$B93)*(Mapa_Data=$A93)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q93)*(Mapa_RelFim&gt;$P93))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I93),$I93&gt;0,COUNTIF(Esp_Nome,$E93)&gt;0,$I93&gt;3*INDEX(Esp_Dur,MATCH($E93,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P93" s="12">
@@ -9162,7 +9180,7 @@
         <v/>
       </c>
       <c r="O94" s="24">
-        <f>IF($B94="","",IF(COUNTIF(Postos_Cod,$B94)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B94)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B94,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E94)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H94)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C94)),NOT(ISNUMBER($D94))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C94),ISNUMBER($D94),MOD($D94-$C94,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J94&gt;0,OR($P94&gt;=Turno_Min,$Q94&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J94&gt;0,$K94&gt;0,COUNTIF(Mapa_Chave,$B94&amp;"#"&amp;$A94&amp;"#"&amp;($K94+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B94&amp;"#"&amp;$A94&amp;"#"&amp;($K94+1),Mapa_Chave,0))-$Q94&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J94&gt;0,SUMPRODUCT((Mapa_Sala=$B94)*(Mapa_Data=$A94)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q94)*(Mapa_RelFim&gt;$P94))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I94),$I94&gt;0,COUNTIF(Esp_Nome,$E94)&gt;0,$I94&gt;3*INDEX(Esp_Dur,MATCH($E94,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B94="","",IF(COUNTIF(Postos_Cod,$B94)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B94)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B94,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E94)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H94)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C94)),NOT(ISNUMBER($D94))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C94),ISNUMBER($D94),MOD($D94-$C94,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J94&gt;0,OR($P94&gt;=Turno_Min,$Q94&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J94&gt;0,SUMPRODUCT((Mapa_Sala=$B94)*(Mapa_Data=$A94)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q94)*(Mapa_RelFim&gt;$P94))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I94),$I94&gt;0,COUNTIF(Esp_Nome,$E94)&gt;0,$I94&gt;3*INDEX(Esp_Dur,MATCH($E94,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P94" s="12">
@@ -9220,7 +9238,7 @@
         <v/>
       </c>
       <c r="O95" s="24">
-        <f>IF($B95="","",IF(COUNTIF(Postos_Cod,$B95)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B95)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B95,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E95)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H95)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C95)),NOT(ISNUMBER($D95))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C95),ISNUMBER($D95),MOD($D95-$C95,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J95&gt;0,OR($P95&gt;=Turno_Min,$Q95&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J95&gt;0,$K95&gt;0,COUNTIF(Mapa_Chave,$B95&amp;"#"&amp;$A95&amp;"#"&amp;($K95+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B95&amp;"#"&amp;$A95&amp;"#"&amp;($K95+1),Mapa_Chave,0))-$Q95&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J95&gt;0,SUMPRODUCT((Mapa_Sala=$B95)*(Mapa_Data=$A95)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q95)*(Mapa_RelFim&gt;$P95))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I95),$I95&gt;0,COUNTIF(Esp_Nome,$E95)&gt;0,$I95&gt;3*INDEX(Esp_Dur,MATCH($E95,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B95="","",IF(COUNTIF(Postos_Cod,$B95)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B95)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B95,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E95)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H95)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C95)),NOT(ISNUMBER($D95))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C95),ISNUMBER($D95),MOD($D95-$C95,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J95&gt;0,OR($P95&gt;=Turno_Min,$Q95&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J95&gt;0,SUMPRODUCT((Mapa_Sala=$B95)*(Mapa_Data=$A95)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q95)*(Mapa_RelFim&gt;$P95))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I95),$I95&gt;0,COUNTIF(Esp_Nome,$E95)&gt;0,$I95&gt;3*INDEX(Esp_Dur,MATCH($E95,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P95" s="12">
@@ -9278,7 +9296,7 @@
         <v/>
       </c>
       <c r="O96" s="24">
-        <f>IF($B96="","",IF(COUNTIF(Postos_Cod,$B96)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B96)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B96,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E96)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H96)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C96)),NOT(ISNUMBER($D96))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C96),ISNUMBER($D96),MOD($D96-$C96,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J96&gt;0,OR($P96&gt;=Turno_Min,$Q96&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J96&gt;0,$K96&gt;0,COUNTIF(Mapa_Chave,$B96&amp;"#"&amp;$A96&amp;"#"&amp;($K96+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B96&amp;"#"&amp;$A96&amp;"#"&amp;($K96+1),Mapa_Chave,0))-$Q96&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J96&gt;0,SUMPRODUCT((Mapa_Sala=$B96)*(Mapa_Data=$A96)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q96)*(Mapa_RelFim&gt;$P96))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I96),$I96&gt;0,COUNTIF(Esp_Nome,$E96)&gt;0,$I96&gt;3*INDEX(Esp_Dur,MATCH($E96,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B96="","",IF(COUNTIF(Postos_Cod,$B96)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B96)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B96,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E96)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H96)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C96)),NOT(ISNUMBER($D96))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C96),ISNUMBER($D96),MOD($D96-$C96,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J96&gt;0,OR($P96&gt;=Turno_Min,$Q96&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J96&gt;0,SUMPRODUCT((Mapa_Sala=$B96)*(Mapa_Data=$A96)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q96)*(Mapa_RelFim&gt;$P96))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I96),$I96&gt;0,COUNTIF(Esp_Nome,$E96)&gt;0,$I96&gt;3*INDEX(Esp_Dur,MATCH($E96,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P96" s="12">
@@ -9336,7 +9354,7 @@
         <v/>
       </c>
       <c r="O97" s="24">
-        <f>IF($B97="","",IF(COUNTIF(Postos_Cod,$B97)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B97)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B97,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E97)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H97)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C97)),NOT(ISNUMBER($D97))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C97),ISNUMBER($D97),MOD($D97-$C97,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J97&gt;0,OR($P97&gt;=Turno_Min,$Q97&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J97&gt;0,$K97&gt;0,COUNTIF(Mapa_Chave,$B97&amp;"#"&amp;$A97&amp;"#"&amp;($K97+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B97&amp;"#"&amp;$A97&amp;"#"&amp;($K97+1),Mapa_Chave,0))-$Q97&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J97&gt;0,SUMPRODUCT((Mapa_Sala=$B97)*(Mapa_Data=$A97)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q97)*(Mapa_RelFim&gt;$P97))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I97),$I97&gt;0,COUNTIF(Esp_Nome,$E97)&gt;0,$I97&gt;3*INDEX(Esp_Dur,MATCH($E97,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B97="","",IF(COUNTIF(Postos_Cod,$B97)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B97)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B97,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E97)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H97)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C97)),NOT(ISNUMBER($D97))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C97),ISNUMBER($D97),MOD($D97-$C97,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J97&gt;0,OR($P97&gt;=Turno_Min,$Q97&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J97&gt;0,SUMPRODUCT((Mapa_Sala=$B97)*(Mapa_Data=$A97)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q97)*(Mapa_RelFim&gt;$P97))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I97),$I97&gt;0,COUNTIF(Esp_Nome,$E97)&gt;0,$I97&gt;3*INDEX(Esp_Dur,MATCH($E97,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P97" s="12">
@@ -9394,7 +9412,7 @@
         <v/>
       </c>
       <c r="O98" s="24">
-        <f>IF($B98="","",IF(COUNTIF(Postos_Cod,$B98)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B98)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B98,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E98)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H98)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C98)),NOT(ISNUMBER($D98))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C98),ISNUMBER($D98),MOD($D98-$C98,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J98&gt;0,OR($P98&gt;=Turno_Min,$Q98&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J98&gt;0,$K98&gt;0,COUNTIF(Mapa_Chave,$B98&amp;"#"&amp;$A98&amp;"#"&amp;($K98+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B98&amp;"#"&amp;$A98&amp;"#"&amp;($K98+1),Mapa_Chave,0))-$Q98&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J98&gt;0,SUMPRODUCT((Mapa_Sala=$B98)*(Mapa_Data=$A98)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q98)*(Mapa_RelFim&gt;$P98))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I98),$I98&gt;0,COUNTIF(Esp_Nome,$E98)&gt;0,$I98&gt;3*INDEX(Esp_Dur,MATCH($E98,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B98="","",IF(COUNTIF(Postos_Cod,$B98)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B98)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B98,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E98)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H98)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C98)),NOT(ISNUMBER($D98))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C98),ISNUMBER($D98),MOD($D98-$C98,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J98&gt;0,OR($P98&gt;=Turno_Min,$Q98&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J98&gt;0,SUMPRODUCT((Mapa_Sala=$B98)*(Mapa_Data=$A98)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q98)*(Mapa_RelFim&gt;$P98))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I98),$I98&gt;0,COUNTIF(Esp_Nome,$E98)&gt;0,$I98&gt;3*INDEX(Esp_Dur,MATCH($E98,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P98" s="12">
@@ -9452,7 +9470,7 @@
         <v/>
       </c>
       <c r="O99" s="24">
-        <f>IF($B99="","",IF(COUNTIF(Postos_Cod,$B99)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B99)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B99,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E99)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H99)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C99)),NOT(ISNUMBER($D99))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C99),ISNUMBER($D99),MOD($D99-$C99,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J99&gt;0,OR($P99&gt;=Turno_Min,$Q99&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J99&gt;0,$K99&gt;0,COUNTIF(Mapa_Chave,$B99&amp;"#"&amp;$A99&amp;"#"&amp;($K99+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B99&amp;"#"&amp;$A99&amp;"#"&amp;($K99+1),Mapa_Chave,0))-$Q99&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J99&gt;0,SUMPRODUCT((Mapa_Sala=$B99)*(Mapa_Data=$A99)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q99)*(Mapa_RelFim&gt;$P99))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I99),$I99&gt;0,COUNTIF(Esp_Nome,$E99)&gt;0,$I99&gt;3*INDEX(Esp_Dur,MATCH($E99,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B99="","",IF(COUNTIF(Postos_Cod,$B99)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B99)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B99,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E99)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H99)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C99)),NOT(ISNUMBER($D99))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C99),ISNUMBER($D99),MOD($D99-$C99,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J99&gt;0,OR($P99&gt;=Turno_Min,$Q99&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J99&gt;0,SUMPRODUCT((Mapa_Sala=$B99)*(Mapa_Data=$A99)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q99)*(Mapa_RelFim&gt;$P99))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I99),$I99&gt;0,COUNTIF(Esp_Nome,$E99)&gt;0,$I99&gt;3*INDEX(Esp_Dur,MATCH($E99,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P99" s="12">
@@ -9510,7 +9528,7 @@
         <v/>
       </c>
       <c r="O100" s="24">
-        <f>IF($B100="","",IF(COUNTIF(Postos_Cod,$B100)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B100)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B100,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E100)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H100)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C100)),NOT(ISNUMBER($D100))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C100),ISNUMBER($D100),MOD($D100-$C100,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J100&gt;0,OR($P100&gt;=Turno_Min,$Q100&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J100&gt;0,$K100&gt;0,COUNTIF(Mapa_Chave,$B100&amp;"#"&amp;$A100&amp;"#"&amp;($K100+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B100&amp;"#"&amp;$A100&amp;"#"&amp;($K100+1),Mapa_Chave,0))-$Q100&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J100&gt;0,SUMPRODUCT((Mapa_Sala=$B100)*(Mapa_Data=$A100)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q100)*(Mapa_RelFim&gt;$P100))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I100),$I100&gt;0,COUNTIF(Esp_Nome,$E100)&gt;0,$I100&gt;3*INDEX(Esp_Dur,MATCH($E100,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B100="","",IF(COUNTIF(Postos_Cod,$B100)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B100)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B100,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E100)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H100)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C100)),NOT(ISNUMBER($D100))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C100),ISNUMBER($D100),MOD($D100-$C100,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J100&gt;0,OR($P100&gt;=Turno_Min,$Q100&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J100&gt;0,SUMPRODUCT((Mapa_Sala=$B100)*(Mapa_Data=$A100)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q100)*(Mapa_RelFim&gt;$P100))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I100),$I100&gt;0,COUNTIF(Esp_Nome,$E100)&gt;0,$I100&gt;3*INDEX(Esp_Dur,MATCH($E100,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P100" s="12">
@@ -9568,7 +9586,7 @@
         <v/>
       </c>
       <c r="O101" s="24">
-        <f>IF($B101="","",IF(COUNTIF(Postos_Cod,$B101)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B101)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B101,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E101)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H101)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C101)),NOT(ISNUMBER($D101))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C101),ISNUMBER($D101),MOD($D101-$C101,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J101&gt;0,OR($P101&gt;=Turno_Min,$Q101&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J101&gt;0,$K101&gt;0,COUNTIF(Mapa_Chave,$B101&amp;"#"&amp;$A101&amp;"#"&amp;($K101+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B101&amp;"#"&amp;$A101&amp;"#"&amp;($K101+1),Mapa_Chave,0))-$Q101&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J101&gt;0,SUMPRODUCT((Mapa_Sala=$B101)*(Mapa_Data=$A101)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q101)*(Mapa_RelFim&gt;$P101))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I101),$I101&gt;0,COUNTIF(Esp_Nome,$E101)&gt;0,$I101&gt;3*INDEX(Esp_Dur,MATCH($E101,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B101="","",IF(COUNTIF(Postos_Cod,$B101)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B101)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B101,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E101)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H101)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C101)),NOT(ISNUMBER($D101))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C101),ISNUMBER($D101),MOD($D101-$C101,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J101&gt;0,OR($P101&gt;=Turno_Min,$Q101&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J101&gt;0,SUMPRODUCT((Mapa_Sala=$B101)*(Mapa_Data=$A101)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q101)*(Mapa_RelFim&gt;$P101))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I101),$I101&gt;0,COUNTIF(Esp_Nome,$E101)&gt;0,$I101&gt;3*INDEX(Esp_Dur,MATCH($E101,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P101" s="12">
@@ -9626,7 +9644,7 @@
         <v/>
       </c>
       <c r="O102" s="24">
-        <f>IF($B102="","",IF(COUNTIF(Postos_Cod,$B102)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B102)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B102,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E102)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H102)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C102)),NOT(ISNUMBER($D102))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C102),ISNUMBER($D102),MOD($D102-$C102,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J102&gt;0,OR($P102&gt;=Turno_Min,$Q102&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J102&gt;0,$K102&gt;0,COUNTIF(Mapa_Chave,$B102&amp;"#"&amp;$A102&amp;"#"&amp;($K102+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B102&amp;"#"&amp;$A102&amp;"#"&amp;($K102+1),Mapa_Chave,0))-$Q102&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J102&gt;0,SUMPRODUCT((Mapa_Sala=$B102)*(Mapa_Data=$A102)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q102)*(Mapa_RelFim&gt;$P102))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I102),$I102&gt;0,COUNTIF(Esp_Nome,$E102)&gt;0,$I102&gt;3*INDEX(Esp_Dur,MATCH($E102,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B102="","",IF(COUNTIF(Postos_Cod,$B102)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B102)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B102,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E102)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H102)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C102)),NOT(ISNUMBER($D102))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C102),ISNUMBER($D102),MOD($D102-$C102,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J102&gt;0,OR($P102&gt;=Turno_Min,$Q102&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J102&gt;0,SUMPRODUCT((Mapa_Sala=$B102)*(Mapa_Data=$A102)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q102)*(Mapa_RelFim&gt;$P102))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I102),$I102&gt;0,COUNTIF(Esp_Nome,$E102)&gt;0,$I102&gt;3*INDEX(Esp_Dur,MATCH($E102,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P102" s="12">
@@ -9684,7 +9702,7 @@
         <v/>
       </c>
       <c r="O103" s="24">
-        <f>IF($B103="","",IF(COUNTIF(Postos_Cod,$B103)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B103)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B103,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E103)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H103)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C103)),NOT(ISNUMBER($D103))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C103),ISNUMBER($D103),MOD($D103-$C103,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J103&gt;0,OR($P103&gt;=Turno_Min,$Q103&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J103&gt;0,$K103&gt;0,COUNTIF(Mapa_Chave,$B103&amp;"#"&amp;$A103&amp;"#"&amp;($K103+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B103&amp;"#"&amp;$A103&amp;"#"&amp;($K103+1),Mapa_Chave,0))-$Q103&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J103&gt;0,SUMPRODUCT((Mapa_Sala=$B103)*(Mapa_Data=$A103)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q103)*(Mapa_RelFim&gt;$P103))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I103),$I103&gt;0,COUNTIF(Esp_Nome,$E103)&gt;0,$I103&gt;3*INDEX(Esp_Dur,MATCH($E103,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B103="","",IF(COUNTIF(Postos_Cod,$B103)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B103)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B103,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E103)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H103)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C103)),NOT(ISNUMBER($D103))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C103),ISNUMBER($D103),MOD($D103-$C103,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J103&gt;0,OR($P103&gt;=Turno_Min,$Q103&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J103&gt;0,SUMPRODUCT((Mapa_Sala=$B103)*(Mapa_Data=$A103)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q103)*(Mapa_RelFim&gt;$P103))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I103),$I103&gt;0,COUNTIF(Esp_Nome,$E103)&gt;0,$I103&gt;3*INDEX(Esp_Dur,MATCH($E103,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P103" s="12">
@@ -9742,7 +9760,7 @@
         <v/>
       </c>
       <c r="O104" s="24">
-        <f>IF($B104="","",IF(COUNTIF(Postos_Cod,$B104)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B104)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B104,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E104)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H104)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C104)),NOT(ISNUMBER($D104))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C104),ISNUMBER($D104),MOD($D104-$C104,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J104&gt;0,OR($P104&gt;=Turno_Min,$Q104&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J104&gt;0,$K104&gt;0,COUNTIF(Mapa_Chave,$B104&amp;"#"&amp;$A104&amp;"#"&amp;($K104+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B104&amp;"#"&amp;$A104&amp;"#"&amp;($K104+1),Mapa_Chave,0))-$Q104&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J104&gt;0,SUMPRODUCT((Mapa_Sala=$B104)*(Mapa_Data=$A104)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q104)*(Mapa_RelFim&gt;$P104))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I104),$I104&gt;0,COUNTIF(Esp_Nome,$E104)&gt;0,$I104&gt;3*INDEX(Esp_Dur,MATCH($E104,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B104="","",IF(COUNTIF(Postos_Cod,$B104)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B104)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B104,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E104)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H104)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C104)),NOT(ISNUMBER($D104))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C104),ISNUMBER($D104),MOD($D104-$C104,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J104&gt;0,OR($P104&gt;=Turno_Min,$Q104&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J104&gt;0,SUMPRODUCT((Mapa_Sala=$B104)*(Mapa_Data=$A104)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q104)*(Mapa_RelFim&gt;$P104))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I104),$I104&gt;0,COUNTIF(Esp_Nome,$E104)&gt;0,$I104&gt;3*INDEX(Esp_Dur,MATCH($E104,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P104" s="12">
@@ -9800,7 +9818,7 @@
         <v/>
       </c>
       <c r="O105" s="24">
-        <f>IF($B105="","",IF(COUNTIF(Postos_Cod,$B105)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B105)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B105,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E105)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H105)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C105)),NOT(ISNUMBER($D105))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C105),ISNUMBER($D105),MOD($D105-$C105,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J105&gt;0,OR($P105&gt;=Turno_Min,$Q105&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J105&gt;0,$K105&gt;0,COUNTIF(Mapa_Chave,$B105&amp;"#"&amp;$A105&amp;"#"&amp;($K105+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B105&amp;"#"&amp;$A105&amp;"#"&amp;($K105+1),Mapa_Chave,0))-$Q105&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J105&gt;0,SUMPRODUCT((Mapa_Sala=$B105)*(Mapa_Data=$A105)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q105)*(Mapa_RelFim&gt;$P105))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I105),$I105&gt;0,COUNTIF(Esp_Nome,$E105)&gt;0,$I105&gt;3*INDEX(Esp_Dur,MATCH($E105,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B105="","",IF(COUNTIF(Postos_Cod,$B105)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B105)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B105,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E105)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H105)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C105)),NOT(ISNUMBER($D105))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C105),ISNUMBER($D105),MOD($D105-$C105,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J105&gt;0,OR($P105&gt;=Turno_Min,$Q105&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J105&gt;0,SUMPRODUCT((Mapa_Sala=$B105)*(Mapa_Data=$A105)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q105)*(Mapa_RelFim&gt;$P105))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I105),$I105&gt;0,COUNTIF(Esp_Nome,$E105)&gt;0,$I105&gt;3*INDEX(Esp_Dur,MATCH($E105,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P105" s="12">
@@ -9858,7 +9876,7 @@
         <v/>
       </c>
       <c r="O106" s="24">
-        <f>IF($B106="","",IF(COUNTIF(Postos_Cod,$B106)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B106)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B106,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E106)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H106)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C106)),NOT(ISNUMBER($D106))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C106),ISNUMBER($D106),MOD($D106-$C106,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J106&gt;0,OR($P106&gt;=Turno_Min,$Q106&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J106&gt;0,$K106&gt;0,COUNTIF(Mapa_Chave,$B106&amp;"#"&amp;$A106&amp;"#"&amp;($K106+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B106&amp;"#"&amp;$A106&amp;"#"&amp;($K106+1),Mapa_Chave,0))-$Q106&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J106&gt;0,SUMPRODUCT((Mapa_Sala=$B106)*(Mapa_Data=$A106)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q106)*(Mapa_RelFim&gt;$P106))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I106),$I106&gt;0,COUNTIF(Esp_Nome,$E106)&gt;0,$I106&gt;3*INDEX(Esp_Dur,MATCH($E106,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B106="","",IF(COUNTIF(Postos_Cod,$B106)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B106)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B106,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E106)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H106)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C106)),NOT(ISNUMBER($D106))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C106),ISNUMBER($D106),MOD($D106-$C106,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J106&gt;0,OR($P106&gt;=Turno_Min,$Q106&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J106&gt;0,SUMPRODUCT((Mapa_Sala=$B106)*(Mapa_Data=$A106)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q106)*(Mapa_RelFim&gt;$P106))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I106),$I106&gt;0,COUNTIF(Esp_Nome,$E106)&gt;0,$I106&gt;3*INDEX(Esp_Dur,MATCH($E106,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P106" s="12">
@@ -9916,7 +9934,7 @@
         <v/>
       </c>
       <c r="O107" s="24">
-        <f>IF($B107="","",IF(COUNTIF(Postos_Cod,$B107)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B107)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B107,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E107)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H107)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C107)),NOT(ISNUMBER($D107))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C107),ISNUMBER($D107),MOD($D107-$C107,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J107&gt;0,OR($P107&gt;=Turno_Min,$Q107&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J107&gt;0,$K107&gt;0,COUNTIF(Mapa_Chave,$B107&amp;"#"&amp;$A107&amp;"#"&amp;($K107+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B107&amp;"#"&amp;$A107&amp;"#"&amp;($K107+1),Mapa_Chave,0))-$Q107&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J107&gt;0,SUMPRODUCT((Mapa_Sala=$B107)*(Mapa_Data=$A107)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q107)*(Mapa_RelFim&gt;$P107))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I107),$I107&gt;0,COUNTIF(Esp_Nome,$E107)&gt;0,$I107&gt;3*INDEX(Esp_Dur,MATCH($E107,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B107="","",IF(COUNTIF(Postos_Cod,$B107)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B107)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B107,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E107)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H107)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C107)),NOT(ISNUMBER($D107))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C107),ISNUMBER($D107),MOD($D107-$C107,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J107&gt;0,OR($P107&gt;=Turno_Min,$Q107&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J107&gt;0,SUMPRODUCT((Mapa_Sala=$B107)*(Mapa_Data=$A107)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q107)*(Mapa_RelFim&gt;$P107))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I107),$I107&gt;0,COUNTIF(Esp_Nome,$E107)&gt;0,$I107&gt;3*INDEX(Esp_Dur,MATCH($E107,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P107" s="12">
@@ -9974,7 +9992,7 @@
         <v/>
       </c>
       <c r="O108" s="24">
-        <f>IF($B108="","",IF(COUNTIF(Postos_Cod,$B108)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B108)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B108,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E108)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H108)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C108)),NOT(ISNUMBER($D108))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C108),ISNUMBER($D108),MOD($D108-$C108,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J108&gt;0,OR($P108&gt;=Turno_Min,$Q108&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J108&gt;0,$K108&gt;0,COUNTIF(Mapa_Chave,$B108&amp;"#"&amp;$A108&amp;"#"&amp;($K108+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B108&amp;"#"&amp;$A108&amp;"#"&amp;($K108+1),Mapa_Chave,0))-$Q108&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J108&gt;0,SUMPRODUCT((Mapa_Sala=$B108)*(Mapa_Data=$A108)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q108)*(Mapa_RelFim&gt;$P108))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I108),$I108&gt;0,COUNTIF(Esp_Nome,$E108)&gt;0,$I108&gt;3*INDEX(Esp_Dur,MATCH($E108,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B108="","",IF(COUNTIF(Postos_Cod,$B108)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B108)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B108,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E108)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H108)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C108)),NOT(ISNUMBER($D108))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C108),ISNUMBER($D108),MOD($D108-$C108,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J108&gt;0,OR($P108&gt;=Turno_Min,$Q108&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J108&gt;0,SUMPRODUCT((Mapa_Sala=$B108)*(Mapa_Data=$A108)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q108)*(Mapa_RelFim&gt;$P108))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I108),$I108&gt;0,COUNTIF(Esp_Nome,$E108)&gt;0,$I108&gt;3*INDEX(Esp_Dur,MATCH($E108,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P108" s="12">
@@ -10032,7 +10050,7 @@
         <v/>
       </c>
       <c r="O109" s="24">
-        <f>IF($B109="","",IF(COUNTIF(Postos_Cod,$B109)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B109)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B109,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E109)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H109)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C109)),NOT(ISNUMBER($D109))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C109),ISNUMBER($D109),MOD($D109-$C109,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J109&gt;0,OR($P109&gt;=Turno_Min,$Q109&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J109&gt;0,$K109&gt;0,COUNTIF(Mapa_Chave,$B109&amp;"#"&amp;$A109&amp;"#"&amp;($K109+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B109&amp;"#"&amp;$A109&amp;"#"&amp;($K109+1),Mapa_Chave,0))-$Q109&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J109&gt;0,SUMPRODUCT((Mapa_Sala=$B109)*(Mapa_Data=$A109)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q109)*(Mapa_RelFim&gt;$P109))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I109),$I109&gt;0,COUNTIF(Esp_Nome,$E109)&gt;0,$I109&gt;3*INDEX(Esp_Dur,MATCH($E109,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B109="","",IF(COUNTIF(Postos_Cod,$B109)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B109)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B109,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E109)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H109)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C109)),NOT(ISNUMBER($D109))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C109),ISNUMBER($D109),MOD($D109-$C109,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J109&gt;0,OR($P109&gt;=Turno_Min,$Q109&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J109&gt;0,SUMPRODUCT((Mapa_Sala=$B109)*(Mapa_Data=$A109)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q109)*(Mapa_RelFim&gt;$P109))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I109),$I109&gt;0,COUNTIF(Esp_Nome,$E109)&gt;0,$I109&gt;3*INDEX(Esp_Dur,MATCH($E109,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P109" s="12">
@@ -10090,7 +10108,7 @@
         <v/>
       </c>
       <c r="O110" s="24">
-        <f>IF($B110="","",IF(COUNTIF(Postos_Cod,$B110)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B110)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B110,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E110)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H110)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C110)),NOT(ISNUMBER($D110))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C110),ISNUMBER($D110),MOD($D110-$C110,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J110&gt;0,OR($P110&gt;=Turno_Min,$Q110&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J110&gt;0,$K110&gt;0,COUNTIF(Mapa_Chave,$B110&amp;"#"&amp;$A110&amp;"#"&amp;($K110+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B110&amp;"#"&amp;$A110&amp;"#"&amp;($K110+1),Mapa_Chave,0))-$Q110&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J110&gt;0,SUMPRODUCT((Mapa_Sala=$B110)*(Mapa_Data=$A110)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q110)*(Mapa_RelFim&gt;$P110))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I110),$I110&gt;0,COUNTIF(Esp_Nome,$E110)&gt;0,$I110&gt;3*INDEX(Esp_Dur,MATCH($E110,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B110="","",IF(COUNTIF(Postos_Cod,$B110)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B110)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B110,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E110)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H110)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C110)),NOT(ISNUMBER($D110))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C110),ISNUMBER($D110),MOD($D110-$C110,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J110&gt;0,OR($P110&gt;=Turno_Min,$Q110&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J110&gt;0,SUMPRODUCT((Mapa_Sala=$B110)*(Mapa_Data=$A110)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q110)*(Mapa_RelFim&gt;$P110))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I110),$I110&gt;0,COUNTIF(Esp_Nome,$E110)&gt;0,$I110&gt;3*INDEX(Esp_Dur,MATCH($E110,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P110" s="12">
@@ -10148,7 +10166,7 @@
         <v/>
       </c>
       <c r="O111" s="24">
-        <f>IF($B111="","",IF(COUNTIF(Postos_Cod,$B111)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B111)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B111,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E111)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H111)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C111)),NOT(ISNUMBER($D111))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C111),ISNUMBER($D111),MOD($D111-$C111,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J111&gt;0,OR($P111&gt;=Turno_Min,$Q111&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J111&gt;0,$K111&gt;0,COUNTIF(Mapa_Chave,$B111&amp;"#"&amp;$A111&amp;"#"&amp;($K111+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B111&amp;"#"&amp;$A111&amp;"#"&amp;($K111+1),Mapa_Chave,0))-$Q111&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J111&gt;0,SUMPRODUCT((Mapa_Sala=$B111)*(Mapa_Data=$A111)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q111)*(Mapa_RelFim&gt;$P111))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I111),$I111&gt;0,COUNTIF(Esp_Nome,$E111)&gt;0,$I111&gt;3*INDEX(Esp_Dur,MATCH($E111,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B111="","",IF(COUNTIF(Postos_Cod,$B111)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B111)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B111,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E111)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H111)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C111)),NOT(ISNUMBER($D111))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C111),ISNUMBER($D111),MOD($D111-$C111,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J111&gt;0,OR($P111&gt;=Turno_Min,$Q111&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J111&gt;0,SUMPRODUCT((Mapa_Sala=$B111)*(Mapa_Data=$A111)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q111)*(Mapa_RelFim&gt;$P111))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I111),$I111&gt;0,COUNTIF(Esp_Nome,$E111)&gt;0,$I111&gt;3*INDEX(Esp_Dur,MATCH($E111,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P111" s="12">
@@ -10206,7 +10224,7 @@
         <v/>
       </c>
       <c r="O112" s="24">
-        <f>IF($B112="","",IF(COUNTIF(Postos_Cod,$B112)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B112)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B112,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E112)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H112)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C112)),NOT(ISNUMBER($D112))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C112),ISNUMBER($D112),MOD($D112-$C112,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J112&gt;0,OR($P112&gt;=Turno_Min,$Q112&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J112&gt;0,$K112&gt;0,COUNTIF(Mapa_Chave,$B112&amp;"#"&amp;$A112&amp;"#"&amp;($K112+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B112&amp;"#"&amp;$A112&amp;"#"&amp;($K112+1),Mapa_Chave,0))-$Q112&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J112&gt;0,SUMPRODUCT((Mapa_Sala=$B112)*(Mapa_Data=$A112)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q112)*(Mapa_RelFim&gt;$P112))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I112),$I112&gt;0,COUNTIF(Esp_Nome,$E112)&gt;0,$I112&gt;3*INDEX(Esp_Dur,MATCH($E112,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B112="","",IF(COUNTIF(Postos_Cod,$B112)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B112)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B112,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E112)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H112)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C112)),NOT(ISNUMBER($D112))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C112),ISNUMBER($D112),MOD($D112-$C112,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J112&gt;0,OR($P112&gt;=Turno_Min,$Q112&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J112&gt;0,SUMPRODUCT((Mapa_Sala=$B112)*(Mapa_Data=$A112)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q112)*(Mapa_RelFim&gt;$P112))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I112),$I112&gt;0,COUNTIF(Esp_Nome,$E112)&gt;0,$I112&gt;3*INDEX(Esp_Dur,MATCH($E112,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P112" s="12">
@@ -10264,7 +10282,7 @@
         <v/>
       </c>
       <c r="O113" s="24">
-        <f>IF($B113="","",IF(COUNTIF(Postos_Cod,$B113)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B113)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B113,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E113)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H113)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C113)),NOT(ISNUMBER($D113))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C113),ISNUMBER($D113),MOD($D113-$C113,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J113&gt;0,OR($P113&gt;=Turno_Min,$Q113&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J113&gt;0,$K113&gt;0,COUNTIF(Mapa_Chave,$B113&amp;"#"&amp;$A113&amp;"#"&amp;($K113+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B113&amp;"#"&amp;$A113&amp;"#"&amp;($K113+1),Mapa_Chave,0))-$Q113&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J113&gt;0,SUMPRODUCT((Mapa_Sala=$B113)*(Mapa_Data=$A113)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q113)*(Mapa_RelFim&gt;$P113))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I113),$I113&gt;0,COUNTIF(Esp_Nome,$E113)&gt;0,$I113&gt;3*INDEX(Esp_Dur,MATCH($E113,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B113="","",IF(COUNTIF(Postos_Cod,$B113)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B113)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B113,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E113)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H113)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C113)),NOT(ISNUMBER($D113))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C113),ISNUMBER($D113),MOD($D113-$C113,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J113&gt;0,OR($P113&gt;=Turno_Min,$Q113&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J113&gt;0,SUMPRODUCT((Mapa_Sala=$B113)*(Mapa_Data=$A113)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q113)*(Mapa_RelFim&gt;$P113))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I113),$I113&gt;0,COUNTIF(Esp_Nome,$E113)&gt;0,$I113&gt;3*INDEX(Esp_Dur,MATCH($E113,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P113" s="12">
@@ -10322,7 +10340,7 @@
         <v/>
       </c>
       <c r="O114" s="24">
-        <f>IF($B114="","",IF(COUNTIF(Postos_Cod,$B114)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B114)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B114,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E114)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H114)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C114)),NOT(ISNUMBER($D114))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C114),ISNUMBER($D114),MOD($D114-$C114,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J114&gt;0,OR($P114&gt;=Turno_Min,$Q114&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J114&gt;0,$K114&gt;0,COUNTIF(Mapa_Chave,$B114&amp;"#"&amp;$A114&amp;"#"&amp;($K114+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B114&amp;"#"&amp;$A114&amp;"#"&amp;($K114+1),Mapa_Chave,0))-$Q114&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J114&gt;0,SUMPRODUCT((Mapa_Sala=$B114)*(Mapa_Data=$A114)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q114)*(Mapa_RelFim&gt;$P114))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I114),$I114&gt;0,COUNTIF(Esp_Nome,$E114)&gt;0,$I114&gt;3*INDEX(Esp_Dur,MATCH($E114,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B114="","",IF(COUNTIF(Postos_Cod,$B114)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B114)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B114,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E114)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H114)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C114)),NOT(ISNUMBER($D114))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C114),ISNUMBER($D114),MOD($D114-$C114,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J114&gt;0,OR($P114&gt;=Turno_Min,$Q114&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J114&gt;0,SUMPRODUCT((Mapa_Sala=$B114)*(Mapa_Data=$A114)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q114)*(Mapa_RelFim&gt;$P114))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I114),$I114&gt;0,COUNTIF(Esp_Nome,$E114)&gt;0,$I114&gt;3*INDEX(Esp_Dur,MATCH($E114,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P114" s="12">
@@ -10380,7 +10398,7 @@
         <v/>
       </c>
       <c r="O115" s="24">
-        <f>IF($B115="","",IF(COUNTIF(Postos_Cod,$B115)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B115)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B115,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E115)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H115)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C115)),NOT(ISNUMBER($D115))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C115),ISNUMBER($D115),MOD($D115-$C115,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J115&gt;0,OR($P115&gt;=Turno_Min,$Q115&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J115&gt;0,$K115&gt;0,COUNTIF(Mapa_Chave,$B115&amp;"#"&amp;$A115&amp;"#"&amp;($K115+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B115&amp;"#"&amp;$A115&amp;"#"&amp;($K115+1),Mapa_Chave,0))-$Q115&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J115&gt;0,SUMPRODUCT((Mapa_Sala=$B115)*(Mapa_Data=$A115)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q115)*(Mapa_RelFim&gt;$P115))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I115),$I115&gt;0,COUNTIF(Esp_Nome,$E115)&gt;0,$I115&gt;3*INDEX(Esp_Dur,MATCH($E115,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B115="","",IF(COUNTIF(Postos_Cod,$B115)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B115)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B115,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E115)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H115)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C115)),NOT(ISNUMBER($D115))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C115),ISNUMBER($D115),MOD($D115-$C115,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J115&gt;0,OR($P115&gt;=Turno_Min,$Q115&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J115&gt;0,SUMPRODUCT((Mapa_Sala=$B115)*(Mapa_Data=$A115)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q115)*(Mapa_RelFim&gt;$P115))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I115),$I115&gt;0,COUNTIF(Esp_Nome,$E115)&gt;0,$I115&gt;3*INDEX(Esp_Dur,MATCH($E115,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P115" s="12">
@@ -10438,7 +10456,7 @@
         <v/>
       </c>
       <c r="O116" s="24">
-        <f>IF($B116="","",IF(COUNTIF(Postos_Cod,$B116)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B116)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B116,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E116)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H116)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C116)),NOT(ISNUMBER($D116))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C116),ISNUMBER($D116),MOD($D116-$C116,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J116&gt;0,OR($P116&gt;=Turno_Min,$Q116&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J116&gt;0,$K116&gt;0,COUNTIF(Mapa_Chave,$B116&amp;"#"&amp;$A116&amp;"#"&amp;($K116+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B116&amp;"#"&amp;$A116&amp;"#"&amp;($K116+1),Mapa_Chave,0))-$Q116&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J116&gt;0,SUMPRODUCT((Mapa_Sala=$B116)*(Mapa_Data=$A116)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q116)*(Mapa_RelFim&gt;$P116))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I116),$I116&gt;0,COUNTIF(Esp_Nome,$E116)&gt;0,$I116&gt;3*INDEX(Esp_Dur,MATCH($E116,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B116="","",IF(COUNTIF(Postos_Cod,$B116)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B116)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B116,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E116)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H116)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C116)),NOT(ISNUMBER($D116))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C116),ISNUMBER($D116),MOD($D116-$C116,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J116&gt;0,OR($P116&gt;=Turno_Min,$Q116&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J116&gt;0,SUMPRODUCT((Mapa_Sala=$B116)*(Mapa_Data=$A116)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q116)*(Mapa_RelFim&gt;$P116))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I116),$I116&gt;0,COUNTIF(Esp_Nome,$E116)&gt;0,$I116&gt;3*INDEX(Esp_Dur,MATCH($E116,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P116" s="12">
@@ -10496,7 +10514,7 @@
         <v/>
       </c>
       <c r="O117" s="24">
-        <f>IF($B117="","",IF(COUNTIF(Postos_Cod,$B117)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B117)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B117,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E117)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H117)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C117)),NOT(ISNUMBER($D117))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C117),ISNUMBER($D117),MOD($D117-$C117,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J117&gt;0,OR($P117&gt;=Turno_Min,$Q117&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J117&gt;0,$K117&gt;0,COUNTIF(Mapa_Chave,$B117&amp;"#"&amp;$A117&amp;"#"&amp;($K117+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B117&amp;"#"&amp;$A117&amp;"#"&amp;($K117+1),Mapa_Chave,0))-$Q117&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J117&gt;0,SUMPRODUCT((Mapa_Sala=$B117)*(Mapa_Data=$A117)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q117)*(Mapa_RelFim&gt;$P117))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I117),$I117&gt;0,COUNTIF(Esp_Nome,$E117)&gt;0,$I117&gt;3*INDEX(Esp_Dur,MATCH($E117,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B117="","",IF(COUNTIF(Postos_Cod,$B117)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B117)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B117,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E117)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H117)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C117)),NOT(ISNUMBER($D117))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C117),ISNUMBER($D117),MOD($D117-$C117,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J117&gt;0,OR($P117&gt;=Turno_Min,$Q117&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J117&gt;0,SUMPRODUCT((Mapa_Sala=$B117)*(Mapa_Data=$A117)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q117)*(Mapa_RelFim&gt;$P117))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I117),$I117&gt;0,COUNTIF(Esp_Nome,$E117)&gt;0,$I117&gt;3*INDEX(Esp_Dur,MATCH($E117,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P117" s="12">
@@ -10554,7 +10572,7 @@
         <v/>
       </c>
       <c r="O118" s="24">
-        <f>IF($B118="","",IF(COUNTIF(Postos_Cod,$B118)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B118)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B118,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E118)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H118)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C118)),NOT(ISNUMBER($D118))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C118),ISNUMBER($D118),MOD($D118-$C118,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J118&gt;0,OR($P118&gt;=Turno_Min,$Q118&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J118&gt;0,$K118&gt;0,COUNTIF(Mapa_Chave,$B118&amp;"#"&amp;$A118&amp;"#"&amp;($K118+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B118&amp;"#"&amp;$A118&amp;"#"&amp;($K118+1),Mapa_Chave,0))-$Q118&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J118&gt;0,SUMPRODUCT((Mapa_Sala=$B118)*(Mapa_Data=$A118)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q118)*(Mapa_RelFim&gt;$P118))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I118),$I118&gt;0,COUNTIF(Esp_Nome,$E118)&gt;0,$I118&gt;3*INDEX(Esp_Dur,MATCH($E118,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B118="","",IF(COUNTIF(Postos_Cod,$B118)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B118)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B118,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E118)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H118)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C118)),NOT(ISNUMBER($D118))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C118),ISNUMBER($D118),MOD($D118-$C118,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J118&gt;0,OR($P118&gt;=Turno_Min,$Q118&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J118&gt;0,SUMPRODUCT((Mapa_Sala=$B118)*(Mapa_Data=$A118)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q118)*(Mapa_RelFim&gt;$P118))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I118),$I118&gt;0,COUNTIF(Esp_Nome,$E118)&gt;0,$I118&gt;3*INDEX(Esp_Dur,MATCH($E118,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P118" s="12">
@@ -10612,7 +10630,7 @@
         <v/>
       </c>
       <c r="O119" s="24">
-        <f>IF($B119="","",IF(COUNTIF(Postos_Cod,$B119)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B119)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B119,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E119)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H119)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C119)),NOT(ISNUMBER($D119))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C119),ISNUMBER($D119),MOD($D119-$C119,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J119&gt;0,OR($P119&gt;=Turno_Min,$Q119&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J119&gt;0,$K119&gt;0,COUNTIF(Mapa_Chave,$B119&amp;"#"&amp;$A119&amp;"#"&amp;($K119+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B119&amp;"#"&amp;$A119&amp;"#"&amp;($K119+1),Mapa_Chave,0))-$Q119&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J119&gt;0,SUMPRODUCT((Mapa_Sala=$B119)*(Mapa_Data=$A119)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q119)*(Mapa_RelFim&gt;$P119))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I119),$I119&gt;0,COUNTIF(Esp_Nome,$E119)&gt;0,$I119&gt;3*INDEX(Esp_Dur,MATCH($E119,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B119="","",IF(COUNTIF(Postos_Cod,$B119)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B119)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B119,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E119)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H119)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C119)),NOT(ISNUMBER($D119))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C119),ISNUMBER($D119),MOD($D119-$C119,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J119&gt;0,OR($P119&gt;=Turno_Min,$Q119&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J119&gt;0,SUMPRODUCT((Mapa_Sala=$B119)*(Mapa_Data=$A119)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q119)*(Mapa_RelFim&gt;$P119))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I119),$I119&gt;0,COUNTIF(Esp_Nome,$E119)&gt;0,$I119&gt;3*INDEX(Esp_Dur,MATCH($E119,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P119" s="12">
@@ -10670,7 +10688,7 @@
         <v/>
       </c>
       <c r="O120" s="24">
-        <f>IF($B120="","",IF(COUNTIF(Postos_Cod,$B120)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B120)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B120,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E120)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H120)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C120)),NOT(ISNUMBER($D120))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C120),ISNUMBER($D120),MOD($D120-$C120,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J120&gt;0,OR($P120&gt;=Turno_Min,$Q120&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J120&gt;0,$K120&gt;0,COUNTIF(Mapa_Chave,$B120&amp;"#"&amp;$A120&amp;"#"&amp;($K120+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B120&amp;"#"&amp;$A120&amp;"#"&amp;($K120+1),Mapa_Chave,0))-$Q120&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J120&gt;0,SUMPRODUCT((Mapa_Sala=$B120)*(Mapa_Data=$A120)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q120)*(Mapa_RelFim&gt;$P120))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I120),$I120&gt;0,COUNTIF(Esp_Nome,$E120)&gt;0,$I120&gt;3*INDEX(Esp_Dur,MATCH($E120,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B120="","",IF(COUNTIF(Postos_Cod,$B120)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B120)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B120,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E120)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H120)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C120)),NOT(ISNUMBER($D120))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C120),ISNUMBER($D120),MOD($D120-$C120,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J120&gt;0,OR($P120&gt;=Turno_Min,$Q120&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J120&gt;0,SUMPRODUCT((Mapa_Sala=$B120)*(Mapa_Data=$A120)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q120)*(Mapa_RelFim&gt;$P120))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I120),$I120&gt;0,COUNTIF(Esp_Nome,$E120)&gt;0,$I120&gt;3*INDEX(Esp_Dur,MATCH($E120,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P120" s="12">
@@ -10728,7 +10746,7 @@
         <v/>
       </c>
       <c r="O121" s="24">
-        <f>IF($B121="","",IF(COUNTIF(Postos_Cod,$B121)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B121)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B121,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E121)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H121)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C121)),NOT(ISNUMBER($D121))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C121),ISNUMBER($D121),MOD($D121-$C121,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J121&gt;0,OR($P121&gt;=Turno_Min,$Q121&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J121&gt;0,$K121&gt;0,COUNTIF(Mapa_Chave,$B121&amp;"#"&amp;$A121&amp;"#"&amp;($K121+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B121&amp;"#"&amp;$A121&amp;"#"&amp;($K121+1),Mapa_Chave,0))-$Q121&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J121&gt;0,SUMPRODUCT((Mapa_Sala=$B121)*(Mapa_Data=$A121)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q121)*(Mapa_RelFim&gt;$P121))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I121),$I121&gt;0,COUNTIF(Esp_Nome,$E121)&gt;0,$I121&gt;3*INDEX(Esp_Dur,MATCH($E121,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B121="","",IF(COUNTIF(Postos_Cod,$B121)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B121)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B121,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E121)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H121)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C121)),NOT(ISNUMBER($D121))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C121),ISNUMBER($D121),MOD($D121-$C121,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J121&gt;0,OR($P121&gt;=Turno_Min,$Q121&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J121&gt;0,SUMPRODUCT((Mapa_Sala=$B121)*(Mapa_Data=$A121)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q121)*(Mapa_RelFim&gt;$P121))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I121),$I121&gt;0,COUNTIF(Esp_Nome,$E121)&gt;0,$I121&gt;3*INDEX(Esp_Dur,MATCH($E121,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P121" s="12">
@@ -10786,7 +10804,7 @@
         <v/>
       </c>
       <c r="O122" s="24">
-        <f>IF($B122="","",IF(COUNTIF(Postos_Cod,$B122)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B122)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B122,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E122)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H122)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C122)),NOT(ISNUMBER($D122))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C122),ISNUMBER($D122),MOD($D122-$C122,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J122&gt;0,OR($P122&gt;=Turno_Min,$Q122&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J122&gt;0,$K122&gt;0,COUNTIF(Mapa_Chave,$B122&amp;"#"&amp;$A122&amp;"#"&amp;($K122+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B122&amp;"#"&amp;$A122&amp;"#"&amp;($K122+1),Mapa_Chave,0))-$Q122&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J122&gt;0,SUMPRODUCT((Mapa_Sala=$B122)*(Mapa_Data=$A122)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q122)*(Mapa_RelFim&gt;$P122))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I122),$I122&gt;0,COUNTIF(Esp_Nome,$E122)&gt;0,$I122&gt;3*INDEX(Esp_Dur,MATCH($E122,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B122="","",IF(COUNTIF(Postos_Cod,$B122)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B122)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B122,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E122)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H122)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C122)),NOT(ISNUMBER($D122))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C122),ISNUMBER($D122),MOD($D122-$C122,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J122&gt;0,OR($P122&gt;=Turno_Min,$Q122&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J122&gt;0,SUMPRODUCT((Mapa_Sala=$B122)*(Mapa_Data=$A122)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q122)*(Mapa_RelFim&gt;$P122))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I122),$I122&gt;0,COUNTIF(Esp_Nome,$E122)&gt;0,$I122&gt;3*INDEX(Esp_Dur,MATCH($E122,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P122" s="12">
@@ -10844,7 +10862,7 @@
         <v/>
       </c>
       <c r="O123" s="24">
-        <f>IF($B123="","",IF(COUNTIF(Postos_Cod,$B123)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B123)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B123,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E123)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H123)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C123)),NOT(ISNUMBER($D123))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C123),ISNUMBER($D123),MOD($D123-$C123,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J123&gt;0,OR($P123&gt;=Turno_Min,$Q123&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J123&gt;0,$K123&gt;0,COUNTIF(Mapa_Chave,$B123&amp;"#"&amp;$A123&amp;"#"&amp;($K123+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B123&amp;"#"&amp;$A123&amp;"#"&amp;($K123+1),Mapa_Chave,0))-$Q123&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J123&gt;0,SUMPRODUCT((Mapa_Sala=$B123)*(Mapa_Data=$A123)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q123)*(Mapa_RelFim&gt;$P123))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I123),$I123&gt;0,COUNTIF(Esp_Nome,$E123)&gt;0,$I123&gt;3*INDEX(Esp_Dur,MATCH($E123,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B123="","",IF(COUNTIF(Postos_Cod,$B123)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B123)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B123,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E123)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H123)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C123)),NOT(ISNUMBER($D123))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C123),ISNUMBER($D123),MOD($D123-$C123,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J123&gt;0,OR($P123&gt;=Turno_Min,$Q123&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J123&gt;0,SUMPRODUCT((Mapa_Sala=$B123)*(Mapa_Data=$A123)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q123)*(Mapa_RelFim&gt;$P123))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I123),$I123&gt;0,COUNTIF(Esp_Nome,$E123)&gt;0,$I123&gt;3*INDEX(Esp_Dur,MATCH($E123,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P123" s="12">
@@ -10902,7 +10920,7 @@
         <v/>
       </c>
       <c r="O124" s="24">
-        <f>IF($B124="","",IF(COUNTIF(Postos_Cod,$B124)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B124)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B124,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E124)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H124)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C124)),NOT(ISNUMBER($D124))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C124),ISNUMBER($D124),MOD($D124-$C124,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J124&gt;0,OR($P124&gt;=Turno_Min,$Q124&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J124&gt;0,$K124&gt;0,COUNTIF(Mapa_Chave,$B124&amp;"#"&amp;$A124&amp;"#"&amp;($K124+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B124&amp;"#"&amp;$A124&amp;"#"&amp;($K124+1),Mapa_Chave,0))-$Q124&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J124&gt;0,SUMPRODUCT((Mapa_Sala=$B124)*(Mapa_Data=$A124)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q124)*(Mapa_RelFim&gt;$P124))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I124),$I124&gt;0,COUNTIF(Esp_Nome,$E124)&gt;0,$I124&gt;3*INDEX(Esp_Dur,MATCH($E124,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B124="","",IF(COUNTIF(Postos_Cod,$B124)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B124)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B124,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E124)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H124)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C124)),NOT(ISNUMBER($D124))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C124),ISNUMBER($D124),MOD($D124-$C124,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J124&gt;0,OR($P124&gt;=Turno_Min,$Q124&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J124&gt;0,SUMPRODUCT((Mapa_Sala=$B124)*(Mapa_Data=$A124)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q124)*(Mapa_RelFim&gt;$P124))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I124),$I124&gt;0,COUNTIF(Esp_Nome,$E124)&gt;0,$I124&gt;3*INDEX(Esp_Dur,MATCH($E124,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P124" s="12">
@@ -10960,7 +10978,7 @@
         <v/>
       </c>
       <c r="O125" s="24">
-        <f>IF($B125="","",IF(COUNTIF(Postos_Cod,$B125)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B125)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B125,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E125)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H125)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C125)),NOT(ISNUMBER($D125))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C125),ISNUMBER($D125),MOD($D125-$C125,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J125&gt;0,OR($P125&gt;=Turno_Min,$Q125&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J125&gt;0,$K125&gt;0,COUNTIF(Mapa_Chave,$B125&amp;"#"&amp;$A125&amp;"#"&amp;($K125+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B125&amp;"#"&amp;$A125&amp;"#"&amp;($K125+1),Mapa_Chave,0))-$Q125&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J125&gt;0,SUMPRODUCT((Mapa_Sala=$B125)*(Mapa_Data=$A125)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q125)*(Mapa_RelFim&gt;$P125))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I125),$I125&gt;0,COUNTIF(Esp_Nome,$E125)&gt;0,$I125&gt;3*INDEX(Esp_Dur,MATCH($E125,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B125="","",IF(COUNTIF(Postos_Cod,$B125)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B125)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B125,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E125)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H125)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C125)),NOT(ISNUMBER($D125))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C125),ISNUMBER($D125),MOD($D125-$C125,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J125&gt;0,OR($P125&gt;=Turno_Min,$Q125&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J125&gt;0,SUMPRODUCT((Mapa_Sala=$B125)*(Mapa_Data=$A125)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q125)*(Mapa_RelFim&gt;$P125))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I125),$I125&gt;0,COUNTIF(Esp_Nome,$E125)&gt;0,$I125&gt;3*INDEX(Esp_Dur,MATCH($E125,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P125" s="12">
@@ -11018,7 +11036,7 @@
         <v/>
       </c>
       <c r="O126" s="24">
-        <f>IF($B126="","",IF(COUNTIF(Postos_Cod,$B126)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B126)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B126,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E126)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H126)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C126)),NOT(ISNUMBER($D126))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C126),ISNUMBER($D126),MOD($D126-$C126,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J126&gt;0,OR($P126&gt;=Turno_Min,$Q126&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J126&gt;0,$K126&gt;0,COUNTIF(Mapa_Chave,$B126&amp;"#"&amp;$A126&amp;"#"&amp;($K126+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B126&amp;"#"&amp;$A126&amp;"#"&amp;($K126+1),Mapa_Chave,0))-$Q126&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J126&gt;0,SUMPRODUCT((Mapa_Sala=$B126)*(Mapa_Data=$A126)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q126)*(Mapa_RelFim&gt;$P126))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I126),$I126&gt;0,COUNTIF(Esp_Nome,$E126)&gt;0,$I126&gt;3*INDEX(Esp_Dur,MATCH($E126,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B126="","",IF(COUNTIF(Postos_Cod,$B126)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B126)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B126,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E126)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H126)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C126)),NOT(ISNUMBER($D126))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C126),ISNUMBER($D126),MOD($D126-$C126,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J126&gt;0,OR($P126&gt;=Turno_Min,$Q126&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J126&gt;0,SUMPRODUCT((Mapa_Sala=$B126)*(Mapa_Data=$A126)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q126)*(Mapa_RelFim&gt;$P126))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I126),$I126&gt;0,COUNTIF(Esp_Nome,$E126)&gt;0,$I126&gt;3*INDEX(Esp_Dur,MATCH($E126,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P126" s="12">
@@ -11076,7 +11094,7 @@
         <v/>
       </c>
       <c r="O127" s="24">
-        <f>IF($B127="","",IF(COUNTIF(Postos_Cod,$B127)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B127)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B127,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E127)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H127)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C127)),NOT(ISNUMBER($D127))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C127),ISNUMBER($D127),MOD($D127-$C127,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J127&gt;0,OR($P127&gt;=Turno_Min,$Q127&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J127&gt;0,$K127&gt;0,COUNTIF(Mapa_Chave,$B127&amp;"#"&amp;$A127&amp;"#"&amp;($K127+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B127&amp;"#"&amp;$A127&amp;"#"&amp;($K127+1),Mapa_Chave,0))-$Q127&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J127&gt;0,SUMPRODUCT((Mapa_Sala=$B127)*(Mapa_Data=$A127)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q127)*(Mapa_RelFim&gt;$P127))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I127),$I127&gt;0,COUNTIF(Esp_Nome,$E127)&gt;0,$I127&gt;3*INDEX(Esp_Dur,MATCH($E127,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B127="","",IF(COUNTIF(Postos_Cod,$B127)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B127)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B127,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E127)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H127)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C127)),NOT(ISNUMBER($D127))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C127),ISNUMBER($D127),MOD($D127-$C127,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J127&gt;0,OR($P127&gt;=Turno_Min,$Q127&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J127&gt;0,SUMPRODUCT((Mapa_Sala=$B127)*(Mapa_Data=$A127)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q127)*(Mapa_RelFim&gt;$P127))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I127),$I127&gt;0,COUNTIF(Esp_Nome,$E127)&gt;0,$I127&gt;3*INDEX(Esp_Dur,MATCH($E127,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P127" s="12">
@@ -11134,7 +11152,7 @@
         <v/>
       </c>
       <c r="O128" s="24">
-        <f>IF($B128="","",IF(COUNTIF(Postos_Cod,$B128)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B128)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B128,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E128)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H128)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C128)),NOT(ISNUMBER($D128))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C128),ISNUMBER($D128),MOD($D128-$C128,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J128&gt;0,OR($P128&gt;=Turno_Min,$Q128&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J128&gt;0,$K128&gt;0,COUNTIF(Mapa_Chave,$B128&amp;"#"&amp;$A128&amp;"#"&amp;($K128+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B128&amp;"#"&amp;$A128&amp;"#"&amp;($K128+1),Mapa_Chave,0))-$Q128&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J128&gt;0,SUMPRODUCT((Mapa_Sala=$B128)*(Mapa_Data=$A128)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q128)*(Mapa_RelFim&gt;$P128))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I128),$I128&gt;0,COUNTIF(Esp_Nome,$E128)&gt;0,$I128&gt;3*INDEX(Esp_Dur,MATCH($E128,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B128="","",IF(COUNTIF(Postos_Cod,$B128)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B128)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B128,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E128)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H128)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C128)),NOT(ISNUMBER($D128))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C128),ISNUMBER($D128),MOD($D128-$C128,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J128&gt;0,OR($P128&gt;=Turno_Min,$Q128&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J128&gt;0,SUMPRODUCT((Mapa_Sala=$B128)*(Mapa_Data=$A128)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q128)*(Mapa_RelFim&gt;$P128))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I128),$I128&gt;0,COUNTIF(Esp_Nome,$E128)&gt;0,$I128&gt;3*INDEX(Esp_Dur,MATCH($E128,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P128" s="12">
@@ -11192,7 +11210,7 @@
         <v/>
       </c>
       <c r="O129" s="24">
-        <f>IF($B129="","",IF(COUNTIF(Postos_Cod,$B129)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B129)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B129,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E129)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H129)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C129)),NOT(ISNUMBER($D129))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C129),ISNUMBER($D129),MOD($D129-$C129,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J129&gt;0,OR($P129&gt;=Turno_Min,$Q129&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J129&gt;0,$K129&gt;0,COUNTIF(Mapa_Chave,$B129&amp;"#"&amp;$A129&amp;"#"&amp;($K129+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B129&amp;"#"&amp;$A129&amp;"#"&amp;($K129+1),Mapa_Chave,0))-$Q129&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J129&gt;0,SUMPRODUCT((Mapa_Sala=$B129)*(Mapa_Data=$A129)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q129)*(Mapa_RelFim&gt;$P129))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I129),$I129&gt;0,COUNTIF(Esp_Nome,$E129)&gt;0,$I129&gt;3*INDEX(Esp_Dur,MATCH($E129,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B129="","",IF(COUNTIF(Postos_Cod,$B129)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B129)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B129,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E129)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H129)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C129)),NOT(ISNUMBER($D129))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C129),ISNUMBER($D129),MOD($D129-$C129,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J129&gt;0,OR($P129&gt;=Turno_Min,$Q129&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J129&gt;0,SUMPRODUCT((Mapa_Sala=$B129)*(Mapa_Data=$A129)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q129)*(Mapa_RelFim&gt;$P129))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I129),$I129&gt;0,COUNTIF(Esp_Nome,$E129)&gt;0,$I129&gt;3*INDEX(Esp_Dur,MATCH($E129,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P129" s="12">
@@ -11250,7 +11268,7 @@
         <v/>
       </c>
       <c r="O130" s="24">
-        <f>IF($B130="","",IF(COUNTIF(Postos_Cod,$B130)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B130)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B130,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E130)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H130)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C130)),NOT(ISNUMBER($D130))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C130),ISNUMBER($D130),MOD($D130-$C130,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J130&gt;0,OR($P130&gt;=Turno_Min,$Q130&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J130&gt;0,$K130&gt;0,COUNTIF(Mapa_Chave,$B130&amp;"#"&amp;$A130&amp;"#"&amp;($K130+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B130&amp;"#"&amp;$A130&amp;"#"&amp;($K130+1),Mapa_Chave,0))-$Q130&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J130&gt;0,SUMPRODUCT((Mapa_Sala=$B130)*(Mapa_Data=$A130)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q130)*(Mapa_RelFim&gt;$P130))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I130),$I130&gt;0,COUNTIF(Esp_Nome,$E130)&gt;0,$I130&gt;3*INDEX(Esp_Dur,MATCH($E130,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B130="","",IF(COUNTIF(Postos_Cod,$B130)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B130)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B130,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E130)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H130)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C130)),NOT(ISNUMBER($D130))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C130),ISNUMBER($D130),MOD($D130-$C130,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J130&gt;0,OR($P130&gt;=Turno_Min,$Q130&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J130&gt;0,SUMPRODUCT((Mapa_Sala=$B130)*(Mapa_Data=$A130)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q130)*(Mapa_RelFim&gt;$P130))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I130),$I130&gt;0,COUNTIF(Esp_Nome,$E130)&gt;0,$I130&gt;3*INDEX(Esp_Dur,MATCH($E130,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P130" s="12">
@@ -11308,7 +11326,7 @@
         <v/>
       </c>
       <c r="O131" s="24">
-        <f>IF($B131="","",IF(COUNTIF(Postos_Cod,$B131)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B131)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B131,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E131)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H131)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C131)),NOT(ISNUMBER($D131))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C131),ISNUMBER($D131),MOD($D131-$C131,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J131&gt;0,OR($P131&gt;=Turno_Min,$Q131&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J131&gt;0,$K131&gt;0,COUNTIF(Mapa_Chave,$B131&amp;"#"&amp;$A131&amp;"#"&amp;($K131+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B131&amp;"#"&amp;$A131&amp;"#"&amp;($K131+1),Mapa_Chave,0))-$Q131&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J131&gt;0,SUMPRODUCT((Mapa_Sala=$B131)*(Mapa_Data=$A131)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q131)*(Mapa_RelFim&gt;$P131))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I131),$I131&gt;0,COUNTIF(Esp_Nome,$E131)&gt;0,$I131&gt;3*INDEX(Esp_Dur,MATCH($E131,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B131="","",IF(COUNTIF(Postos_Cod,$B131)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B131)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B131,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E131)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H131)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C131)),NOT(ISNUMBER($D131))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C131),ISNUMBER($D131),MOD($D131-$C131,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J131&gt;0,OR($P131&gt;=Turno_Min,$Q131&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J131&gt;0,SUMPRODUCT((Mapa_Sala=$B131)*(Mapa_Data=$A131)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q131)*(Mapa_RelFim&gt;$P131))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I131),$I131&gt;0,COUNTIF(Esp_Nome,$E131)&gt;0,$I131&gt;3*INDEX(Esp_Dur,MATCH($E131,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P131" s="12">
@@ -11366,7 +11384,7 @@
         <v/>
       </c>
       <c r="O132" s="24">
-        <f>IF($B132="","",IF(COUNTIF(Postos_Cod,$B132)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B132)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B132,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E132)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H132)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C132)),NOT(ISNUMBER($D132))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C132),ISNUMBER($D132),MOD($D132-$C132,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J132&gt;0,OR($P132&gt;=Turno_Min,$Q132&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J132&gt;0,$K132&gt;0,COUNTIF(Mapa_Chave,$B132&amp;"#"&amp;$A132&amp;"#"&amp;($K132+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B132&amp;"#"&amp;$A132&amp;"#"&amp;($K132+1),Mapa_Chave,0))-$Q132&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J132&gt;0,SUMPRODUCT((Mapa_Sala=$B132)*(Mapa_Data=$A132)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q132)*(Mapa_RelFim&gt;$P132))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I132),$I132&gt;0,COUNTIF(Esp_Nome,$E132)&gt;0,$I132&gt;3*INDEX(Esp_Dur,MATCH($E132,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B132="","",IF(COUNTIF(Postos_Cod,$B132)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B132)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B132,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E132)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H132)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C132)),NOT(ISNUMBER($D132))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C132),ISNUMBER($D132),MOD($D132-$C132,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J132&gt;0,OR($P132&gt;=Turno_Min,$Q132&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J132&gt;0,SUMPRODUCT((Mapa_Sala=$B132)*(Mapa_Data=$A132)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q132)*(Mapa_RelFim&gt;$P132))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I132),$I132&gt;0,COUNTIF(Esp_Nome,$E132)&gt;0,$I132&gt;3*INDEX(Esp_Dur,MATCH($E132,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P132" s="12">
@@ -11424,7 +11442,7 @@
         <v/>
       </c>
       <c r="O133" s="24">
-        <f>IF($B133="","",IF(COUNTIF(Postos_Cod,$B133)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B133)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B133,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E133)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H133)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C133)),NOT(ISNUMBER($D133))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C133),ISNUMBER($D133),MOD($D133-$C133,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J133&gt;0,OR($P133&gt;=Turno_Min,$Q133&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J133&gt;0,$K133&gt;0,COUNTIF(Mapa_Chave,$B133&amp;"#"&amp;$A133&amp;"#"&amp;($K133+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B133&amp;"#"&amp;$A133&amp;"#"&amp;($K133+1),Mapa_Chave,0))-$Q133&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J133&gt;0,SUMPRODUCT((Mapa_Sala=$B133)*(Mapa_Data=$A133)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q133)*(Mapa_RelFim&gt;$P133))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I133),$I133&gt;0,COUNTIF(Esp_Nome,$E133)&gt;0,$I133&gt;3*INDEX(Esp_Dur,MATCH($E133,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B133="","",IF(COUNTIF(Postos_Cod,$B133)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B133)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B133,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E133)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H133)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C133)),NOT(ISNUMBER($D133))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C133),ISNUMBER($D133),MOD($D133-$C133,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J133&gt;0,OR($P133&gt;=Turno_Min,$Q133&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J133&gt;0,SUMPRODUCT((Mapa_Sala=$B133)*(Mapa_Data=$A133)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q133)*(Mapa_RelFim&gt;$P133))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I133),$I133&gt;0,COUNTIF(Esp_Nome,$E133)&gt;0,$I133&gt;3*INDEX(Esp_Dur,MATCH($E133,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P133" s="12">
@@ -11482,7 +11500,7 @@
         <v/>
       </c>
       <c r="O134" s="24">
-        <f>IF($B134="","",IF(COUNTIF(Postos_Cod,$B134)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B134)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B134,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E134)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H134)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C134)),NOT(ISNUMBER($D134))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C134),ISNUMBER($D134),MOD($D134-$C134,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J134&gt;0,OR($P134&gt;=Turno_Min,$Q134&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J134&gt;0,$K134&gt;0,COUNTIF(Mapa_Chave,$B134&amp;"#"&amp;$A134&amp;"#"&amp;($K134+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B134&amp;"#"&amp;$A134&amp;"#"&amp;($K134+1),Mapa_Chave,0))-$Q134&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J134&gt;0,SUMPRODUCT((Mapa_Sala=$B134)*(Mapa_Data=$A134)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q134)*(Mapa_RelFim&gt;$P134))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I134),$I134&gt;0,COUNTIF(Esp_Nome,$E134)&gt;0,$I134&gt;3*INDEX(Esp_Dur,MATCH($E134,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B134="","",IF(COUNTIF(Postos_Cod,$B134)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B134)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B134,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E134)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H134)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C134)),NOT(ISNUMBER($D134))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C134),ISNUMBER($D134),MOD($D134-$C134,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J134&gt;0,OR($P134&gt;=Turno_Min,$Q134&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J134&gt;0,SUMPRODUCT((Mapa_Sala=$B134)*(Mapa_Data=$A134)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q134)*(Mapa_RelFim&gt;$P134))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I134),$I134&gt;0,COUNTIF(Esp_Nome,$E134)&gt;0,$I134&gt;3*INDEX(Esp_Dur,MATCH($E134,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P134" s="12">
@@ -11540,7 +11558,7 @@
         <v/>
       </c>
       <c r="O135" s="24">
-        <f>IF($B135="","",IF(COUNTIF(Postos_Cod,$B135)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B135)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B135,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E135)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H135)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C135)),NOT(ISNUMBER($D135))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C135),ISNUMBER($D135),MOD($D135-$C135,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J135&gt;0,OR($P135&gt;=Turno_Min,$Q135&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J135&gt;0,$K135&gt;0,COUNTIF(Mapa_Chave,$B135&amp;"#"&amp;$A135&amp;"#"&amp;($K135+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B135&amp;"#"&amp;$A135&amp;"#"&amp;($K135+1),Mapa_Chave,0))-$Q135&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J135&gt;0,SUMPRODUCT((Mapa_Sala=$B135)*(Mapa_Data=$A135)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q135)*(Mapa_RelFim&gt;$P135))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I135),$I135&gt;0,COUNTIF(Esp_Nome,$E135)&gt;0,$I135&gt;3*INDEX(Esp_Dur,MATCH($E135,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B135="","",IF(COUNTIF(Postos_Cod,$B135)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B135)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B135,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E135)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H135)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C135)),NOT(ISNUMBER($D135))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C135),ISNUMBER($D135),MOD($D135-$C135,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J135&gt;0,OR($P135&gt;=Turno_Min,$Q135&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J135&gt;0,SUMPRODUCT((Mapa_Sala=$B135)*(Mapa_Data=$A135)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q135)*(Mapa_RelFim&gt;$P135))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I135),$I135&gt;0,COUNTIF(Esp_Nome,$E135)&gt;0,$I135&gt;3*INDEX(Esp_Dur,MATCH($E135,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P135" s="12">
@@ -11598,7 +11616,7 @@
         <v/>
       </c>
       <c r="O136" s="24">
-        <f>IF($B136="","",IF(COUNTIF(Postos_Cod,$B136)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B136)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B136,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E136)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H136)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C136)),NOT(ISNUMBER($D136))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C136),ISNUMBER($D136),MOD($D136-$C136,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J136&gt;0,OR($P136&gt;=Turno_Min,$Q136&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J136&gt;0,$K136&gt;0,COUNTIF(Mapa_Chave,$B136&amp;"#"&amp;$A136&amp;"#"&amp;($K136+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B136&amp;"#"&amp;$A136&amp;"#"&amp;($K136+1),Mapa_Chave,0))-$Q136&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J136&gt;0,SUMPRODUCT((Mapa_Sala=$B136)*(Mapa_Data=$A136)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q136)*(Mapa_RelFim&gt;$P136))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I136),$I136&gt;0,COUNTIF(Esp_Nome,$E136)&gt;0,$I136&gt;3*INDEX(Esp_Dur,MATCH($E136,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B136="","",IF(COUNTIF(Postos_Cod,$B136)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B136)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B136,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E136)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H136)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C136)),NOT(ISNUMBER($D136))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C136),ISNUMBER($D136),MOD($D136-$C136,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J136&gt;0,OR($P136&gt;=Turno_Min,$Q136&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J136&gt;0,SUMPRODUCT((Mapa_Sala=$B136)*(Mapa_Data=$A136)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q136)*(Mapa_RelFim&gt;$P136))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I136),$I136&gt;0,COUNTIF(Esp_Nome,$E136)&gt;0,$I136&gt;3*INDEX(Esp_Dur,MATCH($E136,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P136" s="12">
@@ -11656,7 +11674,7 @@
         <v/>
       </c>
       <c r="O137" s="24">
-        <f>IF($B137="","",IF(COUNTIF(Postos_Cod,$B137)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B137)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B137,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E137)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H137)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C137)),NOT(ISNUMBER($D137))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C137),ISNUMBER($D137),MOD($D137-$C137,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J137&gt;0,OR($P137&gt;=Turno_Min,$Q137&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J137&gt;0,$K137&gt;0,COUNTIF(Mapa_Chave,$B137&amp;"#"&amp;$A137&amp;"#"&amp;($K137+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B137&amp;"#"&amp;$A137&amp;"#"&amp;($K137+1),Mapa_Chave,0))-$Q137&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J137&gt;0,SUMPRODUCT((Mapa_Sala=$B137)*(Mapa_Data=$A137)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q137)*(Mapa_RelFim&gt;$P137))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I137),$I137&gt;0,COUNTIF(Esp_Nome,$E137)&gt;0,$I137&gt;3*INDEX(Esp_Dur,MATCH($E137,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B137="","",IF(COUNTIF(Postos_Cod,$B137)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B137)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B137,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E137)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H137)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C137)),NOT(ISNUMBER($D137))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C137),ISNUMBER($D137),MOD($D137-$C137,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J137&gt;0,OR($P137&gt;=Turno_Min,$Q137&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J137&gt;0,SUMPRODUCT((Mapa_Sala=$B137)*(Mapa_Data=$A137)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q137)*(Mapa_RelFim&gt;$P137))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I137),$I137&gt;0,COUNTIF(Esp_Nome,$E137)&gt;0,$I137&gt;3*INDEX(Esp_Dur,MATCH($E137,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P137" s="12">
@@ -11714,7 +11732,7 @@
         <v/>
       </c>
       <c r="O138" s="24">
-        <f>IF($B138="","",IF(COUNTIF(Postos_Cod,$B138)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B138)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B138,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E138)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H138)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C138)),NOT(ISNUMBER($D138))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C138),ISNUMBER($D138),MOD($D138-$C138,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J138&gt;0,OR($P138&gt;=Turno_Min,$Q138&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J138&gt;0,$K138&gt;0,COUNTIF(Mapa_Chave,$B138&amp;"#"&amp;$A138&amp;"#"&amp;($K138+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B138&amp;"#"&amp;$A138&amp;"#"&amp;($K138+1),Mapa_Chave,0))-$Q138&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J138&gt;0,SUMPRODUCT((Mapa_Sala=$B138)*(Mapa_Data=$A138)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q138)*(Mapa_RelFim&gt;$P138))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I138),$I138&gt;0,COUNTIF(Esp_Nome,$E138)&gt;0,$I138&gt;3*INDEX(Esp_Dur,MATCH($E138,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B138="","",IF(COUNTIF(Postos_Cod,$B138)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B138)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B138,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E138)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H138)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C138)),NOT(ISNUMBER($D138))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C138),ISNUMBER($D138),MOD($D138-$C138,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J138&gt;0,OR($P138&gt;=Turno_Min,$Q138&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J138&gt;0,SUMPRODUCT((Mapa_Sala=$B138)*(Mapa_Data=$A138)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q138)*(Mapa_RelFim&gt;$P138))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I138),$I138&gt;0,COUNTIF(Esp_Nome,$E138)&gt;0,$I138&gt;3*INDEX(Esp_Dur,MATCH($E138,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P138" s="12">
@@ -11772,7 +11790,7 @@
         <v/>
       </c>
       <c r="O139" s="24">
-        <f>IF($B139="","",IF(COUNTIF(Postos_Cod,$B139)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B139)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B139,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E139)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H139)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C139)),NOT(ISNUMBER($D139))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C139),ISNUMBER($D139),MOD($D139-$C139,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J139&gt;0,OR($P139&gt;=Turno_Min,$Q139&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J139&gt;0,$K139&gt;0,COUNTIF(Mapa_Chave,$B139&amp;"#"&amp;$A139&amp;"#"&amp;($K139+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B139&amp;"#"&amp;$A139&amp;"#"&amp;($K139+1),Mapa_Chave,0))-$Q139&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J139&gt;0,SUMPRODUCT((Mapa_Sala=$B139)*(Mapa_Data=$A139)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q139)*(Mapa_RelFim&gt;$P139))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I139),$I139&gt;0,COUNTIF(Esp_Nome,$E139)&gt;0,$I139&gt;3*INDEX(Esp_Dur,MATCH($E139,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B139="","",IF(COUNTIF(Postos_Cod,$B139)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B139)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B139,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E139)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H139)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C139)),NOT(ISNUMBER($D139))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C139),ISNUMBER($D139),MOD($D139-$C139,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J139&gt;0,OR($P139&gt;=Turno_Min,$Q139&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J139&gt;0,SUMPRODUCT((Mapa_Sala=$B139)*(Mapa_Data=$A139)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q139)*(Mapa_RelFim&gt;$P139))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I139),$I139&gt;0,COUNTIF(Esp_Nome,$E139)&gt;0,$I139&gt;3*INDEX(Esp_Dur,MATCH($E139,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P139" s="12">
@@ -11830,7 +11848,7 @@
         <v/>
       </c>
       <c r="O140" s="24">
-        <f>IF($B140="","",IF(COUNTIF(Postos_Cod,$B140)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B140)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B140,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E140)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H140)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C140)),NOT(ISNUMBER($D140))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C140),ISNUMBER($D140),MOD($D140-$C140,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J140&gt;0,OR($P140&gt;=Turno_Min,$Q140&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J140&gt;0,$K140&gt;0,COUNTIF(Mapa_Chave,$B140&amp;"#"&amp;$A140&amp;"#"&amp;($K140+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B140&amp;"#"&amp;$A140&amp;"#"&amp;($K140+1),Mapa_Chave,0))-$Q140&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J140&gt;0,SUMPRODUCT((Mapa_Sala=$B140)*(Mapa_Data=$A140)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q140)*(Mapa_RelFim&gt;$P140))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I140),$I140&gt;0,COUNTIF(Esp_Nome,$E140)&gt;0,$I140&gt;3*INDEX(Esp_Dur,MATCH($E140,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B140="","",IF(COUNTIF(Postos_Cod,$B140)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B140)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B140,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E140)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H140)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C140)),NOT(ISNUMBER($D140))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C140),ISNUMBER($D140),MOD($D140-$C140,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J140&gt;0,OR($P140&gt;=Turno_Min,$Q140&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J140&gt;0,SUMPRODUCT((Mapa_Sala=$B140)*(Mapa_Data=$A140)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q140)*(Mapa_RelFim&gt;$P140))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I140),$I140&gt;0,COUNTIF(Esp_Nome,$E140)&gt;0,$I140&gt;3*INDEX(Esp_Dur,MATCH($E140,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P140" s="12">
@@ -11888,7 +11906,7 @@
         <v/>
       </c>
       <c r="O141" s="24">
-        <f>IF($B141="","",IF(COUNTIF(Postos_Cod,$B141)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B141)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B141,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E141)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H141)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C141)),NOT(ISNUMBER($D141))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C141),ISNUMBER($D141),MOD($D141-$C141,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J141&gt;0,OR($P141&gt;=Turno_Min,$Q141&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J141&gt;0,$K141&gt;0,COUNTIF(Mapa_Chave,$B141&amp;"#"&amp;$A141&amp;"#"&amp;($K141+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B141&amp;"#"&amp;$A141&amp;"#"&amp;($K141+1),Mapa_Chave,0))-$Q141&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J141&gt;0,SUMPRODUCT((Mapa_Sala=$B141)*(Mapa_Data=$A141)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q141)*(Mapa_RelFim&gt;$P141))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I141),$I141&gt;0,COUNTIF(Esp_Nome,$E141)&gt;0,$I141&gt;3*INDEX(Esp_Dur,MATCH($E141,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B141="","",IF(COUNTIF(Postos_Cod,$B141)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B141)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B141,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E141)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H141)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C141)),NOT(ISNUMBER($D141))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C141),ISNUMBER($D141),MOD($D141-$C141,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J141&gt;0,OR($P141&gt;=Turno_Min,$Q141&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J141&gt;0,SUMPRODUCT((Mapa_Sala=$B141)*(Mapa_Data=$A141)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q141)*(Mapa_RelFim&gt;$P141))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I141),$I141&gt;0,COUNTIF(Esp_Nome,$E141)&gt;0,$I141&gt;3*INDEX(Esp_Dur,MATCH($E141,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P141" s="12">
@@ -11946,7 +11964,7 @@
         <v/>
       </c>
       <c r="O142" s="24">
-        <f>IF($B142="","",IF(COUNTIF(Postos_Cod,$B142)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B142)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B142,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E142)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H142)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C142)),NOT(ISNUMBER($D142))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C142),ISNUMBER($D142),MOD($D142-$C142,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J142&gt;0,OR($P142&gt;=Turno_Min,$Q142&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J142&gt;0,$K142&gt;0,COUNTIF(Mapa_Chave,$B142&amp;"#"&amp;$A142&amp;"#"&amp;($K142+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B142&amp;"#"&amp;$A142&amp;"#"&amp;($K142+1),Mapa_Chave,0))-$Q142&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J142&gt;0,SUMPRODUCT((Mapa_Sala=$B142)*(Mapa_Data=$A142)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q142)*(Mapa_RelFim&gt;$P142))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I142),$I142&gt;0,COUNTIF(Esp_Nome,$E142)&gt;0,$I142&gt;3*INDEX(Esp_Dur,MATCH($E142,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B142="","",IF(COUNTIF(Postos_Cod,$B142)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B142)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B142,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E142)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H142)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C142)),NOT(ISNUMBER($D142))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C142),ISNUMBER($D142),MOD($D142-$C142,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J142&gt;0,OR($P142&gt;=Turno_Min,$Q142&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J142&gt;0,SUMPRODUCT((Mapa_Sala=$B142)*(Mapa_Data=$A142)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q142)*(Mapa_RelFim&gt;$P142))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I142),$I142&gt;0,COUNTIF(Esp_Nome,$E142)&gt;0,$I142&gt;3*INDEX(Esp_Dur,MATCH($E142,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P142" s="12">
@@ -12004,7 +12022,7 @@
         <v/>
       </c>
       <c r="O143" s="24">
-        <f>IF($B143="","",IF(COUNTIF(Postos_Cod,$B143)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B143)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B143,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E143)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H143)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C143)),NOT(ISNUMBER($D143))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C143),ISNUMBER($D143),MOD($D143-$C143,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J143&gt;0,OR($P143&gt;=Turno_Min,$Q143&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J143&gt;0,$K143&gt;0,COUNTIF(Mapa_Chave,$B143&amp;"#"&amp;$A143&amp;"#"&amp;($K143+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B143&amp;"#"&amp;$A143&amp;"#"&amp;($K143+1),Mapa_Chave,0))-$Q143&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J143&gt;0,SUMPRODUCT((Mapa_Sala=$B143)*(Mapa_Data=$A143)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q143)*(Mapa_RelFim&gt;$P143))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I143),$I143&gt;0,COUNTIF(Esp_Nome,$E143)&gt;0,$I143&gt;3*INDEX(Esp_Dur,MATCH($E143,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B143="","",IF(COUNTIF(Postos_Cod,$B143)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B143)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B143,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E143)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H143)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C143)),NOT(ISNUMBER($D143))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C143),ISNUMBER($D143),MOD($D143-$C143,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J143&gt;0,OR($P143&gt;=Turno_Min,$Q143&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J143&gt;0,SUMPRODUCT((Mapa_Sala=$B143)*(Mapa_Data=$A143)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q143)*(Mapa_RelFim&gt;$P143))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I143),$I143&gt;0,COUNTIF(Esp_Nome,$E143)&gt;0,$I143&gt;3*INDEX(Esp_Dur,MATCH($E143,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P143" s="12">
@@ -12062,7 +12080,7 @@
         <v/>
       </c>
       <c r="O144" s="24">
-        <f>IF($B144="","",IF(COUNTIF(Postos_Cod,$B144)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B144)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B144,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E144)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H144)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C144)),NOT(ISNUMBER($D144))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C144),ISNUMBER($D144),MOD($D144-$C144,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J144&gt;0,OR($P144&gt;=Turno_Min,$Q144&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J144&gt;0,$K144&gt;0,COUNTIF(Mapa_Chave,$B144&amp;"#"&amp;$A144&amp;"#"&amp;($K144+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B144&amp;"#"&amp;$A144&amp;"#"&amp;($K144+1),Mapa_Chave,0))-$Q144&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J144&gt;0,SUMPRODUCT((Mapa_Sala=$B144)*(Mapa_Data=$A144)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q144)*(Mapa_RelFim&gt;$P144))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I144),$I144&gt;0,COUNTIF(Esp_Nome,$E144)&gt;0,$I144&gt;3*INDEX(Esp_Dur,MATCH($E144,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B144="","",IF(COUNTIF(Postos_Cod,$B144)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B144)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B144,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E144)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H144)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C144)),NOT(ISNUMBER($D144))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C144),ISNUMBER($D144),MOD($D144-$C144,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J144&gt;0,OR($P144&gt;=Turno_Min,$Q144&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J144&gt;0,SUMPRODUCT((Mapa_Sala=$B144)*(Mapa_Data=$A144)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q144)*(Mapa_RelFim&gt;$P144))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I144),$I144&gt;0,COUNTIF(Esp_Nome,$E144)&gt;0,$I144&gt;3*INDEX(Esp_Dur,MATCH($E144,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P144" s="12">
@@ -12120,7 +12138,7 @@
         <v/>
       </c>
       <c r="O145" s="24">
-        <f>IF($B145="","",IF(COUNTIF(Postos_Cod,$B145)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B145)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B145,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E145)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H145)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C145)),NOT(ISNUMBER($D145))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C145),ISNUMBER($D145),MOD($D145-$C145,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J145&gt;0,OR($P145&gt;=Turno_Min,$Q145&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J145&gt;0,$K145&gt;0,COUNTIF(Mapa_Chave,$B145&amp;"#"&amp;$A145&amp;"#"&amp;($K145+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B145&amp;"#"&amp;$A145&amp;"#"&amp;($K145+1),Mapa_Chave,0))-$Q145&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J145&gt;0,SUMPRODUCT((Mapa_Sala=$B145)*(Mapa_Data=$A145)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q145)*(Mapa_RelFim&gt;$P145))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I145),$I145&gt;0,COUNTIF(Esp_Nome,$E145)&gt;0,$I145&gt;3*INDEX(Esp_Dur,MATCH($E145,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B145="","",IF(COUNTIF(Postos_Cod,$B145)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B145)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B145,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E145)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H145)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C145)),NOT(ISNUMBER($D145))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C145),ISNUMBER($D145),MOD($D145-$C145,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J145&gt;0,OR($P145&gt;=Turno_Min,$Q145&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J145&gt;0,SUMPRODUCT((Mapa_Sala=$B145)*(Mapa_Data=$A145)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q145)*(Mapa_RelFim&gt;$P145))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I145),$I145&gt;0,COUNTIF(Esp_Nome,$E145)&gt;0,$I145&gt;3*INDEX(Esp_Dur,MATCH($E145,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P145" s="12">
@@ -12178,7 +12196,7 @@
         <v/>
       </c>
       <c r="O146" s="24">
-        <f>IF($B146="","",IF(COUNTIF(Postos_Cod,$B146)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B146)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B146,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E146)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H146)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C146)),NOT(ISNUMBER($D146))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C146),ISNUMBER($D146),MOD($D146-$C146,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J146&gt;0,OR($P146&gt;=Turno_Min,$Q146&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J146&gt;0,$K146&gt;0,COUNTIF(Mapa_Chave,$B146&amp;"#"&amp;$A146&amp;"#"&amp;($K146+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B146&amp;"#"&amp;$A146&amp;"#"&amp;($K146+1),Mapa_Chave,0))-$Q146&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J146&gt;0,SUMPRODUCT((Mapa_Sala=$B146)*(Mapa_Data=$A146)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q146)*(Mapa_RelFim&gt;$P146))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I146),$I146&gt;0,COUNTIF(Esp_Nome,$E146)&gt;0,$I146&gt;3*INDEX(Esp_Dur,MATCH($E146,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B146="","",IF(COUNTIF(Postos_Cod,$B146)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B146)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B146,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E146)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H146)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C146)),NOT(ISNUMBER($D146))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C146),ISNUMBER($D146),MOD($D146-$C146,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J146&gt;0,OR($P146&gt;=Turno_Min,$Q146&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J146&gt;0,SUMPRODUCT((Mapa_Sala=$B146)*(Mapa_Data=$A146)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q146)*(Mapa_RelFim&gt;$P146))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I146),$I146&gt;0,COUNTIF(Esp_Nome,$E146)&gt;0,$I146&gt;3*INDEX(Esp_Dur,MATCH($E146,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P146" s="12">
@@ -12236,7 +12254,7 @@
         <v/>
       </c>
       <c r="O147" s="24">
-        <f>IF($B147="","",IF(COUNTIF(Postos_Cod,$B147)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B147)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B147,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E147)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H147)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C147)),NOT(ISNUMBER($D147))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C147),ISNUMBER($D147),MOD($D147-$C147,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J147&gt;0,OR($P147&gt;=Turno_Min,$Q147&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J147&gt;0,$K147&gt;0,COUNTIF(Mapa_Chave,$B147&amp;"#"&amp;$A147&amp;"#"&amp;($K147+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B147&amp;"#"&amp;$A147&amp;"#"&amp;($K147+1),Mapa_Chave,0))-$Q147&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J147&gt;0,SUMPRODUCT((Mapa_Sala=$B147)*(Mapa_Data=$A147)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q147)*(Mapa_RelFim&gt;$P147))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I147),$I147&gt;0,COUNTIF(Esp_Nome,$E147)&gt;0,$I147&gt;3*INDEX(Esp_Dur,MATCH($E147,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B147="","",IF(COUNTIF(Postos_Cod,$B147)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B147)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B147,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E147)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H147)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C147)),NOT(ISNUMBER($D147))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C147),ISNUMBER($D147),MOD($D147-$C147,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J147&gt;0,OR($P147&gt;=Turno_Min,$Q147&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J147&gt;0,SUMPRODUCT((Mapa_Sala=$B147)*(Mapa_Data=$A147)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q147)*(Mapa_RelFim&gt;$P147))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I147),$I147&gt;0,COUNTIF(Esp_Nome,$E147)&gt;0,$I147&gt;3*INDEX(Esp_Dur,MATCH($E147,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P147" s="12">
@@ -12294,7 +12312,7 @@
         <v/>
       </c>
       <c r="O148" s="24">
-        <f>IF($B148="","",IF(COUNTIF(Postos_Cod,$B148)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B148)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B148,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E148)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H148)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C148)),NOT(ISNUMBER($D148))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C148),ISNUMBER($D148),MOD($D148-$C148,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J148&gt;0,OR($P148&gt;=Turno_Min,$Q148&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J148&gt;0,$K148&gt;0,COUNTIF(Mapa_Chave,$B148&amp;"#"&amp;$A148&amp;"#"&amp;($K148+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B148&amp;"#"&amp;$A148&amp;"#"&amp;($K148+1),Mapa_Chave,0))-$Q148&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J148&gt;0,SUMPRODUCT((Mapa_Sala=$B148)*(Mapa_Data=$A148)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q148)*(Mapa_RelFim&gt;$P148))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I148),$I148&gt;0,COUNTIF(Esp_Nome,$E148)&gt;0,$I148&gt;3*INDEX(Esp_Dur,MATCH($E148,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B148="","",IF(COUNTIF(Postos_Cod,$B148)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B148)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B148,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E148)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H148)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C148)),NOT(ISNUMBER($D148))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C148),ISNUMBER($D148),MOD($D148-$C148,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J148&gt;0,OR($P148&gt;=Turno_Min,$Q148&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J148&gt;0,SUMPRODUCT((Mapa_Sala=$B148)*(Mapa_Data=$A148)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q148)*(Mapa_RelFim&gt;$P148))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I148),$I148&gt;0,COUNTIF(Esp_Nome,$E148)&gt;0,$I148&gt;3*INDEX(Esp_Dur,MATCH($E148,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P148" s="12">
@@ -12352,7 +12370,7 @@
         <v/>
       </c>
       <c r="O149" s="24">
-        <f>IF($B149="","",IF(COUNTIF(Postos_Cod,$B149)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B149)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B149,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E149)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H149)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C149)),NOT(ISNUMBER($D149))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C149),ISNUMBER($D149),MOD($D149-$C149,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J149&gt;0,OR($P149&gt;=Turno_Min,$Q149&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J149&gt;0,$K149&gt;0,COUNTIF(Mapa_Chave,$B149&amp;"#"&amp;$A149&amp;"#"&amp;($K149+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B149&amp;"#"&amp;$A149&amp;"#"&amp;($K149+1),Mapa_Chave,0))-$Q149&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J149&gt;0,SUMPRODUCT((Mapa_Sala=$B149)*(Mapa_Data=$A149)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q149)*(Mapa_RelFim&gt;$P149))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I149),$I149&gt;0,COUNTIF(Esp_Nome,$E149)&gt;0,$I149&gt;3*INDEX(Esp_Dur,MATCH($E149,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B149="","",IF(COUNTIF(Postos_Cod,$B149)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B149)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B149,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E149)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H149)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C149)),NOT(ISNUMBER($D149))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C149),ISNUMBER($D149),MOD($D149-$C149,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J149&gt;0,OR($P149&gt;=Turno_Min,$Q149&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J149&gt;0,SUMPRODUCT((Mapa_Sala=$B149)*(Mapa_Data=$A149)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q149)*(Mapa_RelFim&gt;$P149))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I149),$I149&gt;0,COUNTIF(Esp_Nome,$E149)&gt;0,$I149&gt;3*INDEX(Esp_Dur,MATCH($E149,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P149" s="12">
@@ -12410,7 +12428,7 @@
         <v/>
       </c>
       <c r="O150" s="24">
-        <f>IF($B150="","",IF(COUNTIF(Postos_Cod,$B150)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B150)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B150,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E150)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H150)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C150)),NOT(ISNUMBER($D150))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C150),ISNUMBER($D150),MOD($D150-$C150,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J150&gt;0,OR($P150&gt;=Turno_Min,$Q150&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J150&gt;0,$K150&gt;0,COUNTIF(Mapa_Chave,$B150&amp;"#"&amp;$A150&amp;"#"&amp;($K150+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B150&amp;"#"&amp;$A150&amp;"#"&amp;($K150+1),Mapa_Chave,0))-$Q150&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J150&gt;0,SUMPRODUCT((Mapa_Sala=$B150)*(Mapa_Data=$A150)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q150)*(Mapa_RelFim&gt;$P150))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I150),$I150&gt;0,COUNTIF(Esp_Nome,$E150)&gt;0,$I150&gt;3*INDEX(Esp_Dur,MATCH($E150,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B150="","",IF(COUNTIF(Postos_Cod,$B150)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B150)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B150,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E150)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H150)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C150)),NOT(ISNUMBER($D150))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C150),ISNUMBER($D150),MOD($D150-$C150,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J150&gt;0,OR($P150&gt;=Turno_Min,$Q150&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J150&gt;0,SUMPRODUCT((Mapa_Sala=$B150)*(Mapa_Data=$A150)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q150)*(Mapa_RelFim&gt;$P150))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I150),$I150&gt;0,COUNTIF(Esp_Nome,$E150)&gt;0,$I150&gt;3*INDEX(Esp_Dur,MATCH($E150,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P150" s="12">
@@ -12468,7 +12486,7 @@
         <v/>
       </c>
       <c r="O151" s="24">
-        <f>IF($B151="","",IF(COUNTIF(Postos_Cod,$B151)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B151)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B151,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E151)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H151)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C151)),NOT(ISNUMBER($D151))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C151),ISNUMBER($D151),MOD($D151-$C151,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J151&gt;0,OR($P151&gt;=Turno_Min,$Q151&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J151&gt;0,$K151&gt;0,COUNTIF(Mapa_Chave,$B151&amp;"#"&amp;$A151&amp;"#"&amp;($K151+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B151&amp;"#"&amp;$A151&amp;"#"&amp;($K151+1),Mapa_Chave,0))-$Q151&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J151&gt;0,SUMPRODUCT((Mapa_Sala=$B151)*(Mapa_Data=$A151)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q151)*(Mapa_RelFim&gt;$P151))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I151),$I151&gt;0,COUNTIF(Esp_Nome,$E151)&gt;0,$I151&gt;3*INDEX(Esp_Dur,MATCH($E151,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B151="","",IF(COUNTIF(Postos_Cod,$B151)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B151)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B151,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E151)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H151)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C151)),NOT(ISNUMBER($D151))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C151),ISNUMBER($D151),MOD($D151-$C151,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J151&gt;0,OR($P151&gt;=Turno_Min,$Q151&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J151&gt;0,SUMPRODUCT((Mapa_Sala=$B151)*(Mapa_Data=$A151)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q151)*(Mapa_RelFim&gt;$P151))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I151),$I151&gt;0,COUNTIF(Esp_Nome,$E151)&gt;0,$I151&gt;3*INDEX(Esp_Dur,MATCH($E151,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P151" s="12">
@@ -12526,7 +12544,7 @@
         <v/>
       </c>
       <c r="O152" s="24">
-        <f>IF($B152="","",IF(COUNTIF(Postos_Cod,$B152)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B152)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B152,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E152)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H152)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C152)),NOT(ISNUMBER($D152))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C152),ISNUMBER($D152),MOD($D152-$C152,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J152&gt;0,OR($P152&gt;=Turno_Min,$Q152&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J152&gt;0,$K152&gt;0,COUNTIF(Mapa_Chave,$B152&amp;"#"&amp;$A152&amp;"#"&amp;($K152+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B152&amp;"#"&amp;$A152&amp;"#"&amp;($K152+1),Mapa_Chave,0))-$Q152&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J152&gt;0,SUMPRODUCT((Mapa_Sala=$B152)*(Mapa_Data=$A152)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q152)*(Mapa_RelFim&gt;$P152))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I152),$I152&gt;0,COUNTIF(Esp_Nome,$E152)&gt;0,$I152&gt;3*INDEX(Esp_Dur,MATCH($E152,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B152="","",IF(COUNTIF(Postos_Cod,$B152)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B152)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B152,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E152)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H152)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C152)),NOT(ISNUMBER($D152))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C152),ISNUMBER($D152),MOD($D152-$C152,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J152&gt;0,OR($P152&gt;=Turno_Min,$Q152&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J152&gt;0,SUMPRODUCT((Mapa_Sala=$B152)*(Mapa_Data=$A152)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q152)*(Mapa_RelFim&gt;$P152))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I152),$I152&gt;0,COUNTIF(Esp_Nome,$E152)&gt;0,$I152&gt;3*INDEX(Esp_Dur,MATCH($E152,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P152" s="12">
@@ -12584,7 +12602,7 @@
         <v/>
       </c>
       <c r="O153" s="24">
-        <f>IF($B153="","",IF(COUNTIF(Postos_Cod,$B153)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B153)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B153,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E153)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H153)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C153)),NOT(ISNUMBER($D153))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C153),ISNUMBER($D153),MOD($D153-$C153,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J153&gt;0,OR($P153&gt;=Turno_Min,$Q153&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J153&gt;0,$K153&gt;0,COUNTIF(Mapa_Chave,$B153&amp;"#"&amp;$A153&amp;"#"&amp;($K153+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B153&amp;"#"&amp;$A153&amp;"#"&amp;($K153+1),Mapa_Chave,0))-$Q153&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J153&gt;0,SUMPRODUCT((Mapa_Sala=$B153)*(Mapa_Data=$A153)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q153)*(Mapa_RelFim&gt;$P153))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I153),$I153&gt;0,COUNTIF(Esp_Nome,$E153)&gt;0,$I153&gt;3*INDEX(Esp_Dur,MATCH($E153,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B153="","",IF(COUNTIF(Postos_Cod,$B153)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B153)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B153,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E153)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H153)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C153)),NOT(ISNUMBER($D153))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C153),ISNUMBER($D153),MOD($D153-$C153,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J153&gt;0,OR($P153&gt;=Turno_Min,$Q153&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J153&gt;0,SUMPRODUCT((Mapa_Sala=$B153)*(Mapa_Data=$A153)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q153)*(Mapa_RelFim&gt;$P153))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I153),$I153&gt;0,COUNTIF(Esp_Nome,$E153)&gt;0,$I153&gt;3*INDEX(Esp_Dur,MATCH($E153,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P153" s="12">
@@ -12642,7 +12660,7 @@
         <v/>
       </c>
       <c r="O154" s="24">
-        <f>IF($B154="","",IF(COUNTIF(Postos_Cod,$B154)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B154)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B154,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E154)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H154)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C154)),NOT(ISNUMBER($D154))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C154),ISNUMBER($D154),MOD($D154-$C154,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J154&gt;0,OR($P154&gt;=Turno_Min,$Q154&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J154&gt;0,$K154&gt;0,COUNTIF(Mapa_Chave,$B154&amp;"#"&amp;$A154&amp;"#"&amp;($K154+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B154&amp;"#"&amp;$A154&amp;"#"&amp;($K154+1),Mapa_Chave,0))-$Q154&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J154&gt;0,SUMPRODUCT((Mapa_Sala=$B154)*(Mapa_Data=$A154)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q154)*(Mapa_RelFim&gt;$P154))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I154),$I154&gt;0,COUNTIF(Esp_Nome,$E154)&gt;0,$I154&gt;3*INDEX(Esp_Dur,MATCH($E154,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B154="","",IF(COUNTIF(Postos_Cod,$B154)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B154)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B154,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E154)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H154)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C154)),NOT(ISNUMBER($D154))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C154),ISNUMBER($D154),MOD($D154-$C154,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J154&gt;0,OR($P154&gt;=Turno_Min,$Q154&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J154&gt;0,SUMPRODUCT((Mapa_Sala=$B154)*(Mapa_Data=$A154)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q154)*(Mapa_RelFim&gt;$P154))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I154),$I154&gt;0,COUNTIF(Esp_Nome,$E154)&gt;0,$I154&gt;3*INDEX(Esp_Dur,MATCH($E154,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P154" s="12">
@@ -12700,7 +12718,7 @@
         <v/>
       </c>
       <c r="O155" s="24">
-        <f>IF($B155="","",IF(COUNTIF(Postos_Cod,$B155)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B155)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B155,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E155)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H155)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C155)),NOT(ISNUMBER($D155))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C155),ISNUMBER($D155),MOD($D155-$C155,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J155&gt;0,OR($P155&gt;=Turno_Min,$Q155&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J155&gt;0,$K155&gt;0,COUNTIF(Mapa_Chave,$B155&amp;"#"&amp;$A155&amp;"#"&amp;($K155+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B155&amp;"#"&amp;$A155&amp;"#"&amp;($K155+1),Mapa_Chave,0))-$Q155&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J155&gt;0,SUMPRODUCT((Mapa_Sala=$B155)*(Mapa_Data=$A155)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q155)*(Mapa_RelFim&gt;$P155))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I155),$I155&gt;0,COUNTIF(Esp_Nome,$E155)&gt;0,$I155&gt;3*INDEX(Esp_Dur,MATCH($E155,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B155="","",IF(COUNTIF(Postos_Cod,$B155)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B155)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B155,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E155)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H155)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C155)),NOT(ISNUMBER($D155))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C155),ISNUMBER($D155),MOD($D155-$C155,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J155&gt;0,OR($P155&gt;=Turno_Min,$Q155&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J155&gt;0,SUMPRODUCT((Mapa_Sala=$B155)*(Mapa_Data=$A155)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q155)*(Mapa_RelFim&gt;$P155))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I155),$I155&gt;0,COUNTIF(Esp_Nome,$E155)&gt;0,$I155&gt;3*INDEX(Esp_Dur,MATCH($E155,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P155" s="12">
@@ -12758,7 +12776,7 @@
         <v/>
       </c>
       <c r="O156" s="24">
-        <f>IF($B156="","",IF(COUNTIF(Postos_Cod,$B156)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B156)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B156,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E156)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H156)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C156)),NOT(ISNUMBER($D156))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C156),ISNUMBER($D156),MOD($D156-$C156,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J156&gt;0,OR($P156&gt;=Turno_Min,$Q156&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J156&gt;0,$K156&gt;0,COUNTIF(Mapa_Chave,$B156&amp;"#"&amp;$A156&amp;"#"&amp;($K156+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B156&amp;"#"&amp;$A156&amp;"#"&amp;($K156+1),Mapa_Chave,0))-$Q156&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J156&gt;0,SUMPRODUCT((Mapa_Sala=$B156)*(Mapa_Data=$A156)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q156)*(Mapa_RelFim&gt;$P156))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I156),$I156&gt;0,COUNTIF(Esp_Nome,$E156)&gt;0,$I156&gt;3*INDEX(Esp_Dur,MATCH($E156,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B156="","",IF(COUNTIF(Postos_Cod,$B156)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B156)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B156,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E156)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H156)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C156)),NOT(ISNUMBER($D156))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C156),ISNUMBER($D156),MOD($D156-$C156,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J156&gt;0,OR($P156&gt;=Turno_Min,$Q156&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J156&gt;0,SUMPRODUCT((Mapa_Sala=$B156)*(Mapa_Data=$A156)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q156)*(Mapa_RelFim&gt;$P156))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I156),$I156&gt;0,COUNTIF(Esp_Nome,$E156)&gt;0,$I156&gt;3*INDEX(Esp_Dur,MATCH($E156,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P156" s="12">
@@ -12816,7 +12834,7 @@
         <v/>
       </c>
       <c r="O157" s="24">
-        <f>IF($B157="","",IF(COUNTIF(Postos_Cod,$B157)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B157)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B157,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E157)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H157)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C157)),NOT(ISNUMBER($D157))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C157),ISNUMBER($D157),MOD($D157-$C157,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J157&gt;0,OR($P157&gt;=Turno_Min,$Q157&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J157&gt;0,$K157&gt;0,COUNTIF(Mapa_Chave,$B157&amp;"#"&amp;$A157&amp;"#"&amp;($K157+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B157&amp;"#"&amp;$A157&amp;"#"&amp;($K157+1),Mapa_Chave,0))-$Q157&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J157&gt;0,SUMPRODUCT((Mapa_Sala=$B157)*(Mapa_Data=$A157)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q157)*(Mapa_RelFim&gt;$P157))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I157),$I157&gt;0,COUNTIF(Esp_Nome,$E157)&gt;0,$I157&gt;3*INDEX(Esp_Dur,MATCH($E157,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B157="","",IF(COUNTIF(Postos_Cod,$B157)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B157)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B157,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E157)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H157)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C157)),NOT(ISNUMBER($D157))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C157),ISNUMBER($D157),MOD($D157-$C157,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J157&gt;0,OR($P157&gt;=Turno_Min,$Q157&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J157&gt;0,SUMPRODUCT((Mapa_Sala=$B157)*(Mapa_Data=$A157)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q157)*(Mapa_RelFim&gt;$P157))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I157),$I157&gt;0,COUNTIF(Esp_Nome,$E157)&gt;0,$I157&gt;3*INDEX(Esp_Dur,MATCH($E157,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P157" s="12">
@@ -12874,7 +12892,7 @@
         <v/>
       </c>
       <c r="O158" s="24">
-        <f>IF($B158="","",IF(COUNTIF(Postos_Cod,$B158)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B158)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B158,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E158)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H158)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C158)),NOT(ISNUMBER($D158))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C158),ISNUMBER($D158),MOD($D158-$C158,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J158&gt;0,OR($P158&gt;=Turno_Min,$Q158&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J158&gt;0,$K158&gt;0,COUNTIF(Mapa_Chave,$B158&amp;"#"&amp;$A158&amp;"#"&amp;($K158+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B158&amp;"#"&amp;$A158&amp;"#"&amp;($K158+1),Mapa_Chave,0))-$Q158&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J158&gt;0,SUMPRODUCT((Mapa_Sala=$B158)*(Mapa_Data=$A158)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q158)*(Mapa_RelFim&gt;$P158))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I158),$I158&gt;0,COUNTIF(Esp_Nome,$E158)&gt;0,$I158&gt;3*INDEX(Esp_Dur,MATCH($E158,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B158="","",IF(COUNTIF(Postos_Cod,$B158)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B158)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B158,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E158)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H158)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C158)),NOT(ISNUMBER($D158))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C158),ISNUMBER($D158),MOD($D158-$C158,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J158&gt;0,OR($P158&gt;=Turno_Min,$Q158&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J158&gt;0,SUMPRODUCT((Mapa_Sala=$B158)*(Mapa_Data=$A158)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q158)*(Mapa_RelFim&gt;$P158))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I158),$I158&gt;0,COUNTIF(Esp_Nome,$E158)&gt;0,$I158&gt;3*INDEX(Esp_Dur,MATCH($E158,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P158" s="12">
@@ -12932,7 +12950,7 @@
         <v/>
       </c>
       <c r="O159" s="24">
-        <f>IF($B159="","",IF(COUNTIF(Postos_Cod,$B159)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B159)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B159,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E159)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H159)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C159)),NOT(ISNUMBER($D159))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C159),ISNUMBER($D159),MOD($D159-$C159,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J159&gt;0,OR($P159&gt;=Turno_Min,$Q159&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J159&gt;0,$K159&gt;0,COUNTIF(Mapa_Chave,$B159&amp;"#"&amp;$A159&amp;"#"&amp;($K159+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B159&amp;"#"&amp;$A159&amp;"#"&amp;($K159+1),Mapa_Chave,0))-$Q159&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J159&gt;0,SUMPRODUCT((Mapa_Sala=$B159)*(Mapa_Data=$A159)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q159)*(Mapa_RelFim&gt;$P159))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I159),$I159&gt;0,COUNTIF(Esp_Nome,$E159)&gt;0,$I159&gt;3*INDEX(Esp_Dur,MATCH($E159,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B159="","",IF(COUNTIF(Postos_Cod,$B159)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B159)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B159,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E159)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H159)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C159)),NOT(ISNUMBER($D159))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C159),ISNUMBER($D159),MOD($D159-$C159,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J159&gt;0,OR($P159&gt;=Turno_Min,$Q159&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J159&gt;0,SUMPRODUCT((Mapa_Sala=$B159)*(Mapa_Data=$A159)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q159)*(Mapa_RelFim&gt;$P159))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I159),$I159&gt;0,COUNTIF(Esp_Nome,$E159)&gt;0,$I159&gt;3*INDEX(Esp_Dur,MATCH($E159,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P159" s="12">
@@ -12990,7 +13008,7 @@
         <v/>
       </c>
       <c r="O160" s="24">
-        <f>IF($B160="","",IF(COUNTIF(Postos_Cod,$B160)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B160)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B160,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E160)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H160)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C160)),NOT(ISNUMBER($D160))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C160),ISNUMBER($D160),MOD($D160-$C160,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J160&gt;0,OR($P160&gt;=Turno_Min,$Q160&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J160&gt;0,$K160&gt;0,COUNTIF(Mapa_Chave,$B160&amp;"#"&amp;$A160&amp;"#"&amp;($K160+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B160&amp;"#"&amp;$A160&amp;"#"&amp;($K160+1),Mapa_Chave,0))-$Q160&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J160&gt;0,SUMPRODUCT((Mapa_Sala=$B160)*(Mapa_Data=$A160)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q160)*(Mapa_RelFim&gt;$P160))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I160),$I160&gt;0,COUNTIF(Esp_Nome,$E160)&gt;0,$I160&gt;3*INDEX(Esp_Dur,MATCH($E160,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B160="","",IF(COUNTIF(Postos_Cod,$B160)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B160)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B160,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E160)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H160)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C160)),NOT(ISNUMBER($D160))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C160),ISNUMBER($D160),MOD($D160-$C160,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J160&gt;0,OR($P160&gt;=Turno_Min,$Q160&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J160&gt;0,SUMPRODUCT((Mapa_Sala=$B160)*(Mapa_Data=$A160)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q160)*(Mapa_RelFim&gt;$P160))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I160),$I160&gt;0,COUNTIF(Esp_Nome,$E160)&gt;0,$I160&gt;3*INDEX(Esp_Dur,MATCH($E160,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P160" s="12">
@@ -13048,7 +13066,7 @@
         <v/>
       </c>
       <c r="O161" s="24">
-        <f>IF($B161="","",IF(COUNTIF(Postos_Cod,$B161)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B161)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B161,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E161)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H161)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C161)),NOT(ISNUMBER($D161))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C161),ISNUMBER($D161),MOD($D161-$C161,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J161&gt;0,OR($P161&gt;=Turno_Min,$Q161&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J161&gt;0,$K161&gt;0,COUNTIF(Mapa_Chave,$B161&amp;"#"&amp;$A161&amp;"#"&amp;($K161+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B161&amp;"#"&amp;$A161&amp;"#"&amp;($K161+1),Mapa_Chave,0))-$Q161&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J161&gt;0,SUMPRODUCT((Mapa_Sala=$B161)*(Mapa_Data=$A161)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q161)*(Mapa_RelFim&gt;$P161))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I161),$I161&gt;0,COUNTIF(Esp_Nome,$E161)&gt;0,$I161&gt;3*INDEX(Esp_Dur,MATCH($E161,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B161="","",IF(COUNTIF(Postos_Cod,$B161)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B161)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B161,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E161)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H161)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C161)),NOT(ISNUMBER($D161))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C161),ISNUMBER($D161),MOD($D161-$C161,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J161&gt;0,OR($P161&gt;=Turno_Min,$Q161&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J161&gt;0,SUMPRODUCT((Mapa_Sala=$B161)*(Mapa_Data=$A161)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q161)*(Mapa_RelFim&gt;$P161))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I161),$I161&gt;0,COUNTIF(Esp_Nome,$E161)&gt;0,$I161&gt;3*INDEX(Esp_Dur,MATCH($E161,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P161" s="12">
@@ -13106,7 +13124,7 @@
         <v/>
       </c>
       <c r="O162" s="24">
-        <f>IF($B162="","",IF(COUNTIF(Postos_Cod,$B162)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B162)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B162,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E162)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H162)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C162)),NOT(ISNUMBER($D162))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C162),ISNUMBER($D162),MOD($D162-$C162,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J162&gt;0,OR($P162&gt;=Turno_Min,$Q162&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J162&gt;0,$K162&gt;0,COUNTIF(Mapa_Chave,$B162&amp;"#"&amp;$A162&amp;"#"&amp;($K162+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B162&amp;"#"&amp;$A162&amp;"#"&amp;($K162+1),Mapa_Chave,0))-$Q162&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J162&gt;0,SUMPRODUCT((Mapa_Sala=$B162)*(Mapa_Data=$A162)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q162)*(Mapa_RelFim&gt;$P162))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I162),$I162&gt;0,COUNTIF(Esp_Nome,$E162)&gt;0,$I162&gt;3*INDEX(Esp_Dur,MATCH($E162,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B162="","",IF(COUNTIF(Postos_Cod,$B162)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B162)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B162,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E162)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H162)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C162)),NOT(ISNUMBER($D162))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C162),ISNUMBER($D162),MOD($D162-$C162,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J162&gt;0,OR($P162&gt;=Turno_Min,$Q162&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J162&gt;0,SUMPRODUCT((Mapa_Sala=$B162)*(Mapa_Data=$A162)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q162)*(Mapa_RelFim&gt;$P162))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I162),$I162&gt;0,COUNTIF(Esp_Nome,$E162)&gt;0,$I162&gt;3*INDEX(Esp_Dur,MATCH($E162,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P162" s="12">
@@ -13164,7 +13182,7 @@
         <v/>
       </c>
       <c r="O163" s="24">
-        <f>IF($B163="","",IF(COUNTIF(Postos_Cod,$B163)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B163)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B163,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E163)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H163)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C163)),NOT(ISNUMBER($D163))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C163),ISNUMBER($D163),MOD($D163-$C163,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J163&gt;0,OR($P163&gt;=Turno_Min,$Q163&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J163&gt;0,$K163&gt;0,COUNTIF(Mapa_Chave,$B163&amp;"#"&amp;$A163&amp;"#"&amp;($K163+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B163&amp;"#"&amp;$A163&amp;"#"&amp;($K163+1),Mapa_Chave,0))-$Q163&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J163&gt;0,SUMPRODUCT((Mapa_Sala=$B163)*(Mapa_Data=$A163)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q163)*(Mapa_RelFim&gt;$P163))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I163),$I163&gt;0,COUNTIF(Esp_Nome,$E163)&gt;0,$I163&gt;3*INDEX(Esp_Dur,MATCH($E163,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B163="","",IF(COUNTIF(Postos_Cod,$B163)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B163)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B163,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E163)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H163)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C163)),NOT(ISNUMBER($D163))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C163),ISNUMBER($D163),MOD($D163-$C163,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J163&gt;0,OR($P163&gt;=Turno_Min,$Q163&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J163&gt;0,SUMPRODUCT((Mapa_Sala=$B163)*(Mapa_Data=$A163)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q163)*(Mapa_RelFim&gt;$P163))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I163),$I163&gt;0,COUNTIF(Esp_Nome,$E163)&gt;0,$I163&gt;3*INDEX(Esp_Dur,MATCH($E163,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P163" s="12">
@@ -13222,7 +13240,7 @@
         <v/>
       </c>
       <c r="O164" s="24">
-        <f>IF($B164="","",IF(COUNTIF(Postos_Cod,$B164)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B164)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B164,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E164)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H164)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C164)),NOT(ISNUMBER($D164))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C164),ISNUMBER($D164),MOD($D164-$C164,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J164&gt;0,OR($P164&gt;=Turno_Min,$Q164&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J164&gt;0,$K164&gt;0,COUNTIF(Mapa_Chave,$B164&amp;"#"&amp;$A164&amp;"#"&amp;($K164+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B164&amp;"#"&amp;$A164&amp;"#"&amp;($K164+1),Mapa_Chave,0))-$Q164&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J164&gt;0,SUMPRODUCT((Mapa_Sala=$B164)*(Mapa_Data=$A164)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q164)*(Mapa_RelFim&gt;$P164))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I164),$I164&gt;0,COUNTIF(Esp_Nome,$E164)&gt;0,$I164&gt;3*INDEX(Esp_Dur,MATCH($E164,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B164="","",IF(COUNTIF(Postos_Cod,$B164)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B164)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B164,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E164)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H164)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C164)),NOT(ISNUMBER($D164))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C164),ISNUMBER($D164),MOD($D164-$C164,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J164&gt;0,OR($P164&gt;=Turno_Min,$Q164&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J164&gt;0,SUMPRODUCT((Mapa_Sala=$B164)*(Mapa_Data=$A164)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q164)*(Mapa_RelFim&gt;$P164))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I164),$I164&gt;0,COUNTIF(Esp_Nome,$E164)&gt;0,$I164&gt;3*INDEX(Esp_Dur,MATCH($E164,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P164" s="12">
@@ -13280,7 +13298,7 @@
         <v/>
       </c>
       <c r="O165" s="24">
-        <f>IF($B165="","",IF(COUNTIF(Postos_Cod,$B165)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B165)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B165,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E165)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H165)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C165)),NOT(ISNUMBER($D165))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C165),ISNUMBER($D165),MOD($D165-$C165,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J165&gt;0,OR($P165&gt;=Turno_Min,$Q165&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J165&gt;0,$K165&gt;0,COUNTIF(Mapa_Chave,$B165&amp;"#"&amp;$A165&amp;"#"&amp;($K165+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B165&amp;"#"&amp;$A165&amp;"#"&amp;($K165+1),Mapa_Chave,0))-$Q165&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J165&gt;0,SUMPRODUCT((Mapa_Sala=$B165)*(Mapa_Data=$A165)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q165)*(Mapa_RelFim&gt;$P165))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I165),$I165&gt;0,COUNTIF(Esp_Nome,$E165)&gt;0,$I165&gt;3*INDEX(Esp_Dur,MATCH($E165,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B165="","",IF(COUNTIF(Postos_Cod,$B165)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B165)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B165,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E165)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H165)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C165)),NOT(ISNUMBER($D165))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C165),ISNUMBER($D165),MOD($D165-$C165,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J165&gt;0,OR($P165&gt;=Turno_Min,$Q165&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J165&gt;0,SUMPRODUCT((Mapa_Sala=$B165)*(Mapa_Data=$A165)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q165)*(Mapa_RelFim&gt;$P165))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I165),$I165&gt;0,COUNTIF(Esp_Nome,$E165)&gt;0,$I165&gt;3*INDEX(Esp_Dur,MATCH($E165,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P165" s="12">
@@ -13338,7 +13356,7 @@
         <v/>
       </c>
       <c r="O166" s="24">
-        <f>IF($B166="","",IF(COUNTIF(Postos_Cod,$B166)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B166)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B166,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E166)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H166)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C166)),NOT(ISNUMBER($D166))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C166),ISNUMBER($D166),MOD($D166-$C166,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J166&gt;0,OR($P166&gt;=Turno_Min,$Q166&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J166&gt;0,$K166&gt;0,COUNTIF(Mapa_Chave,$B166&amp;"#"&amp;$A166&amp;"#"&amp;($K166+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B166&amp;"#"&amp;$A166&amp;"#"&amp;($K166+1),Mapa_Chave,0))-$Q166&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J166&gt;0,SUMPRODUCT((Mapa_Sala=$B166)*(Mapa_Data=$A166)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q166)*(Mapa_RelFim&gt;$P166))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I166),$I166&gt;0,COUNTIF(Esp_Nome,$E166)&gt;0,$I166&gt;3*INDEX(Esp_Dur,MATCH($E166,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B166="","",IF(COUNTIF(Postos_Cod,$B166)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B166)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B166,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E166)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H166)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C166)),NOT(ISNUMBER($D166))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C166),ISNUMBER($D166),MOD($D166-$C166,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J166&gt;0,OR($P166&gt;=Turno_Min,$Q166&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J166&gt;0,SUMPRODUCT((Mapa_Sala=$B166)*(Mapa_Data=$A166)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q166)*(Mapa_RelFim&gt;$P166))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I166),$I166&gt;0,COUNTIF(Esp_Nome,$E166)&gt;0,$I166&gt;3*INDEX(Esp_Dur,MATCH($E166,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P166" s="12">
@@ -13396,7 +13414,7 @@
         <v/>
       </c>
       <c r="O167" s="24">
-        <f>IF($B167="","",IF(COUNTIF(Postos_Cod,$B167)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B167)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B167,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E167)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H167)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C167)),NOT(ISNUMBER($D167))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C167),ISNUMBER($D167),MOD($D167-$C167,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J167&gt;0,OR($P167&gt;=Turno_Min,$Q167&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J167&gt;0,$K167&gt;0,COUNTIF(Mapa_Chave,$B167&amp;"#"&amp;$A167&amp;"#"&amp;($K167+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B167&amp;"#"&amp;$A167&amp;"#"&amp;($K167+1),Mapa_Chave,0))-$Q167&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J167&gt;0,SUMPRODUCT((Mapa_Sala=$B167)*(Mapa_Data=$A167)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q167)*(Mapa_RelFim&gt;$P167))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I167),$I167&gt;0,COUNTIF(Esp_Nome,$E167)&gt;0,$I167&gt;3*INDEX(Esp_Dur,MATCH($E167,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B167="","",IF(COUNTIF(Postos_Cod,$B167)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B167)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B167,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E167)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H167)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C167)),NOT(ISNUMBER($D167))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C167),ISNUMBER($D167),MOD($D167-$C167,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J167&gt;0,OR($P167&gt;=Turno_Min,$Q167&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J167&gt;0,SUMPRODUCT((Mapa_Sala=$B167)*(Mapa_Data=$A167)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q167)*(Mapa_RelFim&gt;$P167))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I167),$I167&gt;0,COUNTIF(Esp_Nome,$E167)&gt;0,$I167&gt;3*INDEX(Esp_Dur,MATCH($E167,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P167" s="12">
@@ -13454,7 +13472,7 @@
         <v/>
       </c>
       <c r="O168" s="24">
-        <f>IF($B168="","",IF(COUNTIF(Postos_Cod,$B168)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B168)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B168,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E168)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H168)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C168)),NOT(ISNUMBER($D168))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C168),ISNUMBER($D168),MOD($D168-$C168,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J168&gt;0,OR($P168&gt;=Turno_Min,$Q168&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J168&gt;0,$K168&gt;0,COUNTIF(Mapa_Chave,$B168&amp;"#"&amp;$A168&amp;"#"&amp;($K168+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B168&amp;"#"&amp;$A168&amp;"#"&amp;($K168+1),Mapa_Chave,0))-$Q168&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J168&gt;0,SUMPRODUCT((Mapa_Sala=$B168)*(Mapa_Data=$A168)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q168)*(Mapa_RelFim&gt;$P168))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I168),$I168&gt;0,COUNTIF(Esp_Nome,$E168)&gt;0,$I168&gt;3*INDEX(Esp_Dur,MATCH($E168,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B168="","",IF(COUNTIF(Postos_Cod,$B168)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B168)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B168,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E168)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H168)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C168)),NOT(ISNUMBER($D168))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C168),ISNUMBER($D168),MOD($D168-$C168,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J168&gt;0,OR($P168&gt;=Turno_Min,$Q168&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J168&gt;0,SUMPRODUCT((Mapa_Sala=$B168)*(Mapa_Data=$A168)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q168)*(Mapa_RelFim&gt;$P168))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I168),$I168&gt;0,COUNTIF(Esp_Nome,$E168)&gt;0,$I168&gt;3*INDEX(Esp_Dur,MATCH($E168,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P168" s="12">
@@ -13512,7 +13530,7 @@
         <v/>
       </c>
       <c r="O169" s="24">
-        <f>IF($B169="","",IF(COUNTIF(Postos_Cod,$B169)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B169)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B169,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E169)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H169)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C169)),NOT(ISNUMBER($D169))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C169),ISNUMBER($D169),MOD($D169-$C169,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J169&gt;0,OR($P169&gt;=Turno_Min,$Q169&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J169&gt;0,$K169&gt;0,COUNTIF(Mapa_Chave,$B169&amp;"#"&amp;$A169&amp;"#"&amp;($K169+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B169&amp;"#"&amp;$A169&amp;"#"&amp;($K169+1),Mapa_Chave,0))-$Q169&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J169&gt;0,SUMPRODUCT((Mapa_Sala=$B169)*(Mapa_Data=$A169)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q169)*(Mapa_RelFim&gt;$P169))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I169),$I169&gt;0,COUNTIF(Esp_Nome,$E169)&gt;0,$I169&gt;3*INDEX(Esp_Dur,MATCH($E169,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B169="","",IF(COUNTIF(Postos_Cod,$B169)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B169)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B169,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E169)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H169)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C169)),NOT(ISNUMBER($D169))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C169),ISNUMBER($D169),MOD($D169-$C169,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J169&gt;0,OR($P169&gt;=Turno_Min,$Q169&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J169&gt;0,SUMPRODUCT((Mapa_Sala=$B169)*(Mapa_Data=$A169)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q169)*(Mapa_RelFim&gt;$P169))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I169),$I169&gt;0,COUNTIF(Esp_Nome,$E169)&gt;0,$I169&gt;3*INDEX(Esp_Dur,MATCH($E169,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P169" s="12">
@@ -13570,7 +13588,7 @@
         <v/>
       </c>
       <c r="O170" s="24">
-        <f>IF($B170="","",IF(COUNTIF(Postos_Cod,$B170)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B170)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B170,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E170)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H170)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C170)),NOT(ISNUMBER($D170))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C170),ISNUMBER($D170),MOD($D170-$C170,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J170&gt;0,OR($P170&gt;=Turno_Min,$Q170&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J170&gt;0,$K170&gt;0,COUNTIF(Mapa_Chave,$B170&amp;"#"&amp;$A170&amp;"#"&amp;($K170+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B170&amp;"#"&amp;$A170&amp;"#"&amp;($K170+1),Mapa_Chave,0))-$Q170&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J170&gt;0,SUMPRODUCT((Mapa_Sala=$B170)*(Mapa_Data=$A170)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q170)*(Mapa_RelFim&gt;$P170))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I170),$I170&gt;0,COUNTIF(Esp_Nome,$E170)&gt;0,$I170&gt;3*INDEX(Esp_Dur,MATCH($E170,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B170="","",IF(COUNTIF(Postos_Cod,$B170)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B170)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B170,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E170)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H170)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C170)),NOT(ISNUMBER($D170))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C170),ISNUMBER($D170),MOD($D170-$C170,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J170&gt;0,OR($P170&gt;=Turno_Min,$Q170&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J170&gt;0,SUMPRODUCT((Mapa_Sala=$B170)*(Mapa_Data=$A170)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q170)*(Mapa_RelFim&gt;$P170))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I170),$I170&gt;0,COUNTIF(Esp_Nome,$E170)&gt;0,$I170&gt;3*INDEX(Esp_Dur,MATCH($E170,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P170" s="12">
@@ -13628,7 +13646,7 @@
         <v/>
       </c>
       <c r="O171" s="24">
-        <f>IF($B171="","",IF(COUNTIF(Postos_Cod,$B171)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B171)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B171,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E171)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H171)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C171)),NOT(ISNUMBER($D171))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C171),ISNUMBER($D171),MOD($D171-$C171,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J171&gt;0,OR($P171&gt;=Turno_Min,$Q171&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J171&gt;0,$K171&gt;0,COUNTIF(Mapa_Chave,$B171&amp;"#"&amp;$A171&amp;"#"&amp;($K171+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B171&amp;"#"&amp;$A171&amp;"#"&amp;($K171+1),Mapa_Chave,0))-$Q171&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J171&gt;0,SUMPRODUCT((Mapa_Sala=$B171)*(Mapa_Data=$A171)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q171)*(Mapa_RelFim&gt;$P171))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I171),$I171&gt;0,COUNTIF(Esp_Nome,$E171)&gt;0,$I171&gt;3*INDEX(Esp_Dur,MATCH($E171,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B171="","",IF(COUNTIF(Postos_Cod,$B171)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B171)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B171,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E171)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H171)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C171)),NOT(ISNUMBER($D171))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C171),ISNUMBER($D171),MOD($D171-$C171,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J171&gt;0,OR($P171&gt;=Turno_Min,$Q171&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J171&gt;0,SUMPRODUCT((Mapa_Sala=$B171)*(Mapa_Data=$A171)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q171)*(Mapa_RelFim&gt;$P171))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I171),$I171&gt;0,COUNTIF(Esp_Nome,$E171)&gt;0,$I171&gt;3*INDEX(Esp_Dur,MATCH($E171,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P171" s="12">
@@ -13686,7 +13704,7 @@
         <v/>
       </c>
       <c r="O172" s="24">
-        <f>IF($B172="","",IF(COUNTIF(Postos_Cod,$B172)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B172)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B172,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E172)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H172)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C172)),NOT(ISNUMBER($D172))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C172),ISNUMBER($D172),MOD($D172-$C172,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J172&gt;0,OR($P172&gt;=Turno_Min,$Q172&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J172&gt;0,$K172&gt;0,COUNTIF(Mapa_Chave,$B172&amp;"#"&amp;$A172&amp;"#"&amp;($K172+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B172&amp;"#"&amp;$A172&amp;"#"&amp;($K172+1),Mapa_Chave,0))-$Q172&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J172&gt;0,SUMPRODUCT((Mapa_Sala=$B172)*(Mapa_Data=$A172)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q172)*(Mapa_RelFim&gt;$P172))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I172),$I172&gt;0,COUNTIF(Esp_Nome,$E172)&gt;0,$I172&gt;3*INDEX(Esp_Dur,MATCH($E172,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B172="","",IF(COUNTIF(Postos_Cod,$B172)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B172)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B172,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E172)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H172)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C172)),NOT(ISNUMBER($D172))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C172),ISNUMBER($D172),MOD($D172-$C172,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J172&gt;0,OR($P172&gt;=Turno_Min,$Q172&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J172&gt;0,SUMPRODUCT((Mapa_Sala=$B172)*(Mapa_Data=$A172)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q172)*(Mapa_RelFim&gt;$P172))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I172),$I172&gt;0,COUNTIF(Esp_Nome,$E172)&gt;0,$I172&gt;3*INDEX(Esp_Dur,MATCH($E172,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P172" s="12">
@@ -13744,7 +13762,7 @@
         <v/>
       </c>
       <c r="O173" s="24">
-        <f>IF($B173="","",IF(COUNTIF(Postos_Cod,$B173)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B173)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B173,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E173)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H173)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C173)),NOT(ISNUMBER($D173))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C173),ISNUMBER($D173),MOD($D173-$C173,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J173&gt;0,OR($P173&gt;=Turno_Min,$Q173&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J173&gt;0,$K173&gt;0,COUNTIF(Mapa_Chave,$B173&amp;"#"&amp;$A173&amp;"#"&amp;($K173+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B173&amp;"#"&amp;$A173&amp;"#"&amp;($K173+1),Mapa_Chave,0))-$Q173&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J173&gt;0,SUMPRODUCT((Mapa_Sala=$B173)*(Mapa_Data=$A173)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q173)*(Mapa_RelFim&gt;$P173))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I173),$I173&gt;0,COUNTIF(Esp_Nome,$E173)&gt;0,$I173&gt;3*INDEX(Esp_Dur,MATCH($E173,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B173="","",IF(COUNTIF(Postos_Cod,$B173)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B173)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B173,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E173)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H173)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C173)),NOT(ISNUMBER($D173))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C173),ISNUMBER($D173),MOD($D173-$C173,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J173&gt;0,OR($P173&gt;=Turno_Min,$Q173&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J173&gt;0,SUMPRODUCT((Mapa_Sala=$B173)*(Mapa_Data=$A173)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q173)*(Mapa_RelFim&gt;$P173))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I173),$I173&gt;0,COUNTIF(Esp_Nome,$E173)&gt;0,$I173&gt;3*INDEX(Esp_Dur,MATCH($E173,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P173" s="12">
@@ -13802,7 +13820,7 @@
         <v/>
       </c>
       <c r="O174" s="24">
-        <f>IF($B174="","",IF(COUNTIF(Postos_Cod,$B174)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B174)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B174,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E174)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H174)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C174)),NOT(ISNUMBER($D174))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C174),ISNUMBER($D174),MOD($D174-$C174,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J174&gt;0,OR($P174&gt;=Turno_Min,$Q174&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J174&gt;0,$K174&gt;0,COUNTIF(Mapa_Chave,$B174&amp;"#"&amp;$A174&amp;"#"&amp;($K174+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B174&amp;"#"&amp;$A174&amp;"#"&amp;($K174+1),Mapa_Chave,0))-$Q174&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J174&gt;0,SUMPRODUCT((Mapa_Sala=$B174)*(Mapa_Data=$A174)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q174)*(Mapa_RelFim&gt;$P174))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I174),$I174&gt;0,COUNTIF(Esp_Nome,$E174)&gt;0,$I174&gt;3*INDEX(Esp_Dur,MATCH($E174,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B174="","",IF(COUNTIF(Postos_Cod,$B174)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B174)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B174,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E174)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H174)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C174)),NOT(ISNUMBER($D174))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C174),ISNUMBER($D174),MOD($D174-$C174,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J174&gt;0,OR($P174&gt;=Turno_Min,$Q174&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J174&gt;0,SUMPRODUCT((Mapa_Sala=$B174)*(Mapa_Data=$A174)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q174)*(Mapa_RelFim&gt;$P174))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I174),$I174&gt;0,COUNTIF(Esp_Nome,$E174)&gt;0,$I174&gt;3*INDEX(Esp_Dur,MATCH($E174,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P174" s="12">
@@ -13860,7 +13878,7 @@
         <v/>
       </c>
       <c r="O175" s="24">
-        <f>IF($B175="","",IF(COUNTIF(Postos_Cod,$B175)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B175)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B175,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E175)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H175)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C175)),NOT(ISNUMBER($D175))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C175),ISNUMBER($D175),MOD($D175-$C175,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J175&gt;0,OR($P175&gt;=Turno_Min,$Q175&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J175&gt;0,$K175&gt;0,COUNTIF(Mapa_Chave,$B175&amp;"#"&amp;$A175&amp;"#"&amp;($K175+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B175&amp;"#"&amp;$A175&amp;"#"&amp;($K175+1),Mapa_Chave,0))-$Q175&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J175&gt;0,SUMPRODUCT((Mapa_Sala=$B175)*(Mapa_Data=$A175)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q175)*(Mapa_RelFim&gt;$P175))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I175),$I175&gt;0,COUNTIF(Esp_Nome,$E175)&gt;0,$I175&gt;3*INDEX(Esp_Dur,MATCH($E175,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B175="","",IF(COUNTIF(Postos_Cod,$B175)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B175)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B175,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E175)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H175)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C175)),NOT(ISNUMBER($D175))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C175),ISNUMBER($D175),MOD($D175-$C175,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J175&gt;0,OR($P175&gt;=Turno_Min,$Q175&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J175&gt;0,SUMPRODUCT((Mapa_Sala=$B175)*(Mapa_Data=$A175)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q175)*(Mapa_RelFim&gt;$P175))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I175),$I175&gt;0,COUNTIF(Esp_Nome,$E175)&gt;0,$I175&gt;3*INDEX(Esp_Dur,MATCH($E175,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P175" s="12">
@@ -13918,7 +13936,7 @@
         <v/>
       </c>
       <c r="O176" s="24">
-        <f>IF($B176="","",IF(COUNTIF(Postos_Cod,$B176)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B176)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B176,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E176)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H176)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C176)),NOT(ISNUMBER($D176))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C176),ISNUMBER($D176),MOD($D176-$C176,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J176&gt;0,OR($P176&gt;=Turno_Min,$Q176&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J176&gt;0,$K176&gt;0,COUNTIF(Mapa_Chave,$B176&amp;"#"&amp;$A176&amp;"#"&amp;($K176+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B176&amp;"#"&amp;$A176&amp;"#"&amp;($K176+1),Mapa_Chave,0))-$Q176&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J176&gt;0,SUMPRODUCT((Mapa_Sala=$B176)*(Mapa_Data=$A176)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q176)*(Mapa_RelFim&gt;$P176))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I176),$I176&gt;0,COUNTIF(Esp_Nome,$E176)&gt;0,$I176&gt;3*INDEX(Esp_Dur,MATCH($E176,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B176="","",IF(COUNTIF(Postos_Cod,$B176)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B176)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B176,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E176)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H176)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C176)),NOT(ISNUMBER($D176))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C176),ISNUMBER($D176),MOD($D176-$C176,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J176&gt;0,OR($P176&gt;=Turno_Min,$Q176&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J176&gt;0,SUMPRODUCT((Mapa_Sala=$B176)*(Mapa_Data=$A176)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q176)*(Mapa_RelFim&gt;$P176))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I176),$I176&gt;0,COUNTIF(Esp_Nome,$E176)&gt;0,$I176&gt;3*INDEX(Esp_Dur,MATCH($E176,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P176" s="12">
@@ -13976,7 +13994,7 @@
         <v/>
       </c>
       <c r="O177" s="24">
-        <f>IF($B177="","",IF(COUNTIF(Postos_Cod,$B177)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B177)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B177,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E177)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H177)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C177)),NOT(ISNUMBER($D177))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C177),ISNUMBER($D177),MOD($D177-$C177,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J177&gt;0,OR($P177&gt;=Turno_Min,$Q177&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J177&gt;0,$K177&gt;0,COUNTIF(Mapa_Chave,$B177&amp;"#"&amp;$A177&amp;"#"&amp;($K177+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B177&amp;"#"&amp;$A177&amp;"#"&amp;($K177+1),Mapa_Chave,0))-$Q177&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J177&gt;0,SUMPRODUCT((Mapa_Sala=$B177)*(Mapa_Data=$A177)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q177)*(Mapa_RelFim&gt;$P177))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I177),$I177&gt;0,COUNTIF(Esp_Nome,$E177)&gt;0,$I177&gt;3*INDEX(Esp_Dur,MATCH($E177,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B177="","",IF(COUNTIF(Postos_Cod,$B177)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B177)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B177,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E177)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H177)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C177)),NOT(ISNUMBER($D177))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C177),ISNUMBER($D177),MOD($D177-$C177,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J177&gt;0,OR($P177&gt;=Turno_Min,$Q177&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J177&gt;0,SUMPRODUCT((Mapa_Sala=$B177)*(Mapa_Data=$A177)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q177)*(Mapa_RelFim&gt;$P177))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I177),$I177&gt;0,COUNTIF(Esp_Nome,$E177)&gt;0,$I177&gt;3*INDEX(Esp_Dur,MATCH($E177,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P177" s="12">
@@ -14034,7 +14052,7 @@
         <v/>
       </c>
       <c r="O178" s="24">
-        <f>IF($B178="","",IF(COUNTIF(Postos_Cod,$B178)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B178)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B178,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E178)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H178)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C178)),NOT(ISNUMBER($D178))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C178),ISNUMBER($D178),MOD($D178-$C178,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J178&gt;0,OR($P178&gt;=Turno_Min,$Q178&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J178&gt;0,$K178&gt;0,COUNTIF(Mapa_Chave,$B178&amp;"#"&amp;$A178&amp;"#"&amp;($K178+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B178&amp;"#"&amp;$A178&amp;"#"&amp;($K178+1),Mapa_Chave,0))-$Q178&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J178&gt;0,SUMPRODUCT((Mapa_Sala=$B178)*(Mapa_Data=$A178)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q178)*(Mapa_RelFim&gt;$P178))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I178),$I178&gt;0,COUNTIF(Esp_Nome,$E178)&gt;0,$I178&gt;3*INDEX(Esp_Dur,MATCH($E178,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B178="","",IF(COUNTIF(Postos_Cod,$B178)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B178)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B178,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E178)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H178)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C178)),NOT(ISNUMBER($D178))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C178),ISNUMBER($D178),MOD($D178-$C178,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J178&gt;0,OR($P178&gt;=Turno_Min,$Q178&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J178&gt;0,SUMPRODUCT((Mapa_Sala=$B178)*(Mapa_Data=$A178)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q178)*(Mapa_RelFim&gt;$P178))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I178),$I178&gt;0,COUNTIF(Esp_Nome,$E178)&gt;0,$I178&gt;3*INDEX(Esp_Dur,MATCH($E178,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P178" s="12">
@@ -14092,7 +14110,7 @@
         <v/>
       </c>
       <c r="O179" s="24">
-        <f>IF($B179="","",IF(COUNTIF(Postos_Cod,$B179)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B179)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B179,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E179)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H179)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C179)),NOT(ISNUMBER($D179))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C179),ISNUMBER($D179),MOD($D179-$C179,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J179&gt;0,OR($P179&gt;=Turno_Min,$Q179&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J179&gt;0,$K179&gt;0,COUNTIF(Mapa_Chave,$B179&amp;"#"&amp;$A179&amp;"#"&amp;($K179+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B179&amp;"#"&amp;$A179&amp;"#"&amp;($K179+1),Mapa_Chave,0))-$Q179&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J179&gt;0,SUMPRODUCT((Mapa_Sala=$B179)*(Mapa_Data=$A179)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q179)*(Mapa_RelFim&gt;$P179))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I179),$I179&gt;0,COUNTIF(Esp_Nome,$E179)&gt;0,$I179&gt;3*INDEX(Esp_Dur,MATCH($E179,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B179="","",IF(COUNTIF(Postos_Cod,$B179)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B179)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B179,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E179)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H179)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C179)),NOT(ISNUMBER($D179))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C179),ISNUMBER($D179),MOD($D179-$C179,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J179&gt;0,OR($P179&gt;=Turno_Min,$Q179&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J179&gt;0,SUMPRODUCT((Mapa_Sala=$B179)*(Mapa_Data=$A179)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q179)*(Mapa_RelFim&gt;$P179))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I179),$I179&gt;0,COUNTIF(Esp_Nome,$E179)&gt;0,$I179&gt;3*INDEX(Esp_Dur,MATCH($E179,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P179" s="12">
@@ -14150,7 +14168,7 @@
         <v/>
       </c>
       <c r="O180" s="24">
-        <f>IF($B180="","",IF(COUNTIF(Postos_Cod,$B180)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B180)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B180,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E180)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H180)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C180)),NOT(ISNUMBER($D180))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C180),ISNUMBER($D180),MOD($D180-$C180,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J180&gt;0,OR($P180&gt;=Turno_Min,$Q180&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J180&gt;0,$K180&gt;0,COUNTIF(Mapa_Chave,$B180&amp;"#"&amp;$A180&amp;"#"&amp;($K180+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B180&amp;"#"&amp;$A180&amp;"#"&amp;($K180+1),Mapa_Chave,0))-$Q180&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J180&gt;0,SUMPRODUCT((Mapa_Sala=$B180)*(Mapa_Data=$A180)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q180)*(Mapa_RelFim&gt;$P180))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I180),$I180&gt;0,COUNTIF(Esp_Nome,$E180)&gt;0,$I180&gt;3*INDEX(Esp_Dur,MATCH($E180,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B180="","",IF(COUNTIF(Postos_Cod,$B180)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B180)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B180,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E180)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H180)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C180)),NOT(ISNUMBER($D180))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C180),ISNUMBER($D180),MOD($D180-$C180,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J180&gt;0,OR($P180&gt;=Turno_Min,$Q180&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J180&gt;0,SUMPRODUCT((Mapa_Sala=$B180)*(Mapa_Data=$A180)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q180)*(Mapa_RelFim&gt;$P180))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I180),$I180&gt;0,COUNTIF(Esp_Nome,$E180)&gt;0,$I180&gt;3*INDEX(Esp_Dur,MATCH($E180,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P180" s="12">
@@ -14208,7 +14226,7 @@
         <v/>
       </c>
       <c r="O181" s="24">
-        <f>IF($B181="","",IF(COUNTIF(Postos_Cod,$B181)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B181)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B181,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E181)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H181)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C181)),NOT(ISNUMBER($D181))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C181),ISNUMBER($D181),MOD($D181-$C181,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J181&gt;0,OR($P181&gt;=Turno_Min,$Q181&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J181&gt;0,$K181&gt;0,COUNTIF(Mapa_Chave,$B181&amp;"#"&amp;$A181&amp;"#"&amp;($K181+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B181&amp;"#"&amp;$A181&amp;"#"&amp;($K181+1),Mapa_Chave,0))-$Q181&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J181&gt;0,SUMPRODUCT((Mapa_Sala=$B181)*(Mapa_Data=$A181)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q181)*(Mapa_RelFim&gt;$P181))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I181),$I181&gt;0,COUNTIF(Esp_Nome,$E181)&gt;0,$I181&gt;3*INDEX(Esp_Dur,MATCH($E181,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B181="","",IF(COUNTIF(Postos_Cod,$B181)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B181)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B181,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E181)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H181)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C181)),NOT(ISNUMBER($D181))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C181),ISNUMBER($D181),MOD($D181-$C181,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J181&gt;0,OR($P181&gt;=Turno_Min,$Q181&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J181&gt;0,SUMPRODUCT((Mapa_Sala=$B181)*(Mapa_Data=$A181)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q181)*(Mapa_RelFim&gt;$P181))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I181),$I181&gt;0,COUNTIF(Esp_Nome,$E181)&gt;0,$I181&gt;3*INDEX(Esp_Dur,MATCH($E181,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P181" s="12">
@@ -14266,7 +14284,7 @@
         <v/>
       </c>
       <c r="O182" s="24">
-        <f>IF($B182="","",IF(COUNTIF(Postos_Cod,$B182)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B182)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B182,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E182)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H182)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C182)),NOT(ISNUMBER($D182))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C182),ISNUMBER($D182),MOD($D182-$C182,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J182&gt;0,OR($P182&gt;=Turno_Min,$Q182&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J182&gt;0,$K182&gt;0,COUNTIF(Mapa_Chave,$B182&amp;"#"&amp;$A182&amp;"#"&amp;($K182+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B182&amp;"#"&amp;$A182&amp;"#"&amp;($K182+1),Mapa_Chave,0))-$Q182&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J182&gt;0,SUMPRODUCT((Mapa_Sala=$B182)*(Mapa_Data=$A182)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q182)*(Mapa_RelFim&gt;$P182))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I182),$I182&gt;0,COUNTIF(Esp_Nome,$E182)&gt;0,$I182&gt;3*INDEX(Esp_Dur,MATCH($E182,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B182="","",IF(COUNTIF(Postos_Cod,$B182)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B182)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B182,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E182)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H182)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C182)),NOT(ISNUMBER($D182))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C182),ISNUMBER($D182),MOD($D182-$C182,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J182&gt;0,OR($P182&gt;=Turno_Min,$Q182&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J182&gt;0,SUMPRODUCT((Mapa_Sala=$B182)*(Mapa_Data=$A182)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q182)*(Mapa_RelFim&gt;$P182))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I182),$I182&gt;0,COUNTIF(Esp_Nome,$E182)&gt;0,$I182&gt;3*INDEX(Esp_Dur,MATCH($E182,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P182" s="12">
@@ -14324,7 +14342,7 @@
         <v/>
       </c>
       <c r="O183" s="24">
-        <f>IF($B183="","",IF(COUNTIF(Postos_Cod,$B183)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B183)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B183,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E183)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H183)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C183)),NOT(ISNUMBER($D183))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C183),ISNUMBER($D183),MOD($D183-$C183,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J183&gt;0,OR($P183&gt;=Turno_Min,$Q183&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J183&gt;0,$K183&gt;0,COUNTIF(Mapa_Chave,$B183&amp;"#"&amp;$A183&amp;"#"&amp;($K183+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B183&amp;"#"&amp;$A183&amp;"#"&amp;($K183+1),Mapa_Chave,0))-$Q183&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J183&gt;0,SUMPRODUCT((Mapa_Sala=$B183)*(Mapa_Data=$A183)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q183)*(Mapa_RelFim&gt;$P183))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I183),$I183&gt;0,COUNTIF(Esp_Nome,$E183)&gt;0,$I183&gt;3*INDEX(Esp_Dur,MATCH($E183,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B183="","",IF(COUNTIF(Postos_Cod,$B183)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B183)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B183,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E183)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H183)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C183)),NOT(ISNUMBER($D183))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C183),ISNUMBER($D183),MOD($D183-$C183,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J183&gt;0,OR($P183&gt;=Turno_Min,$Q183&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J183&gt;0,SUMPRODUCT((Mapa_Sala=$B183)*(Mapa_Data=$A183)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q183)*(Mapa_RelFim&gt;$P183))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I183),$I183&gt;0,COUNTIF(Esp_Nome,$E183)&gt;0,$I183&gt;3*INDEX(Esp_Dur,MATCH($E183,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P183" s="12">
@@ -14382,7 +14400,7 @@
         <v/>
       </c>
       <c r="O184" s="24">
-        <f>IF($B184="","",IF(COUNTIF(Postos_Cod,$B184)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B184)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B184,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E184)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H184)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C184)),NOT(ISNUMBER($D184))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C184),ISNUMBER($D184),MOD($D184-$C184,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J184&gt;0,OR($P184&gt;=Turno_Min,$Q184&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J184&gt;0,$K184&gt;0,COUNTIF(Mapa_Chave,$B184&amp;"#"&amp;$A184&amp;"#"&amp;($K184+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B184&amp;"#"&amp;$A184&amp;"#"&amp;($K184+1),Mapa_Chave,0))-$Q184&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J184&gt;0,SUMPRODUCT((Mapa_Sala=$B184)*(Mapa_Data=$A184)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q184)*(Mapa_RelFim&gt;$P184))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I184),$I184&gt;0,COUNTIF(Esp_Nome,$E184)&gt;0,$I184&gt;3*INDEX(Esp_Dur,MATCH($E184,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B184="","",IF(COUNTIF(Postos_Cod,$B184)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B184)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B184,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E184)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H184)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C184)),NOT(ISNUMBER($D184))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C184),ISNUMBER($D184),MOD($D184-$C184,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J184&gt;0,OR($P184&gt;=Turno_Min,$Q184&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J184&gt;0,SUMPRODUCT((Mapa_Sala=$B184)*(Mapa_Data=$A184)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q184)*(Mapa_RelFim&gt;$P184))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I184),$I184&gt;0,COUNTIF(Esp_Nome,$E184)&gt;0,$I184&gt;3*INDEX(Esp_Dur,MATCH($E184,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P184" s="12">
@@ -14440,7 +14458,7 @@
         <v/>
       </c>
       <c r="O185" s="24">
-        <f>IF($B185="","",IF(COUNTIF(Postos_Cod,$B185)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B185)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B185,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E185)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H185)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C185)),NOT(ISNUMBER($D185))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C185),ISNUMBER($D185),MOD($D185-$C185,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J185&gt;0,OR($P185&gt;=Turno_Min,$Q185&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J185&gt;0,$K185&gt;0,COUNTIF(Mapa_Chave,$B185&amp;"#"&amp;$A185&amp;"#"&amp;($K185+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B185&amp;"#"&amp;$A185&amp;"#"&amp;($K185+1),Mapa_Chave,0))-$Q185&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J185&gt;0,SUMPRODUCT((Mapa_Sala=$B185)*(Mapa_Data=$A185)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q185)*(Mapa_RelFim&gt;$P185))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I185),$I185&gt;0,COUNTIF(Esp_Nome,$E185)&gt;0,$I185&gt;3*INDEX(Esp_Dur,MATCH($E185,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B185="","",IF(COUNTIF(Postos_Cod,$B185)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B185)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B185,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E185)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H185)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C185)),NOT(ISNUMBER($D185))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C185),ISNUMBER($D185),MOD($D185-$C185,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J185&gt;0,OR($P185&gt;=Turno_Min,$Q185&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J185&gt;0,SUMPRODUCT((Mapa_Sala=$B185)*(Mapa_Data=$A185)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q185)*(Mapa_RelFim&gt;$P185))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I185),$I185&gt;0,COUNTIF(Esp_Nome,$E185)&gt;0,$I185&gt;3*INDEX(Esp_Dur,MATCH($E185,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P185" s="12">
@@ -14498,7 +14516,7 @@
         <v/>
       </c>
       <c r="O186" s="24">
-        <f>IF($B186="","",IF(COUNTIF(Postos_Cod,$B186)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B186)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B186,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E186)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H186)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C186)),NOT(ISNUMBER($D186))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C186),ISNUMBER($D186),MOD($D186-$C186,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J186&gt;0,OR($P186&gt;=Turno_Min,$Q186&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J186&gt;0,$K186&gt;0,COUNTIF(Mapa_Chave,$B186&amp;"#"&amp;$A186&amp;"#"&amp;($K186+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B186&amp;"#"&amp;$A186&amp;"#"&amp;($K186+1),Mapa_Chave,0))-$Q186&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J186&gt;0,SUMPRODUCT((Mapa_Sala=$B186)*(Mapa_Data=$A186)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q186)*(Mapa_RelFim&gt;$P186))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I186),$I186&gt;0,COUNTIF(Esp_Nome,$E186)&gt;0,$I186&gt;3*INDEX(Esp_Dur,MATCH($E186,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B186="","",IF(COUNTIF(Postos_Cod,$B186)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B186)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B186,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E186)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H186)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C186)),NOT(ISNUMBER($D186))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C186),ISNUMBER($D186),MOD($D186-$C186,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J186&gt;0,OR($P186&gt;=Turno_Min,$Q186&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J186&gt;0,SUMPRODUCT((Mapa_Sala=$B186)*(Mapa_Data=$A186)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q186)*(Mapa_RelFim&gt;$P186))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I186),$I186&gt;0,COUNTIF(Esp_Nome,$E186)&gt;0,$I186&gt;3*INDEX(Esp_Dur,MATCH($E186,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P186" s="12">
@@ -14556,7 +14574,7 @@
         <v/>
       </c>
       <c r="O187" s="24">
-        <f>IF($B187="","",IF(COUNTIF(Postos_Cod,$B187)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B187)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B187,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E187)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H187)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C187)),NOT(ISNUMBER($D187))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C187),ISNUMBER($D187),MOD($D187-$C187,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J187&gt;0,OR($P187&gt;=Turno_Min,$Q187&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J187&gt;0,$K187&gt;0,COUNTIF(Mapa_Chave,$B187&amp;"#"&amp;$A187&amp;"#"&amp;($K187+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B187&amp;"#"&amp;$A187&amp;"#"&amp;($K187+1),Mapa_Chave,0))-$Q187&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J187&gt;0,SUMPRODUCT((Mapa_Sala=$B187)*(Mapa_Data=$A187)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q187)*(Mapa_RelFim&gt;$P187))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I187),$I187&gt;0,COUNTIF(Esp_Nome,$E187)&gt;0,$I187&gt;3*INDEX(Esp_Dur,MATCH($E187,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B187="","",IF(COUNTIF(Postos_Cod,$B187)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B187)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B187,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E187)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H187)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C187)),NOT(ISNUMBER($D187))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C187),ISNUMBER($D187),MOD($D187-$C187,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J187&gt;0,OR($P187&gt;=Turno_Min,$Q187&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J187&gt;0,SUMPRODUCT((Mapa_Sala=$B187)*(Mapa_Data=$A187)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q187)*(Mapa_RelFim&gt;$P187))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I187),$I187&gt;0,COUNTIF(Esp_Nome,$E187)&gt;0,$I187&gt;3*INDEX(Esp_Dur,MATCH($E187,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P187" s="12">
@@ -14614,7 +14632,7 @@
         <v/>
       </c>
       <c r="O188" s="24">
-        <f>IF($B188="","",IF(COUNTIF(Postos_Cod,$B188)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B188)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B188,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E188)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H188)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C188)),NOT(ISNUMBER($D188))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C188),ISNUMBER($D188),MOD($D188-$C188,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J188&gt;0,OR($P188&gt;=Turno_Min,$Q188&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J188&gt;0,$K188&gt;0,COUNTIF(Mapa_Chave,$B188&amp;"#"&amp;$A188&amp;"#"&amp;($K188+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B188&amp;"#"&amp;$A188&amp;"#"&amp;($K188+1),Mapa_Chave,0))-$Q188&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J188&gt;0,SUMPRODUCT((Mapa_Sala=$B188)*(Mapa_Data=$A188)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q188)*(Mapa_RelFim&gt;$P188))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I188),$I188&gt;0,COUNTIF(Esp_Nome,$E188)&gt;0,$I188&gt;3*INDEX(Esp_Dur,MATCH($E188,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B188="","",IF(COUNTIF(Postos_Cod,$B188)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B188)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B188,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E188)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H188)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C188)),NOT(ISNUMBER($D188))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C188),ISNUMBER($D188),MOD($D188-$C188,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J188&gt;0,OR($P188&gt;=Turno_Min,$Q188&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J188&gt;0,SUMPRODUCT((Mapa_Sala=$B188)*(Mapa_Data=$A188)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q188)*(Mapa_RelFim&gt;$P188))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I188),$I188&gt;0,COUNTIF(Esp_Nome,$E188)&gt;0,$I188&gt;3*INDEX(Esp_Dur,MATCH($E188,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P188" s="12">
@@ -14672,7 +14690,7 @@
         <v/>
       </c>
       <c r="O189" s="24">
-        <f>IF($B189="","",IF(COUNTIF(Postos_Cod,$B189)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B189)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B189,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E189)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H189)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C189)),NOT(ISNUMBER($D189))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C189),ISNUMBER($D189),MOD($D189-$C189,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J189&gt;0,OR($P189&gt;=Turno_Min,$Q189&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J189&gt;0,$K189&gt;0,COUNTIF(Mapa_Chave,$B189&amp;"#"&amp;$A189&amp;"#"&amp;($K189+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B189&amp;"#"&amp;$A189&amp;"#"&amp;($K189+1),Mapa_Chave,0))-$Q189&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J189&gt;0,SUMPRODUCT((Mapa_Sala=$B189)*(Mapa_Data=$A189)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q189)*(Mapa_RelFim&gt;$P189))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I189),$I189&gt;0,COUNTIF(Esp_Nome,$E189)&gt;0,$I189&gt;3*INDEX(Esp_Dur,MATCH($E189,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B189="","",IF(COUNTIF(Postos_Cod,$B189)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B189)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B189,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E189)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H189)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C189)),NOT(ISNUMBER($D189))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C189),ISNUMBER($D189),MOD($D189-$C189,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J189&gt;0,OR($P189&gt;=Turno_Min,$Q189&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J189&gt;0,SUMPRODUCT((Mapa_Sala=$B189)*(Mapa_Data=$A189)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q189)*(Mapa_RelFim&gt;$P189))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I189),$I189&gt;0,COUNTIF(Esp_Nome,$E189)&gt;0,$I189&gt;3*INDEX(Esp_Dur,MATCH($E189,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P189" s="12">
@@ -14730,7 +14748,7 @@
         <v/>
       </c>
       <c r="O190" s="24">
-        <f>IF($B190="","",IF(COUNTIF(Postos_Cod,$B190)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B190)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B190,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E190)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H190)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C190)),NOT(ISNUMBER($D190))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C190),ISNUMBER($D190),MOD($D190-$C190,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J190&gt;0,OR($P190&gt;=Turno_Min,$Q190&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J190&gt;0,$K190&gt;0,COUNTIF(Mapa_Chave,$B190&amp;"#"&amp;$A190&amp;"#"&amp;($K190+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B190&amp;"#"&amp;$A190&amp;"#"&amp;($K190+1),Mapa_Chave,0))-$Q190&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J190&gt;0,SUMPRODUCT((Mapa_Sala=$B190)*(Mapa_Data=$A190)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q190)*(Mapa_RelFim&gt;$P190))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I190),$I190&gt;0,COUNTIF(Esp_Nome,$E190)&gt;0,$I190&gt;3*INDEX(Esp_Dur,MATCH($E190,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B190="","",IF(COUNTIF(Postos_Cod,$B190)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B190)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B190,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E190)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H190)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C190)),NOT(ISNUMBER($D190))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C190),ISNUMBER($D190),MOD($D190-$C190,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J190&gt;0,OR($P190&gt;=Turno_Min,$Q190&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J190&gt;0,SUMPRODUCT((Mapa_Sala=$B190)*(Mapa_Data=$A190)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q190)*(Mapa_RelFim&gt;$P190))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I190),$I190&gt;0,COUNTIF(Esp_Nome,$E190)&gt;0,$I190&gt;3*INDEX(Esp_Dur,MATCH($E190,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P190" s="12">
@@ -14788,7 +14806,7 @@
         <v/>
       </c>
       <c r="O191" s="24">
-        <f>IF($B191="","",IF(COUNTIF(Postos_Cod,$B191)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B191)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B191,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E191)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H191)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C191)),NOT(ISNUMBER($D191))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C191),ISNUMBER($D191),MOD($D191-$C191,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J191&gt;0,OR($P191&gt;=Turno_Min,$Q191&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J191&gt;0,$K191&gt;0,COUNTIF(Mapa_Chave,$B191&amp;"#"&amp;$A191&amp;"#"&amp;($K191+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B191&amp;"#"&amp;$A191&amp;"#"&amp;($K191+1),Mapa_Chave,0))-$Q191&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J191&gt;0,SUMPRODUCT((Mapa_Sala=$B191)*(Mapa_Data=$A191)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q191)*(Mapa_RelFim&gt;$P191))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I191),$I191&gt;0,COUNTIF(Esp_Nome,$E191)&gt;0,$I191&gt;3*INDEX(Esp_Dur,MATCH($E191,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B191="","",IF(COUNTIF(Postos_Cod,$B191)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B191)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B191,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E191)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H191)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C191)),NOT(ISNUMBER($D191))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C191),ISNUMBER($D191),MOD($D191-$C191,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J191&gt;0,OR($P191&gt;=Turno_Min,$Q191&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J191&gt;0,SUMPRODUCT((Mapa_Sala=$B191)*(Mapa_Data=$A191)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q191)*(Mapa_RelFim&gt;$P191))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I191),$I191&gt;0,COUNTIF(Esp_Nome,$E191)&gt;0,$I191&gt;3*INDEX(Esp_Dur,MATCH($E191,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P191" s="12">
@@ -14846,7 +14864,7 @@
         <v/>
       </c>
       <c r="O192" s="24">
-        <f>IF($B192="","",IF(COUNTIF(Postos_Cod,$B192)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B192)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B192,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E192)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H192)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C192)),NOT(ISNUMBER($D192))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C192),ISNUMBER($D192),MOD($D192-$C192,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J192&gt;0,OR($P192&gt;=Turno_Min,$Q192&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J192&gt;0,$K192&gt;0,COUNTIF(Mapa_Chave,$B192&amp;"#"&amp;$A192&amp;"#"&amp;($K192+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B192&amp;"#"&amp;$A192&amp;"#"&amp;($K192+1),Mapa_Chave,0))-$Q192&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J192&gt;0,SUMPRODUCT((Mapa_Sala=$B192)*(Mapa_Data=$A192)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q192)*(Mapa_RelFim&gt;$P192))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I192),$I192&gt;0,COUNTIF(Esp_Nome,$E192)&gt;0,$I192&gt;3*INDEX(Esp_Dur,MATCH($E192,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B192="","",IF(COUNTIF(Postos_Cod,$B192)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B192)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B192,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E192)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H192)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C192)),NOT(ISNUMBER($D192))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C192),ISNUMBER($D192),MOD($D192-$C192,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J192&gt;0,OR($P192&gt;=Turno_Min,$Q192&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J192&gt;0,SUMPRODUCT((Mapa_Sala=$B192)*(Mapa_Data=$A192)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q192)*(Mapa_RelFim&gt;$P192))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I192),$I192&gt;0,COUNTIF(Esp_Nome,$E192)&gt;0,$I192&gt;3*INDEX(Esp_Dur,MATCH($E192,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P192" s="12">
@@ -14904,7 +14922,7 @@
         <v/>
       </c>
       <c r="O193" s="24">
-        <f>IF($B193="","",IF(COUNTIF(Postos_Cod,$B193)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B193)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B193,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E193)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H193)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C193)),NOT(ISNUMBER($D193))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C193),ISNUMBER($D193),MOD($D193-$C193,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J193&gt;0,OR($P193&gt;=Turno_Min,$Q193&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J193&gt;0,$K193&gt;0,COUNTIF(Mapa_Chave,$B193&amp;"#"&amp;$A193&amp;"#"&amp;($K193+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B193&amp;"#"&amp;$A193&amp;"#"&amp;($K193+1),Mapa_Chave,0))-$Q193&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J193&gt;0,SUMPRODUCT((Mapa_Sala=$B193)*(Mapa_Data=$A193)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q193)*(Mapa_RelFim&gt;$P193))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I193),$I193&gt;0,COUNTIF(Esp_Nome,$E193)&gt;0,$I193&gt;3*INDEX(Esp_Dur,MATCH($E193,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B193="","",IF(COUNTIF(Postos_Cod,$B193)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B193)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B193,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E193)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H193)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C193)),NOT(ISNUMBER($D193))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C193),ISNUMBER($D193),MOD($D193-$C193,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J193&gt;0,OR($P193&gt;=Turno_Min,$Q193&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J193&gt;0,SUMPRODUCT((Mapa_Sala=$B193)*(Mapa_Data=$A193)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q193)*(Mapa_RelFim&gt;$P193))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I193),$I193&gt;0,COUNTIF(Esp_Nome,$E193)&gt;0,$I193&gt;3*INDEX(Esp_Dur,MATCH($E193,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P193" s="12">
@@ -14962,7 +14980,7 @@
         <v/>
       </c>
       <c r="O194" s="24">
-        <f>IF($B194="","",IF(COUNTIF(Postos_Cod,$B194)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B194)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B194,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E194)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H194)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C194)),NOT(ISNUMBER($D194))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C194),ISNUMBER($D194),MOD($D194-$C194,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J194&gt;0,OR($P194&gt;=Turno_Min,$Q194&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J194&gt;0,$K194&gt;0,COUNTIF(Mapa_Chave,$B194&amp;"#"&amp;$A194&amp;"#"&amp;($K194+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B194&amp;"#"&amp;$A194&amp;"#"&amp;($K194+1),Mapa_Chave,0))-$Q194&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J194&gt;0,SUMPRODUCT((Mapa_Sala=$B194)*(Mapa_Data=$A194)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q194)*(Mapa_RelFim&gt;$P194))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I194),$I194&gt;0,COUNTIF(Esp_Nome,$E194)&gt;0,$I194&gt;3*INDEX(Esp_Dur,MATCH($E194,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B194="","",IF(COUNTIF(Postos_Cod,$B194)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B194)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B194,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E194)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H194)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C194)),NOT(ISNUMBER($D194))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C194),ISNUMBER($D194),MOD($D194-$C194,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J194&gt;0,OR($P194&gt;=Turno_Min,$Q194&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J194&gt;0,SUMPRODUCT((Mapa_Sala=$B194)*(Mapa_Data=$A194)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q194)*(Mapa_RelFim&gt;$P194))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I194),$I194&gt;0,COUNTIF(Esp_Nome,$E194)&gt;0,$I194&gt;3*INDEX(Esp_Dur,MATCH($E194,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P194" s="12">
@@ -15020,7 +15038,7 @@
         <v/>
       </c>
       <c r="O195" s="24">
-        <f>IF($B195="","",IF(COUNTIF(Postos_Cod,$B195)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B195)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B195,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E195)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H195)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C195)),NOT(ISNUMBER($D195))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C195),ISNUMBER($D195),MOD($D195-$C195,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J195&gt;0,OR($P195&gt;=Turno_Min,$Q195&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J195&gt;0,$K195&gt;0,COUNTIF(Mapa_Chave,$B195&amp;"#"&amp;$A195&amp;"#"&amp;($K195+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B195&amp;"#"&amp;$A195&amp;"#"&amp;($K195+1),Mapa_Chave,0))-$Q195&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J195&gt;0,SUMPRODUCT((Mapa_Sala=$B195)*(Mapa_Data=$A195)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q195)*(Mapa_RelFim&gt;$P195))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I195),$I195&gt;0,COUNTIF(Esp_Nome,$E195)&gt;0,$I195&gt;3*INDEX(Esp_Dur,MATCH($E195,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B195="","",IF(COUNTIF(Postos_Cod,$B195)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B195)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B195,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E195)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H195)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C195)),NOT(ISNUMBER($D195))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C195),ISNUMBER($D195),MOD($D195-$C195,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J195&gt;0,OR($P195&gt;=Turno_Min,$Q195&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J195&gt;0,SUMPRODUCT((Mapa_Sala=$B195)*(Mapa_Data=$A195)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q195)*(Mapa_RelFim&gt;$P195))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I195),$I195&gt;0,COUNTIF(Esp_Nome,$E195)&gt;0,$I195&gt;3*INDEX(Esp_Dur,MATCH($E195,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P195" s="12">
@@ -15078,7 +15096,7 @@
         <v/>
       </c>
       <c r="O196" s="24">
-        <f>IF($B196="","",IF(COUNTIF(Postos_Cod,$B196)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B196)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B196,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E196)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H196)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C196)),NOT(ISNUMBER($D196))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C196),ISNUMBER($D196),MOD($D196-$C196,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J196&gt;0,OR($P196&gt;=Turno_Min,$Q196&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J196&gt;0,$K196&gt;0,COUNTIF(Mapa_Chave,$B196&amp;"#"&amp;$A196&amp;"#"&amp;($K196+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B196&amp;"#"&amp;$A196&amp;"#"&amp;($K196+1),Mapa_Chave,0))-$Q196&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J196&gt;0,SUMPRODUCT((Mapa_Sala=$B196)*(Mapa_Data=$A196)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q196)*(Mapa_RelFim&gt;$P196))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I196),$I196&gt;0,COUNTIF(Esp_Nome,$E196)&gt;0,$I196&gt;3*INDEX(Esp_Dur,MATCH($E196,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B196="","",IF(COUNTIF(Postos_Cod,$B196)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B196)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B196,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E196)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H196)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C196)),NOT(ISNUMBER($D196))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C196),ISNUMBER($D196),MOD($D196-$C196,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J196&gt;0,OR($P196&gt;=Turno_Min,$Q196&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J196&gt;0,SUMPRODUCT((Mapa_Sala=$B196)*(Mapa_Data=$A196)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q196)*(Mapa_RelFim&gt;$P196))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I196),$I196&gt;0,COUNTIF(Esp_Nome,$E196)&gt;0,$I196&gt;3*INDEX(Esp_Dur,MATCH($E196,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P196" s="12">
@@ -15136,7 +15154,7 @@
         <v/>
       </c>
       <c r="O197" s="24">
-        <f>IF($B197="","",IF(COUNTIF(Postos_Cod,$B197)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B197)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B197,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E197)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H197)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C197)),NOT(ISNUMBER($D197))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C197),ISNUMBER($D197),MOD($D197-$C197,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J197&gt;0,OR($P197&gt;=Turno_Min,$Q197&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J197&gt;0,$K197&gt;0,COUNTIF(Mapa_Chave,$B197&amp;"#"&amp;$A197&amp;"#"&amp;($K197+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B197&amp;"#"&amp;$A197&amp;"#"&amp;($K197+1),Mapa_Chave,0))-$Q197&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J197&gt;0,SUMPRODUCT((Mapa_Sala=$B197)*(Mapa_Data=$A197)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q197)*(Mapa_RelFim&gt;$P197))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I197),$I197&gt;0,COUNTIF(Esp_Nome,$E197)&gt;0,$I197&gt;3*INDEX(Esp_Dur,MATCH($E197,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B197="","",IF(COUNTIF(Postos_Cod,$B197)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B197)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B197,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E197)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H197)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C197)),NOT(ISNUMBER($D197))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C197),ISNUMBER($D197),MOD($D197-$C197,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J197&gt;0,OR($P197&gt;=Turno_Min,$Q197&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J197&gt;0,SUMPRODUCT((Mapa_Sala=$B197)*(Mapa_Data=$A197)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q197)*(Mapa_RelFim&gt;$P197))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I197),$I197&gt;0,COUNTIF(Esp_Nome,$E197)&gt;0,$I197&gt;3*INDEX(Esp_Dur,MATCH($E197,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P197" s="12">
@@ -15194,7 +15212,7 @@
         <v/>
       </c>
       <c r="O198" s="24">
-        <f>IF($B198="","",IF(COUNTIF(Postos_Cod,$B198)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B198)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B198,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E198)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H198)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C198)),NOT(ISNUMBER($D198))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C198),ISNUMBER($D198),MOD($D198-$C198,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J198&gt;0,OR($P198&gt;=Turno_Min,$Q198&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J198&gt;0,$K198&gt;0,COUNTIF(Mapa_Chave,$B198&amp;"#"&amp;$A198&amp;"#"&amp;($K198+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B198&amp;"#"&amp;$A198&amp;"#"&amp;($K198+1),Mapa_Chave,0))-$Q198&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J198&gt;0,SUMPRODUCT((Mapa_Sala=$B198)*(Mapa_Data=$A198)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q198)*(Mapa_RelFim&gt;$P198))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I198),$I198&gt;0,COUNTIF(Esp_Nome,$E198)&gt;0,$I198&gt;3*INDEX(Esp_Dur,MATCH($E198,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B198="","",IF(COUNTIF(Postos_Cod,$B198)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B198)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B198,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E198)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H198)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C198)),NOT(ISNUMBER($D198))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C198),ISNUMBER($D198),MOD($D198-$C198,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J198&gt;0,OR($P198&gt;=Turno_Min,$Q198&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J198&gt;0,SUMPRODUCT((Mapa_Sala=$B198)*(Mapa_Data=$A198)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q198)*(Mapa_RelFim&gt;$P198))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I198),$I198&gt;0,COUNTIF(Esp_Nome,$E198)&gt;0,$I198&gt;3*INDEX(Esp_Dur,MATCH($E198,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P198" s="12">
@@ -15252,7 +15270,7 @@
         <v/>
       </c>
       <c r="O199" s="24">
-        <f>IF($B199="","",IF(COUNTIF(Postos_Cod,$B199)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B199)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B199,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E199)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H199)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C199)),NOT(ISNUMBER($D199))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C199),ISNUMBER($D199),MOD($D199-$C199,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J199&gt;0,OR($P199&gt;=Turno_Min,$Q199&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J199&gt;0,$K199&gt;0,COUNTIF(Mapa_Chave,$B199&amp;"#"&amp;$A199&amp;"#"&amp;($K199+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B199&amp;"#"&amp;$A199&amp;"#"&amp;($K199+1),Mapa_Chave,0))-$Q199&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J199&gt;0,SUMPRODUCT((Mapa_Sala=$B199)*(Mapa_Data=$A199)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q199)*(Mapa_RelFim&gt;$P199))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I199),$I199&gt;0,COUNTIF(Esp_Nome,$E199)&gt;0,$I199&gt;3*INDEX(Esp_Dur,MATCH($E199,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B199="","",IF(COUNTIF(Postos_Cod,$B199)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B199)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B199,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E199)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H199)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C199)),NOT(ISNUMBER($D199))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C199),ISNUMBER($D199),MOD($D199-$C199,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J199&gt;0,OR($P199&gt;=Turno_Min,$Q199&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J199&gt;0,SUMPRODUCT((Mapa_Sala=$B199)*(Mapa_Data=$A199)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q199)*(Mapa_RelFim&gt;$P199))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I199),$I199&gt;0,COUNTIF(Esp_Nome,$E199)&gt;0,$I199&gt;3*INDEX(Esp_Dur,MATCH($E199,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P199" s="12">
@@ -15310,7 +15328,7 @@
         <v/>
       </c>
       <c r="O200" s="24">
-        <f>IF($B200="","",IF(COUNTIF(Postos_Cod,$B200)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B200)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B200,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E200)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H200)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C200)),NOT(ISNUMBER($D200))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C200),ISNUMBER($D200),MOD($D200-$C200,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J200&gt;0,OR($P200&gt;=Turno_Min,$Q200&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J200&gt;0,$K200&gt;0,COUNTIF(Mapa_Chave,$B200&amp;"#"&amp;$A200&amp;"#"&amp;($K200+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B200&amp;"#"&amp;$A200&amp;"#"&amp;($K200+1),Mapa_Chave,0))-$Q200&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J200&gt;0,SUMPRODUCT((Mapa_Sala=$B200)*(Mapa_Data=$A200)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q200)*(Mapa_RelFim&gt;$P200))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I200),$I200&gt;0,COUNTIF(Esp_Nome,$E200)&gt;0,$I200&gt;3*INDEX(Esp_Dur,MATCH($E200,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B200="","",IF(COUNTIF(Postos_Cod,$B200)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B200)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B200,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E200)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H200)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C200)),NOT(ISNUMBER($D200))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C200),ISNUMBER($D200),MOD($D200-$C200,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J200&gt;0,OR($P200&gt;=Turno_Min,$Q200&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J200&gt;0,SUMPRODUCT((Mapa_Sala=$B200)*(Mapa_Data=$A200)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q200)*(Mapa_RelFim&gt;$P200))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I200),$I200&gt;0,COUNTIF(Esp_Nome,$E200)&gt;0,$I200&gt;3*INDEX(Esp_Dur,MATCH($E200,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P200" s="12">
@@ -15368,7 +15386,7 @@
         <v/>
       </c>
       <c r="O201" s="24">
-        <f>IF($B201="","",IF(COUNTIF(Postos_Cod,$B201)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B201)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B201,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E201)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H201)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C201)),NOT(ISNUMBER($D201))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C201),ISNUMBER($D201),MOD($D201-$C201,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J201&gt;0,OR($P201&gt;=Turno_Min,$Q201&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IFERROR(IF(AND($J201&gt;0,$K201&gt;0,COUNTIF(Mapa_Chave,$B201&amp;"#"&amp;$A201&amp;"#"&amp;($K201+1))&gt;0,INDEX(Mapa_RelIni,MATCH($B201&amp;"#"&amp;$A201&amp;"#"&amp;($K201+1),Mapa_Chave,0))-$Q201&lt;Limpeza_Min),"Sem intervalo para limpeza | ",""),"")&amp;IF(AND($J201&gt;0,SUMPRODUCT((Mapa_Sala=$B201)*(Mapa_Data=$A201)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q201)*(Mapa_RelFim&gt;$P201))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I201),$I201&gt;0,COUNTIF(Esp_Nome,$E201)&gt;0,$I201&gt;3*INDEX(Esp_Dur,MATCH($E201,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
+        <f>IF($B201="","",IF(COUNTIF(Postos_Cod,$B201)=0,"Sala não cadastrada | ","")&amp;IF(AND(COUNTIF(Postos_Cod,$B201)&gt;0,IFERROR(INDEX(Postos_Tipo,MATCH($B201,Postos_Cod,0)),"")&lt;&gt;"Sala cirúrgica"),"Posto não é sala cirúrgica | ","")&amp;IF(COUNTIF(Esp_Nome,$E201)=0,"Especialidade não cadastrada | ","")&amp;IF(COUNTIF(Lista_StatusCir,$H201)=0,"Status inválido | ","")&amp;IF(OR(NOT(ISNUMBER($C201)),NOT(ISNUMBER($D201))),"Horário inválido | ","")&amp;IFERROR(IF(AND(ISNUMBER($C201),ISNUMBER($D201),MOD($D201-$C201,1)*1440&lt;=0),"Duração nula ou negativa | ",""),"")&amp;IF(AND($J201&gt;0,OR($P201&gt;=Turno_Min,$Q201&gt;Turno_Min)),"Fora da janela do plantão | ","")&amp;IF(AND($J201&gt;0,SUMPRODUCT((Mapa_Sala=$B201)*(Mapa_Data=$A201)*(Mapa_MinOcup&gt;0)*(Mapa_RelIni&lt;$Q201)*(Mapa_RelFim&gt;$P201))&gt;1),"Sobreposição de horário na sala | ","")&amp;IFERROR(IF(AND(ISNUMBER($I201),$I201&gt;0,COUNTIF(Esp_Nome,$E201)&gt;0,$I201&gt;3*INDEX(Esp_Dur,MATCH($E201,Esp_Nome,0))),"Duração atípica (&gt;3x a média) | ",""),""))</f>
         <v/>
       </c>
       <c r="P201" s="12">
@@ -25143,11 +25161,11 @@
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Limpeza a ACRESCENTAR depois de cada cirurgia (min)</t>
+          <t>Limpeza e preparação após cada cirurgia (min)</t>
         </is>
       </c>
       <c r="B16" s="42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -25173,7 +25191,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>A agenda do hospital já reserva a limpeza dentro do horário de cada cirurgia: o horário de término é a sala liberada. Por isso aqui fica 0. Se um dia a agenda passar a trazer só o tempo cirúrgico, ponha 20 e a planilha volta a somar.</t>
+          <t>A limpeza sempre acontece. Quando a agenda emenda uma cirurgia na outra, ela cabe na folga se a cirurgia terminar antes do previsto; se a cirurgia for até o fim do horário, a limpeza empurra a seguinte — é isso que a coluna Atraso previsto mostra.</t>
         </is>
       </c>
     </row>
@@ -33125,7 +33143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E209"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -33154,6 +33172,16 @@
           <t>Duração (min)</t>
         </is>
       </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Cabe até (min)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Atraso acumulado (min)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -33175,6 +33203,14 @@
         <f>IF($C2="","",MAX(0,$D2-$C2))</f>
         <v/>
       </c>
+      <c r="F2">
+        <f>IF($E2="","",MAX(0,$E2-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>IF($C2="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -33196,6 +33232,14 @@
         <f>IF($C3="","",MAX(0,$D3-$C3))</f>
         <v/>
       </c>
+      <c r="F3">
+        <f>IF($E3="","",MAX(0,$E3-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF($C3="","",IF($D3&gt;=Turno_Min,N($G2),MAX(0,N($G2)+$C3-$D3)))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -33217,6 +33261,14 @@
         <f>IF($C4="","",MAX(0,$D4-$C4))</f>
         <v/>
       </c>
+      <c r="F4">
+        <f>IF($E4="","",MAX(0,$E4-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF($C4="","",IF($D4&gt;=Turno_Min,N($G3),MAX(0,N($G3)+$C4-$D4)))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -33238,6 +33290,14 @@
         <f>IF($C5="","",MAX(0,$D5-$C5))</f>
         <v/>
       </c>
+      <c r="F5">
+        <f>IF($E5="","",MAX(0,$E5-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF($C5="","",IF($D5&gt;=Turno_Min,N($G4),MAX(0,N($G4)+$C5-$D5)))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -33259,6 +33319,14 @@
         <f>IF($C6="","",MAX(0,$D6-$C6))</f>
         <v/>
       </c>
+      <c r="F6">
+        <f>IF($E6="","",MAX(0,$E6-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF($C6="","",IF($D6&gt;=Turno_Min,N($G5),MAX(0,N($G5)+$C6-$D6)))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -33280,6 +33348,14 @@
         <f>IF($C7="","",MAX(0,$D7-$C7))</f>
         <v/>
       </c>
+      <c r="F7">
+        <f>IF($E7="","",MAX(0,$E7-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF($C7="","",IF($D7&gt;=Turno_Min,N($G6),MAX(0,N($G6)+$C7-$D7)))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -33301,6 +33377,14 @@
         <f>IF($C8="","",MAX(0,$D8-$C8))</f>
         <v/>
       </c>
+      <c r="F8">
+        <f>IF($E8="","",MAX(0,$E8-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF($C8="","",IF($D8&gt;=Turno_Min,N($G7),MAX(0,N($G7)+$C8-$D8)))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -33322,6 +33406,14 @@
         <f>IF($C9="","",MAX(0,$D9-$C9))</f>
         <v/>
       </c>
+      <c r="F9">
+        <f>IF($E9="","",MAX(0,$E9-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF($C9="","",IF($D9&gt;=Turno_Min,N($G8),MAX(0,N($G8)+$C9-$D9)))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -33343,6 +33435,14 @@
         <f>IF($C10="","",MAX(0,$D10-$C10))</f>
         <v/>
       </c>
+      <c r="F10">
+        <f>IF($E10="","",MAX(0,$E10-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>IF($C10="","",IF($D10&gt;=Turno_Min,N($G9),MAX(0,N($G9)+$C10-$D10)))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -33364,6 +33464,14 @@
         <f>IF($C11="","",MAX(0,$D11-$C11))</f>
         <v/>
       </c>
+      <c r="F11">
+        <f>IF($E11="","",MAX(0,$E11-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF($C11="","",IF($D11&gt;=Turno_Min,N($G10),MAX(0,N($G10)+$C11-$D11)))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -33385,6 +33493,14 @@
         <f>IF($C12="","",MAX(0,$D12-$C12))</f>
         <v/>
       </c>
+      <c r="F12">
+        <f>IF($E12="","",MAX(0,$E12-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IF($C12="","",IF($D12&gt;=Turno_Min,N($G11),MAX(0,N($G11)+$C12-$D12)))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -33406,6 +33522,14 @@
         <f>IF($C13="","",MAX(0,$D13-$C13))</f>
         <v/>
       </c>
+      <c r="F13">
+        <f>IF($E13="","",MAX(0,$E13-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF($C13="","",IF($D13&gt;=Turno_Min,N($G12),MAX(0,N($G12)+$C13-$D13)))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -33427,6 +33551,14 @@
         <f>IF($C14="","",MAX(0,$D14-$C14))</f>
         <v/>
       </c>
+      <c r="F14">
+        <f>IF($E14="","",MAX(0,$E14-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF($C14="","",IF($D14&gt;=Turno_Min,N($G13),MAX(0,N($G13)+$C14-$D14)))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -33448,6 +33580,14 @@
         <f>IF($C15="","",MAX(0,$D15-$C15))</f>
         <v/>
       </c>
+      <c r="F15">
+        <f>IF($E15="","",MAX(0,$E15-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF($C15="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -33469,6 +33609,14 @@
         <f>IF($C16="","",MAX(0,$D16-$C16))</f>
         <v/>
       </c>
+      <c r="F16">
+        <f>IF($E16="","",MAX(0,$E16-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IF($C16="","",IF($D16&gt;=Turno_Min,N($G15),MAX(0,N($G15)+$C16-$D16)))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -33490,6 +33638,14 @@
         <f>IF($C17="","",MAX(0,$D17-$C17))</f>
         <v/>
       </c>
+      <c r="F17">
+        <f>IF($E17="","",MAX(0,$E17-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>IF($C17="","",IF($D17&gt;=Turno_Min,N($G16),MAX(0,N($G16)+$C17-$D17)))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -33511,6 +33667,14 @@
         <f>IF($C18="","",MAX(0,$D18-$C18))</f>
         <v/>
       </c>
+      <c r="F18">
+        <f>IF($E18="","",MAX(0,$E18-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF($C18="","",IF($D18&gt;=Turno_Min,N($G17),MAX(0,N($G17)+$C18-$D18)))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -33532,6 +33696,14 @@
         <f>IF($C19="","",MAX(0,$D19-$C19))</f>
         <v/>
       </c>
+      <c r="F19">
+        <f>IF($E19="","",MAX(0,$E19-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF($C19="","",IF($D19&gt;=Turno_Min,N($G18),MAX(0,N($G18)+$C19-$D19)))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -33553,6 +33725,14 @@
         <f>IF($C20="","",MAX(0,$D20-$C20))</f>
         <v/>
       </c>
+      <c r="F20">
+        <f>IF($E20="","",MAX(0,$E20-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF($C20="","",IF($D20&gt;=Turno_Min,N($G19),MAX(0,N($G19)+$C20-$D20)))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -33574,6 +33754,14 @@
         <f>IF($C21="","",MAX(0,$D21-$C21))</f>
         <v/>
       </c>
+      <c r="F21">
+        <f>IF($E21="","",MAX(0,$E21-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF($C21="","",IF($D21&gt;=Turno_Min,N($G20),MAX(0,N($G20)+$C21-$D21)))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -33595,6 +33783,14 @@
         <f>IF($C22="","",MAX(0,$D22-$C22))</f>
         <v/>
       </c>
+      <c r="F22">
+        <f>IF($E22="","",MAX(0,$E22-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF($C22="","",IF($D22&gt;=Turno_Min,N($G21),MAX(0,N($G21)+$C22-$D22)))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -33616,6 +33812,14 @@
         <f>IF($C23="","",MAX(0,$D23-$C23))</f>
         <v/>
       </c>
+      <c r="F23">
+        <f>IF($E23="","",MAX(0,$E23-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IF($C23="","",IF($D23&gt;=Turno_Min,N($G22),MAX(0,N($G22)+$C23-$D23)))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -33637,6 +33841,14 @@
         <f>IF($C24="","",MAX(0,$D24-$C24))</f>
         <v/>
       </c>
+      <c r="F24">
+        <f>IF($E24="","",MAX(0,$E24-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF($C24="","",IF($D24&gt;=Turno_Min,N($G23),MAX(0,N($G23)+$C24-$D24)))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -33658,6 +33870,14 @@
         <f>IF($C25="","",MAX(0,$D25-$C25))</f>
         <v/>
       </c>
+      <c r="F25">
+        <f>IF($E25="","",MAX(0,$E25-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF($C25="","",IF($D25&gt;=Turno_Min,N($G24),MAX(0,N($G24)+$C25-$D25)))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -33679,6 +33899,14 @@
         <f>IF($C26="","",MAX(0,$D26-$C26))</f>
         <v/>
       </c>
+      <c r="F26">
+        <f>IF($E26="","",MAX(0,$E26-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>IF($C26="","",IF($D26&gt;=Turno_Min,N($G25),MAX(0,N($G25)+$C26-$D26)))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -33700,6 +33928,14 @@
         <f>IF($C27="","",MAX(0,$D27-$C27))</f>
         <v/>
       </c>
+      <c r="F27">
+        <f>IF($E27="","",MAX(0,$E27-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IF($C27="","",IF($D27&gt;=Turno_Min,N($G26),MAX(0,N($G26)+$C27-$D27)))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -33721,6 +33957,14 @@
         <f>IF($C28="","",MAX(0,$D28-$C28))</f>
         <v/>
       </c>
+      <c r="F28">
+        <f>IF($E28="","",MAX(0,$E28-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>IF($C28="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -33742,6 +33986,14 @@
         <f>IF($C29="","",MAX(0,$D29-$C29))</f>
         <v/>
       </c>
+      <c r="F29">
+        <f>IF($E29="","",MAX(0,$E29-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>IF($C29="","",IF($D29&gt;=Turno_Min,N($G28),MAX(0,N($G28)+$C29-$D29)))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -33763,6 +34015,14 @@
         <f>IF($C30="","",MAX(0,$D30-$C30))</f>
         <v/>
       </c>
+      <c r="F30">
+        <f>IF($E30="","",MAX(0,$E30-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF($C30="","",IF($D30&gt;=Turno_Min,N($G29),MAX(0,N($G29)+$C30-$D30)))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -33784,6 +34044,14 @@
         <f>IF($C31="","",MAX(0,$D31-$C31))</f>
         <v/>
       </c>
+      <c r="F31">
+        <f>IF($E31="","",MAX(0,$E31-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>IF($C31="","",IF($D31&gt;=Turno_Min,N($G30),MAX(0,N($G30)+$C31-$D31)))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -33805,6 +34073,14 @@
         <f>IF($C32="","",MAX(0,$D32-$C32))</f>
         <v/>
       </c>
+      <c r="F32">
+        <f>IF($E32="","",MAX(0,$E32-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF($C32="","",IF($D32&gt;=Turno_Min,N($G31),MAX(0,N($G31)+$C32-$D32)))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -33826,6 +34102,14 @@
         <f>IF($C33="","",MAX(0,$D33-$C33))</f>
         <v/>
       </c>
+      <c r="F33">
+        <f>IF($E33="","",MAX(0,$E33-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>IF($C33="","",IF($D33&gt;=Turno_Min,N($G32),MAX(0,N($G32)+$C33-$D33)))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -33847,6 +34131,14 @@
         <f>IF($C34="","",MAX(0,$D34-$C34))</f>
         <v/>
       </c>
+      <c r="F34">
+        <f>IF($E34="","",MAX(0,$E34-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IF($C34="","",IF($D34&gt;=Turno_Min,N($G33),MAX(0,N($G33)+$C34-$D34)))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -33868,6 +34160,14 @@
         <f>IF($C35="","",MAX(0,$D35-$C35))</f>
         <v/>
       </c>
+      <c r="F35">
+        <f>IF($E35="","",MAX(0,$E35-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>IF($C35="","",IF($D35&gt;=Turno_Min,N($G34),MAX(0,N($G34)+$C35-$D35)))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -33889,6 +34189,14 @@
         <f>IF($C36="","",MAX(0,$D36-$C36))</f>
         <v/>
       </c>
+      <c r="F36">
+        <f>IF($E36="","",MAX(0,$E36-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>IF($C36="","",IF($D36&gt;=Turno_Min,N($G35),MAX(0,N($G35)+$C36-$D36)))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -33910,6 +34218,14 @@
         <f>IF($C37="","",MAX(0,$D37-$C37))</f>
         <v/>
       </c>
+      <c r="F37">
+        <f>IF($E37="","",MAX(0,$E37-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>IF($C37="","",IF($D37&gt;=Turno_Min,N($G36),MAX(0,N($G36)+$C37-$D37)))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -33931,6 +34247,14 @@
         <f>IF($C38="","",MAX(0,$D38-$C38))</f>
         <v/>
       </c>
+      <c r="F38">
+        <f>IF($E38="","",MAX(0,$E38-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>IF($C38="","",IF($D38&gt;=Turno_Min,N($G37),MAX(0,N($G37)+$C38-$D38)))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -33952,6 +34276,14 @@
         <f>IF($C39="","",MAX(0,$D39-$C39))</f>
         <v/>
       </c>
+      <c r="F39">
+        <f>IF($E39="","",MAX(0,$E39-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>IF($C39="","",IF($D39&gt;=Turno_Min,N($G38),MAX(0,N($G38)+$C39-$D39)))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -33973,6 +34305,14 @@
         <f>IF($C40="","",MAX(0,$D40-$C40))</f>
         <v/>
       </c>
+      <c r="F40">
+        <f>IF($E40="","",MAX(0,$E40-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>IF($C40="","",IF($D40&gt;=Turno_Min,N($G39),MAX(0,N($G39)+$C40-$D40)))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -33994,6 +34334,14 @@
         <f>IF($C41="","",MAX(0,$D41-$C41))</f>
         <v/>
       </c>
+      <c r="F41">
+        <f>IF($E41="","",MAX(0,$E41-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>IF($C41="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -34015,6 +34363,14 @@
         <f>IF($C42="","",MAX(0,$D42-$C42))</f>
         <v/>
       </c>
+      <c r="F42">
+        <f>IF($E42="","",MAX(0,$E42-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>IF($C42="","",IF($D42&gt;=Turno_Min,N($G41),MAX(0,N($G41)+$C42-$D42)))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -34036,6 +34392,14 @@
         <f>IF($C43="","",MAX(0,$D43-$C43))</f>
         <v/>
       </c>
+      <c r="F43">
+        <f>IF($E43="","",MAX(0,$E43-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>IF($C43="","",IF($D43&gt;=Turno_Min,N($G42),MAX(0,N($G42)+$C43-$D43)))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -34057,6 +34421,14 @@
         <f>IF($C44="","",MAX(0,$D44-$C44))</f>
         <v/>
       </c>
+      <c r="F44">
+        <f>IF($E44="","",MAX(0,$E44-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>IF($C44="","",IF($D44&gt;=Turno_Min,N($G43),MAX(0,N($G43)+$C44-$D44)))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -34078,6 +34450,14 @@
         <f>IF($C45="","",MAX(0,$D45-$C45))</f>
         <v/>
       </c>
+      <c r="F45">
+        <f>IF($E45="","",MAX(0,$E45-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G45">
+        <f>IF($C45="","",IF($D45&gt;=Turno_Min,N($G44),MAX(0,N($G44)+$C45-$D45)))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -34099,6 +34479,14 @@
         <f>IF($C46="","",MAX(0,$D46-$C46))</f>
         <v/>
       </c>
+      <c r="F46">
+        <f>IF($E46="","",MAX(0,$E46-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>IF($C46="","",IF($D46&gt;=Turno_Min,N($G45),MAX(0,N($G45)+$C46-$D46)))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -34120,6 +34508,14 @@
         <f>IF($C47="","",MAX(0,$D47-$C47))</f>
         <v/>
       </c>
+      <c r="F47">
+        <f>IF($E47="","",MAX(0,$E47-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>IF($C47="","",IF($D47&gt;=Turno_Min,N($G46),MAX(0,N($G46)+$C47-$D47)))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -34141,6 +34537,14 @@
         <f>IF($C48="","",MAX(0,$D48-$C48))</f>
         <v/>
       </c>
+      <c r="F48">
+        <f>IF($E48="","",MAX(0,$E48-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>IF($C48="","",IF($D48&gt;=Turno_Min,N($G47),MAX(0,N($G47)+$C48-$D48)))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -34162,6 +34566,14 @@
         <f>IF($C49="","",MAX(0,$D49-$C49))</f>
         <v/>
       </c>
+      <c r="F49">
+        <f>IF($E49="","",MAX(0,$E49-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>IF($C49="","",IF($D49&gt;=Turno_Min,N($G48),MAX(0,N($G48)+$C49-$D49)))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -34183,6 +34595,14 @@
         <f>IF($C50="","",MAX(0,$D50-$C50))</f>
         <v/>
       </c>
+      <c r="F50">
+        <f>IF($E50="","",MAX(0,$E50-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G50">
+        <f>IF($C50="","",IF($D50&gt;=Turno_Min,N($G49),MAX(0,N($G49)+$C50-$D50)))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -34204,6 +34624,14 @@
         <f>IF($C51="","",MAX(0,$D51-$C51))</f>
         <v/>
       </c>
+      <c r="F51">
+        <f>IF($E51="","",MAX(0,$E51-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G51">
+        <f>IF($C51="","",IF($D51&gt;=Turno_Min,N($G50),MAX(0,N($G50)+$C51-$D51)))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -34225,6 +34653,14 @@
         <f>IF($C52="","",MAX(0,$D52-$C52))</f>
         <v/>
       </c>
+      <c r="F52">
+        <f>IF($E52="","",MAX(0,$E52-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G52">
+        <f>IF($C52="","",IF($D52&gt;=Turno_Min,N($G51),MAX(0,N($G51)+$C52-$D52)))</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -34246,6 +34682,14 @@
         <f>IF($C53="","",MAX(0,$D53-$C53))</f>
         <v/>
       </c>
+      <c r="F53">
+        <f>IF($E53="","",MAX(0,$E53-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G53">
+        <f>IF($C53="","",IF($D53&gt;=Turno_Min,N($G52),MAX(0,N($G52)+$C53-$D53)))</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -34267,6 +34711,14 @@
         <f>IF($C54="","",MAX(0,$D54-$C54))</f>
         <v/>
       </c>
+      <c r="F54">
+        <f>IF($E54="","",MAX(0,$E54-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>IF($C54="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -34288,6 +34740,14 @@
         <f>IF($C55="","",MAX(0,$D55-$C55))</f>
         <v/>
       </c>
+      <c r="F55">
+        <f>IF($E55="","",MAX(0,$E55-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>IF($C55="","",IF($D55&gt;=Turno_Min,N($G54),MAX(0,N($G54)+$C55-$D55)))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -34309,6 +34769,14 @@
         <f>IF($C56="","",MAX(0,$D56-$C56))</f>
         <v/>
       </c>
+      <c r="F56">
+        <f>IF($E56="","",MAX(0,$E56-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>IF($C56="","",IF($D56&gt;=Turno_Min,N($G55),MAX(0,N($G55)+$C56-$D56)))</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -34330,6 +34798,14 @@
         <f>IF($C57="","",MAX(0,$D57-$C57))</f>
         <v/>
       </c>
+      <c r="F57">
+        <f>IF($E57="","",MAX(0,$E57-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G57">
+        <f>IF($C57="","",IF($D57&gt;=Turno_Min,N($G56),MAX(0,N($G56)+$C57-$D57)))</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -34351,6 +34827,14 @@
         <f>IF($C58="","",MAX(0,$D58-$C58))</f>
         <v/>
       </c>
+      <c r="F58">
+        <f>IF($E58="","",MAX(0,$E58-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G58">
+        <f>IF($C58="","",IF($D58&gt;=Turno_Min,N($G57),MAX(0,N($G57)+$C58-$D58)))</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -34372,6 +34856,14 @@
         <f>IF($C59="","",MAX(0,$D59-$C59))</f>
         <v/>
       </c>
+      <c r="F59">
+        <f>IF($E59="","",MAX(0,$E59-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>IF($C59="","",IF($D59&gt;=Turno_Min,N($G58),MAX(0,N($G58)+$C59-$D59)))</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -34393,6 +34885,14 @@
         <f>IF($C60="","",MAX(0,$D60-$C60))</f>
         <v/>
       </c>
+      <c r="F60">
+        <f>IF($E60="","",MAX(0,$E60-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>IF($C60="","",IF($D60&gt;=Turno_Min,N($G59),MAX(0,N($G59)+$C60-$D60)))</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -34414,6 +34914,14 @@
         <f>IF($C61="","",MAX(0,$D61-$C61))</f>
         <v/>
       </c>
+      <c r="F61">
+        <f>IF($E61="","",MAX(0,$E61-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G61">
+        <f>IF($C61="","",IF($D61&gt;=Turno_Min,N($G60),MAX(0,N($G60)+$C61-$D61)))</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -34435,6 +34943,14 @@
         <f>IF($C62="","",MAX(0,$D62-$C62))</f>
         <v/>
       </c>
+      <c r="F62">
+        <f>IF($E62="","",MAX(0,$E62-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>IF($C62="","",IF($D62&gt;=Turno_Min,N($G61),MAX(0,N($G61)+$C62-$D62)))</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -34456,6 +34972,14 @@
         <f>IF($C63="","",MAX(0,$D63-$C63))</f>
         <v/>
       </c>
+      <c r="F63">
+        <f>IF($E63="","",MAX(0,$E63-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G63">
+        <f>IF($C63="","",IF($D63&gt;=Turno_Min,N($G62),MAX(0,N($G62)+$C63-$D63)))</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -34477,6 +35001,14 @@
         <f>IF($C64="","",MAX(0,$D64-$C64))</f>
         <v/>
       </c>
+      <c r="F64">
+        <f>IF($E64="","",MAX(0,$E64-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G64">
+        <f>IF($C64="","",IF($D64&gt;=Turno_Min,N($G63),MAX(0,N($G63)+$C64-$D64)))</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -34498,6 +35030,14 @@
         <f>IF($C65="","",MAX(0,$D65-$C65))</f>
         <v/>
       </c>
+      <c r="F65">
+        <f>IF($E65="","",MAX(0,$E65-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>IF($C65="","",IF($D65&gt;=Turno_Min,N($G64),MAX(0,N($G64)+$C65-$D65)))</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -34519,6 +35059,14 @@
         <f>IF($C66="","",MAX(0,$D66-$C66))</f>
         <v/>
       </c>
+      <c r="F66">
+        <f>IF($E66="","",MAX(0,$E66-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G66">
+        <f>IF($C66="","",IF($D66&gt;=Turno_Min,N($G65),MAX(0,N($G65)+$C66-$D66)))</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -34540,6 +35088,14 @@
         <f>IF($C67="","",MAX(0,$D67-$C67))</f>
         <v/>
       </c>
+      <c r="F67">
+        <f>IF($E67="","",MAX(0,$E67-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>IF($C67="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -34561,6 +35117,14 @@
         <f>IF($C68="","",MAX(0,$D68-$C68))</f>
         <v/>
       </c>
+      <c r="F68">
+        <f>IF($E68="","",MAX(0,$E68-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G68">
+        <f>IF($C68="","",IF($D68&gt;=Turno_Min,N($G67),MAX(0,N($G67)+$C68-$D68)))</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -34582,6 +35146,14 @@
         <f>IF($C69="","",MAX(0,$D69-$C69))</f>
         <v/>
       </c>
+      <c r="F69">
+        <f>IF($E69="","",MAX(0,$E69-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G69">
+        <f>IF($C69="","",IF($D69&gt;=Turno_Min,N($G68),MAX(0,N($G68)+$C69-$D69)))</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -34603,6 +35175,14 @@
         <f>IF($C70="","",MAX(0,$D70-$C70))</f>
         <v/>
       </c>
+      <c r="F70">
+        <f>IF($E70="","",MAX(0,$E70-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G70">
+        <f>IF($C70="","",IF($D70&gt;=Turno_Min,N($G69),MAX(0,N($G69)+$C70-$D70)))</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -34624,6 +35204,14 @@
         <f>IF($C71="","",MAX(0,$D71-$C71))</f>
         <v/>
       </c>
+      <c r="F71">
+        <f>IF($E71="","",MAX(0,$E71-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G71">
+        <f>IF($C71="","",IF($D71&gt;=Turno_Min,N($G70),MAX(0,N($G70)+$C71-$D71)))</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -34645,6 +35233,14 @@
         <f>IF($C72="","",MAX(0,$D72-$C72))</f>
         <v/>
       </c>
+      <c r="F72">
+        <f>IF($E72="","",MAX(0,$E72-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>IF($C72="","",IF($D72&gt;=Turno_Min,N($G71),MAX(0,N($G71)+$C72-$D72)))</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -34666,6 +35262,14 @@
         <f>IF($C73="","",MAX(0,$D73-$C73))</f>
         <v/>
       </c>
+      <c r="F73">
+        <f>IF($E73="","",MAX(0,$E73-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>IF($C73="","",IF($D73&gt;=Turno_Min,N($G72),MAX(0,N($G72)+$C73-$D73)))</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -34687,6 +35291,14 @@
         <f>IF($C74="","",MAX(0,$D74-$C74))</f>
         <v/>
       </c>
+      <c r="F74">
+        <f>IF($E74="","",MAX(0,$E74-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G74">
+        <f>IF($C74="","",IF($D74&gt;=Turno_Min,N($G73),MAX(0,N($G73)+$C74-$D74)))</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -34708,6 +35320,14 @@
         <f>IF($C75="","",MAX(0,$D75-$C75))</f>
         <v/>
       </c>
+      <c r="F75">
+        <f>IF($E75="","",MAX(0,$E75-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G75">
+        <f>IF($C75="","",IF($D75&gt;=Turno_Min,N($G74),MAX(0,N($G74)+$C75-$D75)))</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -34729,6 +35349,14 @@
         <f>IF($C76="","",MAX(0,$D76-$C76))</f>
         <v/>
       </c>
+      <c r="F76">
+        <f>IF($E76="","",MAX(0,$E76-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G76">
+        <f>IF($C76="","",IF($D76&gt;=Turno_Min,N($G75),MAX(0,N($G75)+$C76-$D76)))</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -34750,6 +35378,14 @@
         <f>IF($C77="","",MAX(0,$D77-$C77))</f>
         <v/>
       </c>
+      <c r="F77">
+        <f>IF($E77="","",MAX(0,$E77-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>IF($C77="","",IF($D77&gt;=Turno_Min,N($G76),MAX(0,N($G76)+$C77-$D77)))</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -34771,6 +35407,14 @@
         <f>IF($C78="","",MAX(0,$D78-$C78))</f>
         <v/>
       </c>
+      <c r="F78">
+        <f>IF($E78="","",MAX(0,$E78-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>IF($C78="","",IF($D78&gt;=Turno_Min,N($G77),MAX(0,N($G77)+$C78-$D78)))</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -34792,6 +35436,14 @@
         <f>IF($C79="","",MAX(0,$D79-$C79))</f>
         <v/>
       </c>
+      <c r="F79">
+        <f>IF($E79="","",MAX(0,$E79-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>IF($C79="","",IF($D79&gt;=Turno_Min,N($G78),MAX(0,N($G78)+$C79-$D79)))</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -34813,6 +35465,14 @@
         <f>IF($C80="","",MAX(0,$D80-$C80))</f>
         <v/>
       </c>
+      <c r="F80">
+        <f>IF($E80="","",MAX(0,$E80-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>IF($C80="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -34834,6 +35494,14 @@
         <f>IF($C81="","",MAX(0,$D81-$C81))</f>
         <v/>
       </c>
+      <c r="F81">
+        <f>IF($E81="","",MAX(0,$E81-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G81">
+        <f>IF($C81="","",IF($D81&gt;=Turno_Min,N($G80),MAX(0,N($G80)+$C81-$D81)))</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -34855,6 +35523,14 @@
         <f>IF($C82="","",MAX(0,$D82-$C82))</f>
         <v/>
       </c>
+      <c r="F82">
+        <f>IF($E82="","",MAX(0,$E82-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G82">
+        <f>IF($C82="","",IF($D82&gt;=Turno_Min,N($G81),MAX(0,N($G81)+$C82-$D82)))</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -34876,6 +35552,14 @@
         <f>IF($C83="","",MAX(0,$D83-$C83))</f>
         <v/>
       </c>
+      <c r="F83">
+        <f>IF($E83="","",MAX(0,$E83-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G83">
+        <f>IF($C83="","",IF($D83&gt;=Turno_Min,N($G82),MAX(0,N($G82)+$C83-$D83)))</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -34897,6 +35581,14 @@
         <f>IF($C84="","",MAX(0,$D84-$C84))</f>
         <v/>
       </c>
+      <c r="F84">
+        <f>IF($E84="","",MAX(0,$E84-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G84">
+        <f>IF($C84="","",IF($D84&gt;=Turno_Min,N($G83),MAX(0,N($G83)+$C84-$D84)))</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -34918,6 +35610,14 @@
         <f>IF($C85="","",MAX(0,$D85-$C85))</f>
         <v/>
       </c>
+      <c r="F85">
+        <f>IF($E85="","",MAX(0,$E85-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>IF($C85="","",IF($D85&gt;=Turno_Min,N($G84),MAX(0,N($G84)+$C85-$D85)))</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -34939,6 +35639,14 @@
         <f>IF($C86="","",MAX(0,$D86-$C86))</f>
         <v/>
       </c>
+      <c r="F86">
+        <f>IF($E86="","",MAX(0,$E86-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G86">
+        <f>IF($C86="","",IF($D86&gt;=Turno_Min,N($G85),MAX(0,N($G85)+$C86-$D86)))</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -34960,6 +35668,14 @@
         <f>IF($C87="","",MAX(0,$D87-$C87))</f>
         <v/>
       </c>
+      <c r="F87">
+        <f>IF($E87="","",MAX(0,$E87-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G87">
+        <f>IF($C87="","",IF($D87&gt;=Turno_Min,N($G86),MAX(0,N($G86)+$C87-$D87)))</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -34981,6 +35697,14 @@
         <f>IF($C88="","",MAX(0,$D88-$C88))</f>
         <v/>
       </c>
+      <c r="F88">
+        <f>IF($E88="","",MAX(0,$E88-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G88">
+        <f>IF($C88="","",IF($D88&gt;=Turno_Min,N($G87),MAX(0,N($G87)+$C88-$D88)))</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -35002,6 +35726,14 @@
         <f>IF($C89="","",MAX(0,$D89-$C89))</f>
         <v/>
       </c>
+      <c r="F89">
+        <f>IF($E89="","",MAX(0,$E89-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G89">
+        <f>IF($C89="","",IF($D89&gt;=Turno_Min,N($G88),MAX(0,N($G88)+$C89-$D89)))</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -35023,6 +35755,14 @@
         <f>IF($C90="","",MAX(0,$D90-$C90))</f>
         <v/>
       </c>
+      <c r="F90">
+        <f>IF($E90="","",MAX(0,$E90-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G90">
+        <f>IF($C90="","",IF($D90&gt;=Turno_Min,N($G89),MAX(0,N($G89)+$C90-$D90)))</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -35044,6 +35784,14 @@
         <f>IF($C91="","",MAX(0,$D91-$C91))</f>
         <v/>
       </c>
+      <c r="F91">
+        <f>IF($E91="","",MAX(0,$E91-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G91">
+        <f>IF($C91="","",IF($D91&gt;=Turno_Min,N($G90),MAX(0,N($G90)+$C91-$D91)))</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -35065,6 +35813,14 @@
         <f>IF($C92="","",MAX(0,$D92-$C92))</f>
         <v/>
       </c>
+      <c r="F92">
+        <f>IF($E92="","",MAX(0,$E92-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G92">
+        <f>IF($C92="","",IF($D92&gt;=Turno_Min,N($G91),MAX(0,N($G91)+$C92-$D92)))</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -35086,6 +35842,14 @@
         <f>IF($C93="","",MAX(0,$D93-$C93))</f>
         <v/>
       </c>
+      <c r="F93">
+        <f>IF($E93="","",MAX(0,$E93-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G93">
+        <f>IF($C93="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -35107,6 +35871,14 @@
         <f>IF($C94="","",MAX(0,$D94-$C94))</f>
         <v/>
       </c>
+      <c r="F94">
+        <f>IF($E94="","",MAX(0,$E94-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G94">
+        <f>IF($C94="","",IF($D94&gt;=Turno_Min,N($G93),MAX(0,N($G93)+$C94-$D94)))</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -35128,6 +35900,14 @@
         <f>IF($C95="","",MAX(0,$D95-$C95))</f>
         <v/>
       </c>
+      <c r="F95">
+        <f>IF($E95="","",MAX(0,$E95-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G95">
+        <f>IF($C95="","",IF($D95&gt;=Turno_Min,N($G94),MAX(0,N($G94)+$C95-$D95)))</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -35149,6 +35929,14 @@
         <f>IF($C96="","",MAX(0,$D96-$C96))</f>
         <v/>
       </c>
+      <c r="F96">
+        <f>IF($E96="","",MAX(0,$E96-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G96">
+        <f>IF($C96="","",IF($D96&gt;=Turno_Min,N($G95),MAX(0,N($G95)+$C96-$D96)))</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -35170,6 +35958,14 @@
         <f>IF($C97="","",MAX(0,$D97-$C97))</f>
         <v/>
       </c>
+      <c r="F97">
+        <f>IF($E97="","",MAX(0,$E97-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G97">
+        <f>IF($C97="","",IF($D97&gt;=Turno_Min,N($G96),MAX(0,N($G96)+$C97-$D97)))</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -35191,6 +35987,14 @@
         <f>IF($C98="","",MAX(0,$D98-$C98))</f>
         <v/>
       </c>
+      <c r="F98">
+        <f>IF($E98="","",MAX(0,$E98-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G98">
+        <f>IF($C98="","",IF($D98&gt;=Turno_Min,N($G97),MAX(0,N($G97)+$C98-$D98)))</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -35212,6 +36016,14 @@
         <f>IF($C99="","",MAX(0,$D99-$C99))</f>
         <v/>
       </c>
+      <c r="F99">
+        <f>IF($E99="","",MAX(0,$E99-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G99">
+        <f>IF($C99="","",IF($D99&gt;=Turno_Min,N($G98),MAX(0,N($G98)+$C99-$D99)))</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -35233,6 +36045,14 @@
         <f>IF($C100="","",MAX(0,$D100-$C100))</f>
         <v/>
       </c>
+      <c r="F100">
+        <f>IF($E100="","",MAX(0,$E100-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G100">
+        <f>IF($C100="","",IF($D100&gt;=Turno_Min,N($G99),MAX(0,N($G99)+$C100-$D100)))</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -35254,6 +36074,14 @@
         <f>IF($C101="","",MAX(0,$D101-$C101))</f>
         <v/>
       </c>
+      <c r="F101">
+        <f>IF($E101="","",MAX(0,$E101-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G101">
+        <f>IF($C101="","",IF($D101&gt;=Turno_Min,N($G100),MAX(0,N($G100)+$C101-$D101)))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -35275,6 +36103,14 @@
         <f>IF($C102="","",MAX(0,$D102-$C102))</f>
         <v/>
       </c>
+      <c r="F102">
+        <f>IF($E102="","",MAX(0,$E102-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G102">
+        <f>IF($C102="","",IF($D102&gt;=Turno_Min,N($G101),MAX(0,N($G101)+$C102-$D102)))</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -35296,6 +36132,14 @@
         <f>IF($C103="","",MAX(0,$D103-$C103))</f>
         <v/>
       </c>
+      <c r="F103">
+        <f>IF($E103="","",MAX(0,$E103-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G103">
+        <f>IF($C103="","",IF($D103&gt;=Turno_Min,N($G102),MAX(0,N($G102)+$C103-$D103)))</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -35317,6 +36161,14 @@
         <f>IF($C104="","",MAX(0,$D104-$C104))</f>
         <v/>
       </c>
+      <c r="F104">
+        <f>IF($E104="","",MAX(0,$E104-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G104">
+        <f>IF($C104="","",IF($D104&gt;=Turno_Min,N($G103),MAX(0,N($G103)+$C104-$D104)))</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -35338,6 +36190,14 @@
         <f>IF($C105="","",MAX(0,$D105-$C105))</f>
         <v/>
       </c>
+      <c r="F105">
+        <f>IF($E105="","",MAX(0,$E105-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G105">
+        <f>IF($C105="","",IF($D105&gt;=Turno_Min,N($G104),MAX(0,N($G104)+$C105-$D105)))</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -35359,6 +36219,14 @@
         <f>IF($C106="","",MAX(0,$D106-$C106))</f>
         <v/>
       </c>
+      <c r="F106">
+        <f>IF($E106="","",MAX(0,$E106-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G106">
+        <f>IF($C106="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -35380,6 +36248,14 @@
         <f>IF($C107="","",MAX(0,$D107-$C107))</f>
         <v/>
       </c>
+      <c r="F107">
+        <f>IF($E107="","",MAX(0,$E107-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G107">
+        <f>IF($C107="","",IF($D107&gt;=Turno_Min,N($G106),MAX(0,N($G106)+$C107-$D107)))</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -35401,6 +36277,14 @@
         <f>IF($C108="","",MAX(0,$D108-$C108))</f>
         <v/>
       </c>
+      <c r="F108">
+        <f>IF($E108="","",MAX(0,$E108-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G108">
+        <f>IF($C108="","",IF($D108&gt;=Turno_Min,N($G107),MAX(0,N($G107)+$C108-$D108)))</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -35422,6 +36306,14 @@
         <f>IF($C109="","",MAX(0,$D109-$C109))</f>
         <v/>
       </c>
+      <c r="F109">
+        <f>IF($E109="","",MAX(0,$E109-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G109">
+        <f>IF($C109="","",IF($D109&gt;=Turno_Min,N($G108),MAX(0,N($G108)+$C109-$D109)))</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -35443,6 +36335,14 @@
         <f>IF($C110="","",MAX(0,$D110-$C110))</f>
         <v/>
       </c>
+      <c r="F110">
+        <f>IF($E110="","",MAX(0,$E110-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G110">
+        <f>IF($C110="","",IF($D110&gt;=Turno_Min,N($G109),MAX(0,N($G109)+$C110-$D110)))</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -35464,6 +36364,14 @@
         <f>IF($C111="","",MAX(0,$D111-$C111))</f>
         <v/>
       </c>
+      <c r="F111">
+        <f>IF($E111="","",MAX(0,$E111-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G111">
+        <f>IF($C111="","",IF($D111&gt;=Turno_Min,N($G110),MAX(0,N($G110)+$C111-$D111)))</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -35485,6 +36393,14 @@
         <f>IF($C112="","",MAX(0,$D112-$C112))</f>
         <v/>
       </c>
+      <c r="F112">
+        <f>IF($E112="","",MAX(0,$E112-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G112">
+        <f>IF($C112="","",IF($D112&gt;=Turno_Min,N($G111),MAX(0,N($G111)+$C112-$D112)))</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -35506,6 +36422,14 @@
         <f>IF($C113="","",MAX(0,$D113-$C113))</f>
         <v/>
       </c>
+      <c r="F113">
+        <f>IF($E113="","",MAX(0,$E113-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G113">
+        <f>IF($C113="","",IF($D113&gt;=Turno_Min,N($G112),MAX(0,N($G112)+$C113-$D113)))</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -35527,6 +36451,14 @@
         <f>IF($C114="","",MAX(0,$D114-$C114))</f>
         <v/>
       </c>
+      <c r="F114">
+        <f>IF($E114="","",MAX(0,$E114-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G114">
+        <f>IF($C114="","",IF($D114&gt;=Turno_Min,N($G113),MAX(0,N($G113)+$C114-$D114)))</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -35548,6 +36480,14 @@
         <f>IF($C115="","",MAX(0,$D115-$C115))</f>
         <v/>
       </c>
+      <c r="F115">
+        <f>IF($E115="","",MAX(0,$E115-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G115">
+        <f>IF($C115="","",IF($D115&gt;=Turno_Min,N($G114),MAX(0,N($G114)+$C115-$D115)))</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -35569,6 +36509,14 @@
         <f>IF($C116="","",MAX(0,$D116-$C116))</f>
         <v/>
       </c>
+      <c r="F116">
+        <f>IF($E116="","",MAX(0,$E116-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G116">
+        <f>IF($C116="","",IF($D116&gt;=Turno_Min,N($G115),MAX(0,N($G115)+$C116-$D116)))</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -35590,6 +36538,14 @@
         <f>IF($C117="","",MAX(0,$D117-$C117))</f>
         <v/>
       </c>
+      <c r="F117">
+        <f>IF($E117="","",MAX(0,$E117-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G117">
+        <f>IF($C117="","",IF($D117&gt;=Turno_Min,N($G116),MAX(0,N($G116)+$C117-$D117)))</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -35611,6 +36567,14 @@
         <f>IF($C118="","",MAX(0,$D118-$C118))</f>
         <v/>
       </c>
+      <c r="F118">
+        <f>IF($E118="","",MAX(0,$E118-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G118">
+        <f>IF($C118="","",IF($D118&gt;=Turno_Min,N($G117),MAX(0,N($G117)+$C118-$D118)))</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -35632,6 +36596,14 @@
         <f>IF($C119="","",MAX(0,$D119-$C119))</f>
         <v/>
       </c>
+      <c r="F119">
+        <f>IF($E119="","",MAX(0,$E119-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G119">
+        <f>IF($C119="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -35653,6 +36625,14 @@
         <f>IF($C120="","",MAX(0,$D120-$C120))</f>
         <v/>
       </c>
+      <c r="F120">
+        <f>IF($E120="","",MAX(0,$E120-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G120">
+        <f>IF($C120="","",IF($D120&gt;=Turno_Min,N($G119),MAX(0,N($G119)+$C120-$D120)))</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -35674,6 +36654,14 @@
         <f>IF($C121="","",MAX(0,$D121-$C121))</f>
         <v/>
       </c>
+      <c r="F121">
+        <f>IF($E121="","",MAX(0,$E121-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G121">
+        <f>IF($C121="","",IF($D121&gt;=Turno_Min,N($G120),MAX(0,N($G120)+$C121-$D121)))</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -35695,6 +36683,14 @@
         <f>IF($C122="","",MAX(0,$D122-$C122))</f>
         <v/>
       </c>
+      <c r="F122">
+        <f>IF($E122="","",MAX(0,$E122-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G122">
+        <f>IF($C122="","",IF($D122&gt;=Turno_Min,N($G121),MAX(0,N($G121)+$C122-$D122)))</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -35716,6 +36712,14 @@
         <f>IF($C123="","",MAX(0,$D123-$C123))</f>
         <v/>
       </c>
+      <c r="F123">
+        <f>IF($E123="","",MAX(0,$E123-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G123">
+        <f>IF($C123="","",IF($D123&gt;=Turno_Min,N($G122),MAX(0,N($G122)+$C123-$D123)))</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -35737,6 +36741,14 @@
         <f>IF($C124="","",MAX(0,$D124-$C124))</f>
         <v/>
       </c>
+      <c r="F124">
+        <f>IF($E124="","",MAX(0,$E124-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G124">
+        <f>IF($C124="","",IF($D124&gt;=Turno_Min,N($G123),MAX(0,N($G123)+$C124-$D124)))</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -35758,6 +36770,14 @@
         <f>IF($C125="","",MAX(0,$D125-$C125))</f>
         <v/>
       </c>
+      <c r="F125">
+        <f>IF($E125="","",MAX(0,$E125-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G125">
+        <f>IF($C125="","",IF($D125&gt;=Turno_Min,N($G124),MAX(0,N($G124)+$C125-$D125)))</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -35779,6 +36799,14 @@
         <f>IF($C126="","",MAX(0,$D126-$C126))</f>
         <v/>
       </c>
+      <c r="F126">
+        <f>IF($E126="","",MAX(0,$E126-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G126">
+        <f>IF($C126="","",IF($D126&gt;=Turno_Min,N($G125),MAX(0,N($G125)+$C126-$D126)))</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -35800,6 +36828,14 @@
         <f>IF($C127="","",MAX(0,$D127-$C127))</f>
         <v/>
       </c>
+      <c r="F127">
+        <f>IF($E127="","",MAX(0,$E127-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G127">
+        <f>IF($C127="","",IF($D127&gt;=Turno_Min,N($G126),MAX(0,N($G126)+$C127-$D127)))</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -35821,6 +36857,14 @@
         <f>IF($C128="","",MAX(0,$D128-$C128))</f>
         <v/>
       </c>
+      <c r="F128">
+        <f>IF($E128="","",MAX(0,$E128-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G128">
+        <f>IF($C128="","",IF($D128&gt;=Turno_Min,N($G127),MAX(0,N($G127)+$C128-$D128)))</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -35842,6 +36886,14 @@
         <f>IF($C129="","",MAX(0,$D129-$C129))</f>
         <v/>
       </c>
+      <c r="F129">
+        <f>IF($E129="","",MAX(0,$E129-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G129">
+        <f>IF($C129="","",IF($D129&gt;=Turno_Min,N($G128),MAX(0,N($G128)+$C129-$D129)))</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -35863,6 +36915,14 @@
         <f>IF($C130="","",MAX(0,$D130-$C130))</f>
         <v/>
       </c>
+      <c r="F130">
+        <f>IF($E130="","",MAX(0,$E130-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G130">
+        <f>IF($C130="","",IF($D130&gt;=Turno_Min,N($G129),MAX(0,N($G129)+$C130-$D130)))</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -35884,6 +36944,14 @@
         <f>IF($C131="","",MAX(0,$D131-$C131))</f>
         <v/>
       </c>
+      <c r="F131">
+        <f>IF($E131="","",MAX(0,$E131-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G131">
+        <f>IF($C131="","",IF($D131&gt;=Turno_Min,N($G130),MAX(0,N($G130)+$C131-$D131)))</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -35905,6 +36973,14 @@
         <f>IF($C132="","",MAX(0,$D132-$C132))</f>
         <v/>
       </c>
+      <c r="F132">
+        <f>IF($E132="","",MAX(0,$E132-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G132">
+        <f>IF($C132="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -35926,6 +37002,14 @@
         <f>IF($C133="","",MAX(0,$D133-$C133))</f>
         <v/>
       </c>
+      <c r="F133">
+        <f>IF($E133="","",MAX(0,$E133-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G133">
+        <f>IF($C133="","",IF($D133&gt;=Turno_Min,N($G132),MAX(0,N($G132)+$C133-$D133)))</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -35947,6 +37031,14 @@
         <f>IF($C134="","",MAX(0,$D134-$C134))</f>
         <v/>
       </c>
+      <c r="F134">
+        <f>IF($E134="","",MAX(0,$E134-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G134">
+        <f>IF($C134="","",IF($D134&gt;=Turno_Min,N($G133),MAX(0,N($G133)+$C134-$D134)))</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -35968,6 +37060,14 @@
         <f>IF($C135="","",MAX(0,$D135-$C135))</f>
         <v/>
       </c>
+      <c r="F135">
+        <f>IF($E135="","",MAX(0,$E135-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G135">
+        <f>IF($C135="","",IF($D135&gt;=Turno_Min,N($G134),MAX(0,N($G134)+$C135-$D135)))</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -35989,6 +37089,14 @@
         <f>IF($C136="","",MAX(0,$D136-$C136))</f>
         <v/>
       </c>
+      <c r="F136">
+        <f>IF($E136="","",MAX(0,$E136-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G136">
+        <f>IF($C136="","",IF($D136&gt;=Turno_Min,N($G135),MAX(0,N($G135)+$C136-$D136)))</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -36010,6 +37118,14 @@
         <f>IF($C137="","",MAX(0,$D137-$C137))</f>
         <v/>
       </c>
+      <c r="F137">
+        <f>IF($E137="","",MAX(0,$E137-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G137">
+        <f>IF($C137="","",IF($D137&gt;=Turno_Min,N($G136),MAX(0,N($G136)+$C137-$D137)))</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -36031,6 +37147,14 @@
         <f>IF($C138="","",MAX(0,$D138-$C138))</f>
         <v/>
       </c>
+      <c r="F138">
+        <f>IF($E138="","",MAX(0,$E138-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G138">
+        <f>IF($C138="","",IF($D138&gt;=Turno_Min,N($G137),MAX(0,N($G137)+$C138-$D138)))</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -36052,6 +37176,14 @@
         <f>IF($C139="","",MAX(0,$D139-$C139))</f>
         <v/>
       </c>
+      <c r="F139">
+        <f>IF($E139="","",MAX(0,$E139-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G139">
+        <f>IF($C139="","",IF($D139&gt;=Turno_Min,N($G138),MAX(0,N($G138)+$C139-$D139)))</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -36073,6 +37205,14 @@
         <f>IF($C140="","",MAX(0,$D140-$C140))</f>
         <v/>
       </c>
+      <c r="F140">
+        <f>IF($E140="","",MAX(0,$E140-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G140">
+        <f>IF($C140="","",IF($D140&gt;=Turno_Min,N($G139),MAX(0,N($G139)+$C140-$D140)))</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -36094,6 +37234,14 @@
         <f>IF($C141="","",MAX(0,$D141-$C141))</f>
         <v/>
       </c>
+      <c r="F141">
+        <f>IF($E141="","",MAX(0,$E141-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G141">
+        <f>IF($C141="","",IF($D141&gt;=Turno_Min,N($G140),MAX(0,N($G140)+$C141-$D141)))</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -36115,6 +37263,14 @@
         <f>IF($C142="","",MAX(0,$D142-$C142))</f>
         <v/>
       </c>
+      <c r="F142">
+        <f>IF($E142="","",MAX(0,$E142-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G142">
+        <f>IF($C142="","",IF($D142&gt;=Turno_Min,N($G141),MAX(0,N($G141)+$C142-$D142)))</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -36136,6 +37292,14 @@
         <f>IF($C143="","",MAX(0,$D143-$C143))</f>
         <v/>
       </c>
+      <c r="F143">
+        <f>IF($E143="","",MAX(0,$E143-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G143">
+        <f>IF($C143="","",IF($D143&gt;=Turno_Min,N($G142),MAX(0,N($G142)+$C143-$D143)))</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -36157,6 +37321,14 @@
         <f>IF($C144="","",MAX(0,$D144-$C144))</f>
         <v/>
       </c>
+      <c r="F144">
+        <f>IF($E144="","",MAX(0,$E144-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G144">
+        <f>IF($C144="","",IF($D144&gt;=Turno_Min,N($G143),MAX(0,N($G143)+$C144-$D144)))</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -36178,6 +37350,14 @@
         <f>IF($C145="","",MAX(0,$D145-$C145))</f>
         <v/>
       </c>
+      <c r="F145">
+        <f>IF($E145="","",MAX(0,$E145-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G145">
+        <f>IF($C145="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -36199,6 +37379,14 @@
         <f>IF($C146="","",MAX(0,$D146-$C146))</f>
         <v/>
       </c>
+      <c r="F146">
+        <f>IF($E146="","",MAX(0,$E146-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G146">
+        <f>IF($C146="","",IF($D146&gt;=Turno_Min,N($G145),MAX(0,N($G145)+$C146-$D146)))</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -36220,6 +37408,14 @@
         <f>IF($C147="","",MAX(0,$D147-$C147))</f>
         <v/>
       </c>
+      <c r="F147">
+        <f>IF($E147="","",MAX(0,$E147-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G147">
+        <f>IF($C147="","",IF($D147&gt;=Turno_Min,N($G146),MAX(0,N($G146)+$C147-$D147)))</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -36241,6 +37437,14 @@
         <f>IF($C148="","",MAX(0,$D148-$C148))</f>
         <v/>
       </c>
+      <c r="F148">
+        <f>IF($E148="","",MAX(0,$E148-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G148">
+        <f>IF($C148="","",IF($D148&gt;=Turno_Min,N($G147),MAX(0,N($G147)+$C148-$D148)))</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -36262,6 +37466,14 @@
         <f>IF($C149="","",MAX(0,$D149-$C149))</f>
         <v/>
       </c>
+      <c r="F149">
+        <f>IF($E149="","",MAX(0,$E149-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G149">
+        <f>IF($C149="","",IF($D149&gt;=Turno_Min,N($G148),MAX(0,N($G148)+$C149-$D149)))</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -36283,6 +37495,14 @@
         <f>IF($C150="","",MAX(0,$D150-$C150))</f>
         <v/>
       </c>
+      <c r="F150">
+        <f>IF($E150="","",MAX(0,$E150-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G150">
+        <f>IF($C150="","",IF($D150&gt;=Turno_Min,N($G149),MAX(0,N($G149)+$C150-$D150)))</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -36304,6 +37524,14 @@
         <f>IF($C151="","",MAX(0,$D151-$C151))</f>
         <v/>
       </c>
+      <c r="F151">
+        <f>IF($E151="","",MAX(0,$E151-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G151">
+        <f>IF($C151="","",IF($D151&gt;=Turno_Min,N($G150),MAX(0,N($G150)+$C151-$D151)))</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -36325,6 +37553,14 @@
         <f>IF($C152="","",MAX(0,$D152-$C152))</f>
         <v/>
       </c>
+      <c r="F152">
+        <f>IF($E152="","",MAX(0,$E152-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G152">
+        <f>IF($C152="","",IF($D152&gt;=Turno_Min,N($G151),MAX(0,N($G151)+$C152-$D152)))</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -36346,6 +37582,14 @@
         <f>IF($C153="","",MAX(0,$D153-$C153))</f>
         <v/>
       </c>
+      <c r="F153">
+        <f>IF($E153="","",MAX(0,$E153-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G153">
+        <f>IF($C153="","",IF($D153&gt;=Turno_Min,N($G152),MAX(0,N($G152)+$C153-$D153)))</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -36367,6 +37611,14 @@
         <f>IF($C154="","",MAX(0,$D154-$C154))</f>
         <v/>
       </c>
+      <c r="F154">
+        <f>IF($E154="","",MAX(0,$E154-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G154">
+        <f>IF($C154="","",IF($D154&gt;=Turno_Min,N($G153),MAX(0,N($G153)+$C154-$D154)))</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -36388,6 +37640,14 @@
         <f>IF($C155="","",MAX(0,$D155-$C155))</f>
         <v/>
       </c>
+      <c r="F155">
+        <f>IF($E155="","",MAX(0,$E155-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G155">
+        <f>IF($C155="","",IF($D155&gt;=Turno_Min,N($G154),MAX(0,N($G154)+$C155-$D155)))</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -36409,6 +37669,14 @@
         <f>IF($C156="","",MAX(0,$D156-$C156))</f>
         <v/>
       </c>
+      <c r="F156">
+        <f>IF($E156="","",MAX(0,$E156-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G156">
+        <f>IF($C156="","",IF($D156&gt;=Turno_Min,N($G155),MAX(0,N($G155)+$C156-$D156)))</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -36430,6 +37698,14 @@
         <f>IF($C157="","",MAX(0,$D157-$C157))</f>
         <v/>
       </c>
+      <c r="F157">
+        <f>IF($E157="","",MAX(0,$E157-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G157">
+        <f>IF($C157="","",IF($D157&gt;=Turno_Min,N($G156),MAX(0,N($G156)+$C157-$D157)))</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -36451,6 +37727,14 @@
         <f>IF($C158="","",MAX(0,$D158-$C158))</f>
         <v/>
       </c>
+      <c r="F158">
+        <f>IF($E158="","",MAX(0,$E158-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G158">
+        <f>IF($C158="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -36472,6 +37756,14 @@
         <f>IF($C159="","",MAX(0,$D159-$C159))</f>
         <v/>
       </c>
+      <c r="F159">
+        <f>IF($E159="","",MAX(0,$E159-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G159">
+        <f>IF($C159="","",IF($D159&gt;=Turno_Min,N($G158),MAX(0,N($G158)+$C159-$D159)))</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -36493,6 +37785,14 @@
         <f>IF($C160="","",MAX(0,$D160-$C160))</f>
         <v/>
       </c>
+      <c r="F160">
+        <f>IF($E160="","",MAX(0,$E160-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G160">
+        <f>IF($C160="","",IF($D160&gt;=Turno_Min,N($G159),MAX(0,N($G159)+$C160-$D160)))</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -36514,6 +37814,14 @@
         <f>IF($C161="","",MAX(0,$D161-$C161))</f>
         <v/>
       </c>
+      <c r="F161">
+        <f>IF($E161="","",MAX(0,$E161-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G161">
+        <f>IF($C161="","",IF($D161&gt;=Turno_Min,N($G160),MAX(0,N($G160)+$C161-$D161)))</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -36535,6 +37843,14 @@
         <f>IF($C162="","",MAX(0,$D162-$C162))</f>
         <v/>
       </c>
+      <c r="F162">
+        <f>IF($E162="","",MAX(0,$E162-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G162">
+        <f>IF($C162="","",IF($D162&gt;=Turno_Min,N($G161),MAX(0,N($G161)+$C162-$D162)))</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -36556,6 +37872,14 @@
         <f>IF($C163="","",MAX(0,$D163-$C163))</f>
         <v/>
       </c>
+      <c r="F163">
+        <f>IF($E163="","",MAX(0,$E163-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G163">
+        <f>IF($C163="","",IF($D163&gt;=Turno_Min,N($G162),MAX(0,N($G162)+$C163-$D163)))</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -36577,6 +37901,14 @@
         <f>IF($C164="","",MAX(0,$D164-$C164))</f>
         <v/>
       </c>
+      <c r="F164">
+        <f>IF($E164="","",MAX(0,$E164-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G164">
+        <f>IF($C164="","",IF($D164&gt;=Turno_Min,N($G163),MAX(0,N($G163)+$C164-$D164)))</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -36598,6 +37930,14 @@
         <f>IF($C165="","",MAX(0,$D165-$C165))</f>
         <v/>
       </c>
+      <c r="F165">
+        <f>IF($E165="","",MAX(0,$E165-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G165">
+        <f>IF($C165="","",IF($D165&gt;=Turno_Min,N($G164),MAX(0,N($G164)+$C165-$D165)))</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -36619,6 +37959,14 @@
         <f>IF($C166="","",MAX(0,$D166-$C166))</f>
         <v/>
       </c>
+      <c r="F166">
+        <f>IF($E166="","",MAX(0,$E166-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G166">
+        <f>IF($C166="","",IF($D166&gt;=Turno_Min,N($G165),MAX(0,N($G165)+$C166-$D166)))</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -36640,6 +37988,14 @@
         <f>IF($C167="","",MAX(0,$D167-$C167))</f>
         <v/>
       </c>
+      <c r="F167">
+        <f>IF($E167="","",MAX(0,$E167-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G167">
+        <f>IF($C167="","",IF($D167&gt;=Turno_Min,N($G166),MAX(0,N($G166)+$C167-$D167)))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -36661,6 +38017,14 @@
         <f>IF($C168="","",MAX(0,$D168-$C168))</f>
         <v/>
       </c>
+      <c r="F168">
+        <f>IF($E168="","",MAX(0,$E168-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G168">
+        <f>IF($C168="","",IF($D168&gt;=Turno_Min,N($G167),MAX(0,N($G167)+$C168-$D168)))</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -36682,6 +38046,14 @@
         <f>IF($C169="","",MAX(0,$D169-$C169))</f>
         <v/>
       </c>
+      <c r="F169">
+        <f>IF($E169="","",MAX(0,$E169-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G169">
+        <f>IF($C169="","",IF($D169&gt;=Turno_Min,N($G168),MAX(0,N($G168)+$C169-$D169)))</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -36703,6 +38075,14 @@
         <f>IF($C170="","",MAX(0,$D170-$C170))</f>
         <v/>
       </c>
+      <c r="F170">
+        <f>IF($E170="","",MAX(0,$E170-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G170">
+        <f>IF($C170="","",IF($D170&gt;=Turno_Min,N($G169),MAX(0,N($G169)+$C170-$D170)))</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -36724,6 +38104,14 @@
         <f>IF($C171="","",MAX(0,$D171-$C171))</f>
         <v/>
       </c>
+      <c r="F171">
+        <f>IF($E171="","",MAX(0,$E171-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G171">
+        <f>IF($C171="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -36745,6 +38133,14 @@
         <f>IF($C172="","",MAX(0,$D172-$C172))</f>
         <v/>
       </c>
+      <c r="F172">
+        <f>IF($E172="","",MAX(0,$E172-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G172">
+        <f>IF($C172="","",IF($D172&gt;=Turno_Min,N($G171),MAX(0,N($G171)+$C172-$D172)))</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -36766,6 +38162,14 @@
         <f>IF($C173="","",MAX(0,$D173-$C173))</f>
         <v/>
       </c>
+      <c r="F173">
+        <f>IF($E173="","",MAX(0,$E173-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G173">
+        <f>IF($C173="","",IF($D173&gt;=Turno_Min,N($G172),MAX(0,N($G172)+$C173-$D173)))</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -36787,6 +38191,14 @@
         <f>IF($C174="","",MAX(0,$D174-$C174))</f>
         <v/>
       </c>
+      <c r="F174">
+        <f>IF($E174="","",MAX(0,$E174-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G174">
+        <f>IF($C174="","",IF($D174&gt;=Turno_Min,N($G173),MAX(0,N($G173)+$C174-$D174)))</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -36808,6 +38220,14 @@
         <f>IF($C175="","",MAX(0,$D175-$C175))</f>
         <v/>
       </c>
+      <c r="F175">
+        <f>IF($E175="","",MAX(0,$E175-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G175">
+        <f>IF($C175="","",IF($D175&gt;=Turno_Min,N($G174),MAX(0,N($G174)+$C175-$D175)))</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -36829,6 +38249,14 @@
         <f>IF($C176="","",MAX(0,$D176-$C176))</f>
         <v/>
       </c>
+      <c r="F176">
+        <f>IF($E176="","",MAX(0,$E176-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G176">
+        <f>IF($C176="","",IF($D176&gt;=Turno_Min,N($G175),MAX(0,N($G175)+$C176-$D176)))</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -36850,6 +38278,14 @@
         <f>IF($C177="","",MAX(0,$D177-$C177))</f>
         <v/>
       </c>
+      <c r="F177">
+        <f>IF($E177="","",MAX(0,$E177-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G177">
+        <f>IF($C177="","",IF($D177&gt;=Turno_Min,N($G176),MAX(0,N($G176)+$C177-$D177)))</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -36871,6 +38307,14 @@
         <f>IF($C178="","",MAX(0,$D178-$C178))</f>
         <v/>
       </c>
+      <c r="F178">
+        <f>IF($E178="","",MAX(0,$E178-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G178">
+        <f>IF($C178="","",IF($D178&gt;=Turno_Min,N($G177),MAX(0,N($G177)+$C178-$D178)))</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -36892,6 +38336,14 @@
         <f>IF($C179="","",MAX(0,$D179-$C179))</f>
         <v/>
       </c>
+      <c r="F179">
+        <f>IF($E179="","",MAX(0,$E179-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G179">
+        <f>IF($C179="","",IF($D179&gt;=Turno_Min,N($G178),MAX(0,N($G178)+$C179-$D179)))</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -36913,6 +38365,14 @@
         <f>IF($C180="","",MAX(0,$D180-$C180))</f>
         <v/>
       </c>
+      <c r="F180">
+        <f>IF($E180="","",MAX(0,$E180-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G180">
+        <f>IF($C180="","",IF($D180&gt;=Turno_Min,N($G179),MAX(0,N($G179)+$C180-$D180)))</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -36934,6 +38394,14 @@
         <f>IF($C181="","",MAX(0,$D181-$C181))</f>
         <v/>
       </c>
+      <c r="F181">
+        <f>IF($E181="","",MAX(0,$E181-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G181">
+        <f>IF($C181="","",IF($D181&gt;=Turno_Min,N($G180),MAX(0,N($G180)+$C181-$D181)))</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -36955,6 +38423,14 @@
         <f>IF($C182="","",MAX(0,$D182-$C182))</f>
         <v/>
       </c>
+      <c r="F182">
+        <f>IF($E182="","",MAX(0,$E182-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G182">
+        <f>IF($C182="","",IF($D182&gt;=Turno_Min,N($G181),MAX(0,N($G181)+$C182-$D182)))</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -36976,6 +38452,14 @@
         <f>IF($C183="","",MAX(0,$D183-$C183))</f>
         <v/>
       </c>
+      <c r="F183">
+        <f>IF($E183="","",MAX(0,$E183-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G183">
+        <f>IF($C183="","",IF($D183&gt;=Turno_Min,N($G182),MAX(0,N($G182)+$C183-$D183)))</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -36997,6 +38481,14 @@
         <f>IF($C184="","",MAX(0,$D184-$C184))</f>
         <v/>
       </c>
+      <c r="F184">
+        <f>IF($E184="","",MAX(0,$E184-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G184">
+        <f>IF($C184="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -37018,6 +38510,14 @@
         <f>IF($C185="","",MAX(0,$D185-$C185))</f>
         <v/>
       </c>
+      <c r="F185">
+        <f>IF($E185="","",MAX(0,$E185-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G185">
+        <f>IF($C185="","",IF($D185&gt;=Turno_Min,N($G184),MAX(0,N($G184)+$C185-$D185)))</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -37039,6 +38539,14 @@
         <f>IF($C186="","",MAX(0,$D186-$C186))</f>
         <v/>
       </c>
+      <c r="F186">
+        <f>IF($E186="","",MAX(0,$E186-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G186">
+        <f>IF($C186="","",IF($D186&gt;=Turno_Min,N($G185),MAX(0,N($G185)+$C186-$D186)))</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -37060,6 +38568,14 @@
         <f>IF($C187="","",MAX(0,$D187-$C187))</f>
         <v/>
       </c>
+      <c r="F187">
+        <f>IF($E187="","",MAX(0,$E187-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G187">
+        <f>IF($C187="","",IF($D187&gt;=Turno_Min,N($G186),MAX(0,N($G186)+$C187-$D187)))</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -37081,6 +38597,14 @@
         <f>IF($C188="","",MAX(0,$D188-$C188))</f>
         <v/>
       </c>
+      <c r="F188">
+        <f>IF($E188="","",MAX(0,$E188-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G188">
+        <f>IF($C188="","",IF($D188&gt;=Turno_Min,N($G187),MAX(0,N($G187)+$C188-$D188)))</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -37102,6 +38626,14 @@
         <f>IF($C189="","",MAX(0,$D189-$C189))</f>
         <v/>
       </c>
+      <c r="F189">
+        <f>IF($E189="","",MAX(0,$E189-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G189">
+        <f>IF($C189="","",IF($D189&gt;=Turno_Min,N($G188),MAX(0,N($G188)+$C189-$D189)))</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -37123,6 +38655,14 @@
         <f>IF($C190="","",MAX(0,$D190-$C190))</f>
         <v/>
       </c>
+      <c r="F190">
+        <f>IF($E190="","",MAX(0,$E190-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G190">
+        <f>IF($C190="","",IF($D190&gt;=Turno_Min,N($G189),MAX(0,N($G189)+$C190-$D190)))</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -37144,6 +38684,14 @@
         <f>IF($C191="","",MAX(0,$D191-$C191))</f>
         <v/>
       </c>
+      <c r="F191">
+        <f>IF($E191="","",MAX(0,$E191-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G191">
+        <f>IF($C191="","",IF($D191&gt;=Turno_Min,N($G190),MAX(0,N($G190)+$C191-$D191)))</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -37165,6 +38713,14 @@
         <f>IF($C192="","",MAX(0,$D192-$C192))</f>
         <v/>
       </c>
+      <c r="F192">
+        <f>IF($E192="","",MAX(0,$E192-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G192">
+        <f>IF($C192="","",IF($D192&gt;=Turno_Min,N($G191),MAX(0,N($G191)+$C192-$D192)))</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -37186,6 +38742,14 @@
         <f>IF($C193="","",MAX(0,$D193-$C193))</f>
         <v/>
       </c>
+      <c r="F193">
+        <f>IF($E193="","",MAX(0,$E193-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G193">
+        <f>IF($C193="","",IF($D193&gt;=Turno_Min,N($G192),MAX(0,N($G192)+$C193-$D193)))</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -37207,6 +38771,14 @@
         <f>IF($C194="","",MAX(0,$D194-$C194))</f>
         <v/>
       </c>
+      <c r="F194">
+        <f>IF($E194="","",MAX(0,$E194-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G194">
+        <f>IF($C194="","",IF($D194&gt;=Turno_Min,N($G193),MAX(0,N($G193)+$C194-$D194)))</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -37228,6 +38800,14 @@
         <f>IF($C195="","",MAX(0,$D195-$C195))</f>
         <v/>
       </c>
+      <c r="F195">
+        <f>IF($E195="","",MAX(0,$E195-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G195">
+        <f>IF($C195="","",IF($D195&gt;=Turno_Min,N($G194),MAX(0,N($G194)+$C195-$D195)))</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -37249,6 +38829,14 @@
         <f>IF($C196="","",MAX(0,$D196-$C196))</f>
         <v/>
       </c>
+      <c r="F196">
+        <f>IF($E196="","",MAX(0,$E196-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G196">
+        <f>IF($C196="","",IF($D196&gt;=Turno_Min,N($G195),MAX(0,N($G195)+$C196-$D196)))</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -37270,6 +38858,14 @@
         <f>IF($C197="","",MAX(0,$D197-$C197))</f>
         <v/>
       </c>
+      <c r="F197">
+        <f>IF($E197="","",MAX(0,$E197-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G197">
+        <f>IF($C197="","",0)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -37291,6 +38887,14 @@
         <f>IF($C198="","",MAX(0,$D198-$C198))</f>
         <v/>
       </c>
+      <c r="F198">
+        <f>IF($E198="","",MAX(0,$E198-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G198">
+        <f>IF($C198="","",IF($D198&gt;=Turno_Min,N($G197),MAX(0,N($G197)+$C198-$D198)))</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -37312,6 +38916,14 @@
         <f>IF($C199="","",MAX(0,$D199-$C199))</f>
         <v/>
       </c>
+      <c r="F199">
+        <f>IF($E199="","",MAX(0,$E199-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G199">
+        <f>IF($C199="","",IF($D199&gt;=Turno_Min,N($G198),MAX(0,N($G198)+$C199-$D199)))</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -37333,6 +38945,14 @@
         <f>IF($C200="","",MAX(0,$D200-$C200))</f>
         <v/>
       </c>
+      <c r="F200">
+        <f>IF($E200="","",MAX(0,$E200-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G200">
+        <f>IF($C200="","",IF($D200&gt;=Turno_Min,N($G199),MAX(0,N($G199)+$C200-$D200)))</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -37354,6 +38974,14 @@
         <f>IF($C201="","",MAX(0,$D201-$C201))</f>
         <v/>
       </c>
+      <c r="F201">
+        <f>IF($E201="","",MAX(0,$E201-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G201">
+        <f>IF($C201="","",IF($D201&gt;=Turno_Min,N($G200),MAX(0,N($G200)+$C201-$D201)))</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -37375,6 +39003,14 @@
         <f>IF($C202="","",MAX(0,$D202-$C202))</f>
         <v/>
       </c>
+      <c r="F202">
+        <f>IF($E202="","",MAX(0,$E202-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G202">
+        <f>IF($C202="","",IF($D202&gt;=Turno_Min,N($G201),MAX(0,N($G201)+$C202-$D202)))</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -37396,6 +39032,14 @@
         <f>IF($C203="","",MAX(0,$D203-$C203))</f>
         <v/>
       </c>
+      <c r="F203">
+        <f>IF($E203="","",MAX(0,$E203-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G203">
+        <f>IF($C203="","",IF($D203&gt;=Turno_Min,N($G202),MAX(0,N($G202)+$C203-$D203)))</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -37417,6 +39061,14 @@
         <f>IF($C204="","",MAX(0,$D204-$C204))</f>
         <v/>
       </c>
+      <c r="F204">
+        <f>IF($E204="","",MAX(0,$E204-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G204">
+        <f>IF($C204="","",IF($D204&gt;=Turno_Min,N($G203),MAX(0,N($G203)+$C204-$D204)))</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -37438,6 +39090,14 @@
         <f>IF($C205="","",MAX(0,$D205-$C205))</f>
         <v/>
       </c>
+      <c r="F205">
+        <f>IF($E205="","",MAX(0,$E205-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G205">
+        <f>IF($C205="","",IF($D205&gt;=Turno_Min,N($G204),MAX(0,N($G204)+$C205-$D205)))</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -37459,6 +39119,14 @@
         <f>IF($C206="","",MAX(0,$D206-$C206))</f>
         <v/>
       </c>
+      <c r="F206">
+        <f>IF($E206="","",MAX(0,$E206-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G206">
+        <f>IF($C206="","",IF($D206&gt;=Turno_Min,N($G205),MAX(0,N($G205)+$C206-$D206)))</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -37480,6 +39148,14 @@
         <f>IF($C207="","",MAX(0,$D207-$C207))</f>
         <v/>
       </c>
+      <c r="F207">
+        <f>IF($E207="","",MAX(0,$E207-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G207">
+        <f>IF($C207="","",IF($D207&gt;=Turno_Min,N($G206),MAX(0,N($G206)+$C207-$D207)))</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -37501,6 +39177,14 @@
         <f>IF($C208="","",MAX(0,$D208-$C208))</f>
         <v/>
       </c>
+      <c r="F208">
+        <f>IF($E208="","",MAX(0,$E208-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G208">
+        <f>IF($C208="","",IF($D208&gt;=Turno_Min,N($G207),MAX(0,N($G207)+$C208-$D208)))</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -37520,6 +39204,14 @@
       </c>
       <c r="E209">
         <f>IF($C209="","",MAX(0,$D209-$C209))</f>
+        <v/>
+      </c>
+      <c r="F209">
+        <f>IF($E209="","",MAX(0,$E209-Limpeza_Min))</f>
+        <v/>
+      </c>
+      <c r="G209">
+        <f>IF($C209="","",IF($D209&gt;=Turno_Min,N($G208),MAX(0,N($G208)+$C209-$D209)))</f>
         <v/>
       </c>
     </row>
